--- a/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
+++ b/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1550492020363536</v>
+        <v>0.1579117507680596</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1715696504315213</v>
+        <v>0.1740679758248979</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1730661384400685</v>
+        <v>0.2057238869812682</v>
       </c>
       <c r="E2" t="n">
-        <v>0.165349965554964</v>
+        <v>0.1720860246432098</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1294197924636379</v>
+        <v>0.131979538815709</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1576738582491632</v>
+        <v>0.1621908873837076</v>
       </c>
       <c r="H2" t="n">
         <v>0.7166120797150832</v>
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2028557360496014</v>
+        <v>0.2043305030917656</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1946444235566862</v>
+        <v>0.1965886852111632</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1474642005326664</v>
+        <v>0.1476844369546735</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1430591299085997</v>
+        <v>0.1467325311721351</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1716852914608432</v>
+        <v>0.1739358452044829</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2010040174818766</v>
+        <v>0.2041231323367976</v>
       </c>
       <c r="H3" t="n">
         <v>0.7455856917047092</v>
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9983111364487347</v>
+        <v>1.014118759408285</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9477971944543147</v>
+        <v>0.9638252520237753</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3229390899623056</v>
+        <v>0.3127347675843605</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3233076276711602</v>
+        <v>0.313998201622595</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3847755050158757</v>
+        <v>0.4057833744270291</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3525086753384584</v>
+        <v>0.3732647546446137</v>
       </c>
       <c r="H4" t="n">
         <v>1.753597408313792</v>
@@ -838,22 +838,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.13693186201818</v>
+        <v>5.243195112562935</v>
       </c>
       <c r="C5" t="n">
-        <v>5.060056655888511</v>
+        <v>5.166941564361436</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5890944275813086</v>
+        <v>0.9630766114056604</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6011725375549197</v>
+        <v>0.8938254607364218</v>
       </c>
       <c r="F5" t="n">
-        <v>1.90276637777686</v>
+        <v>2.057173173298867</v>
       </c>
       <c r="G5" t="n">
-        <v>1.896656005792972</v>
+        <v>2.035286833462917</v>
       </c>
       <c r="H5" t="n">
         <v>7.107461973628843</v>
@@ -929,22 +929,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3091059976049743</v>
+        <v>0.3132039402088189</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3463656596795339</v>
+        <v>0.3506631218404138</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1133585118382898</v>
+        <v>0.09710073730632504</v>
       </c>
       <c r="E6" t="n">
-        <v>0.10955691270468</v>
+        <v>0.09137818446875293</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1378080973619097</v>
+        <v>0.1418956335184769</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1644237213293298</v>
+        <v>0.1694736885376539</v>
       </c>
       <c r="H6" t="n">
         <v>0.9001384470221278</v>
@@ -1020,22 +1020,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3418262425438525</v>
+        <v>0.3434942079489071</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3605569818630408</v>
+        <v>0.3624075030777073</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1757310327395859</v>
+        <v>0.1600487101812928</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1791282339914612</v>
+        <v>0.1636387163519396</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1472165900294944</v>
+        <v>0.1474792558737474</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1802592408248958</v>
+        <v>0.1810847605610292</v>
       </c>
       <c r="H7" t="n">
         <v>0.8514955388435604</v>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2904425633798753</v>
+        <v>0.2923729604292518</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2435729506449796</v>
+        <v>0.2449955119307025</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1684110885091735</v>
+        <v>0.1795042584615387</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1678351159527568</v>
+        <v>0.1736541581897918</v>
       </c>
       <c r="F8" t="n">
-        <v>0.270717959645616</v>
+        <v>0.2731102566094739</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2065161315329205</v>
+        <v>0.2084815713401154</v>
       </c>
       <c r="H8" t="n">
         <v>0.8218833647220964</v>
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3041824570089012</v>
+        <v>0.3038469416724189</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2665276164716558</v>
+        <v>0.2664802318111055</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3753812981319536</v>
+        <v>0.3040106936128512</v>
       </c>
       <c r="E9" t="n">
-        <v>0.359403959075735</v>
+        <v>0.2666309112809248</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2883364471072509</v>
+        <v>0.2874819016355921</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2720948208849636</v>
+        <v>0.2721571449037711</v>
       </c>
       <c r="H9" t="n">
         <v>0.4755023523128038</v>
@@ -1289,22 +1289,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5058720195059705</v>
+        <v>0.5123386570784337</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6098985080237529</v>
+        <v>0.6166961246108762</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3288176470572186</v>
+        <v>0.3399072976960608</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3133111921750433</v>
+        <v>0.3247393788989229</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3321056483018141</v>
+        <v>0.3405235018906729</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5472669343766547</v>
+        <v>0.5576494127906528</v>
       </c>
       <c r="H10" t="n">
         <v>1.126897749532528</v>
@@ -1380,22 +1380,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.05490462359394863</v>
+        <v>0.0548987986634983</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05043884488285524</v>
+        <v>0.05043681071314247</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03472756920196013</v>
+        <v>0.03293969915098341</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03244956832710972</v>
+        <v>0.03136588166417283</v>
       </c>
       <c r="F11" t="n">
-        <v>0.008578317272917564</v>
+        <v>0.008580474295952229</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006101404686545013</v>
+        <v>0.006109318962971988</v>
       </c>
       <c r="H11" t="n">
         <v>0.2600988575656265</v>
@@ -1471,22 +1471,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7449766684307553</v>
+        <v>0.7535164775973885</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7760359338348061</v>
+        <v>0.7844580791732065</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3368624094669627</v>
+        <v>0.3092875230603637</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3314834134838942</v>
+        <v>0.3050554147939886</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4039220459210355</v>
+        <v>0.4172176474705269</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5288766767096451</v>
+        <v>0.542783575332459</v>
       </c>
       <c r="H12" t="n">
         <v>1.373425403558954</v>
@@ -1562,22 +1562,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3025263775821483</v>
+        <v>0.3051383967140744</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3398686885321672</v>
+        <v>0.3427674292607265</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1306237321421879</v>
+        <v>0.115370626172102</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1252379827846588</v>
+        <v>0.1078043511487605</v>
       </c>
       <c r="F13" t="n">
-        <v>0.124912836603002</v>
+        <v>0.1256921628289678</v>
       </c>
       <c r="G13" t="n">
-        <v>0.174804522316247</v>
+        <v>0.1766249318219888</v>
       </c>
       <c r="H13" t="n">
         <v>0.8934721382063724</v>
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2920671255271093</v>
+        <v>0.2932412115747531</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1041860149381777</v>
+        <v>0.1046349187084708</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1968653069685685</v>
+        <v>0.1965580513942289</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08062512054822907</v>
+        <v>0.07905761631300896</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2585078949733587</v>
+        <v>0.2595628525499616</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0867431976271803</v>
+        <v>0.0868888799509927</v>
       </c>
       <c r="H14" t="n">
         <v>0.5768557783561169</v>
@@ -1744,22 +1744,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5591812673748398</v>
+        <v>0.5620314611665793</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3983761988174742</v>
+        <v>0.4005005943763199</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2208517871001409</v>
+        <v>0.1697377313713465</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1653279834894521</v>
+        <v>0.1192092154191906</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2432285256190652</v>
+        <v>0.244222625209899</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1337512841790293</v>
+        <v>0.1339762895652925</v>
       </c>
       <c r="H15" t="n">
         <v>0.9740152227653087</v>
@@ -1835,22 +1835,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.442286207790443</v>
+        <v>0.4431110251831236</v>
       </c>
       <c r="C16" t="n">
-        <v>0.211920865206254</v>
+        <v>0.2119657789465685</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5145689578152761</v>
+        <v>0.6393940890752158</v>
       </c>
       <c r="E16" t="n">
-        <v>0.276151992190457</v>
+        <v>0.2120875018020139</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5960186701784498</v>
+        <v>0.5974690054540226</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2230456176603372</v>
+        <v>0.2232638951252287</v>
       </c>
       <c r="H16" t="n">
         <v>0.4381367147839849</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6423115683707827</v>
+        <v>0.6479219387602613</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6269419505926814</v>
+        <v>0.6328189223419141</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2757186692487619</v>
+        <v>0.2208205716346336</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2584610224057182</v>
+        <v>0.2160907278267805</v>
       </c>
       <c r="F17" t="n">
-        <v>0.286630144093278</v>
+        <v>0.2914639257766018</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2583452387262152</v>
+        <v>0.2638465548788085</v>
       </c>
       <c r="H17" t="n">
         <v>1.267429584043156</v>
@@ -2013,22 +2013,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.637848744230143</v>
+        <v>0.6406279695536129</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6511593181866413</v>
+        <v>0.654072195018223</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6019179516358679</v>
+        <v>0.6207277136611566</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6202999232563511</v>
+        <v>0.64030076757404</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6969688094413131</v>
+        <v>0.7025184375689592</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7864022075388453</v>
+        <v>0.792195435161309</v>
       </c>
       <c r="H18" t="n">
         <v>1.125928035226928</v>
@@ -2100,22 +2100,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1904163051400614</v>
+        <v>0.1896278569531041</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1884332286168046</v>
+        <v>0.188118634723341</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1565451600019258</v>
+        <v>0.1537774145378446</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1503655220126983</v>
+        <v>0.1432952211848578</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1910513920805034</v>
+        <v>0.1901435867294042</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1905351303278199</v>
+        <v>0.1898537073372083</v>
       </c>
       <c r="H19" t="n">
         <v>0.5491815241612263</v>
@@ -2191,22 +2191,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7293593490944378</v>
+        <v>0.7406468574923799</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4488879984604806</v>
+        <v>0.4574777834158045</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2002676952233996</v>
+        <v>0.186486781650812</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2011106069772561</v>
+        <v>0.1679186370778793</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5005641281952541</v>
+        <v>0.5131285652563626</v>
       </c>
       <c r="G20" t="n">
-        <v>0.297647384682605</v>
+        <v>0.3094729701462228</v>
       </c>
       <c r="H20" t="n">
         <v>1.089294365184146</v>
@@ -2282,22 +2282,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7239740436556632</v>
+        <v>0.7303025044867844</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4143180747888571</v>
+        <v>0.4179685807933835</v>
       </c>
       <c r="D21" t="n">
-        <v>0.229592248433986</v>
+        <v>0.1993850063364833</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2273870515325826</v>
+        <v>0.1959113675490289</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5314619300578343</v>
+        <v>0.5397447604860646</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2797781015077668</v>
+        <v>0.2853456092299797</v>
       </c>
       <c r="H21" t="n">
         <v>1.062546466477206</v>
@@ -2373,22 +2373,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7322707309508582</v>
+        <v>0.7389075598362194</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9213997600646255</v>
+        <v>0.9285619804635556</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4161492719640932</v>
+        <v>0.3888982418054168</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4183727070294904</v>
+        <v>0.3908363836904335</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4068273428105633</v>
+        <v>0.4135126407101541</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6572066433314125</v>
+        <v>0.6681327325023453</v>
       </c>
       <c r="H22" t="n">
         <v>1.313835537124292</v>
@@ -2464,22 +2464,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1512329026839858</v>
+        <v>0.1506717094638826</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1751177478773834</v>
+        <v>0.1751068087826258</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1115254930489307</v>
+        <v>0.1014638664029113</v>
       </c>
       <c r="E23" t="n">
-        <v>0.08807732527743281</v>
+        <v>0.05475782605272433</v>
       </c>
       <c r="F23" t="n">
-        <v>0.097137036862703</v>
+        <v>0.09603481377764664</v>
       </c>
       <c r="G23" t="n">
-        <v>0.09652282279685863</v>
+        <v>0.09628151140645312</v>
       </c>
       <c r="H23" t="n">
         <v>0.6014370052190726</v>
@@ -2555,22 +2555,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3869735630580513</v>
+        <v>0.3879212202361371</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3052003975854282</v>
+        <v>0.3060617672104368</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3089724144336009</v>
+        <v>0.3011984837515304</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2274284158346076</v>
+        <v>0.2203032240731948</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3903020583515717</v>
+        <v>0.392115580446842</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2747411246806065</v>
+        <v>0.276300479019369</v>
       </c>
       <c r="H24" t="n">
         <v>0.821026555289418</v>
@@ -2646,22 +2646,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3268569102081422</v>
+        <v>0.3295116663328739</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2538937462940787</v>
+        <v>0.2561222235387318</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1375218180182489</v>
+        <v>0.1162607454884587</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1082437298401514</v>
+        <v>0.08587497005443874</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2188270305443488</v>
+        <v>0.2215196251820541</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1194657674598903</v>
+        <v>0.1217121658615752</v>
       </c>
       <c r="H25" t="n">
         <v>0.8337220581801408</v>
@@ -2737,22 +2737,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.872883871615844</v>
+        <v>0.883211571559205</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7507428374206743</v>
+        <v>0.7604182013317495</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2848335346344756</v>
+        <v>0.2568436513644693</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2438520534556891</v>
+        <v>0.2162202262127234</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2978628948733776</v>
+        <v>0.3049341588356663</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2316464428886921</v>
+        <v>0.2381621173820295</v>
       </c>
       <c r="H26" t="n">
         <v>1.470782642072603</v>
@@ -2828,22 +2828,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.06209070135997041</v>
+        <v>0.06209220599517896</v>
       </c>
       <c r="C27" t="n">
-        <v>0.06058843569037616</v>
+        <v>0.0605726526230637</v>
       </c>
       <c r="D27" t="n">
-        <v>0.05450869935344153</v>
+        <v>0.05461616686306563</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04659918417406012</v>
+        <v>0.04623868421689228</v>
       </c>
       <c r="F27" t="n">
-        <v>0.04329214410308385</v>
+        <v>0.04329301900702714</v>
       </c>
       <c r="G27" t="n">
-        <v>0.03785599298397062</v>
+        <v>0.03785270690103291</v>
       </c>
       <c r="H27" t="n">
         <v>0.3074293300784401</v>
@@ -2919,22 +2919,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1789555169163922</v>
+        <v>0.1789506407839042</v>
       </c>
       <c r="C28" t="n">
-        <v>0.08621468211764582</v>
+        <v>0.08619385602205371</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1874346835849784</v>
+        <v>0.1937587760809739</v>
       </c>
       <c r="E28" t="n">
-        <v>0.09385636190596726</v>
+        <v>0.0861956375987431</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1832064545457336</v>
+        <v>0.1832017044101036</v>
       </c>
       <c r="G28" t="n">
-        <v>0.07976367325126485</v>
+        <v>0.07970759094368303</v>
       </c>
       <c r="H28" t="n">
         <v>0.3217073324512321</v>
@@ -3010,22 +3010,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.05062202091798106</v>
+        <v>0.05062347217280656</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03198477387495208</v>
+        <v>0.03198416287305984</v>
       </c>
       <c r="D29" t="n">
-        <v>0.04824924038581283</v>
+        <v>0.04653655240745246</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03104488529530007</v>
+        <v>0.03036483750533457</v>
       </c>
       <c r="F29" t="n">
-        <v>0.06017545084932899</v>
+        <v>0.06017572089167608</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03727301590486713</v>
+        <v>0.0372744770238319</v>
       </c>
       <c r="H29" t="n">
         <v>0.09125397575447609</v>
@@ -3101,22 +3101,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.08745317829444096</v>
+        <v>0.08740411312750856</v>
       </c>
       <c r="C30" t="n">
-        <v>0.07502031317468091</v>
+        <v>0.07498045169947692</v>
       </c>
       <c r="D30" t="n">
-        <v>0.05261315395249391</v>
+        <v>0.04116516601734409</v>
       </c>
       <c r="E30" t="n">
-        <v>0.04775550660191168</v>
+        <v>0.03221851295698297</v>
       </c>
       <c r="F30" t="n">
-        <v>0.04851589516782567</v>
+        <v>0.04851349675833913</v>
       </c>
       <c r="G30" t="n">
-        <v>0.03127086920263209</v>
+        <v>0.03127203433905391</v>
       </c>
       <c r="H30" t="n">
         <v>0.3364356123183577</v>
@@ -3192,22 +3192,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.08182635300630269</v>
+        <v>0.08182893705165355</v>
       </c>
       <c r="C31" t="n">
-        <v>0.06478582825837849</v>
+        <v>0.06479137392805756</v>
       </c>
       <c r="D31" t="n">
-        <v>0.08526911994492654</v>
+        <v>0.08908041772602046</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0700581191994345</v>
+        <v>0.06482343969746326</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1167905013042666</v>
+        <v>0.1167938068341898</v>
       </c>
       <c r="G31" t="n">
-        <v>0.07792697457924286</v>
+        <v>0.07792868571710398</v>
       </c>
       <c r="H31" t="n">
         <v>0.1898985606099392</v>
@@ -3283,22 +3283,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.08980306113039802</v>
+        <v>0.08980417516897896</v>
       </c>
       <c r="C32" t="n">
-        <v>0.04868215756582811</v>
+        <v>0.04867463037246214</v>
       </c>
       <c r="D32" t="n">
-        <v>0.07584796390215202</v>
+        <v>0.06835947207071258</v>
       </c>
       <c r="E32" t="n">
-        <v>0.04060711421612441</v>
+        <v>0.03852836558066905</v>
       </c>
       <c r="F32" t="n">
-        <v>0.08159418531519663</v>
+        <v>0.08158890131868768</v>
       </c>
       <c r="G32" t="n">
-        <v>0.04488211374051127</v>
+        <v>0.04487584215704166</v>
       </c>
       <c r="H32" t="n">
         <v>0.2272640433410283</v>
@@ -3374,22 +3374,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6440622190979554</v>
+        <v>0.6527772214040108</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5552354546608347</v>
+        <v>0.563245596371019</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2254124320560223</v>
+        <v>0.2037849108871594</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2184649778789399</v>
+        <v>0.1940490257510064</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4099940096962347</v>
+        <v>0.4218473544903005</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3822070154140901</v>
+        <v>0.3940136292074076</v>
       </c>
       <c r="H33" t="n">
         <v>1.247560275116454</v>
@@ -3465,22 +3465,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0854477862377236</v>
+        <v>0.08536305205716556</v>
       </c>
       <c r="C34" t="n">
-        <v>0.08509368781631851</v>
+        <v>0.08501923761903513</v>
       </c>
       <c r="D34" t="n">
-        <v>0.04862215708513989</v>
+        <v>0.04378010929919791</v>
       </c>
       <c r="E34" t="n">
-        <v>0.04789330228804726</v>
+        <v>0.04348458337406332</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01561872394026753</v>
+        <v>0.01561224212945124</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01768913577074501</v>
+        <v>0.01767254215939238</v>
       </c>
       <c r="H34" t="n">
         <v>0.463096312708327</v>
@@ -3556,22 +3556,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0483846818421164</v>
+        <v>0.04836425064970992</v>
       </c>
       <c r="C35" t="n">
-        <v>0.05110848708469201</v>
+        <v>0.05108781164030386</v>
       </c>
       <c r="D35" t="n">
-        <v>0.02607058764047995</v>
+        <v>0.02903071827914915</v>
       </c>
       <c r="E35" t="n">
-        <v>0.02794815596606998</v>
+        <v>0.0259860054391326</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02593182569228906</v>
+        <v>0.0259253034777502</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02502633535002009</v>
+        <v>0.0250120887060904</v>
       </c>
       <c r="H35" t="n">
         <v>0.3093751617228926</v>
@@ -3647,22 +3647,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0668863528938848</v>
+        <v>0.06675795015819569</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07025283137544314</v>
+        <v>0.07000986079852171</v>
       </c>
       <c r="D36" t="n">
-        <v>0.04341436111775326</v>
+        <v>0.04111648293305144</v>
       </c>
       <c r="E36" t="n">
-        <v>0.04894410327525936</v>
+        <v>0.04638968454756125</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01888819681058778</v>
+        <v>0.01889917391006096</v>
       </c>
       <c r="G36" t="n">
-        <v>0.01991588171852154</v>
+        <v>0.01980702482975925</v>
       </c>
       <c r="H36" t="n">
         <v>0.4447191641064449</v>
@@ -3738,22 +3738,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1464917618367143</v>
+        <v>0.14634961076987</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1409317732063562</v>
+        <v>0.1408043783363082</v>
       </c>
       <c r="D37" t="n">
-        <v>0.09619722974221739</v>
+        <v>0.08802569492734642</v>
       </c>
       <c r="E37" t="n">
-        <v>0.09662552067638767</v>
+        <v>0.08792673443779837</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1182552454175291</v>
+        <v>0.118008980587572</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1009976241980374</v>
+        <v>0.1007515737883619</v>
       </c>
       <c r="H37" t="n">
         <v>0.5039765573286296</v>
@@ -3829,22 +3829,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.09885212019616649</v>
+        <v>0.09876249192127846</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1027781491885576</v>
+        <v>0.1026693005871327</v>
       </c>
       <c r="D38" t="n">
-        <v>0.05400269989339657</v>
+        <v>0.03468468189346886</v>
       </c>
       <c r="E38" t="n">
-        <v>0.05430832365399961</v>
+        <v>0.03567638319215124</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01141995888986078</v>
+        <v>0.01143173644988334</v>
       </c>
       <c r="G38" t="n">
-        <v>0.01369342307155825</v>
+        <v>0.01369476158309697</v>
       </c>
       <c r="H38" t="n">
         <v>0.3771355762613469</v>
@@ -3920,22 +3920,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.2292632798573149</v>
+        <v>0.2323461754632751</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2470648518336619</v>
+        <v>0.2499494337485818</v>
       </c>
       <c r="D39" t="n">
-        <v>0.09932298189321746</v>
+        <v>0.1687390987338374</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1056972843730601</v>
+        <v>0.1183132221393223</v>
       </c>
       <c r="F39" t="n">
-        <v>0.177576102821746</v>
+        <v>0.1827674719427196</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1826107516956683</v>
+        <v>0.1869240753790934</v>
       </c>
       <c r="H39" t="n">
         <v>0.7973738576699186</v>
@@ -4011,22 +4011,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.176659470403294</v>
+        <v>2.20726662494302</v>
       </c>
       <c r="C40" t="n">
-        <v>1.440598954072454</v>
+        <v>1.471058876534665</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4985854483545043</v>
+        <v>0.5923958774020528</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4283723242020085</v>
+        <v>0.4591292957244525</v>
       </c>
       <c r="F40" t="n">
-        <v>1.291081265500372</v>
+        <v>1.332875044856526</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8217666368891547</v>
+        <v>0.861559449388288</v>
       </c>
       <c r="H40" t="n">
         <v>2.891582446522646</v>
@@ -4102,22 +4102,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1374789593221603</v>
+        <v>0.138271207485173</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1674945255161757</v>
+        <v>0.1690372876687692</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1231080035805337</v>
+        <v>0.1217941967342034</v>
       </c>
       <c r="E41" t="n">
-        <v>0.09617000663982304</v>
+        <v>0.09778313137220958</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1032329714397236</v>
+        <v>0.103268511605077</v>
       </c>
       <c r="G41" t="n">
-        <v>0.09797046564580314</v>
+        <v>0.0988943115843503</v>
       </c>
       <c r="H41" t="n">
         <v>0.6797073731912212</v>
@@ -4193,22 +4193,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.1138839432127154</v>
+        <v>0.1137540587471809</v>
       </c>
       <c r="C42" t="n">
-        <v>0.06944885831821999</v>
+        <v>0.06945355244657436</v>
       </c>
       <c r="D42" t="n">
-        <v>0.107764259893201</v>
+        <v>0.1171555275060012</v>
       </c>
       <c r="E42" t="n">
-        <v>0.06076044686371557</v>
+        <v>0.06041729594430501</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1525932806823556</v>
+        <v>0.1525091787535633</v>
       </c>
       <c r="G42" t="n">
-        <v>0.08168133771083164</v>
+        <v>0.08167519798796011</v>
       </c>
       <c r="H42" t="n">
         <v>0.2705128397863901</v>
@@ -4284,22 +4284,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3444924546686243</v>
+        <v>0.3446482940635034</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3438834497616556</v>
+        <v>0.3440874118987211</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4777109793646692</v>
+        <v>0.3448294206419265</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4779420532169195</v>
+        <v>0.3442702888129965</v>
       </c>
       <c r="F43" t="n">
-        <v>0.337272558177458</v>
+        <v>0.3378604868055509</v>
       </c>
       <c r="G43" t="n">
-        <v>0.35662233738989</v>
+        <v>0.3573042806323476</v>
       </c>
       <c r="H43" t="n">
         <v>0.5606279224051089</v>
@@ -4371,22 +4371,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.612951150599275</v>
+        <v>2.655287961883142</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9194275985726272</v>
+        <v>0.9573762377795885</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2404087927617125</v>
+        <v>0.3414221180999144</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1770103518960476</v>
+        <v>0.1801894130515869</v>
       </c>
       <c r="F44" t="n">
-        <v>1.319054026459224</v>
+        <v>1.371088009161491</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4072431677384767</v>
+        <v>0.4448171954293003</v>
       </c>
       <c r="H44" t="n">
         <v>2.229510190828526</v>
@@ -4462,22 +4462,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.03331598819380426</v>
+        <v>0.03332803834677197</v>
       </c>
       <c r="C45" t="n">
-        <v>0.03195033527153886</v>
+        <v>0.03193866572211082</v>
       </c>
       <c r="D45" t="n">
-        <v>0.03436419611839148</v>
+        <v>0.03316634188493844</v>
       </c>
       <c r="E45" t="n">
-        <v>0.03244838530861169</v>
+        <v>0.03192361493182582</v>
       </c>
       <c r="F45" t="n">
-        <v>0.02143373418196085</v>
+        <v>0.02144053441184001</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02523983426284379</v>
+        <v>0.02525841726459214</v>
       </c>
       <c r="H45" t="n">
         <v>0.219637958318896</v>
@@ -4553,22 +4553,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0322194516340248</v>
+        <v>0.03222301259357571</v>
       </c>
       <c r="C46" t="n">
-        <v>0.03275967145154728</v>
+        <v>0.03274604300008147</v>
       </c>
       <c r="D46" t="n">
-        <v>0.02616279193495407</v>
+        <v>0.0259369108901331</v>
       </c>
       <c r="E46" t="n">
-        <v>0.02544025391311809</v>
+        <v>0.02454787902311676</v>
       </c>
       <c r="F46" t="n">
-        <v>0.02352467013804313</v>
+        <v>0.02352756451655235</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02384707088720667</v>
+        <v>0.0238456191265252</v>
       </c>
       <c r="H46" t="n">
         <v>0.2253013199805374</v>
@@ -4644,22 +4644,22 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.09631777172591401</v>
+        <v>0.09631688033969857</v>
       </c>
       <c r="C47" t="n">
-        <v>0.05391899678332773</v>
+        <v>0.05391620063076814</v>
       </c>
       <c r="D47" t="n">
-        <v>0.08885543685280874</v>
+        <v>0.08686628374878885</v>
       </c>
       <c r="E47" t="n">
-        <v>0.04607369985264685</v>
+        <v>0.05174559238114183</v>
       </c>
       <c r="F47" t="n">
-        <v>0.09710057510023476</v>
+        <v>0.09709946130910892</v>
       </c>
       <c r="G47" t="n">
-        <v>0.04481351055790582</v>
+        <v>0.04480399718747517</v>
       </c>
       <c r="H47" t="n">
         <v>0.2500371999588092</v>
@@ -4735,22 +4735,22 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.06368047523613517</v>
+        <v>0.06368051490744006</v>
       </c>
       <c r="C48" t="n">
-        <v>0.04580288234433263</v>
+        <v>0.04579888969273014</v>
       </c>
       <c r="D48" t="n">
-        <v>0.07182106631692292</v>
+        <v>0.06372858256602375</v>
       </c>
       <c r="E48" t="n">
-        <v>0.05593343266479125</v>
+        <v>0.04583886555291042</v>
       </c>
       <c r="F48" t="n">
-        <v>0.05536977813515351</v>
+        <v>0.05537294625574413</v>
       </c>
       <c r="G48" t="n">
-        <v>0.04970289974600225</v>
+        <v>0.04969645943058117</v>
       </c>
       <c r="H48" t="n">
         <v>0.2334066842779279</v>
@@ -4826,22 +4826,22 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.3060418550935764</v>
+        <v>0.3059927557710973</v>
       </c>
       <c r="C49" t="n">
-        <v>0.07175429402834671</v>
+        <v>0.07169326760165609</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1805187922362755</v>
+        <v>0.1371160641778377</v>
       </c>
       <c r="E49" t="n">
-        <v>0.05455273800695817</v>
+        <v>0.05564348626170174</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2450898706422214</v>
+        <v>0.2449324430605841</v>
       </c>
       <c r="G49" t="n">
-        <v>0.062826540815278</v>
+        <v>0.06279262666724007</v>
       </c>
       <c r="H49" t="n">
         <v>0.3379122681153697</v>
@@ -4917,22 +4917,22 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6840985940218069</v>
+        <v>0.6909651190270951</v>
       </c>
       <c r="C50" t="n">
-        <v>0.5903853788154254</v>
+        <v>0.5979419600217496</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3212627902668799</v>
+        <v>0.2909470387874272</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2001038385942729</v>
+        <v>0.1774640663746824</v>
       </c>
       <c r="F50" t="n">
-        <v>0.458720197710584</v>
+        <v>0.4682451549912295</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3680109533718217</v>
+        <v>0.3786749325392345</v>
       </c>
       <c r="H50" t="n">
         <v>1.363451004429825</v>
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.204786427927824</v>
+        <v>0.2051319963174478</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2149953799025232</v>
+        <v>0.2153930489723502</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1337957632409009</v>
+        <v>0.122807371894588</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1299887319900975</v>
+        <v>0.1115520870578637</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1272845194754229</v>
+        <v>0.1262412621544324</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1344765159890682</v>
+        <v>0.1345613439814875</v>
       </c>
       <c r="H51" t="n">
         <v>0.670665120055479</v>
@@ -5099,22 +5099,22 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.873165239494961</v>
+        <v>1.894771884312891</v>
       </c>
       <c r="C52" t="n">
-        <v>1.790519812538393</v>
+        <v>1.812001984309809</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5379122238773966</v>
+        <v>0.5887883204810218</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5366040227450868</v>
+        <v>0.5757460453968697</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7676073478717342</v>
+        <v>0.8010718873641539</v>
       </c>
       <c r="G52" t="n">
-        <v>0.7482497034087562</v>
+        <v>0.7791724793142314</v>
       </c>
       <c r="H52" t="n">
         <v>2.498364972397039</v>
@@ -5190,22 +5190,22 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.289916854190355</v>
+        <v>1.308702605760026</v>
       </c>
       <c r="C53" t="n">
-        <v>1.233430361005032</v>
+        <v>1.252326923232601</v>
       </c>
       <c r="D53" t="n">
-        <v>0.5086743021041202</v>
+        <v>0.5273374400992735</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5064510597699509</v>
+        <v>0.5198032238083613</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6088718951208986</v>
+        <v>0.6526072934147202</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5805282805545847</v>
+        <v>0.6229467913638486</v>
       </c>
       <c r="H53" t="n">
         <v>2.028441185139194</v>
@@ -5281,22 +5281,22 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2138914660573546</v>
+        <v>0.213056838755463</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1740842141177434</v>
+        <v>0.1739100192788041</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2448301919883127</v>
+        <v>0.2910446101855437</v>
       </c>
       <c r="E54" t="n">
-        <v>0.1455294294101821</v>
+        <v>0.1461670215316392</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2417386773967952</v>
+        <v>0.2406049859659714</v>
       </c>
       <c r="G54" t="n">
-        <v>0.1823492736243789</v>
+        <v>0.1819613869179339</v>
       </c>
       <c r="H54" t="n">
         <v>0.4376089963335965</v>
@@ -5372,22 +5372,22 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.04714627582562514</v>
+        <v>0.04714998855346699</v>
       </c>
       <c r="C55" t="n">
-        <v>0.03961353625630516</v>
+        <v>0.03961087926114863</v>
       </c>
       <c r="D55" t="n">
-        <v>0.06242285418121878</v>
+        <v>0.04716150579924855</v>
       </c>
       <c r="E55" t="n">
-        <v>0.04338152522241618</v>
+        <v>0.03958345147957278</v>
       </c>
       <c r="F55" t="n">
-        <v>0.05499052834902712</v>
+        <v>0.05498032633931599</v>
       </c>
       <c r="G55" t="n">
-        <v>0.03783717571723985</v>
+        <v>0.03783347192799719</v>
       </c>
       <c r="H55" t="n">
         <v>0.236689300497001</v>
@@ -5463,22 +5463,22 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2521829696999432</v>
+        <v>0.2527411499812227</v>
       </c>
       <c r="C56" t="n">
-        <v>0.238316414300351</v>
+        <v>0.238700262635395</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2826406787859352</v>
+        <v>0.3705614831269311</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2752588977143555</v>
+        <v>0.382411423631514</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3151929039205348</v>
+        <v>0.3165282661758949</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2817020181357339</v>
+        <v>0.2829634898298001</v>
       </c>
       <c r="H56" t="n">
         <v>0.6666406779747964</v>
@@ -5554,22 +5554,22 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.1023787290167538</v>
+        <v>0.1027988154319533</v>
       </c>
       <c r="C57" t="n">
-        <v>0.09847606932852988</v>
+        <v>0.09880985155960867</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1504283230663902</v>
+        <v>0.1074578636293353</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1583237715490425</v>
+        <v>0.100515956161974</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1035755152201526</v>
+        <v>0.104282529496099</v>
       </c>
       <c r="G57" t="n">
-        <v>0.09960801785201528</v>
+        <v>0.1004864794446268</v>
       </c>
       <c r="H57" t="n">
         <v>0.5431663794570629</v>
@@ -5645,22 +5645,22 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5496034090183648</v>
+        <v>0.5545646363365251</v>
       </c>
       <c r="C58" t="n">
-        <v>0.3077934321238844</v>
+        <v>0.3114093782532871</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1660624272574176</v>
+        <v>0.1306651476089649</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1168231152033335</v>
+        <v>0.09084150395632271</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3380100503185614</v>
+        <v>0.3427456975396489</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1557150092806882</v>
+        <v>0.1588725788136234</v>
       </c>
       <c r="H58" t="n">
         <v>0.9187102398267176</v>
@@ -5736,22 +5736,22 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.01069965717021816</v>
+        <v>0.01070180768731761</v>
       </c>
       <c r="C59" t="n">
-        <v>0.00348980243758668</v>
+        <v>0.003505680930805725</v>
       </c>
       <c r="D59" t="n">
-        <v>0.01067535233912223</v>
+        <v>0.01010799363433923</v>
       </c>
       <c r="E59" t="n">
-        <v>0.003474121995865</v>
+        <v>0.002045224741455347</v>
       </c>
       <c r="F59" t="n">
-        <v>0.01218136814033164</v>
+        <v>0.01218386234700448</v>
       </c>
       <c r="G59" t="n">
-        <v>0.003872300574445101</v>
+        <v>0.003878637513017395</v>
       </c>
       <c r="H59" t="n">
         <v>0.006201137995202942</v>
@@ -5823,22 +5823,22 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.200734901867383</v>
+        <v>1.213570924243425</v>
       </c>
       <c r="C60" t="n">
-        <v>0.9947367775508236</v>
+        <v>1.007183481380457</v>
       </c>
       <c r="D60" t="n">
-        <v>0.5666852183427289</v>
+        <v>0.5767649320092227</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5324711109684928</v>
+        <v>0.5287418907149984</v>
       </c>
       <c r="F60" t="n">
-        <v>1.09770371264433</v>
+        <v>1.118752094583926</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9308857052019616</v>
+        <v>0.9516889148506655</v>
       </c>
       <c r="H60" t="n">
         <v>1.935074098502654</v>
@@ -5914,22 +5914,22 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8948468711014095</v>
+        <v>0.9036267729760226</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8237799758796103</v>
+        <v>0.8327522241917067</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4139583564774589</v>
+        <v>0.4030928101472567</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3701469398155657</v>
+        <v>0.3576351673817741</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6187637424997073</v>
+        <v>0.6305351296495791</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6068591097220837</v>
+        <v>0.6188532450670831</v>
       </c>
       <c r="H61" t="n">
         <v>1.482727576453942</v>
@@ -6005,22 +6005,22 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4473683277229435</v>
+        <v>0.4564630016561046</v>
       </c>
       <c r="C62" t="n">
-        <v>0.5268601341972636</v>
+        <v>0.5364328134386336</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1411543848494224</v>
+        <v>0.111314903893637</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1335603011135824</v>
+        <v>0.09822912572090017</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1239217122501966</v>
+        <v>0.1316441382711224</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2047731826126356</v>
+        <v>0.216000490883848</v>
       </c>
       <c r="H62" t="n">
         <v>1.170048173221576</v>
@@ -6096,22 +6096,22 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.1888796810650156</v>
+        <v>0.1887737044319772</v>
       </c>
       <c r="C63" t="n">
-        <v>0.09466409946582822</v>
+        <v>0.09455052318571666</v>
       </c>
       <c r="D63" t="n">
-        <v>0.1166109985121835</v>
+        <v>0.09675026292982283</v>
       </c>
       <c r="E63" t="n">
-        <v>0.07483400995299294</v>
+        <v>0.07228009391647686</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1532514685574587</v>
+        <v>0.1531616659823475</v>
       </c>
       <c r="G63" t="n">
-        <v>0.08765895572620511</v>
+        <v>0.08755751238176694</v>
       </c>
       <c r="H63" t="n">
         <v>0.3847615424008634</v>
@@ -6187,22 +6187,22 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.404451742840073</v>
+        <v>0.4070565983226671</v>
       </c>
       <c r="C64" t="n">
-        <v>0.4486733299467988</v>
+        <v>0.4520187022178964</v>
       </c>
       <c r="D64" t="n">
-        <v>0.2833871379803188</v>
+        <v>0.2497286531485543</v>
       </c>
       <c r="E64" t="n">
-        <v>0.2613926705832405</v>
+        <v>0.2384426269210413</v>
       </c>
       <c r="F64" t="n">
-        <v>0.2574342269295922</v>
+        <v>0.2598138693543705</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3550939014215055</v>
+        <v>0.3603051201140942</v>
       </c>
       <c r="H64" t="n">
         <v>0.9613842667655157</v>
@@ -6278,22 +6278,22 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8100503163597574</v>
+        <v>0.8151406208621141</v>
       </c>
       <c r="C65" t="n">
-        <v>0.8503065253938112</v>
+        <v>0.8557139004397631</v>
       </c>
       <c r="D65" t="n">
-        <v>0.477666647424627</v>
+        <v>0.4136129644443014</v>
       </c>
       <c r="E65" t="n">
-        <v>0.4762394414357909</v>
+        <v>0.4151763266802893</v>
       </c>
       <c r="F65" t="n">
-        <v>0.5659520771867892</v>
+        <v>0.5733066533221627</v>
       </c>
       <c r="G65" t="n">
-        <v>0.6513086109747082</v>
+        <v>0.6601094192053441</v>
       </c>
       <c r="H65" t="n">
         <v>1.364498070866812</v>
@@ -6369,22 +6369,22 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5500107779183755</v>
+        <v>0.5560811269541756</v>
       </c>
       <c r="C66" t="n">
-        <v>0.2452764265298352</v>
+        <v>0.2488801367927591</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1901568000549805</v>
+        <v>0.1763583548488111</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1366454833290355</v>
+        <v>0.1294012003798869</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4264021569968425</v>
+        <v>0.4335790808506703</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1837905659310665</v>
+        <v>0.1894164891156891</v>
       </c>
       <c r="H66" t="n">
         <v>0.8762976441872627</v>
@@ -6460,22 +6460,22 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.3069902745692473</v>
+        <v>0.3089713355605678</v>
       </c>
       <c r="C67" t="n">
-        <v>0.3385205575315248</v>
+        <v>0.3407940458350395</v>
       </c>
       <c r="D67" t="n">
-        <v>0.1608878936637572</v>
+        <v>0.1232504414075233</v>
       </c>
       <c r="E67" t="n">
-        <v>0.1538895778675722</v>
+        <v>0.1181106148798783</v>
       </c>
       <c r="F67" t="n">
-        <v>0.05688195082219435</v>
+        <v>0.05676080471115953</v>
       </c>
       <c r="G67" t="n">
-        <v>0.06095615734232597</v>
+        <v>0.06118083554809368</v>
       </c>
       <c r="H67" t="n">
         <v>0.8890729753981951</v>
@@ -6551,22 +6551,22 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.662448280208053</v>
+        <v>0.6631777913600052</v>
       </c>
       <c r="C68" t="n">
-        <v>0.66810504772255</v>
+        <v>0.6705564120270601</v>
       </c>
       <c r="D68" t="n">
-        <v>0.7728923487573137</v>
+        <v>0.8349100857559916</v>
       </c>
       <c r="E68" t="n">
-        <v>0.6469316610256572</v>
+        <v>0.6967626147329891</v>
       </c>
       <c r="F68" t="n">
-        <v>0.5842137924534123</v>
+        <v>0.5809149818137502</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6838813150955632</v>
+        <v>0.6888483953701938</v>
       </c>
       <c r="H68" t="n">
         <v>0.822053537981963</v>
@@ -6642,22 +6642,22 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.05047562623546362</v>
+        <v>0.05047220636443453</v>
       </c>
       <c r="C69" t="n">
-        <v>0.04231524861368141</v>
+        <v>0.04230920210331721</v>
       </c>
       <c r="D69" t="n">
-        <v>0.05341973827046485</v>
+        <v>0.0504964250446171</v>
       </c>
       <c r="E69" t="n">
-        <v>0.04466509657035847</v>
+        <v>0.04233260812396031</v>
       </c>
       <c r="F69" t="n">
-        <v>0.06990368499969123</v>
+        <v>0.06990335025584646</v>
       </c>
       <c r="G69" t="n">
-        <v>0.05181889340397892</v>
+        <v>0.05181706434817195</v>
       </c>
       <c r="H69" t="n">
         <v>0.1158922377181897</v>
@@ -6733,22 +6733,22 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.1273963128320198</v>
+        <v>0.1273872508930199</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1236690984014929</v>
+        <v>0.1236600940350201</v>
       </c>
       <c r="D70" t="n">
-        <v>0.133155329887615</v>
+        <v>0.1274038515006694</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1288691853248473</v>
+        <v>0.1236753522000469</v>
       </c>
       <c r="F70" t="n">
-        <v>0.124037060869984</v>
+        <v>0.1240148688696252</v>
       </c>
       <c r="G70" t="n">
-        <v>0.1298619911241934</v>
+        <v>0.1298159387574236</v>
       </c>
       <c r="H70" t="n">
         <v>0.2999663024798833</v>
@@ -6824,22 +6824,22 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6425903599198878</v>
+        <v>0.6516565396681242</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5172800449691167</v>
+        <v>0.5259812140853551</v>
       </c>
       <c r="D71" t="n">
-        <v>0.1707059884103302</v>
+        <v>0.1452827997299384</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1308324049592298</v>
+        <v>0.1076709468327376</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2686177537039045</v>
+        <v>0.2786131820503252</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2038562595353702</v>
+        <v>0.2130458724335875</v>
       </c>
       <c r="H71" t="n">
         <v>1.182881379043306</v>
@@ -6915,22 +6915,22 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3.293212784629119</v>
+        <v>3.350387418268979</v>
       </c>
       <c r="C72" t="n">
-        <v>3.520505742783079</v>
+        <v>3.577659658279347</v>
       </c>
       <c r="D72" t="n">
-        <v>0.7153083021040144</v>
+        <v>0.8737723244635797</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7233558838753511</v>
+        <v>0.9316682414789437</v>
       </c>
       <c r="F72" t="n">
-        <v>1.147964431322103</v>
+        <v>1.227948464409322</v>
       </c>
       <c r="G72" t="n">
-        <v>1.534853602272551</v>
+        <v>1.618670079357371</v>
       </c>
       <c r="H72" t="n">
         <v>4.167768298998758</v>
@@ -7006,22 +7006,22 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.1845991271489243</v>
+        <v>0.1847881227531005</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1906756033821027</v>
+        <v>0.1909440198993982</v>
       </c>
       <c r="D73" t="n">
-        <v>0.06141357604124117</v>
+        <v>0.03835691720416959</v>
       </c>
       <c r="E73" t="n">
-        <v>0.06439185500807461</v>
+        <v>0.04036955990711219</v>
       </c>
       <c r="F73" t="n">
-        <v>0.03218089471606202</v>
+        <v>0.03176629783439618</v>
       </c>
       <c r="G73" t="n">
-        <v>0.04278883743759212</v>
+        <v>0.042483375849534</v>
       </c>
       <c r="H73" t="n">
         <v>0.668404623200426</v>
@@ -7097,22 +7097,22 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.1353924339769865</v>
+        <v>0.1353285334913661</v>
       </c>
       <c r="C74" t="n">
-        <v>0.07068549879727005</v>
+        <v>0.0706640673046199</v>
       </c>
       <c r="D74" t="n">
-        <v>0.147445857455968</v>
+        <v>0.1536640538217375</v>
       </c>
       <c r="E74" t="n">
-        <v>0.08033887933527084</v>
+        <v>0.07068272011491204</v>
       </c>
       <c r="F74" t="n">
-        <v>0.1415945632648525</v>
+        <v>0.1415480457992404</v>
       </c>
       <c r="G74" t="n">
-        <v>0.07561744244088869</v>
+        <v>0.07554228023362257</v>
       </c>
       <c r="H74" t="n">
         <v>0.3266677650070184</v>
@@ -7188,22 +7188,22 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4839077449916938</v>
+        <v>0.485487049704903</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4740256538946969</v>
+        <v>0.4755706811882146</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4646588298286941</v>
+        <v>0.4917437421507509</v>
       </c>
       <c r="E75" t="n">
-        <v>0.4522829614887505</v>
+        <v>0.4778745033745449</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5161974729917418</v>
+        <v>0.5197976002511773</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5080554833853561</v>
+        <v>0.5114549341073915</v>
       </c>
       <c r="H75" t="n">
         <v>0.9493752443193544</v>
@@ -7279,22 +7279,22 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.05680098241601657</v>
+        <v>0.05668207815560468</v>
       </c>
       <c r="C76" t="n">
-        <v>0.07772695300113576</v>
+        <v>0.07760132626553273</v>
       </c>
       <c r="D76" t="n">
-        <v>0.06508706523566304</v>
+        <v>0.06150672614568146</v>
       </c>
       <c r="E76" t="n">
-        <v>0.06339999228306879</v>
+        <v>0.06571364627998162</v>
       </c>
       <c r="F76" t="n">
-        <v>0.05207225791951461</v>
+        <v>0.05204542838263079</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0521624891861768</v>
+        <v>0.05202131913271273</v>
       </c>
       <c r="H76" t="n">
         <v>0.4181268703617883</v>
@@ -7370,22 +7370,22 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.452423585095831</v>
+        <v>0.4560973693380577</v>
       </c>
       <c r="C77" t="n">
-        <v>0.4293620667935875</v>
+        <v>0.4327602875442319</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2026615052619459</v>
+        <v>0.1753063497338901</v>
       </c>
       <c r="E77" t="n">
-        <v>0.2162451255794264</v>
+        <v>0.1804258979309288</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1835066644147286</v>
+        <v>0.185690276354786</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1919652221842012</v>
+        <v>0.1939623591508854</v>
       </c>
       <c r="H77" t="n">
         <v>0.9740670823972597</v>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.04193238420574749</v>
+        <v>0.04192308441823638</v>
       </c>
       <c r="C78" t="n">
-        <v>0.03823736934336364</v>
+        <v>0.03823689010608669</v>
       </c>
       <c r="D78" t="n">
-        <v>0.03254558021831363</v>
+        <v>0.03220530403184958</v>
       </c>
       <c r="E78" t="n">
-        <v>0.02382936757673709</v>
+        <v>0.02573356602782632</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0354828573689759</v>
+        <v>0.03548802700540128</v>
       </c>
       <c r="G78" t="n">
-        <v>0.02299361485054811</v>
+        <v>0.0229989616065663</v>
       </c>
       <c r="H78" t="n">
         <v>0.2724125086601074</v>
@@ -7552,22 +7552,22 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.04773620914881126</v>
+        <v>0.04768038653178022</v>
       </c>
       <c r="C79" t="n">
-        <v>0.03696043925709222</v>
+        <v>0.03695758665776566</v>
       </c>
       <c r="D79" t="n">
-        <v>0.02376322984016314</v>
+        <v>0.02387395440319208</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0164747389479921</v>
+        <v>0.01414324716831614</v>
       </c>
       <c r="F79" t="n">
-        <v>0.03259225650611045</v>
+        <v>0.03259144092452313</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0187681529587576</v>
+        <v>0.01877024924355914</v>
       </c>
       <c r="H79" t="n">
         <v>0.2823531843116658</v>
@@ -7643,22 +7643,22 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4439405340524532</v>
+        <v>0.4451411360154857</v>
       </c>
       <c r="C80" t="n">
-        <v>0.4097069607606008</v>
+        <v>0.4106466389541653</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2637600086223316</v>
+        <v>0.2273081823840675</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2762473276393793</v>
+        <v>0.238598667621214</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3145615558490886</v>
+        <v>0.3165184675901519</v>
       </c>
       <c r="G80" t="n">
-        <v>0.2675585508784515</v>
+        <v>0.2688966341496576</v>
       </c>
       <c r="H80" t="n">
         <v>0.9166327752016876</v>
@@ -7734,22 +7734,22 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.1932324323840491</v>
+        <v>0.1931900827163729</v>
       </c>
       <c r="C81" t="n">
-        <v>0.1850011865960572</v>
+        <v>0.1849764482176594</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2247524556740328</v>
+        <v>0.1932565142188136</v>
       </c>
       <c r="E81" t="n">
-        <v>0.225689796956986</v>
+        <v>0.1850535555573287</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1625152173025559</v>
+        <v>0.1622183733960993</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1711785783124165</v>
+        <v>0.1711579563257946</v>
       </c>
       <c r="H81" t="n">
         <v>0.4638560507984801</v>
@@ -7825,22 +7825,22 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.1745949277397718</v>
+        <v>0.175731116853999</v>
       </c>
       <c r="C82" t="n">
-        <v>0.1937871232271339</v>
+        <v>0.1949730517241973</v>
       </c>
       <c r="D82" t="n">
-        <v>0.1646959507931701</v>
+        <v>0.1955475094318966</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1570065992338538</v>
+        <v>0.1867454436277563</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1111443420534798</v>
+        <v>0.1121051447128653</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1571858986358178</v>
+        <v>0.1594189571199458</v>
       </c>
       <c r="H82" t="n">
         <v>0.7015311782717396</v>
@@ -7916,22 +7916,22 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4148229520931013</v>
+        <v>0.4149946399151719</v>
       </c>
       <c r="C83" t="n">
-        <v>0.3400424078799716</v>
+        <v>0.3398436331489901</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2859288383952585</v>
+        <v>0.2131007723176298</v>
       </c>
       <c r="E83" t="n">
-        <v>0.2120628695412612</v>
+        <v>0.1441034777410879</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2708225214381461</v>
+        <v>0.2707612399366178</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1717092471153511</v>
+        <v>0.171162502077699</v>
       </c>
       <c r="H83" t="n">
         <v>0.7520441762890825</v>
@@ -8007,22 +8007,22 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.1211412341739032</v>
+        <v>0.1210964294675984</v>
       </c>
       <c r="C84" t="n">
-        <v>0.06817005998149861</v>
+        <v>0.06816893956209111</v>
       </c>
       <c r="D84" t="n">
-        <v>0.129936494587774</v>
+        <v>0.1195755864341048</v>
       </c>
       <c r="E84" t="n">
-        <v>0.06396572852290711</v>
+        <v>0.06389656552322329</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1338064858466766</v>
+        <v>0.133674115406255</v>
       </c>
       <c r="G84" t="n">
-        <v>0.05665348899092821</v>
+        <v>0.05663860313480173</v>
       </c>
       <c r="H84" t="n">
         <v>0.2231897293196931</v>
@@ -8098,22 +8098,22 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.510422582218822</v>
+        <v>0.5134568511776598</v>
       </c>
       <c r="C85" t="n">
-        <v>0.4397463657368531</v>
+        <v>0.4423549872220918</v>
       </c>
       <c r="D85" t="n">
-        <v>0.2696310255395803</v>
+        <v>0.2253463356779155</v>
       </c>
       <c r="E85" t="n">
-        <v>0.2564132745203953</v>
+        <v>0.2058105708765144</v>
       </c>
       <c r="F85" t="n">
-        <v>0.3362286071829013</v>
+        <v>0.3396050305073505</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1914935748245721</v>
+        <v>0.1931323905399069</v>
       </c>
       <c r="H85" t="n">
         <v>0.9954997516854572</v>
@@ -8189,22 +8189,22 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.3202059067660491</v>
+        <v>0.318521834830125</v>
       </c>
       <c r="C86" t="n">
-        <v>0.3573716986561182</v>
+        <v>0.3606749140695932</v>
       </c>
       <c r="D86" t="n">
-        <v>0.5407083388679276</v>
+        <v>0.5775798131984072</v>
       </c>
       <c r="E86" t="n">
-        <v>0.209439641439104</v>
+        <v>0.2266939034529027</v>
       </c>
       <c r="F86" t="n">
-        <v>0.3644815555340168</v>
+        <v>0.3601302514379101</v>
       </c>
       <c r="G86" t="n">
-        <v>0.3029969838179791</v>
+        <v>0.3079378018379147</v>
       </c>
       <c r="H86" t="n">
         <v>0.7662289278414284</v>
@@ -8280,22 +8280,22 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.1923719069534917</v>
+        <v>0.1922771564913701</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1970371336006093</v>
+        <v>0.1969659347380368</v>
       </c>
       <c r="D87" t="n">
-        <v>0.1205584589227223</v>
+        <v>0.1158358232167569</v>
       </c>
       <c r="E87" t="n">
-        <v>0.128386810325648</v>
+        <v>0.112450366577684</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1342366707659907</v>
+        <v>0.1336106464101122</v>
       </c>
       <c r="G87" t="n">
-        <v>0.1456429765870829</v>
+        <v>0.1454582511313159</v>
       </c>
       <c r="H87" t="n">
         <v>0.6211718381693592</v>
@@ -8371,22 +8371,22 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.2500518805500822</v>
+        <v>0.2498146035911715</v>
       </c>
       <c r="C88" t="n">
-        <v>0.2253461942215374</v>
+        <v>0.2250743739489326</v>
       </c>
       <c r="D88" t="n">
-        <v>0.1836589150026674</v>
+        <v>0.1740465573592646</v>
       </c>
       <c r="E88" t="n">
-        <v>0.1633708305723015</v>
+        <v>0.1468791610224586</v>
       </c>
       <c r="F88" t="n">
-        <v>0.2100103433432283</v>
+        <v>0.2098013315741654</v>
       </c>
       <c r="G88" t="n">
-        <v>0.170745993873321</v>
+        <v>0.1704231739774071</v>
       </c>
       <c r="H88" t="n">
         <v>0.5425971346865082</v>
@@ -8462,22 +8462,22 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.1240746344852505</v>
+        <v>0.1240731402737125</v>
       </c>
       <c r="C89" t="n">
-        <v>0.10721562880885</v>
+        <v>0.1072150119112024</v>
       </c>
       <c r="D89" t="n">
-        <v>0.1175988628687091</v>
+        <v>0.1169118752503499</v>
       </c>
       <c r="E89" t="n">
-        <v>0.09870456176702924</v>
+        <v>0.08795776493967382</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1391611800045885</v>
+        <v>0.1391606600477753</v>
       </c>
       <c r="G89" t="n">
-        <v>0.1090084520034156</v>
+        <v>0.1090101807465273</v>
       </c>
       <c r="H89" t="n">
         <v>0.190759435338714</v>
@@ -8553,22 +8553,22 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.1237987896069652</v>
+        <v>0.1239208804852275</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0895204969101239</v>
+        <v>0.08946455253497157</v>
       </c>
       <c r="D90" t="n">
-        <v>0.1240439009153018</v>
+        <v>0.1238402298880464</v>
       </c>
       <c r="E90" t="n">
-        <v>0.09859070490057775</v>
+        <v>0.08845743782659278</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1464505321003367</v>
+        <v>0.1465996237813318</v>
       </c>
       <c r="G90" t="n">
-        <v>0.098512786202688</v>
+        <v>0.09839574785023122</v>
       </c>
       <c r="H90" t="n">
         <v>0.4537308513006609</v>
@@ -8644,22 +8644,22 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.1952195881680046</v>
+        <v>0.1952531656077584</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1881362251508838</v>
+        <v>0.1879454717026323</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1589188806514904</v>
+        <v>0.1657094297541303</v>
       </c>
       <c r="E91" t="n">
-        <v>0.15416089792945</v>
+        <v>0.155149130453718</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1471341792616021</v>
+        <v>0.1466640876877139</v>
       </c>
       <c r="G91" t="n">
-        <v>0.1188300783745485</v>
+        <v>0.1184146413424235</v>
       </c>
       <c r="H91" t="n">
         <v>0.6277099064094847</v>
@@ -8735,22 +8735,22 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.8456660401131435</v>
+        <v>0.8576937447960855</v>
       </c>
       <c r="C92" t="n">
-        <v>0.9767861886354666</v>
+        <v>0.9888837269216366</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3563273127023726</v>
+        <v>0.335330810253567</v>
       </c>
       <c r="E92" t="n">
-        <v>0.3816727887375128</v>
+        <v>0.3681962388429534</v>
       </c>
       <c r="F92" t="n">
-        <v>0.2195117517801227</v>
+        <v>0.2274919886084814</v>
       </c>
       <c r="G92" t="n">
-        <v>0.3669666622311407</v>
+        <v>0.3829546148099282</v>
       </c>
       <c r="H92" t="n">
         <v>1.486341126158328</v>
@@ -8826,22 +8826,22 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.1715359834888787</v>
+        <v>0.1717056402946943</v>
       </c>
       <c r="C93" t="n">
-        <v>0.1672112204409905</v>
+        <v>0.1673793892983393</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1339859580032167</v>
+        <v>0.1343344686536336</v>
       </c>
       <c r="E93" t="n">
-        <v>0.132259873242053</v>
+        <v>0.1396814974513654</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1571011094565268</v>
+        <v>0.1570570902007696</v>
       </c>
       <c r="G93" t="n">
-        <v>0.1400536721949763</v>
+        <v>0.1399106196576736</v>
       </c>
       <c r="H93" t="n">
         <v>0.575614988254466</v>
@@ -8917,22 +8917,22 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6080455303125727</v>
+        <v>0.6147044898013378</v>
       </c>
       <c r="C94" t="n">
-        <v>0.6155512728798691</v>
+        <v>0.6221435814253926</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3204580513379031</v>
+        <v>0.303532459145473</v>
       </c>
       <c r="E94" t="n">
-        <v>0.3254754593923791</v>
+        <v>0.3126300896715725</v>
       </c>
       <c r="F94" t="n">
-        <v>0.4424429953919577</v>
+        <v>0.4534591943483687</v>
       </c>
       <c r="G94" t="n">
-        <v>0.5196826002345455</v>
+        <v>0.531138444402274</v>
       </c>
       <c r="H94" t="n">
         <v>1.236937243017472</v>
@@ -9008,22 +9008,22 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.2828035015291684</v>
+        <v>0.2843717171365708</v>
       </c>
       <c r="C95" t="n">
-        <v>0.07606529509327981</v>
+        <v>0.07651056468218326</v>
       </c>
       <c r="D95" t="n">
-        <v>0.1338377838739848</v>
+        <v>0.1386240743615314</v>
       </c>
       <c r="E95" t="n">
-        <v>0.06416876821348751</v>
+        <v>0.0638123239152574</v>
       </c>
       <c r="F95" t="n">
-        <v>0.213463666650303</v>
+        <v>0.2146133225581265</v>
       </c>
       <c r="G95" t="n">
-        <v>0.06617432181180979</v>
+        <v>0.06608706189881056</v>
       </c>
       <c r="H95" t="n">
         <v>0.5594639660662479</v>
@@ -9099,22 +9099,22 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5534655637248057</v>
+        <v>0.5591830735531318</v>
       </c>
       <c r="C96" t="n">
-        <v>0.7565180095737463</v>
+        <v>0.7640293208274819</v>
       </c>
       <c r="D96" t="n">
-        <v>0.2265858349366641</v>
+        <v>0.21454219956666</v>
       </c>
       <c r="E96" t="n">
-        <v>0.2525439284476074</v>
+        <v>0.2247824687911161</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1257594109047786</v>
+        <v>0.1250620711408253</v>
       </c>
       <c r="G96" t="n">
-        <v>0.2103823415856315</v>
+        <v>0.2148600079192438</v>
       </c>
       <c r="H96" t="n">
         <v>1.284271140273298</v>
@@ -9190,22 +9190,22 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.2091007902315323</v>
+        <v>0.2090658748283882</v>
       </c>
       <c r="C97" t="n">
-        <v>0.06781453531399254</v>
+        <v>0.06780222432650819</v>
       </c>
       <c r="D97" t="n">
-        <v>0.1675549513126359</v>
+        <v>0.1351553226387834</v>
       </c>
       <c r="E97" t="n">
-        <v>0.05962175229336203</v>
+        <v>0.05691390605230952</v>
       </c>
       <c r="F97" t="n">
-        <v>0.197197859838389</v>
+        <v>0.197194264756038</v>
       </c>
       <c r="G97" t="n">
-        <v>0.05536121393959428</v>
+        <v>0.0553460035577288</v>
       </c>
       <c r="H97" t="n">
         <v>0.2177031397462812</v>
@@ -9281,22 +9281,22 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.2291376269681573</v>
+        <v>0.230598323750427</v>
       </c>
       <c r="C98" t="n">
-        <v>0.2222416392560704</v>
+        <v>0.2236125043047838</v>
       </c>
       <c r="D98" t="n">
-        <v>0.3415549115533909</v>
+        <v>0.2306047675261614</v>
       </c>
       <c r="E98" t="n">
-        <v>0.3413520757290811</v>
+        <v>0.2236513630438572</v>
       </c>
       <c r="F98" t="n">
-        <v>0.287783132689733</v>
+        <v>0.2910891741402319</v>
       </c>
       <c r="G98" t="n">
-        <v>0.2858478904254332</v>
+        <v>0.2891659078039812</v>
       </c>
       <c r="H98" t="n">
         <v>0.7651940787133369</v>
@@ -9372,22 +9372,22 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.4401773234147583</v>
+        <v>0.4467583021343722</v>
       </c>
       <c r="C99" t="n">
-        <v>0.271578622879944</v>
+        <v>0.2772564808734791</v>
       </c>
       <c r="D99" t="n">
-        <v>0.1496455574274299</v>
+        <v>0.1478972113645169</v>
       </c>
       <c r="E99" t="n">
-        <v>0.08956234479786521</v>
+        <v>0.1102132991859153</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2902566324671955</v>
+        <v>0.2996335618166658</v>
       </c>
       <c r="G99" t="n">
-        <v>0.1493898849291092</v>
+        <v>0.1573207272664319</v>
       </c>
       <c r="H99" t="n">
         <v>0.9127531883440781</v>
@@ -9463,22 +9463,22 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6748616996298552</v>
+        <v>0.6829196404785</v>
       </c>
       <c r="C100" t="n">
-        <v>0.4129770484178095</v>
+        <v>0.4197310918247357</v>
       </c>
       <c r="D100" t="n">
-        <v>0.2546141105606861</v>
+        <v>0.2532451715449641</v>
       </c>
       <c r="E100" t="n">
-        <v>0.1699760029385513</v>
+        <v>0.1570934386527884</v>
       </c>
       <c r="F100" t="n">
-        <v>0.5815039456955743</v>
+        <v>0.5920940652324238</v>
       </c>
       <c r="G100" t="n">
-        <v>0.2750434216100591</v>
+        <v>0.2819078278299025</v>
       </c>
       <c r="H100" t="n">
         <v>1.04262150654369</v>
@@ -9554,22 +9554,22 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.3046743618382409</v>
+        <v>0.3061434163667398</v>
       </c>
       <c r="C101" t="n">
-        <v>0.08513201653531259</v>
+        <v>0.0849367447967064</v>
       </c>
       <c r="D101" t="n">
-        <v>0.164525698793518</v>
+        <v>0.1922713566412032</v>
       </c>
       <c r="E101" t="n">
-        <v>0.09765974188988123</v>
+        <v>0.09003259155030501</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2250478788959168</v>
+        <v>0.2243129053176406</v>
       </c>
       <c r="G101" t="n">
-        <v>0.06620431093594506</v>
+        <v>0.06581684477911824</v>
       </c>
       <c r="H101" t="n">
         <v>0.4678895287272094</v>
@@ -9645,22 +9645,22 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.03571159537714073</v>
+        <v>0.03570898262747438</v>
       </c>
       <c r="C102" t="n">
-        <v>0.02738334571564239</v>
+        <v>0.02739077908604821</v>
       </c>
       <c r="D102" t="n">
-        <v>0.03114593254650058</v>
+        <v>0.01981534658050626</v>
       </c>
       <c r="E102" t="n">
-        <v>0.02324978305606144</v>
+        <v>0.01400818481728265</v>
       </c>
       <c r="F102" t="n">
-        <v>0.03011555935054061</v>
+        <v>0.03011689873335743</v>
       </c>
       <c r="G102" t="n">
-        <v>0.02076619560079476</v>
+        <v>0.0207588871649772</v>
       </c>
       <c r="H102" t="n">
         <v>0.1147432029708231</v>
@@ -9736,22 +9736,22 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>10.69889587376468</v>
+        <v>10.92774024835317</v>
       </c>
       <c r="C103" t="n">
-        <v>10.4289482208561</v>
+        <v>10.65807978599021</v>
       </c>
       <c r="D103" t="n">
-        <v>0.8612623895783404</v>
+        <v>1.641143427548984</v>
       </c>
       <c r="E103" t="n">
-        <v>0.862156040424265</v>
+        <v>1.581580416673479</v>
       </c>
       <c r="F103" t="n">
-        <v>3.805878398622513</v>
+        <v>4.142982621511965</v>
       </c>
       <c r="G103" t="n">
-        <v>4.040195765815305</v>
+        <v>4.3570873215527</v>
       </c>
       <c r="H103" t="n">
         <v>13.40409564039896</v>
@@ -9827,22 +9827,22 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.1348431251134068</v>
+        <v>0.1346145233633526</v>
       </c>
       <c r="C104" t="n">
-        <v>0.109401956159647</v>
+        <v>0.1092314534953667</v>
       </c>
       <c r="D104" t="n">
-        <v>0.07768802304636578</v>
+        <v>0.07341275131329915</v>
       </c>
       <c r="E104" t="n">
-        <v>0.07164362933070173</v>
+        <v>0.07022701871687015</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0410377818672782</v>
+        <v>0.04102985459252931</v>
       </c>
       <c r="G104" t="n">
-        <v>0.03419208569125703</v>
+        <v>0.03418131909984273</v>
       </c>
       <c r="H104" t="n">
         <v>0.3786825381440391</v>
@@ -9918,22 +9918,22 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6717680297191808</v>
+        <v>0.6821826283417045</v>
       </c>
       <c r="C105" t="n">
-        <v>0.7934812203405127</v>
+        <v>0.8036315011375185</v>
       </c>
       <c r="D105" t="n">
-        <v>0.2988751670769865</v>
+        <v>0.288366049971629</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2587774017672684</v>
+        <v>0.2389954831576384</v>
       </c>
       <c r="F105" t="n">
-        <v>0.2601399695983996</v>
+        <v>0.2730719236958599</v>
       </c>
       <c r="G105" t="n">
-        <v>0.4758339188759488</v>
+        <v>0.4919724343377241</v>
       </c>
       <c r="H105" t="n">
         <v>1.33446238571039</v>
@@ -10009,22 +10009,22 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.02382463979492826</v>
+        <v>0.02382371000229128</v>
       </c>
       <c r="C106" t="n">
-        <v>0.02413098532985582</v>
+        <v>0.02412986494980979</v>
       </c>
       <c r="D106" t="n">
-        <v>0.005341762520854252</v>
+        <v>0.003891128287518297</v>
       </c>
       <c r="E106" t="n">
-        <v>0.005523756277225551</v>
+        <v>0.003903726054257696</v>
       </c>
       <c r="F106" t="n">
-        <v>0.002975165452168819</v>
+        <v>0.002972213905213556</v>
       </c>
       <c r="G106" t="n">
-        <v>0.003531454375782875</v>
+        <v>0.003537402368925798</v>
       </c>
       <c r="H106" t="n">
         <v>0.2493107544939339</v>
@@ -10100,22 +10100,22 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.01875967723422169</v>
+        <v>0.01875795019854319</v>
       </c>
       <c r="C107" t="n">
-        <v>0.01920161615674755</v>
+        <v>0.01920085534960884</v>
       </c>
       <c r="D107" t="n">
-        <v>0.003379721260626023</v>
+        <v>0.003410800873290537</v>
       </c>
       <c r="E107" t="n">
-        <v>0.003436214884641365</v>
+        <v>0.003462519821082707</v>
       </c>
       <c r="F107" t="n">
-        <v>0.002203826211690008</v>
+        <v>0.002211417323696687</v>
       </c>
       <c r="G107" t="n">
-        <v>0.002841657014743304</v>
+        <v>0.002859091788827896</v>
       </c>
       <c r="H107" t="n">
         <v>0.2431184488471118</v>
@@ -10191,22 +10191,22 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.01212697873506915</v>
+        <v>0.01211857737633174</v>
       </c>
       <c r="C108" t="n">
-        <v>0.01241283139508255</v>
+        <v>0.01240567385470582</v>
       </c>
       <c r="D108" t="n">
-        <v>0.01135831133740289</v>
+        <v>0.008345759369360122</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0102643555203941</v>
+        <v>0.008195547529182877</v>
       </c>
       <c r="F108" t="n">
-        <v>0.003880473487464705</v>
+        <v>0.003889368089883496</v>
       </c>
       <c r="G108" t="n">
-        <v>0.003711885584144819</v>
+        <v>0.003716062112603385</v>
       </c>
       <c r="H108" t="n">
         <v>0.2447316180012817</v>
@@ -10282,22 +10282,22 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.02163890695970775</v>
+        <v>0.02162785341314849</v>
       </c>
       <c r="C109" t="n">
-        <v>0.01975686404891122</v>
+        <v>0.01974487678779715</v>
       </c>
       <c r="D109" t="n">
-        <v>0.03927826281917397</v>
+        <v>0.02647420065543236</v>
       </c>
       <c r="E109" t="n">
-        <v>0.03669017648427918</v>
+        <v>0.0229287772940192</v>
       </c>
       <c r="F109" t="n">
-        <v>0.01094374994971883</v>
+        <v>0.01095171727741152</v>
       </c>
       <c r="G109" t="n">
-        <v>0.007937739532661633</v>
+        <v>0.007933331962871043</v>
       </c>
       <c r="H109" t="n">
         <v>0.2967165783205413</v>
@@ -10373,22 +10373,22 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.01792938868140888</v>
+        <v>0.01792427212202553</v>
       </c>
       <c r="C110" t="n">
-        <v>0.01587939391601306</v>
+        <v>0.0158706180630374</v>
       </c>
       <c r="D110" t="n">
-        <v>0.00927595500361034</v>
+        <v>0.008987180292485672</v>
       </c>
       <c r="E110" t="n">
-        <v>0.01027857238282098</v>
+        <v>0.009136679650261695</v>
       </c>
       <c r="F110" t="n">
-        <v>0.006678541593620236</v>
+        <v>0.00667144484744806</v>
       </c>
       <c r="G110" t="n">
-        <v>0.004861646679997928</v>
+        <v>0.004872607935825926</v>
       </c>
       <c r="H110" t="n">
         <v>0.2496204874837848</v>
@@ -10464,22 +10464,22 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.0798459708328353</v>
+        <v>0.07969118302103703</v>
       </c>
       <c r="C111" t="n">
-        <v>0.07902009800958557</v>
+        <v>0.07885551632454917</v>
       </c>
       <c r="D111" t="n">
-        <v>0.02448007539964291</v>
+        <v>0.01476412503290059</v>
       </c>
       <c r="E111" t="n">
-        <v>0.02352644652012797</v>
+        <v>0.01449679666553838</v>
       </c>
       <c r="F111" t="n">
-        <v>0.007836070644217848</v>
+        <v>0.007852362534987365</v>
       </c>
       <c r="G111" t="n">
-        <v>0.009896672535999799</v>
+        <v>0.009894084047604969</v>
       </c>
       <c r="H111" t="n">
         <v>0.4667631816385235</v>
@@ -10555,22 +10555,22 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.3373382533220241</v>
+        <v>0.3400643999581208</v>
       </c>
       <c r="C112" t="n">
-        <v>0.3345377417654366</v>
+        <v>0.3372322383771206</v>
       </c>
       <c r="D112" t="n">
-        <v>0.1736827549143224</v>
+        <v>0.1435398675811958</v>
       </c>
       <c r="E112" t="n">
-        <v>0.1775968732708106</v>
+        <v>0.147447388732114</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1204243772922454</v>
+        <v>0.1222955932484568</v>
       </c>
       <c r="G112" t="n">
-        <v>0.1357012195869874</v>
+        <v>0.1377730992651008</v>
       </c>
       <c r="H112" t="n">
         <v>0.9342361934783976</v>
@@ -10646,22 +10646,22 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5566116411470221</v>
+        <v>0.5591421456199412</v>
       </c>
       <c r="C113" t="n">
-        <v>0.5648829125448219</v>
+        <v>0.5674442055444691</v>
       </c>
       <c r="D113" t="n">
-        <v>0.260354790304912</v>
+        <v>0.2243371809869525</v>
       </c>
       <c r="E113" t="n">
-        <v>0.2649579502423348</v>
+        <v>0.2286475797645283</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1052835014267217</v>
+        <v>0.1054542205085662</v>
       </c>
       <c r="G113" t="n">
-        <v>0.1368941890638848</v>
+        <v>0.1376602269008681</v>
       </c>
       <c r="H113" t="n">
         <v>1.084354343907561</v>
@@ -10737,22 +10737,22 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.08167240911101456</v>
+        <v>0.08166888814237851</v>
       </c>
       <c r="C114" t="n">
-        <v>0.08268956075485551</v>
+        <v>0.08269349664589358</v>
       </c>
       <c r="D114" t="n">
-        <v>0.0933105711323715</v>
+        <v>0.08174200124607806</v>
       </c>
       <c r="E114" t="n">
-        <v>0.09602727762984009</v>
+        <v>0.0827735265571856</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0708927551284522</v>
+        <v>0.07088826156162083</v>
       </c>
       <c r="G114" t="n">
-        <v>0.06212050429763054</v>
+        <v>0.06212566559303891</v>
       </c>
       <c r="H114" t="n">
         <v>0.2052640089593039</v>
@@ -10828,22 +10828,22 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.1709534992466884</v>
+        <v>0.1736170819464353</v>
       </c>
       <c r="C115" t="n">
-        <v>0.2055181933494548</v>
+        <v>0.2081410617551657</v>
       </c>
       <c r="D115" t="n">
-        <v>0.1703518278220959</v>
+        <v>0.2108848407534259</v>
       </c>
       <c r="E115" t="n">
-        <v>0.1443800969850437</v>
+        <v>0.1884899539434938</v>
       </c>
       <c r="F115" t="n">
-        <v>0.09811176474910235</v>
+        <v>0.09944266173050463</v>
       </c>
       <c r="G115" t="n">
-        <v>0.1517315332584976</v>
+        <v>0.1557893837388853</v>
       </c>
       <c r="H115" t="n">
         <v>0.745973544696887</v>
@@ -10919,22 +10919,22 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.3592965762758218</v>
+        <v>0.3607080039561872</v>
       </c>
       <c r="C116" t="n">
-        <v>0.3473197136499691</v>
+        <v>0.3485392636705892</v>
       </c>
       <c r="D116" t="n">
-        <v>0.2201876545970398</v>
+        <v>0.2091398685758772</v>
       </c>
       <c r="E116" t="n">
-        <v>0.2283838195139015</v>
+        <v>0.2161324775894491</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2223110496193521</v>
+        <v>0.2243944175300679</v>
       </c>
       <c r="G116" t="n">
-        <v>0.2066363659188849</v>
+        <v>0.2084589400619517</v>
       </c>
       <c r="H116" t="n">
         <v>0.8791106428021422</v>
@@ -11010,22 +11010,22 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.02022346337663995</v>
+        <v>0.02022255179434573</v>
       </c>
       <c r="C117" t="n">
-        <v>0.01734228486367657</v>
+        <v>0.01734680018096111</v>
       </c>
       <c r="D117" t="n">
-        <v>0.0201640729382175</v>
+        <v>0.020610549561881</v>
       </c>
       <c r="E117" t="n">
-        <v>0.02034253497722198</v>
+        <v>0.01874731439354337</v>
       </c>
       <c r="F117" t="n">
-        <v>0.01813042609433066</v>
+        <v>0.01813054979322128</v>
       </c>
       <c r="G117" t="n">
-        <v>0.01836299021303554</v>
+        <v>0.01834240042474868</v>
       </c>
       <c r="H117" t="n">
         <v>0.2183882729589028</v>
@@ -11101,22 +11101,22 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.01292666328783285</v>
+        <v>0.01293262924810876</v>
       </c>
       <c r="C118" t="n">
-        <v>0.009901496664625533</v>
+        <v>0.009898062763932116</v>
       </c>
       <c r="D118" t="n">
-        <v>0.01123397651386768</v>
+        <v>0.01098410169691732</v>
       </c>
       <c r="E118" t="n">
-        <v>0.009702642011028566</v>
+        <v>0.009061516450549619</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0109990354427247</v>
+        <v>0.01101351535264305</v>
       </c>
       <c r="G118" t="n">
-        <v>0.00924045858057004</v>
+        <v>0.009239445137645453</v>
       </c>
       <c r="H118" t="n">
         <v>0.1647401054134016</v>
@@ -11192,22 +11192,22 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.02326335271665214</v>
+        <v>0.02326392553017943</v>
       </c>
       <c r="C119" t="n">
-        <v>0.02249698463288722</v>
+        <v>0.02250538219734631</v>
       </c>
       <c r="D119" t="n">
-        <v>0.01852525646779624</v>
+        <v>0.01843051430379153</v>
       </c>
       <c r="E119" t="n">
-        <v>0.01961364887515957</v>
+        <v>0.01964576803818497</v>
       </c>
       <c r="F119" t="n">
-        <v>0.01775787213345357</v>
+        <v>0.01776444370705442</v>
       </c>
       <c r="G119" t="n">
-        <v>0.01183357192982816</v>
+        <v>0.01182909467612855</v>
       </c>
       <c r="H119" t="n">
         <v>0.1959608041850188</v>
@@ -11283,22 +11283,22 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.1218277647087102</v>
+        <v>0.1218293490008251</v>
       </c>
       <c r="C120" t="n">
-        <v>0.09220306185706414</v>
+        <v>0.09220865952051852</v>
       </c>
       <c r="D120" t="n">
-        <v>0.1259889500403108</v>
+        <v>0.144616355368143</v>
       </c>
       <c r="E120" t="n">
-        <v>0.09532578516878062</v>
+        <v>0.09221646573179659</v>
       </c>
       <c r="F120" t="n">
-        <v>0.1383532588822703</v>
+        <v>0.1383487949788311</v>
       </c>
       <c r="G120" t="n">
-        <v>0.1081825524437051</v>
+        <v>0.1081838485764769</v>
       </c>
       <c r="H120" t="n">
         <v>0.2169573885097784</v>
@@ -11374,22 +11374,22 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.03284660629937099</v>
+        <v>0.03284540274001947</v>
       </c>
       <c r="C121" t="n">
-        <v>0.02797208261916394</v>
+        <v>0.02796987764592603</v>
       </c>
       <c r="D121" t="n">
-        <v>0.0230690139616877</v>
+        <v>0.020483832974817</v>
       </c>
       <c r="E121" t="n">
-        <v>0.02050120747837773</v>
+        <v>0.01809470170044845</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0253432122504804</v>
+        <v>0.02534401390324391</v>
       </c>
       <c r="G121" t="n">
-        <v>0.01761909963980175</v>
+        <v>0.01762433403534535</v>
       </c>
       <c r="H121" t="n">
         <v>0.1861185602553873</v>
@@ -11465,22 +11465,22 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.079247813276054</v>
+        <v>0.07923430657206081</v>
       </c>
       <c r="C122" t="n">
-        <v>0.09503776538995465</v>
+        <v>0.0950327243814096</v>
       </c>
       <c r="D122" t="n">
-        <v>0.06144067108815231</v>
+        <v>0.0507612211309937</v>
       </c>
       <c r="E122" t="n">
-        <v>0.0694430190245519</v>
+        <v>0.04967587733612646</v>
       </c>
       <c r="F122" t="n">
-        <v>0.04607241722638127</v>
+        <v>0.04606926734787022</v>
       </c>
       <c r="G122" t="n">
-        <v>0.05072528289683194</v>
+        <v>0.05071726163831866</v>
       </c>
       <c r="H122" t="n">
         <v>0.278485987840173</v>
@@ -11556,22 +11556,22 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.2242031385646418</v>
+        <v>0.2241120651840995</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1892622581287646</v>
+        <v>0.1890845800804842</v>
       </c>
       <c r="D123" t="n">
-        <v>0.2189176816685326</v>
+        <v>0.2171356640255903</v>
       </c>
       <c r="E123" t="n">
-        <v>0.1453352912379623</v>
+        <v>0.1381698460164195</v>
       </c>
       <c r="F123" t="n">
-        <v>0.2092372762548289</v>
+        <v>0.2092256314623753</v>
       </c>
       <c r="G123" t="n">
-        <v>0.1591663905397518</v>
+        <v>0.1590027548666282</v>
       </c>
       <c r="H123" t="n">
         <v>0.4358591106778351</v>
@@ -11647,22 +11647,22 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.06366743831783087</v>
+        <v>0.06366449065049024</v>
       </c>
       <c r="C124" t="n">
-        <v>0.06158531976136584</v>
+        <v>0.06158459413170859</v>
       </c>
       <c r="D124" t="n">
-        <v>0.06288757342647137</v>
+        <v>0.06359608007490654</v>
       </c>
       <c r="E124" t="n">
-        <v>0.06032259353255617</v>
+        <v>0.06696826455044233</v>
       </c>
       <c r="F124" t="n">
-        <v>0.06139429558757668</v>
+        <v>0.06139424014191206</v>
       </c>
       <c r="G124" t="n">
-        <v>0.06936075000069521</v>
+        <v>0.06935644710580072</v>
       </c>
       <c r="H124" t="n">
         <v>0.2375175161157313</v>
@@ -11738,22 +11738,22 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.2229054035323166</v>
+        <v>0.2223906463592042</v>
       </c>
       <c r="C125" t="n">
-        <v>0.1689130537646064</v>
+        <v>0.1684052107591407</v>
       </c>
       <c r="D125" t="n">
-        <v>0.108013415162909</v>
+        <v>0.09655907990974942</v>
       </c>
       <c r="E125" t="n">
-        <v>0.08369272172775463</v>
+        <v>0.07652871069541536</v>
       </c>
       <c r="F125" t="n">
-        <v>0.1153384183987471</v>
+        <v>0.1151119158059892</v>
       </c>
       <c r="G125" t="n">
-        <v>0.08605249373113408</v>
+        <v>0.08579250997818041</v>
       </c>
       <c r="H125" t="n">
         <v>0.5139083244130161</v>
@@ -11829,22 +11829,22 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.7536485250838907</v>
+        <v>0.7633572061806128</v>
       </c>
       <c r="C126" t="n">
-        <v>0.3911359908950566</v>
+        <v>0.3974864585217165</v>
       </c>
       <c r="D126" t="n">
-        <v>0.3614652479922385</v>
+        <v>0.374815161830878</v>
       </c>
       <c r="E126" t="n">
-        <v>0.2935920480548678</v>
+        <v>0.3256464167387856</v>
       </c>
       <c r="F126" t="n">
-        <v>0.7252702604819246</v>
+        <v>0.7402101130109464</v>
       </c>
       <c r="G126" t="n">
-        <v>0.3732418066006369</v>
+        <v>0.3837469658950153</v>
       </c>
       <c r="H126" t="n">
         <v>1.052655847663158</v>
@@ -11920,22 +11920,22 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.05720083464565817</v>
+        <v>0.05719778995349321</v>
       </c>
       <c r="C127" t="n">
-        <v>0.05505676372381253</v>
+        <v>0.05504196992996413</v>
       </c>
       <c r="D127" t="n">
-        <v>0.05759052555259431</v>
+        <v>0.05669198293535255</v>
       </c>
       <c r="E127" t="n">
-        <v>0.05282792940461542</v>
+        <v>0.05205516902535588</v>
       </c>
       <c r="F127" t="n">
-        <v>0.05267697556728944</v>
+        <v>0.05266381205386683</v>
       </c>
       <c r="G127" t="n">
-        <v>0.05209806189118199</v>
+        <v>0.05209501878246995</v>
       </c>
       <c r="H127" t="n">
         <v>0.2993369040417522</v>
@@ -12011,22 +12011,22 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5518502698667895</v>
+        <v>0.5542821547541514</v>
       </c>
       <c r="C128" t="n">
-        <v>0.4738451050159266</v>
+        <v>0.4761265700246667</v>
       </c>
       <c r="D128" t="n">
-        <v>0.3119477132132782</v>
+        <v>0.2677585566763096</v>
       </c>
       <c r="E128" t="n">
-        <v>0.2760033833729188</v>
+        <v>0.2364746105131447</v>
       </c>
       <c r="F128" t="n">
-        <v>0.3777003102828383</v>
+        <v>0.3806539474411484</v>
       </c>
       <c r="G128" t="n">
-        <v>0.3487367147498278</v>
+        <v>0.3514022361863682</v>
       </c>
       <c r="H128" t="n">
         <v>1.006886985595747</v>
@@ -12102,22 +12102,22 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.03650138753689912</v>
+        <v>0.03650091120697645</v>
       </c>
       <c r="C129" t="n">
-        <v>0.02895896867068899</v>
+        <v>0.02896218865509</v>
       </c>
       <c r="D129" t="n">
-        <v>0.02726631903187018</v>
+        <v>0.01622234106303301</v>
       </c>
       <c r="E129" t="n">
-        <v>0.02435729770917328</v>
+        <v>0.01404682664169479</v>
       </c>
       <c r="F129" t="n">
-        <v>0.02647656460952299</v>
+        <v>0.02648148692615052</v>
       </c>
       <c r="G129" t="n">
-        <v>0.01707302454281298</v>
+        <v>0.01707383496364671</v>
       </c>
       <c r="H129" t="n">
         <v>0.129182604735649</v>
@@ -12193,22 +12193,22 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.2520606605151842</v>
+        <v>0.2548188455773535</v>
       </c>
       <c r="C130" t="n">
-        <v>0.2878259725298332</v>
+        <v>0.2902292829210268</v>
       </c>
       <c r="D130" t="n">
-        <v>0.2702411417951749</v>
+        <v>0.3512355044054678</v>
       </c>
       <c r="E130" t="n">
-        <v>0.2503966475292719</v>
+        <v>0.2825370106397438</v>
       </c>
       <c r="F130" t="n">
-        <v>0.1862210181892948</v>
+        <v>0.1898645941149175</v>
       </c>
       <c r="G130" t="n">
-        <v>0.267429525915011</v>
+        <v>0.2718895495394331</v>
       </c>
       <c r="H130" t="n">
         <v>0.7778554304874405</v>
@@ -12284,22 +12284,22 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.1401599429628987</v>
+        <v>0.1398974881555076</v>
       </c>
       <c r="C131" t="n">
-        <v>0.07903141796976935</v>
+        <v>0.0789832111609249</v>
       </c>
       <c r="D131" t="n">
-        <v>0.1029292851229353</v>
+        <v>0.1171150530365744</v>
       </c>
       <c r="E131" t="n">
-        <v>0.07799801279556952</v>
+        <v>0.07671664578867474</v>
       </c>
       <c r="F131" t="n">
-        <v>0.1658373486211999</v>
+        <v>0.16559703985541</v>
       </c>
       <c r="G131" t="n">
-        <v>0.09123815542333844</v>
+        <v>0.09106985113663832</v>
       </c>
       <c r="H131" t="n">
         <v>0.3482352089914686</v>
@@ -12375,22 +12375,22 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.1901309942242352</v>
+        <v>0.1916403163303129</v>
       </c>
       <c r="C132" t="n">
-        <v>0.1179327147097811</v>
+        <v>0.1188137424074162</v>
       </c>
       <c r="D132" t="n">
-        <v>0.1261335432285553</v>
+        <v>0.1305723396332828</v>
       </c>
       <c r="E132" t="n">
-        <v>0.09646442324398886</v>
+        <v>0.09241961747205141</v>
       </c>
       <c r="F132" t="n">
-        <v>0.1810469186730326</v>
+        <v>0.1822986947282859</v>
       </c>
       <c r="G132" t="n">
-        <v>0.09688591218864875</v>
+        <v>0.09743874967140002</v>
       </c>
       <c r="H132" t="n">
         <v>0.5850765240017057</v>
@@ -12466,22 +12466,22 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.8096311844804638</v>
+        <v>0.8212051835409249</v>
       </c>
       <c r="C133" t="n">
-        <v>0.5599247017988076</v>
+        <v>0.570814659812197</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3062605495577138</v>
+        <v>0.3061815579964894</v>
       </c>
       <c r="E133" t="n">
-        <v>0.1960142166788554</v>
+        <v>0.1665759667256722</v>
       </c>
       <c r="F133" t="n">
-        <v>0.5909909919988352</v>
+        <v>0.6102304443310116</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3500273433542156</v>
+        <v>0.3681425354393535</v>
       </c>
       <c r="H133" t="n">
         <v>1.40754481138985</v>
@@ -12557,22 +12557,22 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.7604887802697218</v>
+        <v>0.7689287446491848</v>
       </c>
       <c r="C134" t="n">
-        <v>0.682296711940575</v>
+        <v>0.690232064500526</v>
       </c>
       <c r="D134" t="n">
-        <v>0.2555995297515219</v>
+        <v>0.2285178705926094</v>
       </c>
       <c r="E134" t="n">
-        <v>0.258027972042663</v>
+        <v>0.2225362651727793</v>
       </c>
       <c r="F134" t="n">
-        <v>0.3712845594264924</v>
+        <v>0.3790931230261947</v>
       </c>
       <c r="G134" t="n">
-        <v>0.3572418900243073</v>
+        <v>0.3645091629601232</v>
       </c>
       <c r="H134" t="n">
         <v>1.310460382339101</v>
@@ -12648,22 +12648,22 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.2342530491783264</v>
+        <v>0.2354275534748884</v>
       </c>
       <c r="C135" t="n">
-        <v>0.2386906990864824</v>
+        <v>0.2399057276373681</v>
       </c>
       <c r="D135" t="n">
-        <v>0.1621338006201034</v>
+        <v>0.1913815735907635</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1646845512929427</v>
+        <v>0.1894000350173234</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1538076112642033</v>
+        <v>0.15546894649545</v>
       </c>
       <c r="G135" t="n">
-        <v>0.1764816052314601</v>
+        <v>0.1785851811475817</v>
       </c>
       <c r="H135" t="n">
         <v>0.7232811916098527</v>
@@ -12739,22 +12739,22 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.6855082990349322</v>
+        <v>0.6920785936621305</v>
       </c>
       <c r="C136" t="n">
-        <v>0.6314408460853549</v>
+        <v>0.6380441251544235</v>
       </c>
       <c r="D136" t="n">
-        <v>0.3008960129976778</v>
+        <v>0.2605160855994468</v>
       </c>
       <c r="E136" t="n">
-        <v>0.281489483470119</v>
+        <v>0.2435661535021833</v>
       </c>
       <c r="F136" t="n">
-        <v>0.4011114624041335</v>
+        <v>0.4107964026693026</v>
       </c>
       <c r="G136" t="n">
-        <v>0.3307443410160896</v>
+        <v>0.3398433661253663</v>
       </c>
       <c r="H136" t="n">
         <v>1.245537054766756</v>
@@ -12830,22 +12830,22 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.181223970288993</v>
+        <v>0.1819793153000726</v>
       </c>
       <c r="C137" t="n">
-        <v>0.1923865956402004</v>
+        <v>0.1933850581528877</v>
       </c>
       <c r="D137" t="n">
-        <v>0.1639188771572878</v>
+        <v>0.1743715090208504</v>
       </c>
       <c r="E137" t="n">
-        <v>0.1689404080840741</v>
+        <v>0.1788194337159455</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1426908527284386</v>
+        <v>0.1432765627841191</v>
       </c>
       <c r="G137" t="n">
-        <v>0.1725175752489483</v>
+        <v>0.1736939563947988</v>
       </c>
       <c r="H137" t="n">
         <v>0.6575556533639743</v>
@@ -12921,22 +12921,22 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1.003281577616096</v>
+        <v>1.011407331524651</v>
       </c>
       <c r="C138" t="n">
-        <v>0.3723331703322708</v>
+        <v>0.3791329657605487</v>
       </c>
       <c r="D138" t="n">
-        <v>0.517191372257082</v>
+        <v>0.4931784823591041</v>
       </c>
       <c r="E138" t="n">
-        <v>0.1642724773996304</v>
+        <v>0.1196984841591649</v>
       </c>
       <c r="F138" t="n">
-        <v>1.080534372369095</v>
+        <v>1.09318410663465</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2757305261794443</v>
+        <v>0.2845015045140236</v>
       </c>
       <c r="H138" t="n">
         <v>1.272182588215972</v>
@@ -13012,22 +13012,22 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.1937100314171159</v>
+        <v>0.193724871727142</v>
       </c>
       <c r="C139" t="n">
-        <v>0.1089474631990488</v>
+        <v>0.1089048181743815</v>
       </c>
       <c r="D139" t="n">
-        <v>0.1749476991837263</v>
+        <v>0.172903304215616</v>
       </c>
       <c r="E139" t="n">
-        <v>0.09126534193129693</v>
+        <v>0.1170661748165055</v>
       </c>
       <c r="F139" t="n">
-        <v>0.1783447394369647</v>
+        <v>0.178361579159854</v>
       </c>
       <c r="G139" t="n">
-        <v>0.1031113603410376</v>
+        <v>0.1029478662497653</v>
       </c>
       <c r="H139" t="n">
         <v>0.4595522319585266</v>
@@ -13103,22 +13103,22 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1.536075345290276</v>
+        <v>1.563554567728067</v>
       </c>
       <c r="C140" t="n">
-        <v>1.577048236340946</v>
+        <v>1.603845610262348</v>
       </c>
       <c r="D140" t="n">
-        <v>0.5591648365892415</v>
+        <v>0.6147355877298267</v>
       </c>
       <c r="E140" t="n">
-        <v>0.5580472274486519</v>
+        <v>0.6271805761179865</v>
       </c>
       <c r="F140" t="n">
-        <v>0.6789699919076965</v>
+        <v>0.7089618898198431</v>
       </c>
       <c r="G140" t="n">
-        <v>0.8376457739592177</v>
+        <v>0.880838987011583</v>
       </c>
       <c r="H140" t="n">
         <v>2.199285093667711</v>
@@ -13194,22 +13194,22 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.3609088288901675</v>
+        <v>0.3662744880133005</v>
       </c>
       <c r="C141" t="n">
-        <v>0.4949522543809782</v>
+        <v>0.500775383654272</v>
       </c>
       <c r="D141" t="n">
-        <v>0.1600897556879427</v>
+        <v>0.1491487849298938</v>
       </c>
       <c r="E141" t="n">
-        <v>0.1512823936198824</v>
+        <v>0.1159372083374286</v>
       </c>
       <c r="F141" t="n">
-        <v>0.08743537063031045</v>
+        <v>0.08904486202623338</v>
       </c>
       <c r="G141" t="n">
-        <v>0.1924999565029793</v>
+        <v>0.1982515041563579</v>
       </c>
       <c r="H141" t="n">
         <v>1.034221944058446</v>
@@ -13285,22 +13285,22 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.9540602242475633</v>
+        <v>0.9622878130602048</v>
       </c>
       <c r="C142" t="n">
-        <v>1.203363207395421</v>
+        <v>1.212627717261468</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4925726060114002</v>
+        <v>0.4386191876296217</v>
       </c>
       <c r="E142" t="n">
-        <v>0.5193181109343249</v>
+        <v>0.4751017764463643</v>
       </c>
       <c r="F142" t="n">
-        <v>0.3885473707150491</v>
+        <v>0.3924179100027597</v>
       </c>
       <c r="G142" t="n">
-        <v>0.6038471506710392</v>
+        <v>0.6164791222918644</v>
       </c>
       <c r="H142" t="n">
         <v>1.568007141874413</v>
@@ -13376,22 +13376,22 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.1699028973496732</v>
+        <v>0.1697730569607195</v>
       </c>
       <c r="C143" t="n">
-        <v>0.1707287317721416</v>
+        <v>0.1706645246156291</v>
       </c>
       <c r="D143" t="n">
-        <v>0.1796523310277371</v>
+        <v>0.2641900630602997</v>
       </c>
       <c r="E143" t="n">
-        <v>0.1774102831707513</v>
+        <v>0.2612831845767706</v>
       </c>
       <c r="F143" t="n">
-        <v>0.1843189944414889</v>
+        <v>0.1839146758732833</v>
       </c>
       <c r="G143" t="n">
-        <v>0.1838825631457044</v>
+        <v>0.183626301457463</v>
       </c>
       <c r="H143" t="n">
         <v>0.3989257195156556</v>
@@ -13463,22 +13463,22 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4167556828177301</v>
+        <v>0.4222540350733293</v>
       </c>
       <c r="C144" t="n">
-        <v>0.3991778634792384</v>
+        <v>0.404470814232269</v>
       </c>
       <c r="D144" t="n">
-        <v>0.1655494894599853</v>
+        <v>0.1415481519353839</v>
       </c>
       <c r="E144" t="n">
-        <v>0.145289237504063</v>
+        <v>0.1337120246751101</v>
       </c>
       <c r="F144" t="n">
-        <v>0.1147507869477581</v>
+        <v>0.1179136146004363</v>
       </c>
       <c r="G144" t="n">
-        <v>0.09717864976172039</v>
+        <v>0.1002936061616974</v>
       </c>
       <c r="H144" t="n">
         <v>0.9837663146858279</v>
@@ -13554,22 +13554,22 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.2589661434579068</v>
+        <v>0.2619724860018365</v>
       </c>
       <c r="C145" t="n">
-        <v>0.2489109445684327</v>
+        <v>0.2513362772565932</v>
       </c>
       <c r="D145" t="n">
-        <v>0.1248973546828197</v>
+        <v>0.1397505398218033</v>
       </c>
       <c r="E145" t="n">
-        <v>0.1183436645482296</v>
+        <v>0.1265298485155069</v>
       </c>
       <c r="F145" t="n">
-        <v>0.146386776332044</v>
+        <v>0.1458466886528677</v>
       </c>
       <c r="G145" t="n">
-        <v>0.146547450757388</v>
+        <v>0.1486961838764625</v>
       </c>
       <c r="H145" t="n">
         <v>0.7490184834473188</v>
@@ -13645,22 +13645,22 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.3210615132391003</v>
+        <v>0.3234921770774981</v>
       </c>
       <c r="C146" t="n">
-        <v>0.2271188735504947</v>
+        <v>0.2288424982993892</v>
       </c>
       <c r="D146" t="n">
-        <v>0.1958666420590489</v>
+        <v>0.1919519246754832</v>
       </c>
       <c r="E146" t="n">
-        <v>0.1235960445701396</v>
+        <v>0.1219578055977806</v>
       </c>
       <c r="F146" t="n">
-        <v>0.2773575004491964</v>
+        <v>0.2798243212363288</v>
       </c>
       <c r="G146" t="n">
-        <v>0.1390924191324815</v>
+        <v>0.1407370451635932</v>
       </c>
       <c r="H146" t="n">
         <v>0.7619135220461626</v>
@@ -13736,22 +13736,22 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.1925724160942985</v>
+        <v>0.1949025965643612</v>
       </c>
       <c r="C147" t="n">
-        <v>0.2084130644373393</v>
+        <v>0.2106230896176913</v>
       </c>
       <c r="D147" t="n">
-        <v>0.1360157265655975</v>
+        <v>0.1476382452068859</v>
       </c>
       <c r="E147" t="n">
-        <v>0.1297376981102736</v>
+        <v>0.1337151129423892</v>
       </c>
       <c r="F147" t="n">
-        <v>0.09938709630902717</v>
+        <v>0.1003173336968477</v>
       </c>
       <c r="G147" t="n">
-        <v>0.1241655964329</v>
+        <v>0.1259289161421396</v>
       </c>
       <c r="H147" t="n">
         <v>0.7272922710971119</v>
@@ -13827,22 +13827,22 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.3047938453788169</v>
+        <v>0.3052551400158964</v>
       </c>
       <c r="C148" t="n">
-        <v>0.1317719994097047</v>
+        <v>0.1316283835020373</v>
       </c>
       <c r="D148" t="n">
-        <v>0.2606374205125487</v>
+        <v>0.2660163353615496</v>
       </c>
       <c r="E148" t="n">
-        <v>0.1415762195635621</v>
+        <v>0.1367483991725467</v>
       </c>
       <c r="F148" t="n">
-        <v>0.3313243754726952</v>
+        <v>0.3317438836834629</v>
       </c>
       <c r="G148" t="n">
-        <v>0.1421229096874667</v>
+        <v>0.1418431015847322</v>
       </c>
       <c r="H148" t="n">
         <v>0.4845021405176518</v>
@@ -13918,22 +13918,22 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.1904852473813701</v>
+        <v>0.190144806363119</v>
       </c>
       <c r="C149" t="n">
-        <v>0.1771408666913522</v>
+        <v>0.1770251182679213</v>
       </c>
       <c r="D149" t="n">
-        <v>0.2029865342933182</v>
+        <v>0.2658747529708257</v>
       </c>
       <c r="E149" t="n">
-        <v>0.1747194291496176</v>
+        <v>0.241331831114811</v>
       </c>
       <c r="F149" t="n">
-        <v>0.2026924687718545</v>
+        <v>0.202138357650541</v>
       </c>
       <c r="G149" t="n">
-        <v>0.1933082075482281</v>
+        <v>0.1930415124759428</v>
       </c>
       <c r="H149" t="n">
         <v>0.4204852656376782</v>
@@ -14009,22 +14009,22 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.1589500990634563</v>
+        <v>0.1588434262714089</v>
       </c>
       <c r="C150" t="n">
-        <v>0.07831283412734105</v>
+        <v>0.07826764487422852</v>
       </c>
       <c r="D150" t="n">
-        <v>0.1470799472289142</v>
+        <v>0.152766089848965</v>
       </c>
       <c r="E150" t="n">
-        <v>0.105737206287585</v>
+        <v>0.07834503336702708</v>
       </c>
       <c r="F150" t="n">
-        <v>0.1916784287702019</v>
+        <v>0.1914959531195725</v>
       </c>
       <c r="G150" t="n">
-        <v>0.08388609570027999</v>
+        <v>0.08366029058421448</v>
       </c>
       <c r="H150" t="n">
         <v>0.3367819149821296</v>

--- a/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
+++ b/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
@@ -577,7 +577,7 @@
         <v>0.1720860246432098</v>
       </c>
       <c r="F2" t="n">
-        <v>0.131979538815709</v>
+        <v>0.1273740515060551</v>
       </c>
       <c r="G2" t="n">
         <v>0.1621908873837076</v>
@@ -759,10 +759,10 @@
         <v>0.313998201622595</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4057833744270291</v>
+        <v>0.1419277002486848</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3732647546446137</v>
+        <v>0.05491573579732845</v>
       </c>
       <c r="H4" t="n">
         <v>1.753597408313792</v>
@@ -850,10 +850,10 @@
         <v>0.8938254607364218</v>
       </c>
       <c r="F5" t="n">
-        <v>2.057173173298867</v>
+        <v>1.07713806557835</v>
       </c>
       <c r="G5" t="n">
-        <v>2.035286833462917</v>
+        <v>0.784576932530652</v>
       </c>
       <c r="H5" t="n">
         <v>7.107461973628843</v>
@@ -941,10 +941,10 @@
         <v>0.09137818446875293</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1418956335184769</v>
+        <v>0.1153528592591858</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1694736885376539</v>
+        <v>0.1111403414535778</v>
       </c>
       <c r="H6" t="n">
         <v>0.9001384470221278</v>
@@ -1032,7 +1032,7 @@
         <v>0.1636387163519396</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1474792558737474</v>
+        <v>0.09213262856284368</v>
       </c>
       <c r="G7" t="n">
         <v>0.1810847605610292</v>
@@ -1392,10 +1392,10 @@
         <v>0.03136588166417283</v>
       </c>
       <c r="F11" t="n">
-        <v>0.008580474295952229</v>
+        <v>0.006335478397541333</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006109318962971988</v>
+        <v>0.003159282383521565</v>
       </c>
       <c r="H11" t="n">
         <v>0.2600988575656265</v>
@@ -1483,7 +1483,7 @@
         <v>0.3050554147939886</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4172176474705269</v>
+        <v>0.1756797636372625</v>
       </c>
       <c r="G12" t="n">
         <v>0.542783575332459</v>
@@ -1574,10 +1574,10 @@
         <v>0.1078043511487605</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1256921628289678</v>
+        <v>0.08944856136092495</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1766249318219888</v>
+        <v>0.09695015703106676</v>
       </c>
       <c r="H13" t="n">
         <v>0.8934721382063724</v>
@@ -1756,10 +1756,10 @@
         <v>0.1192092154191906</v>
       </c>
       <c r="F15" t="n">
-        <v>0.244222625209899</v>
+        <v>0.1194818276079066</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1339762895652925</v>
+        <v>0.03488176031903047</v>
       </c>
       <c r="H15" t="n">
         <v>0.9740152227653087</v>
@@ -1934,10 +1934,10 @@
         <v>0.2160907278267805</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2914639257766018</v>
+        <v>0.1305474070891448</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2638465548788085</v>
+        <v>0.05211856444568599</v>
       </c>
       <c r="H17" t="n">
         <v>1.267429584043156</v>
@@ -2203,7 +2203,7 @@
         <v>0.1679186370778793</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5131285652563626</v>
+        <v>0.3177717005346725</v>
       </c>
       <c r="G20" t="n">
         <v>0.3094729701462228</v>
@@ -2294,7 +2294,7 @@
         <v>0.1959113675490289</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5397447604860646</v>
+        <v>0.3072942669735372</v>
       </c>
       <c r="G21" t="n">
         <v>0.2853456092299797</v>
@@ -2476,10 +2476,10 @@
         <v>0.05475782605272433</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09603481377764664</v>
+        <v>0.106701504780846</v>
       </c>
       <c r="G23" t="n">
-        <v>0.09628151140645312</v>
+        <v>0.06280291162765497</v>
       </c>
       <c r="H23" t="n">
         <v>0.6014370052190726</v>
@@ -2658,10 +2658,10 @@
         <v>0.08587497005443874</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2215196251820541</v>
+        <v>0.189696964757167</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1217121658615752</v>
+        <v>0.07977923407374726</v>
       </c>
       <c r="H25" t="n">
         <v>0.8337220581801408</v>
@@ -2749,10 +2749,10 @@
         <v>0.2162202262127234</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3049341588356663</v>
+        <v>0.1058820209050863</v>
       </c>
       <c r="G26" t="n">
-        <v>0.2381621173820295</v>
+        <v>0.03056958614848407</v>
       </c>
       <c r="H26" t="n">
         <v>1.470782642072603</v>
@@ -2840,10 +2840,10 @@
         <v>0.04623868421689228</v>
       </c>
       <c r="F27" t="n">
-        <v>0.04329301900702714</v>
+        <v>0.04331180505959858</v>
       </c>
       <c r="G27" t="n">
-        <v>0.03785270690103291</v>
+        <v>0.03175851063359768</v>
       </c>
       <c r="H27" t="n">
         <v>0.3074293300784401</v>
@@ -3113,10 +3113,10 @@
         <v>0.03221851295698297</v>
       </c>
       <c r="F30" t="n">
-        <v>0.04851349675833913</v>
+        <v>0.03938381638888737</v>
       </c>
       <c r="G30" t="n">
-        <v>0.03127203433905391</v>
+        <v>0.02059666431109758</v>
       </c>
       <c r="H30" t="n">
         <v>0.3364356123183577</v>
@@ -3295,7 +3295,7 @@
         <v>0.03852836558066905</v>
       </c>
       <c r="F32" t="n">
-        <v>0.08158890131868768</v>
+        <v>0.07390302168492037</v>
       </c>
       <c r="G32" t="n">
         <v>0.04487584215704166</v>
@@ -3386,7 +3386,7 @@
         <v>0.1940490257510064</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4218473544903005</v>
+        <v>0.2591531886278792</v>
       </c>
       <c r="G33" t="n">
         <v>0.3940136292074076</v>
@@ -3477,10 +3477,10 @@
         <v>0.04348458337406332</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01561224212945124</v>
+        <v>0.01346906948871128</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01767254215939238</v>
+        <v>0.01403619999745217</v>
       </c>
       <c r="H34" t="n">
         <v>0.463096312708327</v>
@@ -3568,10 +3568,10 @@
         <v>0.0259860054391326</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0259253034777502</v>
+        <v>0.02253845990618396</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0250120887060904</v>
+        <v>0.02048879191160358</v>
       </c>
       <c r="H35" t="n">
         <v>0.3093751617228926</v>
@@ -3659,10 +3659,10 @@
         <v>0.04638968454756125</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01889917391006096</v>
+        <v>0.0163535838971354</v>
       </c>
       <c r="G36" t="n">
-        <v>0.01980702482975925</v>
+        <v>0.01218324244693524</v>
       </c>
       <c r="H36" t="n">
         <v>0.4447191641064449</v>
@@ -3841,10 +3841,10 @@
         <v>0.03567638319215124</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01143173644988334</v>
+        <v>0.007666460820901324</v>
       </c>
       <c r="G38" t="n">
-        <v>0.01369476158309697</v>
+        <v>0.006868611149209673</v>
       </c>
       <c r="H38" t="n">
         <v>0.3771355762613469</v>
@@ -3932,7 +3932,7 @@
         <v>0.1183132221393223</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1827674719427196</v>
+        <v>0.1580591804767361</v>
       </c>
       <c r="G39" t="n">
         <v>0.1869240753790934</v>
@@ -4023,10 +4023,10 @@
         <v>0.4591292957244525</v>
       </c>
       <c r="F40" t="n">
-        <v>1.332875044856526</v>
+        <v>0.8475628415509217</v>
       </c>
       <c r="G40" t="n">
-        <v>0.861559449388288</v>
+        <v>0.5455642074598317</v>
       </c>
       <c r="H40" t="n">
         <v>2.891582446522646</v>
@@ -4114,10 +4114,10 @@
         <v>0.09778313137220958</v>
       </c>
       <c r="F41" t="n">
-        <v>0.103268511605077</v>
+        <v>0.1139819799079507</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0988943115843503</v>
+        <v>0.07645372197028777</v>
       </c>
       <c r="H41" t="n">
         <v>0.6797073731912212</v>
@@ -4383,10 +4383,10 @@
         <v>0.1801894130515869</v>
       </c>
       <c r="F44" t="n">
-        <v>1.371088009161491</v>
+        <v>0.4303237965188933</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4448171954293003</v>
+        <v>0.07623190326256561</v>
       </c>
       <c r="H44" t="n">
         <v>2.229510190828526</v>
@@ -4474,10 +4474,10 @@
         <v>0.03192361493182582</v>
       </c>
       <c r="F45" t="n">
-        <v>0.02144053441184001</v>
+        <v>0.01936614899146277</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02525841726459214</v>
+        <v>0.02154673984353353</v>
       </c>
       <c r="H45" t="n">
         <v>0.219637958318896</v>
@@ -4565,10 +4565,10 @@
         <v>0.02454787902311676</v>
       </c>
       <c r="F46" t="n">
-        <v>0.02352756451655235</v>
+        <v>0.01845343295255689</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0238456191265252</v>
+        <v>0.01729974555910638</v>
       </c>
       <c r="H46" t="n">
         <v>0.2253013199805374</v>
@@ -4656,7 +4656,7 @@
         <v>0.05174559238114183</v>
       </c>
       <c r="F47" t="n">
-        <v>0.09709946130910892</v>
+        <v>0.0929386397926536</v>
       </c>
       <c r="G47" t="n">
         <v>0.04480399718747517</v>
@@ -4747,7 +4747,7 @@
         <v>0.04583886555291042</v>
       </c>
       <c r="F48" t="n">
-        <v>0.05537294625574413</v>
+        <v>0.05398308085058456</v>
       </c>
       <c r="G48" t="n">
         <v>0.04969645943058117</v>
@@ -4838,7 +4838,7 @@
         <v>0.05564348626170174</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2449324430605841</v>
+        <v>0.1793179169418565</v>
       </c>
       <c r="G49" t="n">
         <v>0.06279262666724007</v>
@@ -4929,10 +4929,10 @@
         <v>0.1774640663746824</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4682451549912295</v>
+        <v>0.4038510420974185</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3786749325392345</v>
+        <v>0.2491540479599458</v>
       </c>
       <c r="H50" t="n">
         <v>1.363451004429825</v>
@@ -5020,7 +5020,7 @@
         <v>0.1115520870578637</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1262412621544324</v>
+        <v>0.1130308060538432</v>
       </c>
       <c r="G51" t="n">
         <v>0.1345613439814875</v>
@@ -5111,10 +5111,10 @@
         <v>0.5757460453968697</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8010718873641539</v>
+        <v>0.1434335287113982</v>
       </c>
       <c r="G52" t="n">
-        <v>0.7791724793142314</v>
+        <v>0.06545856645476436</v>
       </c>
       <c r="H52" t="n">
         <v>2.498364972397039</v>
@@ -5202,10 +5202,10 @@
         <v>0.5198032238083613</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6526072934147202</v>
+        <v>0.382326291461463</v>
       </c>
       <c r="G53" t="n">
-        <v>0.6229467913638486</v>
+        <v>0.2847844139064604</v>
       </c>
       <c r="H53" t="n">
         <v>2.028441185139194</v>
@@ -5384,10 +5384,10 @@
         <v>0.03958345147957278</v>
       </c>
       <c r="F55" t="n">
-        <v>0.05498032633931599</v>
+        <v>0.0479940251873797</v>
       </c>
       <c r="G55" t="n">
-        <v>0.03783347192799719</v>
+        <v>0.02055370868847309</v>
       </c>
       <c r="H55" t="n">
         <v>0.236689300497001</v>
@@ -5566,7 +5566,7 @@
         <v>0.100515956161974</v>
       </c>
       <c r="F57" t="n">
-        <v>0.104282529496099</v>
+        <v>0.09521977406248446</v>
       </c>
       <c r="G57" t="n">
         <v>0.1004864794446268</v>
@@ -5657,7 +5657,7 @@
         <v>0.09084150395632271</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3427456975396489</v>
+        <v>0.1934569082709603</v>
       </c>
       <c r="G58" t="n">
         <v>0.1588725788136234</v>
@@ -6017,10 +6017,10 @@
         <v>0.09822912572090017</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1316441382711224</v>
+        <v>0.08615999050911302</v>
       </c>
       <c r="G62" t="n">
-        <v>0.216000490883848</v>
+        <v>0.1018971081825266</v>
       </c>
       <c r="H62" t="n">
         <v>1.170048173221576</v>
@@ -6381,7 +6381,7 @@
         <v>0.1294012003798869</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4335790808506703</v>
+        <v>0.2796813892801031</v>
       </c>
       <c r="G66" t="n">
         <v>0.1894164891156891</v>
@@ -6472,10 +6472,10 @@
         <v>0.1181106148798783</v>
       </c>
       <c r="F67" t="n">
-        <v>0.05676080471115953</v>
+        <v>0.03691938445856589</v>
       </c>
       <c r="G67" t="n">
-        <v>0.06118083554809368</v>
+        <v>0.02180494038786013</v>
       </c>
       <c r="H67" t="n">
         <v>0.8890729753981951</v>
@@ -6836,10 +6836,10 @@
         <v>0.1076709468327376</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2786131820503252</v>
+        <v>0.1349873389243418</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2130458724335875</v>
+        <v>0.07994470141923268</v>
       </c>
       <c r="H71" t="n">
         <v>1.182881379043306</v>
@@ -6927,10 +6927,10 @@
         <v>0.9316682414789437</v>
       </c>
       <c r="F72" t="n">
-        <v>1.227948464409322</v>
+        <v>0.1395937281168461</v>
       </c>
       <c r="G72" t="n">
-        <v>1.618670079357371</v>
+        <v>0.1833738750036863</v>
       </c>
       <c r="H72" t="n">
         <v>4.167768298998758</v>
@@ -7018,10 +7018,10 @@
         <v>0.04036955990711219</v>
       </c>
       <c r="F73" t="n">
-        <v>0.03176629783439618</v>
+        <v>0.0231072509249596</v>
       </c>
       <c r="G73" t="n">
-        <v>0.042483375849534</v>
+        <v>0.02036457786133488</v>
       </c>
       <c r="H73" t="n">
         <v>0.668404623200426</v>
@@ -7291,10 +7291,10 @@
         <v>0.06571364627998162</v>
       </c>
       <c r="F76" t="n">
-        <v>0.05204542838263079</v>
+        <v>0.05023924641571906</v>
       </c>
       <c r="G76" t="n">
-        <v>0.05202131913271273</v>
+        <v>0.04239929452702773</v>
       </c>
       <c r="H76" t="n">
         <v>0.4181268703617883</v>
@@ -7382,10 +7382,10 @@
         <v>0.1804258979309288</v>
       </c>
       <c r="F77" t="n">
-        <v>0.185690276354786</v>
+        <v>0.08679804901368707</v>
       </c>
       <c r="G77" t="n">
-        <v>0.1939623591508854</v>
+        <v>0.05796260430067558</v>
       </c>
       <c r="H77" t="n">
         <v>0.9740670823972597</v>
@@ -7473,10 +7473,10 @@
         <v>0.02573356602782632</v>
       </c>
       <c r="F78" t="n">
-        <v>0.03548802700540128</v>
+        <v>0.03180019974772018</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0229989616065663</v>
+        <v>0.01679729602538183</v>
       </c>
       <c r="H78" t="n">
         <v>0.2724125086601074</v>
@@ -7564,10 +7564,10 @@
         <v>0.01414324716831614</v>
       </c>
       <c r="F79" t="n">
-        <v>0.03259144092452313</v>
+        <v>0.02758503199957514</v>
       </c>
       <c r="G79" t="n">
-        <v>0.01877024924355914</v>
+        <v>0.01506284378545471</v>
       </c>
       <c r="H79" t="n">
         <v>0.2823531843116658</v>
@@ -7655,7 +7655,7 @@
         <v>0.238598667621214</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3165184675901519</v>
+        <v>0.1260361777125463</v>
       </c>
       <c r="G80" t="n">
         <v>0.2688966341496576</v>
@@ -7928,7 +7928,7 @@
         <v>0.1441034777410879</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2707612399366178</v>
+        <v>0.1862702414531865</v>
       </c>
       <c r="G83" t="n">
         <v>0.171162502077699</v>
@@ -8110,10 +8110,10 @@
         <v>0.2058105708765144</v>
       </c>
       <c r="F85" t="n">
-        <v>0.3396050305073505</v>
+        <v>0.1738792722529016</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1931323905399069</v>
+        <v>0.05044381014536069</v>
       </c>
       <c r="H85" t="n">
         <v>0.9954997516854572</v>
@@ -8292,7 +8292,7 @@
         <v>0.112450366577684</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1336106464101122</v>
+        <v>0.112438900029015</v>
       </c>
       <c r="G87" t="n">
         <v>0.1454582511313159</v>
@@ -8656,10 +8656,10 @@
         <v>0.155149130453718</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1466640876877139</v>
+        <v>0.1264489514266609</v>
       </c>
       <c r="G91" t="n">
-        <v>0.1184146413424235</v>
+        <v>0.08279291411922507</v>
       </c>
       <c r="H91" t="n">
         <v>0.6277099064094847</v>
@@ -8747,10 +8747,10 @@
         <v>0.3681962388429534</v>
       </c>
       <c r="F92" t="n">
-        <v>0.2274919886084814</v>
+        <v>0.1236447565676127</v>
       </c>
       <c r="G92" t="n">
-        <v>0.3829546148099282</v>
+        <v>0.07722032133719388</v>
       </c>
       <c r="H92" t="n">
         <v>1.486341126158328</v>
@@ -8929,7 +8929,7 @@
         <v>0.3126300896715725</v>
       </c>
       <c r="F94" t="n">
-        <v>0.4534591943483687</v>
+        <v>0.2512767817324205</v>
       </c>
       <c r="G94" t="n">
         <v>0.531138444402274</v>
@@ -9020,7 +9020,7 @@
         <v>0.0638123239152574</v>
       </c>
       <c r="F95" t="n">
-        <v>0.2146133225581265</v>
+        <v>0.18267413818875</v>
       </c>
       <c r="G95" t="n">
         <v>0.06608706189881056</v>
@@ -9111,10 +9111,10 @@
         <v>0.2247824687911161</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1250620711408253</v>
+        <v>0.1204703373663014</v>
       </c>
       <c r="G96" t="n">
-        <v>0.2148600079192438</v>
+        <v>0.04631349375353633</v>
       </c>
       <c r="H96" t="n">
         <v>1.284271140273298</v>
@@ -9384,10 +9384,10 @@
         <v>0.1102132991859153</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2996335618166658</v>
+        <v>0.2394548509284524</v>
       </c>
       <c r="G99" t="n">
-        <v>0.1573207272664319</v>
+        <v>0.1344856736544428</v>
       </c>
       <c r="H99" t="n">
         <v>0.9127531883440781</v>
@@ -9566,10 +9566,10 @@
         <v>0.09003259155030501</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2243129053176406</v>
+        <v>0.1733703548482827</v>
       </c>
       <c r="G101" t="n">
-        <v>0.06581684477911824</v>
+        <v>0.05422874891323599</v>
       </c>
       <c r="H101" t="n">
         <v>0.4678895287272094</v>
@@ -9657,7 +9657,7 @@
         <v>0.01400818481728265</v>
       </c>
       <c r="F102" t="n">
-        <v>0.03011689873335743</v>
+        <v>0.02687532904477473</v>
       </c>
       <c r="G102" t="n">
         <v>0.0207588871649772</v>
@@ -9748,10 +9748,10 @@
         <v>1.581580416673479</v>
       </c>
       <c r="F103" t="n">
-        <v>4.142982621511965</v>
+        <v>1.278618643667651</v>
       </c>
       <c r="G103" t="n">
-        <v>4.3570873215527</v>
+        <v>1.292698938084762</v>
       </c>
       <c r="H103" t="n">
         <v>13.40409564039896</v>
@@ -9839,10 +9839,10 @@
         <v>0.07022701871687015</v>
       </c>
       <c r="F104" t="n">
-        <v>0.04102985459252931</v>
+        <v>0.02971926021924808</v>
       </c>
       <c r="G104" t="n">
-        <v>0.03418131909984273</v>
+        <v>0.01625670772907324</v>
       </c>
       <c r="H104" t="n">
         <v>0.3786825381440391</v>
@@ -9930,10 +9930,10 @@
         <v>0.2389954831576384</v>
       </c>
       <c r="F105" t="n">
-        <v>0.2730719236958599</v>
+        <v>0.1588875607613346</v>
       </c>
       <c r="G105" t="n">
-        <v>0.4919724343377241</v>
+        <v>0.303290578719158</v>
       </c>
       <c r="H105" t="n">
         <v>1.33446238571039</v>
@@ -10021,10 +10021,10 @@
         <v>0.003903726054257696</v>
       </c>
       <c r="F106" t="n">
-        <v>0.002972213905213556</v>
+        <v>0.002567539863701115</v>
       </c>
       <c r="G106" t="n">
-        <v>0.003537402368925798</v>
+        <v>0.002744425647463013</v>
       </c>
       <c r="H106" t="n">
         <v>0.2493107544939339</v>
@@ -10112,10 +10112,10 @@
         <v>0.003462519821082707</v>
       </c>
       <c r="F107" t="n">
-        <v>0.002211417323696687</v>
+        <v>0.002070748508195912</v>
       </c>
       <c r="G107" t="n">
-        <v>0.002859091788827896</v>
+        <v>0.002337790536656086</v>
       </c>
       <c r="H107" t="n">
         <v>0.2431184488471118</v>
@@ -10203,10 +10203,10 @@
         <v>0.008195547529182877</v>
       </c>
       <c r="F108" t="n">
-        <v>0.003889368089883496</v>
+        <v>0.003549544296572218</v>
       </c>
       <c r="G108" t="n">
-        <v>0.003716062112603385</v>
+        <v>0.002961112162262018</v>
       </c>
       <c r="H108" t="n">
         <v>0.2447316180012817</v>
@@ -10294,10 +10294,10 @@
         <v>0.0229287772940192</v>
       </c>
       <c r="F109" t="n">
-        <v>0.01095171727741152</v>
+        <v>0.009427338787905332</v>
       </c>
       <c r="G109" t="n">
-        <v>0.007933331962871043</v>
+        <v>0.005634847864555317</v>
       </c>
       <c r="H109" t="n">
         <v>0.2967165783205413</v>
@@ -10385,10 +10385,10 @@
         <v>0.009136679650261695</v>
       </c>
       <c r="F110" t="n">
-        <v>0.00667144484744806</v>
+        <v>0.006034507346243276</v>
       </c>
       <c r="G110" t="n">
-        <v>0.004872607935825926</v>
+        <v>0.003905238283342884</v>
       </c>
       <c r="H110" t="n">
         <v>0.2496204874837848</v>
@@ -10476,10 +10476,10 @@
         <v>0.01449679666553838</v>
       </c>
       <c r="F111" t="n">
-        <v>0.007852362534987365</v>
+        <v>0.006128637276738195</v>
       </c>
       <c r="G111" t="n">
-        <v>0.009894084047604969</v>
+        <v>0.007122449146175676</v>
       </c>
       <c r="H111" t="n">
         <v>0.4667631816385235</v>
@@ -10567,10 +10567,10 @@
         <v>0.147447388732114</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1222955932484568</v>
+        <v>0.05842328861639837</v>
       </c>
       <c r="G112" t="n">
-        <v>0.1377730992651008</v>
+        <v>0.04556778637263123</v>
       </c>
       <c r="H112" t="n">
         <v>0.9342361934783976</v>
@@ -10658,10 +10658,10 @@
         <v>0.2286475797645283</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1054542205085662</v>
+        <v>0.0295903256503137</v>
       </c>
       <c r="G113" t="n">
-        <v>0.1376602269008681</v>
+        <v>0.022867940537699</v>
       </c>
       <c r="H113" t="n">
         <v>1.084354343907561</v>
@@ -10840,10 +10840,10 @@
         <v>0.1884899539434938</v>
       </c>
       <c r="F115" t="n">
-        <v>0.09944266173050463</v>
+        <v>0.095975282564396</v>
       </c>
       <c r="G115" t="n">
-        <v>0.1557893837388853</v>
+        <v>0.1286399757668549</v>
       </c>
       <c r="H115" t="n">
         <v>0.745973544696887</v>
@@ -10931,10 +10931,10 @@
         <v>0.2161324775894491</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2243944175300679</v>
+        <v>0.1430504284929129</v>
       </c>
       <c r="G116" t="n">
-        <v>0.2084589400619517</v>
+        <v>0.1026486004329924</v>
       </c>
       <c r="H116" t="n">
         <v>0.8791106428021422</v>
@@ -11022,10 +11022,10 @@
         <v>0.01874731439354337</v>
       </c>
       <c r="F117" t="n">
-        <v>0.01813054979322128</v>
+        <v>0.01717630988365427</v>
       </c>
       <c r="G117" t="n">
-        <v>0.01834240042474868</v>
+        <v>0.01512689717165412</v>
       </c>
       <c r="H117" t="n">
         <v>0.2183882729589028</v>
@@ -11113,10 +11113,10 @@
         <v>0.009061516450549619</v>
       </c>
       <c r="F118" t="n">
-        <v>0.01101351535264305</v>
+        <v>0.01008626667992845</v>
       </c>
       <c r="G118" t="n">
-        <v>0.009239445137645453</v>
+        <v>0.007653461075037736</v>
       </c>
       <c r="H118" t="n">
         <v>0.1647401054134016</v>
@@ -11204,10 +11204,10 @@
         <v>0.01964576803818497</v>
       </c>
       <c r="F119" t="n">
-        <v>0.01776444370705442</v>
+        <v>0.01577672210436288</v>
       </c>
       <c r="G119" t="n">
-        <v>0.01182909467612855</v>
+        <v>0.009606417163219506</v>
       </c>
       <c r="H119" t="n">
         <v>0.1959608041850188</v>
@@ -11386,10 +11386,10 @@
         <v>0.01809470170044845</v>
       </c>
       <c r="F121" t="n">
-        <v>0.02534401390324391</v>
+        <v>0.02255881004644447</v>
       </c>
       <c r="G121" t="n">
-        <v>0.01762433403534535</v>
+        <v>0.01457183946276761</v>
       </c>
       <c r="H121" t="n">
         <v>0.1861185602553873</v>
@@ -11477,10 +11477,10 @@
         <v>0.04967587733612646</v>
       </c>
       <c r="F122" t="n">
-        <v>0.04606926734787022</v>
+        <v>0.03890910685417902</v>
       </c>
       <c r="G122" t="n">
-        <v>0.05071726163831866</v>
+        <v>0.03667968206703212</v>
       </c>
       <c r="H122" t="n">
         <v>0.278485987840173</v>
@@ -11750,10 +11750,10 @@
         <v>0.07652871069541536</v>
       </c>
       <c r="F125" t="n">
-        <v>0.1151119158059892</v>
+        <v>0.06384417130343652</v>
       </c>
       <c r="G125" t="n">
-        <v>0.08579250997818041</v>
+        <v>0.03258321381367214</v>
       </c>
       <c r="H125" t="n">
         <v>0.5139083244130161</v>
@@ -11932,10 +11932,10 @@
         <v>0.05205516902535588</v>
       </c>
       <c r="F127" t="n">
-        <v>0.05266381205386683</v>
+        <v>0.0477515975066941</v>
       </c>
       <c r="G127" t="n">
-        <v>0.05209501878246995</v>
+        <v>0.03778689535253126</v>
       </c>
       <c r="H127" t="n">
         <v>0.2993369040417522</v>
@@ -12114,10 +12114,10 @@
         <v>0.01404682664169479</v>
       </c>
       <c r="F129" t="n">
-        <v>0.02648148692615052</v>
+        <v>0.02230769985141002</v>
       </c>
       <c r="G129" t="n">
-        <v>0.01707383496364671</v>
+        <v>0.01395673740741249</v>
       </c>
       <c r="H129" t="n">
         <v>0.129182604735649</v>
@@ -12478,10 +12478,10 @@
         <v>0.1665759667256722</v>
       </c>
       <c r="F133" t="n">
-        <v>0.6102304443310116</v>
+        <v>0.4829359857889134</v>
       </c>
       <c r="G133" t="n">
-        <v>0.3681425354393535</v>
+        <v>0.2793887409357622</v>
       </c>
       <c r="H133" t="n">
         <v>1.40754481138985</v>
@@ -12569,7 +12569,7 @@
         <v>0.2225362651727793</v>
       </c>
       <c r="F134" t="n">
-        <v>0.3790931230261947</v>
+        <v>0.08923385197820913</v>
       </c>
       <c r="G134" t="n">
         <v>0.3645091629601232</v>
@@ -12751,7 +12751,7 @@
         <v>0.2435661535021833</v>
       </c>
       <c r="F136" t="n">
-        <v>0.4107964026693026</v>
+        <v>0.1627989797773725</v>
       </c>
       <c r="G136" t="n">
         <v>0.3398433661253663</v>
@@ -13115,10 +13115,10 @@
         <v>0.6271805761179865</v>
       </c>
       <c r="F140" t="n">
-        <v>0.7089618898198431</v>
+        <v>0.3444718552330144</v>
       </c>
       <c r="G140" t="n">
-        <v>0.880838987011583</v>
+        <v>0.2547595111969015</v>
       </c>
       <c r="H140" t="n">
         <v>2.199285093667711</v>
@@ -13206,10 +13206,10 @@
         <v>0.1159372083374286</v>
       </c>
       <c r="F141" t="n">
-        <v>0.08904486202623338</v>
+        <v>0.09258465912369279</v>
       </c>
       <c r="G141" t="n">
-        <v>0.1982515041563579</v>
+        <v>0.07558486367840019</v>
       </c>
       <c r="H141" t="n">
         <v>1.034221944058446</v>
@@ -13297,10 +13297,10 @@
         <v>0.4751017764463643</v>
       </c>
       <c r="F142" t="n">
-        <v>0.3924179100027597</v>
+        <v>0.2117382522170572</v>
       </c>
       <c r="G142" t="n">
-        <v>0.6164791222918644</v>
+        <v>0.06111396606437294</v>
       </c>
       <c r="H142" t="n">
         <v>1.568007141874413</v>
@@ -13475,10 +13475,10 @@
         <v>0.1337120246751101</v>
       </c>
       <c r="F144" t="n">
-        <v>0.1179136146004363</v>
+        <v>0.07513908384716733</v>
       </c>
       <c r="G144" t="n">
-        <v>0.1002936061616974</v>
+        <v>0.03954289101888558</v>
       </c>
       <c r="H144" t="n">
         <v>0.9837663146858279</v>
@@ -13566,7 +13566,7 @@
         <v>0.1265298485155069</v>
       </c>
       <c r="F145" t="n">
-        <v>0.1458466886528677</v>
+        <v>0.1434345429253467</v>
       </c>
       <c r="G145" t="n">
         <v>0.1486961838764625</v>
@@ -13657,7 +13657,7 @@
         <v>0.1219578055977806</v>
       </c>
       <c r="F146" t="n">
-        <v>0.2798243212363288</v>
+        <v>0.2105031452254743</v>
       </c>
       <c r="G146" t="n">
         <v>0.1407370451635932</v>
@@ -13748,10 +13748,10 @@
         <v>0.1337151129423892</v>
       </c>
       <c r="F147" t="n">
-        <v>0.1003173336968477</v>
+        <v>0.08397766131928372</v>
       </c>
       <c r="G147" t="n">
-        <v>0.1259289161421396</v>
+        <v>0.1015613734751795</v>
       </c>
       <c r="H147" t="n">
         <v>0.7272922710971119</v>

--- a/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
+++ b/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
@@ -580,7 +580,7 @@
         <v>0.1273740515060551</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1621908873837076</v>
+        <v>0.1400390548721461</v>
       </c>
       <c r="H2" t="n">
         <v>0.7166120797150832</v>
@@ -668,10 +668,10 @@
         <v>0.1467325311721351</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1739358452044829</v>
+        <v>0.1573648151022616</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2041231323367976</v>
+        <v>0.1775298075696203</v>
       </c>
       <c r="H3" t="n">
         <v>0.7455856917047092</v>
@@ -1035,7 +1035,7 @@
         <v>0.09213262856284368</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1810847605610292</v>
+        <v>0.1442557465663686</v>
       </c>
       <c r="H7" t="n">
         <v>0.8514955388435604</v>
@@ -1123,10 +1123,10 @@
         <v>0.1736541581897918</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2731102566094739</v>
+        <v>0.2376049682552512</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2084815713401154</v>
+        <v>0.1763318386041289</v>
       </c>
       <c r="H8" t="n">
         <v>0.8218833647220964</v>
@@ -1214,10 +1214,10 @@
         <v>0.2666309112809248</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2874819016355921</v>
+        <v>0.2812971012410094</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2721571449037711</v>
+        <v>0.2469102413904404</v>
       </c>
       <c r="H9" t="n">
         <v>0.4755023523128038</v>
@@ -1301,10 +1301,10 @@
         <v>0.3247393788989229</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3405235018906729</v>
+        <v>0.308501760061826</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5576494127906528</v>
+        <v>0.4909539752890018</v>
       </c>
       <c r="H10" t="n">
         <v>1.126897749532528</v>
@@ -1486,7 +1486,7 @@
         <v>0.1756797636372625</v>
       </c>
       <c r="G12" t="n">
-        <v>0.542783575332459</v>
+        <v>0.4665940537865853</v>
       </c>
       <c r="H12" t="n">
         <v>1.373425403558954</v>
@@ -1665,10 +1665,10 @@
         <v>0.07905761631300896</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2595628525499616</v>
+        <v>0.243123914299106</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0868888799509927</v>
+        <v>0.07453067733107507</v>
       </c>
       <c r="H14" t="n">
         <v>0.5768557783561169</v>
@@ -1847,10 +1847,10 @@
         <v>0.2120875018020139</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5974690054540226</v>
+        <v>0.5672645296321478</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2232638951252287</v>
+        <v>0.2009399728488693</v>
       </c>
       <c r="H16" t="n">
         <v>0.4381367147839849</v>
@@ -2025,10 +2025,10 @@
         <v>0.64030076757404</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7025184375689592</v>
+        <v>0.6334147036955725</v>
       </c>
       <c r="G18" t="n">
-        <v>0.792195435161309</v>
+        <v>0.7212781478056187</v>
       </c>
       <c r="H18" t="n">
         <v>1.125928035226928</v>
@@ -2112,10 +2112,10 @@
         <v>0.1432952211848578</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1901435867294042</v>
+        <v>0.1744901373815973</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1898537073372083</v>
+        <v>0.1694076912449964</v>
       </c>
       <c r="H19" t="n">
         <v>0.5491815241612263</v>
@@ -2206,7 +2206,7 @@
         <v>0.3177717005346725</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3094729701462228</v>
+        <v>0.2585525221441749</v>
       </c>
       <c r="H20" t="n">
         <v>1.089294365184146</v>
@@ -2297,7 +2297,7 @@
         <v>0.3072942669735372</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2853456092299797</v>
+        <v>0.2383820000216629</v>
       </c>
       <c r="H21" t="n">
         <v>1.062546466477206</v>
@@ -2385,10 +2385,10 @@
         <v>0.3908363836904335</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4135126407101541</v>
+        <v>0.3571123820132335</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6681327325023453</v>
+        <v>0.5607169233760476</v>
       </c>
       <c r="H22" t="n">
         <v>1.313835537124292</v>
@@ -2567,10 +2567,10 @@
         <v>0.2203032240731948</v>
       </c>
       <c r="F24" t="n">
-        <v>0.392115580446842</v>
+        <v>0.3549278531027266</v>
       </c>
       <c r="G24" t="n">
-        <v>0.276300479019369</v>
+        <v>0.2349687559732749</v>
       </c>
       <c r="H24" t="n">
         <v>0.821026555289418</v>
@@ -2931,10 +2931,10 @@
         <v>0.0861956375987431</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1832017044101036</v>
+        <v>0.1826432065218835</v>
       </c>
       <c r="G28" t="n">
-        <v>0.07970759094368303</v>
+        <v>0.06945222718704025</v>
       </c>
       <c r="H28" t="n">
         <v>0.3217073324512321</v>
@@ -3022,10 +3022,10 @@
         <v>0.03036483750533457</v>
       </c>
       <c r="F29" t="n">
-        <v>0.06017572089167608</v>
+        <v>0.05504613382302184</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0372744770238319</v>
+        <v>0.03312565956983074</v>
       </c>
       <c r="H29" t="n">
         <v>0.09125397575447609</v>
@@ -3204,10 +3204,10 @@
         <v>0.06482343969746326</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1167938068341898</v>
+        <v>0.1087807638857484</v>
       </c>
       <c r="G31" t="n">
-        <v>0.07792868571710398</v>
+        <v>0.06964511772122746</v>
       </c>
       <c r="H31" t="n">
         <v>0.1898985606099392</v>
@@ -3298,7 +3298,7 @@
         <v>0.07390302168492037</v>
       </c>
       <c r="G32" t="n">
-        <v>0.04487584215704166</v>
+        <v>0.03806254417138709</v>
       </c>
       <c r="H32" t="n">
         <v>0.2272640433410283</v>
@@ -3389,7 +3389,7 @@
         <v>0.2591531886278792</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3940136292074076</v>
+        <v>0.3397615516898658</v>
       </c>
       <c r="H33" t="n">
         <v>1.247560275116454</v>
@@ -3750,10 +3750,10 @@
         <v>0.08792673443779837</v>
       </c>
       <c r="F37" t="n">
-        <v>0.118008980587572</v>
+        <v>0.100946962285316</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1007515737883619</v>
+        <v>0.08581322817038285</v>
       </c>
       <c r="H37" t="n">
         <v>0.5039765573286296</v>
@@ -3935,7 +3935,7 @@
         <v>0.1580591804767361</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1869240753790934</v>
+        <v>0.1571382293628559</v>
       </c>
       <c r="H39" t="n">
         <v>0.7973738576699186</v>
@@ -4205,10 +4205,10 @@
         <v>0.06041729594430501</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1525091787535633</v>
+        <v>0.1435575817741239</v>
       </c>
       <c r="G42" t="n">
-        <v>0.08167519798796011</v>
+        <v>0.06958372192400065</v>
       </c>
       <c r="H42" t="n">
         <v>0.2705128397863901</v>
@@ -4296,10 +4296,10 @@
         <v>0.3442702888129965</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3378604868055509</v>
+        <v>0.3047263883142536</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3573042806323476</v>
+        <v>0.3248896993693345</v>
       </c>
       <c r="H43" t="n">
         <v>0.5606279224051089</v>
@@ -4659,7 +4659,7 @@
         <v>0.0929386397926536</v>
       </c>
       <c r="G47" t="n">
-        <v>0.04480399718747517</v>
+        <v>0.03870416265059731</v>
       </c>
       <c r="H47" t="n">
         <v>0.2500371999588092</v>
@@ -4750,7 +4750,7 @@
         <v>0.05398308085058456</v>
       </c>
       <c r="G48" t="n">
-        <v>0.04969645943058117</v>
+        <v>0.04321498528053278</v>
       </c>
       <c r="H48" t="n">
         <v>0.2334066842779279</v>
@@ -4841,7 +4841,7 @@
         <v>0.1793179169418565</v>
       </c>
       <c r="G49" t="n">
-        <v>0.06279262666724007</v>
+        <v>0.05428570210519246</v>
       </c>
       <c r="H49" t="n">
         <v>0.3379122681153697</v>
@@ -5023,7 +5023,7 @@
         <v>0.1130308060538432</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1345613439814875</v>
+        <v>0.1141402275917825</v>
       </c>
       <c r="H51" t="n">
         <v>0.670665120055479</v>
@@ -5293,10 +5293,10 @@
         <v>0.1461670215316392</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2406049859659714</v>
+        <v>0.2431414389419841</v>
       </c>
       <c r="G54" t="n">
-        <v>0.1819613869179339</v>
+        <v>0.1612973421204605</v>
       </c>
       <c r="H54" t="n">
         <v>0.4376089963335965</v>
@@ -5475,10 +5475,10 @@
         <v>0.382411423631514</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3165282661758949</v>
+        <v>0.287288487169398</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2829634898298001</v>
+        <v>0.2544657841423403</v>
       </c>
       <c r="H56" t="n">
         <v>0.6666406779747964</v>
@@ -5569,7 +5569,7 @@
         <v>0.09521977406248446</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1004864794446268</v>
+        <v>0.08887672030661672</v>
       </c>
       <c r="H57" t="n">
         <v>0.5431663794570629</v>
@@ -5660,7 +5660,7 @@
         <v>0.1934569082709603</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1588725788136234</v>
+        <v>0.126656721375907</v>
       </c>
       <c r="H58" t="n">
         <v>0.9187102398267176</v>
@@ -5748,10 +5748,10 @@
         <v>0.002045224741455347</v>
       </c>
       <c r="F59" t="n">
-        <v>0.01218386234700448</v>
+        <v>0.01161240889596611</v>
       </c>
       <c r="G59" t="n">
-        <v>0.003878637513017395</v>
+        <v>0.003430083554543807</v>
       </c>
       <c r="H59" t="n">
         <v>0.006201137995202942</v>
@@ -5835,10 +5835,10 @@
         <v>0.5287418907149984</v>
       </c>
       <c r="F60" t="n">
-        <v>1.118752094583926</v>
+        <v>1.030351550415582</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9516889148506655</v>
+        <v>0.8669611505019319</v>
       </c>
       <c r="H60" t="n">
         <v>1.935074098502654</v>
@@ -5926,10 +5926,10 @@
         <v>0.3576351673817741</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6305351296495791</v>
+        <v>0.5546181233245268</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6188532450670831</v>
+        <v>0.5171499157970105</v>
       </c>
       <c r="H61" t="n">
         <v>1.482727576453942</v>
@@ -6108,10 +6108,10 @@
         <v>0.07228009391647686</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1531616659823475</v>
+        <v>0.1380224210042882</v>
       </c>
       <c r="G63" t="n">
-        <v>0.08755751238176694</v>
+        <v>0.07543652984507819</v>
       </c>
       <c r="H63" t="n">
         <v>0.3847615424008634</v>
@@ -6199,10 +6199,10 @@
         <v>0.2384426269210413</v>
       </c>
       <c r="F64" t="n">
-        <v>0.2598138693543705</v>
+        <v>0.2438753888014948</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3603051201140942</v>
+        <v>0.3021856555868332</v>
       </c>
       <c r="H64" t="n">
         <v>0.9613842667655157</v>
@@ -6290,10 +6290,10 @@
         <v>0.4151763266802893</v>
       </c>
       <c r="F65" t="n">
-        <v>0.5733066533221627</v>
+        <v>0.4879493971214461</v>
       </c>
       <c r="G65" t="n">
-        <v>0.6601094192053441</v>
+        <v>0.5541226334982552</v>
       </c>
       <c r="H65" t="n">
         <v>1.364498070866812</v>
@@ -6384,7 +6384,7 @@
         <v>0.2796813892801031</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1894164891156891</v>
+        <v>0.1571210200996109</v>
       </c>
       <c r="H66" t="n">
         <v>0.8762976441872627</v>
@@ -6563,10 +6563,10 @@
         <v>0.6967626147329891</v>
       </c>
       <c r="F68" t="n">
-        <v>0.5809149818137502</v>
+        <v>0.6062587935082824</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6888483953701938</v>
+        <v>0.6059161602749761</v>
       </c>
       <c r="H68" t="n">
         <v>0.822053537981963</v>
@@ -6654,10 +6654,10 @@
         <v>0.04233260812396031</v>
       </c>
       <c r="F69" t="n">
-        <v>0.06990335025584646</v>
+        <v>0.06302718278062479</v>
       </c>
       <c r="G69" t="n">
-        <v>0.05181706434817195</v>
+        <v>0.04504951444231538</v>
       </c>
       <c r="H69" t="n">
         <v>0.1158922377181897</v>
@@ -6745,10 +6745,10 @@
         <v>0.1236753522000469</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1240148688696252</v>
+        <v>0.1113282040033945</v>
       </c>
       <c r="G70" t="n">
-        <v>0.1298159387574236</v>
+        <v>0.1156167528527651</v>
       </c>
       <c r="H70" t="n">
         <v>0.2999663024798833</v>
@@ -7109,10 +7109,10 @@
         <v>0.07068272011491204</v>
       </c>
       <c r="F74" t="n">
-        <v>0.1415480457992404</v>
+        <v>0.1386272802852584</v>
       </c>
       <c r="G74" t="n">
-        <v>0.07554228023362257</v>
+        <v>0.06505871611247036</v>
       </c>
       <c r="H74" t="n">
         <v>0.3266677650070184</v>
@@ -7200,10 +7200,10 @@
         <v>0.4778745033745449</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5197976002511773</v>
+        <v>0.4687750409265702</v>
       </c>
       <c r="G75" t="n">
-        <v>0.5114549341073915</v>
+        <v>0.4572430001447724</v>
       </c>
       <c r="H75" t="n">
         <v>0.9493752443193544</v>
@@ -7658,7 +7658,7 @@
         <v>0.1260361777125463</v>
       </c>
       <c r="G80" t="n">
-        <v>0.2688966341496576</v>
+        <v>0.2277751072159404</v>
       </c>
       <c r="H80" t="n">
         <v>0.9166327752016876</v>
@@ -7746,10 +7746,10 @@
         <v>0.1850535555573287</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1622183733960993</v>
+        <v>0.1537792968128227</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1711579563257946</v>
+        <v>0.1519475576872357</v>
       </c>
       <c r="H81" t="n">
         <v>0.4638560507984801</v>
@@ -7837,10 +7837,10 @@
         <v>0.1867454436277563</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1121051447128653</v>
+        <v>0.09872815529090528</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1594189571199458</v>
+        <v>0.1317773973004435</v>
       </c>
       <c r="H82" t="n">
         <v>0.7015311782717396</v>
@@ -7931,7 +7931,7 @@
         <v>0.1862702414531865</v>
       </c>
       <c r="G83" t="n">
-        <v>0.171162502077699</v>
+        <v>0.1408374915582134</v>
       </c>
       <c r="H83" t="n">
         <v>0.7520441762890825</v>
@@ -8019,10 +8019,10 @@
         <v>0.06389656552322329</v>
       </c>
       <c r="F84" t="n">
-        <v>0.133674115406255</v>
+        <v>0.1229021650545556</v>
       </c>
       <c r="G84" t="n">
-        <v>0.05663860313480173</v>
+        <v>0.04599844410388158</v>
       </c>
       <c r="H84" t="n">
         <v>0.2231897293196931</v>
@@ -8201,10 +8201,10 @@
         <v>0.2266939034529027</v>
       </c>
       <c r="F86" t="n">
-        <v>0.3601302514379101</v>
+        <v>0.3971355277028613</v>
       </c>
       <c r="G86" t="n">
-        <v>0.3079378018379147</v>
+        <v>0.263134582497879</v>
       </c>
       <c r="H86" t="n">
         <v>0.7662289278414284</v>
@@ -8295,7 +8295,7 @@
         <v>0.112438900029015</v>
       </c>
       <c r="G87" t="n">
-        <v>0.1454582511313159</v>
+        <v>0.1255143654652407</v>
       </c>
       <c r="H87" t="n">
         <v>0.6211718381693592</v>
@@ -8383,10 +8383,10 @@
         <v>0.1468791610224586</v>
       </c>
       <c r="F88" t="n">
-        <v>0.2098013315741654</v>
+        <v>0.1837310097084097</v>
       </c>
       <c r="G88" t="n">
-        <v>0.1704231739774071</v>
+        <v>0.1424008683056959</v>
       </c>
       <c r="H88" t="n">
         <v>0.5425971346865082</v>
@@ -8474,10 +8474,10 @@
         <v>0.08795776493967382</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1391606600477753</v>
+        <v>0.1275708032778044</v>
       </c>
       <c r="G89" t="n">
-        <v>0.1090101807465273</v>
+        <v>0.09447344937759243</v>
       </c>
       <c r="H89" t="n">
         <v>0.190759435338714</v>
@@ -8565,10 +8565,10 @@
         <v>0.08845743782659278</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1465996237813318</v>
+        <v>0.1385606590994197</v>
       </c>
       <c r="G90" t="n">
-        <v>0.09839574785023122</v>
+        <v>0.0865845757669616</v>
       </c>
       <c r="H90" t="n">
         <v>0.4537308513006609</v>
@@ -8838,10 +8838,10 @@
         <v>0.1396814974513654</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1570570902007696</v>
+        <v>0.1509017704730491</v>
       </c>
       <c r="G93" t="n">
-        <v>0.1399106196576736</v>
+        <v>0.1226821766423035</v>
       </c>
       <c r="H93" t="n">
         <v>0.575614988254466</v>
@@ -8932,7 +8932,7 @@
         <v>0.2512767817324205</v>
       </c>
       <c r="G94" t="n">
-        <v>0.531138444402274</v>
+        <v>0.4659309483618734</v>
       </c>
       <c r="H94" t="n">
         <v>1.236937243017472</v>
@@ -9023,7 +9023,7 @@
         <v>0.18267413818875</v>
       </c>
       <c r="G95" t="n">
-        <v>0.06608706189881056</v>
+        <v>0.05751738667158389</v>
       </c>
       <c r="H95" t="n">
         <v>0.5594639660662479</v>
@@ -9202,10 +9202,10 @@
         <v>0.05691390605230952</v>
       </c>
       <c r="F97" t="n">
-        <v>0.197194264756038</v>
+        <v>0.1835927197368755</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0553460035577288</v>
+        <v>0.04809851057485914</v>
       </c>
       <c r="H97" t="n">
         <v>0.2177031397462812</v>
@@ -9293,10 +9293,10 @@
         <v>0.2236513630438572</v>
       </c>
       <c r="F98" t="n">
-        <v>0.2910891741402319</v>
+        <v>0.2707490502261118</v>
       </c>
       <c r="G98" t="n">
-        <v>0.2891659078039812</v>
+        <v>0.2638116164380204</v>
       </c>
       <c r="H98" t="n">
         <v>0.7651940787133369</v>
@@ -9475,10 +9475,10 @@
         <v>0.1570934386527884</v>
       </c>
       <c r="F100" t="n">
-        <v>0.5920940652324238</v>
+        <v>0.5242744079697134</v>
       </c>
       <c r="G100" t="n">
-        <v>0.2819078278299025</v>
+        <v>0.2277043430529767</v>
       </c>
       <c r="H100" t="n">
         <v>1.04262150654369</v>
@@ -9660,7 +9660,7 @@
         <v>0.02687532904477473</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0207588871649772</v>
+        <v>0.01773998700395731</v>
       </c>
       <c r="H102" t="n">
         <v>0.1147432029708231</v>
@@ -10749,10 +10749,10 @@
         <v>0.0827735265571856</v>
       </c>
       <c r="F114" t="n">
-        <v>0.07088826156162083</v>
+        <v>0.06501121197298165</v>
       </c>
       <c r="G114" t="n">
-        <v>0.06212566559303891</v>
+        <v>0.05187494477529539</v>
       </c>
       <c r="H114" t="n">
         <v>0.2052640089593039</v>
@@ -11295,10 +11295,10 @@
         <v>0.09221646573179659</v>
       </c>
       <c r="F120" t="n">
-        <v>0.1383487949788311</v>
+        <v>0.1294307936834268</v>
       </c>
       <c r="G120" t="n">
-        <v>0.1081838485764769</v>
+        <v>0.09627477826946783</v>
       </c>
       <c r="H120" t="n">
         <v>0.2169573885097784</v>
@@ -11568,10 +11568,10 @@
         <v>0.1381698460164195</v>
       </c>
       <c r="F123" t="n">
-        <v>0.2092256314623753</v>
+        <v>0.2073808365177841</v>
       </c>
       <c r="G123" t="n">
-        <v>0.1590027548666282</v>
+        <v>0.138855547354429</v>
       </c>
       <c r="H123" t="n">
         <v>0.4358591106778351</v>
@@ -11659,10 +11659,10 @@
         <v>0.06696826455044233</v>
       </c>
       <c r="F124" t="n">
-        <v>0.06139424014191206</v>
+        <v>0.05689703393935722</v>
       </c>
       <c r="G124" t="n">
-        <v>0.06935644710580072</v>
+        <v>0.06124543306164329</v>
       </c>
       <c r="H124" t="n">
         <v>0.2375175161157313</v>
@@ -11841,10 +11841,10 @@
         <v>0.3256464167387856</v>
       </c>
       <c r="F126" t="n">
-        <v>0.7402101130109464</v>
+        <v>0.6727522289968535</v>
       </c>
       <c r="G126" t="n">
-        <v>0.3837469658950153</v>
+        <v>0.3375657558032504</v>
       </c>
       <c r="H126" t="n">
         <v>1.052655847663158</v>
@@ -12023,10 +12023,10 @@
         <v>0.2364746105131447</v>
       </c>
       <c r="F128" t="n">
-        <v>0.3806539474411484</v>
+        <v>0.3231363996707271</v>
       </c>
       <c r="G128" t="n">
-        <v>0.3514022361863682</v>
+        <v>0.2885524714865467</v>
       </c>
       <c r="H128" t="n">
         <v>1.006886985595747</v>
@@ -12205,10 +12205,10 @@
         <v>0.2825370106397438</v>
       </c>
       <c r="F130" t="n">
-        <v>0.1898645941149175</v>
+        <v>0.1637980018307499</v>
       </c>
       <c r="G130" t="n">
-        <v>0.2718895495394331</v>
+        <v>0.2343844772776312</v>
       </c>
       <c r="H130" t="n">
         <v>0.7778554304874405</v>
@@ -12296,10 +12296,10 @@
         <v>0.07671664578867474</v>
       </c>
       <c r="F131" t="n">
-        <v>0.16559703985541</v>
+        <v>0.1497395030858048</v>
       </c>
       <c r="G131" t="n">
-        <v>0.09106985113663832</v>
+        <v>0.080429094745254</v>
       </c>
       <c r="H131" t="n">
         <v>0.3482352089914686</v>
@@ -12387,10 +12387,10 @@
         <v>0.09241961747205141</v>
       </c>
       <c r="F132" t="n">
-        <v>0.1822986947282859</v>
+        <v>0.1619272377675503</v>
       </c>
       <c r="G132" t="n">
-        <v>0.09743874967140002</v>
+        <v>0.08525566519149724</v>
       </c>
       <c r="H132" t="n">
         <v>0.5850765240017057</v>
@@ -12572,7 +12572,7 @@
         <v>0.08923385197820913</v>
       </c>
       <c r="G134" t="n">
-        <v>0.3645091629601232</v>
+        <v>0.2926566267244143</v>
       </c>
       <c r="H134" t="n">
         <v>1.310460382339101</v>
@@ -12660,10 +12660,10 @@
         <v>0.1894000350173234</v>
       </c>
       <c r="F135" t="n">
-        <v>0.15546894649545</v>
+        <v>0.1348361186767563</v>
       </c>
       <c r="G135" t="n">
-        <v>0.1785851811475817</v>
+        <v>0.1481791784382658</v>
       </c>
       <c r="H135" t="n">
         <v>0.7232811916098527</v>
@@ -12754,7 +12754,7 @@
         <v>0.1627989797773725</v>
       </c>
       <c r="G136" t="n">
-        <v>0.3398433661253663</v>
+        <v>0.275619918385709</v>
       </c>
       <c r="H136" t="n">
         <v>1.245537054766756</v>
@@ -12842,10 +12842,10 @@
         <v>0.1788194337159455</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1432765627841191</v>
+        <v>0.1333808554548116</v>
       </c>
       <c r="G137" t="n">
-        <v>0.1736939563947988</v>
+        <v>0.1541852170912223</v>
       </c>
       <c r="H137" t="n">
         <v>0.6575556533639743</v>
@@ -12933,10 +12933,10 @@
         <v>0.1196984841591649</v>
       </c>
       <c r="F138" t="n">
-        <v>1.09318410663465</v>
+        <v>1.001696572773989</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2845015045140236</v>
+        <v>0.2352065092399827</v>
       </c>
       <c r="H138" t="n">
         <v>1.272182588215972</v>
@@ -13024,10 +13024,10 @@
         <v>0.1170661748165055</v>
       </c>
       <c r="F139" t="n">
-        <v>0.178361579159854</v>
+        <v>0.1729284444312357</v>
       </c>
       <c r="G139" t="n">
-        <v>0.1029478662497653</v>
+        <v>0.09222640954862085</v>
       </c>
       <c r="H139" t="n">
         <v>0.4595522319585266</v>
@@ -13388,10 +13388,10 @@
         <v>0.2612831845767706</v>
       </c>
       <c r="F143" t="n">
-        <v>0.1839146758732833</v>
+        <v>0.1735547947539693</v>
       </c>
       <c r="G143" t="n">
-        <v>0.183626301457463</v>
+        <v>0.169140188527995</v>
       </c>
       <c r="H143" t="n">
         <v>0.3989257195156556</v>
@@ -13569,7 +13569,7 @@
         <v>0.1434345429253467</v>
       </c>
       <c r="G145" t="n">
-        <v>0.1486961838764625</v>
+        <v>0.1258605961919481</v>
       </c>
       <c r="H145" t="n">
         <v>0.7490184834473188</v>
@@ -13660,7 +13660,7 @@
         <v>0.2105031452254743</v>
       </c>
       <c r="G146" t="n">
-        <v>0.1407370451635932</v>
+        <v>0.1163385721003859</v>
       </c>
       <c r="H146" t="n">
         <v>0.7619135220461626</v>
@@ -13839,10 +13839,10 @@
         <v>0.1367483991725467</v>
       </c>
       <c r="F148" t="n">
-        <v>0.3317438836834629</v>
+        <v>0.3122949767513783</v>
       </c>
       <c r="G148" t="n">
-        <v>0.1418431015847322</v>
+        <v>0.1279130184091268</v>
       </c>
       <c r="H148" t="n">
         <v>0.4845021405176518</v>
@@ -13930,10 +13930,10 @@
         <v>0.241331831114811</v>
       </c>
       <c r="F149" t="n">
-        <v>0.202138357650541</v>
+        <v>0.1973063816292741</v>
       </c>
       <c r="G149" t="n">
-        <v>0.1930415124759428</v>
+        <v>0.1805939988813581</v>
       </c>
       <c r="H149" t="n">
         <v>0.4204852656376782</v>
@@ -14021,10 +14021,10 @@
         <v>0.07834503336702708</v>
       </c>
       <c r="F150" t="n">
-        <v>0.1914959531195725</v>
+        <v>0.1772166013950209</v>
       </c>
       <c r="G150" t="n">
-        <v>0.08366029058421448</v>
+        <v>0.07412487343656173</v>
       </c>
       <c r="H150" t="n">
         <v>0.3367819149821296</v>

--- a/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
+++ b/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
@@ -577,10 +577,10 @@
         <v>0.1720860246432098</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1273740515060551</v>
+        <v>0.1273740542584842</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1400390548721461</v>
+        <v>0.1400390726444159</v>
       </c>
       <c r="H2" t="n">
         <v>0.7166120797150832</v>
@@ -668,10 +668,10 @@
         <v>0.1467325311721351</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1573648151022616</v>
+        <v>0.1573648241743622</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1775298075696203</v>
+        <v>0.1775298224001822</v>
       </c>
       <c r="H3" t="n">
         <v>0.7455856917047092</v>
@@ -759,10 +759,10 @@
         <v>0.313998201622595</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1419277002486848</v>
+        <v>0.1419279000171653</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05491573579732845</v>
+        <v>0.05491595376520338</v>
       </c>
       <c r="H4" t="n">
         <v>1.753597408313792</v>
@@ -850,10 +850,10 @@
         <v>0.8938254607364218</v>
       </c>
       <c r="F5" t="n">
-        <v>1.07713806557835</v>
+        <v>1.077116590101312</v>
       </c>
       <c r="G5" t="n">
-        <v>0.784576932530652</v>
+        <v>0.7845630453968993</v>
       </c>
       <c r="H5" t="n">
         <v>7.107461973628843</v>
@@ -941,10 +941,10 @@
         <v>0.09137818446875293</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1153528592591858</v>
+        <v>0.1153528808962908</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1111403414535778</v>
+        <v>0.1111403729493941</v>
       </c>
       <c r="H6" t="n">
         <v>0.9001384470221278</v>
@@ -1032,10 +1032,10 @@
         <v>0.1636387163519396</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09213262856284368</v>
+        <v>0.09213263163930216</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1442557465663686</v>
+        <v>0.1442557739768458</v>
       </c>
       <c r="H7" t="n">
         <v>0.8514955388435604</v>
@@ -1123,10 +1123,10 @@
         <v>0.1736541581897918</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2376049682552512</v>
+        <v>0.2376049888306456</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1763318386041289</v>
+        <v>0.1763318582883934</v>
       </c>
       <c r="H8" t="n">
         <v>0.8218833647220964</v>
@@ -1214,10 +1214,10 @@
         <v>0.2666309112809248</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2812971012410094</v>
+        <v>0.2812971030545254</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2469102413904404</v>
+        <v>0.2469102482581059</v>
       </c>
       <c r="H9" t="n">
         <v>0.4755023523128038</v>
@@ -1301,10 +1301,10 @@
         <v>0.3247393788989229</v>
       </c>
       <c r="F10" t="n">
-        <v>0.308501760061826</v>
+        <v>0.3085017787144878</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4909539752890018</v>
+        <v>0.4909540193772712</v>
       </c>
       <c r="H10" t="n">
         <v>1.126897749532528</v>
@@ -1392,10 +1392,10 @@
         <v>0.03136588166417283</v>
       </c>
       <c r="F11" t="n">
-        <v>0.006335478397541333</v>
+        <v>0.006335482454821448</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003159282383521565</v>
+        <v>0.003159287104943196</v>
       </c>
       <c r="H11" t="n">
         <v>0.2600988575656265</v>
@@ -1483,10 +1483,10 @@
         <v>0.3050554147939886</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1756797636372625</v>
+        <v>0.1756797844410787</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4665940537865853</v>
+        <v>0.4665941072374336</v>
       </c>
       <c r="H12" t="n">
         <v>1.373425403558954</v>
@@ -1574,10 +1574,10 @@
         <v>0.1078043511487605</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08944856136092495</v>
+        <v>0.08944856859919559</v>
       </c>
       <c r="G13" t="n">
-        <v>0.09695015703106676</v>
+        <v>0.09695018629000249</v>
       </c>
       <c r="H13" t="n">
         <v>0.8934721382063724</v>
@@ -1665,10 +1665,10 @@
         <v>0.07905761631300896</v>
       </c>
       <c r="F14" t="n">
-        <v>0.243123914299106</v>
+        <v>0.2431239268906061</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07453067733107507</v>
+        <v>0.07453068819359338</v>
       </c>
       <c r="H14" t="n">
         <v>0.5768557783561169</v>
@@ -1756,10 +1756,10 @@
         <v>0.1192092154191906</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1194818276079066</v>
+        <v>0.1194818471064708</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03488176031903047</v>
+        <v>0.03488179007474622</v>
       </c>
       <c r="H15" t="n">
         <v>0.9740152227653087</v>
@@ -1847,10 +1847,10 @@
         <v>0.2120875018020139</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5672645296321478</v>
+        <v>0.5672645445490903</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2009399728488693</v>
+        <v>0.2009399902647157</v>
       </c>
       <c r="H16" t="n">
         <v>0.4381367147839849</v>
@@ -1934,10 +1934,10 @@
         <v>0.2160907278267805</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1305474070891448</v>
+        <v>0.1305474512840755</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05211856444568599</v>
+        <v>0.05211861221050579</v>
       </c>
       <c r="H17" t="n">
         <v>1.267429584043156</v>
@@ -2025,10 +2025,10 @@
         <v>0.64030076757404</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6334147036955725</v>
+        <v>0.6334147271751526</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7212781478056187</v>
+        <v>0.7212781824496957</v>
       </c>
       <c r="H18" t="n">
         <v>1.125928035226928</v>
@@ -2112,10 +2112,10 @@
         <v>0.1432952211848578</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1744901373815973</v>
+        <v>0.1744901483636978</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1694076912449964</v>
+        <v>0.1694077001538937</v>
       </c>
       <c r="H19" t="n">
         <v>0.5491815241612263</v>
@@ -2203,10 +2203,10 @@
         <v>0.1679186370778793</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3177717005346725</v>
+        <v>0.3177717463832374</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2585525221441749</v>
+        <v>0.2585525949178351</v>
       </c>
       <c r="H20" t="n">
         <v>1.089294365184146</v>
@@ -2294,10 +2294,10 @@
         <v>0.1959113675490289</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3072942669735372</v>
+        <v>0.3072943092144789</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2383820000216629</v>
+        <v>0.2383820560929755</v>
       </c>
       <c r="H21" t="n">
         <v>1.062546466477206</v>
@@ -2385,10 +2385,10 @@
         <v>0.3908363836904335</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3571123820132335</v>
+        <v>0.3571124160388545</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5607169233760476</v>
+        <v>0.560716996428976</v>
       </c>
       <c r="H22" t="n">
         <v>1.313835537124292</v>
@@ -2476,10 +2476,10 @@
         <v>0.05475782605272433</v>
       </c>
       <c r="F23" t="n">
-        <v>0.106701504780846</v>
+        <v>0.1067015024276023</v>
       </c>
       <c r="G23" t="n">
-        <v>0.06280291162765497</v>
+        <v>0.0628029259425547</v>
       </c>
       <c r="H23" t="n">
         <v>0.6014370052190726</v>
@@ -2567,10 +2567,10 @@
         <v>0.2203032240731948</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3549278531027266</v>
+        <v>0.3549278683596653</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2349687559732749</v>
+        <v>0.2349687770242841</v>
       </c>
       <c r="H24" t="n">
         <v>0.821026555289418</v>
@@ -2658,10 +2658,10 @@
         <v>0.08587497005443874</v>
       </c>
       <c r="F25" t="n">
-        <v>0.189696964757167</v>
+        <v>0.1896969874558544</v>
       </c>
       <c r="G25" t="n">
-        <v>0.07977923407374726</v>
+        <v>0.07977925622478291</v>
       </c>
       <c r="H25" t="n">
         <v>0.8337220581801408</v>
@@ -2749,10 +2749,10 @@
         <v>0.2162202262127234</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1058820209050863</v>
+        <v>0.1058820842209599</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03056958614848407</v>
+        <v>0.030569648360533</v>
       </c>
       <c r="H26" t="n">
         <v>1.470782642072603</v>
@@ -2840,10 +2840,10 @@
         <v>0.04623868421689228</v>
       </c>
       <c r="F27" t="n">
-        <v>0.04331180505959858</v>
+        <v>0.04331180491745713</v>
       </c>
       <c r="G27" t="n">
-        <v>0.03175851063359768</v>
+        <v>0.03175851567364049</v>
       </c>
       <c r="H27" t="n">
         <v>0.3074293300784401</v>
@@ -2931,10 +2931,10 @@
         <v>0.0861956375987431</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1826432065218835</v>
+        <v>0.1826432066121919</v>
       </c>
       <c r="G28" t="n">
-        <v>0.06945222718704025</v>
+        <v>0.06945223307838413</v>
       </c>
       <c r="H28" t="n">
         <v>0.3217073324512321</v>
@@ -3022,10 +3022,10 @@
         <v>0.03036483750533457</v>
       </c>
       <c r="F29" t="n">
-        <v>0.05504613382302184</v>
+        <v>0.05504613725488824</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03312565956983074</v>
+        <v>0.03312566231462633</v>
       </c>
       <c r="H29" t="n">
         <v>0.09125397575447609</v>
@@ -3113,10 +3113,10 @@
         <v>0.03221851295698297</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03938381638888737</v>
+        <v>0.0393838223659965</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02059666431109758</v>
+        <v>0.02059667152757904</v>
       </c>
       <c r="H30" t="n">
         <v>0.3364356123183577</v>
@@ -3204,10 +3204,10 @@
         <v>0.06482343969746326</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1087807638857484</v>
+        <v>0.1087807681972566</v>
       </c>
       <c r="G31" t="n">
-        <v>0.06964511772122746</v>
+        <v>0.06964512133161786</v>
       </c>
       <c r="H31" t="n">
         <v>0.1898985606099392</v>
@@ -3295,10 +3295,10 @@
         <v>0.03852836558066905</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07390302168492037</v>
+        <v>0.07390302492749348</v>
       </c>
       <c r="G32" t="n">
-        <v>0.03806254417138709</v>
+        <v>0.03806254976290487</v>
       </c>
       <c r="H32" t="n">
         <v>0.2272640433410283</v>
@@ -3386,10 +3386,10 @@
         <v>0.1940490257510064</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2591531886278792</v>
+        <v>0.259153224005454</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3397615516898658</v>
+        <v>0.339761599961465</v>
       </c>
       <c r="H33" t="n">
         <v>1.247560275116454</v>
@@ -3477,10 +3477,10 @@
         <v>0.04348458337406332</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01346906948871128</v>
+        <v>0.01346907431322228</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01403619999745217</v>
+        <v>0.01403620669519386</v>
       </c>
       <c r="H34" t="n">
         <v>0.463096312708327</v>
@@ -3568,10 +3568,10 @@
         <v>0.0259860054391326</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02253845990618396</v>
+        <v>0.02253846416659469</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02048879191160358</v>
+        <v>0.02048879720718558</v>
       </c>
       <c r="H35" t="n">
         <v>0.3093751617228926</v>
@@ -3659,10 +3659,10 @@
         <v>0.04638968454756125</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0163535838971354</v>
+        <v>0.01635358780568565</v>
       </c>
       <c r="G36" t="n">
-        <v>0.01218324244693524</v>
+        <v>0.01218325201718701</v>
       </c>
       <c r="H36" t="n">
         <v>0.4447191641064449</v>
@@ -3750,10 +3750,10 @@
         <v>0.08792673443779837</v>
       </c>
       <c r="F37" t="n">
-        <v>0.100946962285316</v>
+        <v>0.1009469725886986</v>
       </c>
       <c r="G37" t="n">
-        <v>0.08581322817038285</v>
+        <v>0.0858132376117228</v>
       </c>
       <c r="H37" t="n">
         <v>0.5039765573286296</v>
@@ -3841,10 +3841,10 @@
         <v>0.03567638319215124</v>
       </c>
       <c r="F38" t="n">
-        <v>0.007666460820901324</v>
+        <v>0.00766646736416937</v>
       </c>
       <c r="G38" t="n">
-        <v>0.006868611149209673</v>
+        <v>0.00686862154816409</v>
       </c>
       <c r="H38" t="n">
         <v>0.3771355762613469</v>
@@ -3932,10 +3932,10 @@
         <v>0.1183132221393223</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1580591804767361</v>
+        <v>0.158059197515376</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1571382293628559</v>
+        <v>0.1571382477854752</v>
       </c>
       <c r="H39" t="n">
         <v>0.7973738576699186</v>
@@ -4023,10 +4023,10 @@
         <v>0.4591292957244525</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8475628415509217</v>
+        <v>0.8475630726521852</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5455642074598317</v>
+        <v>0.545564436833207</v>
       </c>
       <c r="H40" t="n">
         <v>2.891582446522646</v>
@@ -4114,10 +4114,10 @@
         <v>0.09778313137220958</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1139819799079507</v>
+        <v>0.1139819738602772</v>
       </c>
       <c r="G41" t="n">
-        <v>0.07645372197028777</v>
+        <v>0.07645373973253095</v>
       </c>
       <c r="H41" t="n">
         <v>0.6797073731912212</v>
@@ -4205,10 +4205,10 @@
         <v>0.06041729594430501</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1435575817741239</v>
+        <v>0.1435575876224533</v>
       </c>
       <c r="G42" t="n">
-        <v>0.06958372192400065</v>
+        <v>0.06958372774369592</v>
       </c>
       <c r="H42" t="n">
         <v>0.2705128397863901</v>
@@ -4296,10 +4296,10 @@
         <v>0.3442702888129965</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3047263883142536</v>
+        <v>0.3047264049561575</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3248896993693345</v>
+        <v>0.3248897114670982</v>
       </c>
       <c r="H43" t="n">
         <v>0.5606279224051089</v>
@@ -4383,10 +4383,10 @@
         <v>0.1801894130515869</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4303237965188933</v>
+        <v>0.4303250134745844</v>
       </c>
       <c r="G44" t="n">
-        <v>0.07623190326256561</v>
+        <v>0.0762329505872211</v>
       </c>
       <c r="H44" t="n">
         <v>2.229510190828526</v>
@@ -4474,10 +4474,10 @@
         <v>0.03192361493182582</v>
       </c>
       <c r="F45" t="n">
-        <v>0.01936614899146277</v>
+        <v>0.01936615053964751</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02154673984353353</v>
+        <v>0.02154674223558054</v>
       </c>
       <c r="H45" t="n">
         <v>0.219637958318896</v>
@@ -4565,10 +4565,10 @@
         <v>0.02454787902311676</v>
       </c>
       <c r="F46" t="n">
-        <v>0.01845343295255689</v>
+        <v>0.01845343614192424</v>
       </c>
       <c r="G46" t="n">
-        <v>0.01729974555910638</v>
+        <v>0.01729974914431417</v>
       </c>
       <c r="H46" t="n">
         <v>0.2253013199805374</v>
@@ -4656,10 +4656,10 @@
         <v>0.05174559238114183</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0929386397926536</v>
+        <v>0.09293864197937197</v>
       </c>
       <c r="G47" t="n">
-        <v>0.03870416265059731</v>
+        <v>0.03870416641070391</v>
       </c>
       <c r="H47" t="n">
         <v>0.2500371999588092</v>
@@ -4747,10 +4747,10 @@
         <v>0.04583886555291042</v>
       </c>
       <c r="F48" t="n">
-        <v>0.05398308085058456</v>
+        <v>0.05398308160788012</v>
       </c>
       <c r="G48" t="n">
-        <v>0.04321498528053278</v>
+        <v>0.04321498853737334</v>
       </c>
       <c r="H48" t="n">
         <v>0.2334066842779279</v>
@@ -4838,10 +4838,10 @@
         <v>0.05564348626170174</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1793179169418565</v>
+        <v>0.179317927629405</v>
       </c>
       <c r="G49" t="n">
-        <v>0.05428570210519246</v>
+        <v>0.05428571473020685</v>
       </c>
       <c r="H49" t="n">
         <v>0.3379122681153697</v>
@@ -4929,10 +4929,10 @@
         <v>0.1774640663746824</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4038510420974185</v>
+        <v>0.4038510805080942</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2491540479599458</v>
+        <v>0.2491540847866877</v>
       </c>
       <c r="H50" t="n">
         <v>1.363451004429825</v>
@@ -5020,10 +5020,10 @@
         <v>0.1115520870578637</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1130308060538432</v>
+        <v>0.1130308119804937</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1141402275917825</v>
+        <v>0.1141402443308982</v>
       </c>
       <c r="H51" t="n">
         <v>0.670665120055479</v>
@@ -5111,10 +5111,10 @@
         <v>0.5757460453968697</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1434335287113982</v>
+        <v>0.1434336818139095</v>
       </c>
       <c r="G52" t="n">
-        <v>0.06545856645476436</v>
+        <v>0.06545887409551812</v>
       </c>
       <c r="H52" t="n">
         <v>2.498364972397039</v>
@@ -5202,10 +5202,10 @@
         <v>0.5198032238083613</v>
       </c>
       <c r="F53" t="n">
-        <v>0.382326291461463</v>
+        <v>0.3823268548098838</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2847844139064604</v>
+        <v>0.2847849757982353</v>
       </c>
       <c r="H53" t="n">
         <v>2.028441185139194</v>
@@ -5293,10 +5293,10 @@
         <v>0.1461670215316392</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2431414389419841</v>
+        <v>0.2431414379640667</v>
       </c>
       <c r="G54" t="n">
-        <v>0.1612973421204605</v>
+        <v>0.1612973517414728</v>
       </c>
       <c r="H54" t="n">
         <v>0.4376089963335965</v>
@@ -5384,10 +5384,10 @@
         <v>0.03958345147957278</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0479940251873797</v>
+        <v>0.04799402851400786</v>
       </c>
       <c r="G55" t="n">
-        <v>0.02055370868847309</v>
+        <v>0.02055371301835657</v>
       </c>
       <c r="H55" t="n">
         <v>0.236689300497001</v>
@@ -5475,10 +5475,10 @@
         <v>0.382411423631514</v>
       </c>
       <c r="F56" t="n">
-        <v>0.287288487169398</v>
+        <v>0.2872885036427356</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2544657841423403</v>
+        <v>0.2544658003741348</v>
       </c>
       <c r="H56" t="n">
         <v>0.6666406779747964</v>
@@ -5566,10 +5566,10 @@
         <v>0.100515956161974</v>
       </c>
       <c r="F57" t="n">
-        <v>0.09521977406248446</v>
+        <v>0.09521978077929036</v>
       </c>
       <c r="G57" t="n">
-        <v>0.08887672030661672</v>
+        <v>0.08887673068112426</v>
       </c>
       <c r="H57" t="n">
         <v>0.5431663794570629</v>
@@ -5657,10 +5657,10 @@
         <v>0.09084150395632271</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1934569082709603</v>
+        <v>0.193456926768778</v>
       </c>
       <c r="G58" t="n">
-        <v>0.126656721375907</v>
+        <v>0.1266567521439173</v>
       </c>
       <c r="H58" t="n">
         <v>0.9187102398267176</v>
@@ -5748,10 +5748,10 @@
         <v>0.002045224741455347</v>
       </c>
       <c r="F59" t="n">
-        <v>0.01161240889596611</v>
+        <v>0.01161240912094508</v>
       </c>
       <c r="G59" t="n">
-        <v>0.003430083554543807</v>
+        <v>0.003430083797853129</v>
       </c>
       <c r="H59" t="n">
         <v>0.006201137995202942</v>
@@ -5835,10 +5835,10 @@
         <v>0.5287418907149984</v>
       </c>
       <c r="F60" t="n">
-        <v>1.030351550415582</v>
+        <v>1.030351615500399</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8669611505019319</v>
+        <v>0.8669612099256673</v>
       </c>
       <c r="H60" t="n">
         <v>1.935074098502654</v>
@@ -5926,10 +5926,10 @@
         <v>0.3576351673817741</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5546181233245268</v>
+        <v>0.5546181699272787</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5171499157970105</v>
+        <v>0.5171499766514787</v>
       </c>
       <c r="H61" t="n">
         <v>1.482727576453942</v>
@@ -6017,10 +6017,10 @@
         <v>0.09822912572090017</v>
       </c>
       <c r="F62" t="n">
-        <v>0.08615999050911302</v>
+        <v>0.08616001049285782</v>
       </c>
       <c r="G62" t="n">
-        <v>0.1018971081825266</v>
+        <v>0.1018971910396627</v>
       </c>
       <c r="H62" t="n">
         <v>1.170048173221576</v>
@@ -6108,10 +6108,10 @@
         <v>0.07228009391647686</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1380224210042882</v>
+        <v>0.1380224318073058</v>
       </c>
       <c r="G63" t="n">
-        <v>0.07543652984507819</v>
+        <v>0.07543653946723078</v>
       </c>
       <c r="H63" t="n">
         <v>0.3847615424008634</v>
@@ -6199,10 +6199,10 @@
         <v>0.2384426269210413</v>
       </c>
       <c r="F64" t="n">
-        <v>0.2438753888014948</v>
+        <v>0.2438754000605045</v>
       </c>
       <c r="G64" t="n">
-        <v>0.3021856555868332</v>
+        <v>0.3021856899741042</v>
       </c>
       <c r="H64" t="n">
         <v>0.9613842667655157</v>
@@ -6290,10 +6290,10 @@
         <v>0.4151763266802893</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4879493971214461</v>
+        <v>0.4879494466561585</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5541226334982552</v>
+        <v>0.5541227011653553</v>
       </c>
       <c r="H65" t="n">
         <v>1.364498070866812</v>
@@ -6381,10 +6381,10 @@
         <v>0.1294012003798869</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2796813892801031</v>
+        <v>0.2796814332296188</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1571210200996109</v>
+        <v>0.157121059169276</v>
       </c>
       <c r="H66" t="n">
         <v>0.8762976441872627</v>
@@ -6472,10 +6472,10 @@
         <v>0.1181106148798783</v>
       </c>
       <c r="F67" t="n">
-        <v>0.03691938445856589</v>
+        <v>0.03691941172092143</v>
       </c>
       <c r="G67" t="n">
-        <v>0.02180494038786013</v>
+        <v>0.02180497634582821</v>
       </c>
       <c r="H67" t="n">
         <v>0.8890729753981951</v>
@@ -6563,10 +6563,10 @@
         <v>0.6967626147329891</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6062587935082824</v>
+        <v>0.6062587762442808</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6059161602749761</v>
+        <v>0.6059162098715113</v>
       </c>
       <c r="H68" t="n">
         <v>0.822053537981963</v>
@@ -6654,10 +6654,10 @@
         <v>0.04233260812396031</v>
       </c>
       <c r="F69" t="n">
-        <v>0.06302718278062479</v>
+        <v>0.06302718579308185</v>
       </c>
       <c r="G69" t="n">
-        <v>0.04504951444231538</v>
+        <v>0.04504951793631422</v>
       </c>
       <c r="H69" t="n">
         <v>0.1158922377181897</v>
@@ -6745,10 +6745,10 @@
         <v>0.1236753522000469</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1113282040033945</v>
+        <v>0.1113282116605571</v>
       </c>
       <c r="G70" t="n">
-        <v>0.1156167528527651</v>
+        <v>0.1156167595940635</v>
       </c>
       <c r="H70" t="n">
         <v>0.2999663024798833</v>
@@ -6836,10 +6836,10 @@
         <v>0.1076709468327376</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1349873389243418</v>
+        <v>0.1349873957491418</v>
       </c>
       <c r="G71" t="n">
-        <v>0.07994470141923268</v>
+        <v>0.079944758287669</v>
       </c>
       <c r="H71" t="n">
         <v>1.182881379043306</v>
@@ -6927,10 +6927,10 @@
         <v>0.9316682414789437</v>
       </c>
       <c r="F72" t="n">
-        <v>0.1395937281168461</v>
+        <v>0.1395975989892526</v>
       </c>
       <c r="G72" t="n">
-        <v>0.1833738750036863</v>
+        <v>0.1833782751147583</v>
       </c>
       <c r="H72" t="n">
         <v>4.167768298998758</v>
@@ -7018,10 +7018,10 @@
         <v>0.04036955990711219</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0231072509249596</v>
+        <v>0.0231072581365963</v>
       </c>
       <c r="G73" t="n">
-        <v>0.02036457786133488</v>
+        <v>0.020364603507702</v>
       </c>
       <c r="H73" t="n">
         <v>0.668404623200426</v>
@@ -7109,10 +7109,10 @@
         <v>0.07068272011491204</v>
       </c>
       <c r="F74" t="n">
-        <v>0.1386272802852584</v>
+        <v>0.1386272820896443</v>
       </c>
       <c r="G74" t="n">
-        <v>0.06505871611247036</v>
+        <v>0.06505872083983669</v>
       </c>
       <c r="H74" t="n">
         <v>0.3266677650070184</v>
@@ -7200,10 +7200,10 @@
         <v>0.4778745033745449</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4687750409265702</v>
+        <v>0.4687750654133777</v>
       </c>
       <c r="G75" t="n">
-        <v>0.4572430001447724</v>
+        <v>0.4572430322399906</v>
       </c>
       <c r="H75" t="n">
         <v>0.9493752443193544</v>
@@ -7291,10 +7291,10 @@
         <v>0.06571364627998162</v>
       </c>
       <c r="F76" t="n">
-        <v>0.05023924641571906</v>
+        <v>0.05023924867827139</v>
       </c>
       <c r="G76" t="n">
-        <v>0.04239929452702773</v>
+        <v>0.04239930400619293</v>
       </c>
       <c r="H76" t="n">
         <v>0.4181268703617883</v>
@@ -7382,10 +7382,10 @@
         <v>0.1804258979309288</v>
       </c>
       <c r="F77" t="n">
-        <v>0.08679804901368707</v>
+        <v>0.0867980355586728</v>
       </c>
       <c r="G77" t="n">
-        <v>0.05796260430067558</v>
+        <v>0.0579626271862215</v>
       </c>
       <c r="H77" t="n">
         <v>0.9740670823972597</v>
@@ -7473,10 +7473,10 @@
         <v>0.02573356602782632</v>
       </c>
       <c r="F78" t="n">
-        <v>0.03180019974772018</v>
+        <v>0.03180020358458894</v>
       </c>
       <c r="G78" t="n">
-        <v>0.01679729602538183</v>
+        <v>0.01679730265803739</v>
       </c>
       <c r="H78" t="n">
         <v>0.2724125086601074</v>
@@ -7564,10 +7564,10 @@
         <v>0.01414324716831614</v>
       </c>
       <c r="F79" t="n">
-        <v>0.02758503199957514</v>
+        <v>0.02758504248195386</v>
       </c>
       <c r="G79" t="n">
-        <v>0.01506284378545471</v>
+        <v>0.01506285574563983</v>
       </c>
       <c r="H79" t="n">
         <v>0.2823531843116658</v>
@@ -7655,10 +7655,10 @@
         <v>0.238598667621214</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1260361777125463</v>
+        <v>0.1260361984012641</v>
       </c>
       <c r="G80" t="n">
-        <v>0.2277751072159404</v>
+        <v>0.2277751361195661</v>
       </c>
       <c r="H80" t="n">
         <v>0.9166327752016876</v>
@@ -7746,10 +7746,10 @@
         <v>0.1850535555573287</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1537792968128227</v>
+        <v>0.1537793017001665</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1519475576872357</v>
+        <v>0.1519475677281417</v>
       </c>
       <c r="H81" t="n">
         <v>0.4638560507984801</v>
@@ -7837,10 +7837,10 @@
         <v>0.1867454436277563</v>
       </c>
       <c r="F82" t="n">
-        <v>0.09872815529090528</v>
+        <v>0.09872816318761739</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1317773973004435</v>
+        <v>0.1317774167889548</v>
       </c>
       <c r="H82" t="n">
         <v>0.7015311782717396</v>
@@ -7928,10 +7928,10 @@
         <v>0.1441034777410879</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1862702414531865</v>
+        <v>0.1862702558919239</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1408374915582134</v>
+        <v>0.1408375197216066</v>
       </c>
       <c r="H83" t="n">
         <v>0.7520441762890825</v>
@@ -8019,10 +8019,10 @@
         <v>0.06389656552322329</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1229021650545556</v>
+        <v>0.1229021731329112</v>
       </c>
       <c r="G84" t="n">
-        <v>0.04599844410388158</v>
+        <v>0.04599845336065581</v>
       </c>
       <c r="H84" t="n">
         <v>0.2231897293196931</v>
@@ -8110,10 +8110,10 @@
         <v>0.2058105708765144</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1738792722529016</v>
+        <v>0.1738792950713167</v>
       </c>
       <c r="G85" t="n">
-        <v>0.05044381014536069</v>
+        <v>0.05044383135062347</v>
       </c>
       <c r="H85" t="n">
         <v>0.9954997516854572</v>
@@ -8201,10 +8201,10 @@
         <v>0.2266939034529027</v>
       </c>
       <c r="F86" t="n">
-        <v>0.3971355277028613</v>
+        <v>0.3971354999046038</v>
       </c>
       <c r="G86" t="n">
-        <v>0.263134582497879</v>
+        <v>0.2631346074869656</v>
       </c>
       <c r="H86" t="n">
         <v>0.7662289278414284</v>
@@ -8292,10 +8292,10 @@
         <v>0.112450366577684</v>
       </c>
       <c r="F87" t="n">
-        <v>0.112438900029015</v>
+        <v>0.1124389031926789</v>
       </c>
       <c r="G87" t="n">
-        <v>0.1255143654652407</v>
+        <v>0.1255143831906435</v>
       </c>
       <c r="H87" t="n">
         <v>0.6211718381693592</v>
@@ -8383,10 +8383,10 @@
         <v>0.1468791610224586</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1837310097084097</v>
+        <v>0.1837310280784069</v>
       </c>
       <c r="G88" t="n">
-        <v>0.1424008683056959</v>
+        <v>0.1424008878147927</v>
       </c>
       <c r="H88" t="n">
         <v>0.5425971346865082</v>
@@ -8474,10 +8474,10 @@
         <v>0.08795776493967382</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1275708032778044</v>
+        <v>0.1275708098222418</v>
       </c>
       <c r="G89" t="n">
-        <v>0.09447344937759243</v>
+        <v>0.0944734550986594</v>
       </c>
       <c r="H89" t="n">
         <v>0.190759435338714</v>
@@ -8565,10 +8565,10 @@
         <v>0.08845743782659278</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1385606590994197</v>
+        <v>0.1385606646733512</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0865845757669616</v>
+        <v>0.08658458350994461</v>
       </c>
       <c r="H90" t="n">
         <v>0.4537308513006609</v>
@@ -8656,10 +8656,10 @@
         <v>0.155149130453718</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1264489514266609</v>
+        <v>0.1264489626935457</v>
       </c>
       <c r="G91" t="n">
-        <v>0.08279291411922507</v>
+        <v>0.08279293124880685</v>
       </c>
       <c r="H91" t="n">
         <v>0.6277099064094847</v>
@@ -8747,10 +8747,10 @@
         <v>0.3681962388429534</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1236447565676127</v>
+        <v>0.1236447422801688</v>
       </c>
       <c r="G92" t="n">
-        <v>0.07722032133719388</v>
+        <v>0.07722040900588766</v>
       </c>
       <c r="H92" t="n">
         <v>1.486341126158328</v>
@@ -8838,10 +8838,10 @@
         <v>0.1396814974513654</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1509017704730491</v>
+        <v>0.1509017732246477</v>
       </c>
       <c r="G93" t="n">
-        <v>0.1226821766423035</v>
+        <v>0.1226821874121262</v>
       </c>
       <c r="H93" t="n">
         <v>0.575614988254466</v>
@@ -8929,10 +8929,10 @@
         <v>0.3126300896715725</v>
       </c>
       <c r="F94" t="n">
-        <v>0.2512767817324205</v>
+        <v>0.2512768139179933</v>
       </c>
       <c r="G94" t="n">
-        <v>0.4659309483618734</v>
+        <v>0.4659309995229346</v>
       </c>
       <c r="H94" t="n">
         <v>1.236937243017472</v>
@@ -9020,10 +9020,10 @@
         <v>0.0638123239152574</v>
       </c>
       <c r="F95" t="n">
-        <v>0.18267413818875</v>
+        <v>0.1826741599737865</v>
       </c>
       <c r="G95" t="n">
-        <v>0.05751738667158389</v>
+        <v>0.05751739863306474</v>
       </c>
       <c r="H95" t="n">
         <v>0.5594639660662479</v>
@@ -9111,10 +9111,10 @@
         <v>0.2247824687911161</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1204703373663014</v>
+        <v>0.1204703072800358</v>
       </c>
       <c r="G96" t="n">
-        <v>0.04631349375353633</v>
+        <v>0.04631353435453027</v>
       </c>
       <c r="H96" t="n">
         <v>1.284271140273298</v>
@@ -9202,10 +9202,10 @@
         <v>0.05691390605230952</v>
       </c>
       <c r="F97" t="n">
-        <v>0.1835927197368755</v>
+        <v>0.1835927285279103</v>
       </c>
       <c r="G97" t="n">
-        <v>0.04809851057485914</v>
+        <v>0.0480985175036994</v>
       </c>
       <c r="H97" t="n">
         <v>0.2177031397462812</v>
@@ -9293,10 +9293,10 @@
         <v>0.2236513630438572</v>
       </c>
       <c r="F98" t="n">
-        <v>0.2707490502261118</v>
+        <v>0.2707490597345543</v>
       </c>
       <c r="G98" t="n">
-        <v>0.2638116164380204</v>
+        <v>0.2638116311229052</v>
       </c>
       <c r="H98" t="n">
         <v>0.7651940787133369</v>
@@ -9384,10 +9384,10 @@
         <v>0.1102132991859153</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2394548509284524</v>
+        <v>0.2394548926561686</v>
       </c>
       <c r="G99" t="n">
-        <v>0.1344856736544428</v>
+        <v>0.1344857095114406</v>
       </c>
       <c r="H99" t="n">
         <v>0.9127531883440781</v>
@@ -9475,10 +9475,10 @@
         <v>0.1570934386527884</v>
       </c>
       <c r="F100" t="n">
-        <v>0.5242744079697134</v>
+        <v>0.5242744569073967</v>
       </c>
       <c r="G100" t="n">
-        <v>0.2277043430529767</v>
+        <v>0.2277043817293981</v>
       </c>
       <c r="H100" t="n">
         <v>1.04262150654369</v>
@@ -9566,10 +9566,10 @@
         <v>0.09003259155030501</v>
       </c>
       <c r="F101" t="n">
-        <v>0.1733703548482827</v>
+        <v>0.1733703766554069</v>
       </c>
       <c r="G101" t="n">
-        <v>0.05422874891323599</v>
+        <v>0.05422877064175191</v>
       </c>
       <c r="H101" t="n">
         <v>0.4678895287272094</v>
@@ -9657,10 +9657,10 @@
         <v>0.01400818481728265</v>
       </c>
       <c r="F102" t="n">
-        <v>0.02687532904477473</v>
+        <v>0.02687533143881958</v>
       </c>
       <c r="G102" t="n">
-        <v>0.01773998700395731</v>
+        <v>0.01773998963467797</v>
       </c>
       <c r="H102" t="n">
         <v>0.1147432029708231</v>
@@ -9748,10 +9748,10 @@
         <v>1.581580416673479</v>
       </c>
       <c r="F103" t="n">
-        <v>1.278618643667651</v>
+        <v>1.277735089320522</v>
       </c>
       <c r="G103" t="n">
-        <v>1.292698938084762</v>
+        <v>1.292397975605213</v>
       </c>
       <c r="H103" t="n">
         <v>13.40409564039896</v>
@@ -9839,10 +9839,10 @@
         <v>0.07022701871687015</v>
       </c>
       <c r="F104" t="n">
-        <v>0.02971926021924808</v>
+        <v>0.02971926623301586</v>
       </c>
       <c r="G104" t="n">
-        <v>0.01625670772907324</v>
+        <v>0.01625671930986485</v>
       </c>
       <c r="H104" t="n">
         <v>0.3786825381440391</v>
@@ -9930,10 +9930,10 @@
         <v>0.2389954831576384</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1588875607613346</v>
+        <v>0.1588875832806832</v>
       </c>
       <c r="G105" t="n">
-        <v>0.303290578719158</v>
+        <v>0.303290637923062</v>
       </c>
       <c r="H105" t="n">
         <v>1.33446238571039</v>
@@ -10021,10 +10021,10 @@
         <v>0.003903726054257696</v>
       </c>
       <c r="F106" t="n">
-        <v>0.002567539863701115</v>
+        <v>0.00256754203938992</v>
       </c>
       <c r="G106" t="n">
-        <v>0.002744425647463013</v>
+        <v>0.0027444286909228</v>
       </c>
       <c r="H106" t="n">
         <v>0.2493107544939339</v>
@@ -10112,10 +10112,10 @@
         <v>0.003462519821082707</v>
       </c>
       <c r="F107" t="n">
-        <v>0.002070748508195912</v>
+        <v>0.002070749657900144</v>
       </c>
       <c r="G107" t="n">
-        <v>0.002337790536656086</v>
+        <v>0.002337794684092714</v>
       </c>
       <c r="H107" t="n">
         <v>0.2431184488471118</v>
@@ -10203,10 +10203,10 @@
         <v>0.008195547529182877</v>
       </c>
       <c r="F108" t="n">
-        <v>0.003549544296572218</v>
+        <v>0.003549546306436448</v>
       </c>
       <c r="G108" t="n">
-        <v>0.002961112162262018</v>
+        <v>0.002961116073382836</v>
       </c>
       <c r="H108" t="n">
         <v>0.2447316180012817</v>
@@ -10294,10 +10294,10 @@
         <v>0.0229287772940192</v>
       </c>
       <c r="F109" t="n">
-        <v>0.009427338787905332</v>
+        <v>0.009427342827301241</v>
       </c>
       <c r="G109" t="n">
-        <v>0.005634847864555317</v>
+        <v>0.005634852582150887</v>
       </c>
       <c r="H109" t="n">
         <v>0.2967165783205413</v>
@@ -10385,10 +10385,10 @@
         <v>0.009136679650261695</v>
       </c>
       <c r="F110" t="n">
-        <v>0.006034507346243276</v>
+        <v>0.006034511699066506</v>
       </c>
       <c r="G110" t="n">
-        <v>0.003905238283342884</v>
+        <v>0.00390524413825604</v>
       </c>
       <c r="H110" t="n">
         <v>0.2496204874837848</v>
@@ -10476,10 +10476,10 @@
         <v>0.01449679666553838</v>
       </c>
       <c r="F111" t="n">
-        <v>0.006128637276738195</v>
+        <v>0.006128649794285152</v>
       </c>
       <c r="G111" t="n">
-        <v>0.007122449146175676</v>
+        <v>0.007122468771629018</v>
       </c>
       <c r="H111" t="n">
         <v>0.4667631816385235</v>
@@ -10567,10 +10567,10 @@
         <v>0.147447388732114</v>
       </c>
       <c r="F112" t="n">
-        <v>0.05842328861639837</v>
+        <v>0.05842332243852807</v>
       </c>
       <c r="G112" t="n">
-        <v>0.04556778637263123</v>
+        <v>0.04556782809660388</v>
       </c>
       <c r="H112" t="n">
         <v>0.9342361934783976</v>
@@ -10658,10 +10658,10 @@
         <v>0.2286475797645283</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0295903256503137</v>
+        <v>0.02959033678276873</v>
       </c>
       <c r="G113" t="n">
-        <v>0.022867940537699</v>
+        <v>0.02286796641940448</v>
       </c>
       <c r="H113" t="n">
         <v>1.084354343907561</v>
@@ -10749,10 +10749,10 @@
         <v>0.0827735265571856</v>
       </c>
       <c r="F114" t="n">
-        <v>0.06501121197298165</v>
+        <v>0.06501121579889166</v>
       </c>
       <c r="G114" t="n">
-        <v>0.05187494477529539</v>
+        <v>0.05187495246131572</v>
       </c>
       <c r="H114" t="n">
         <v>0.2052640089593039</v>
@@ -10840,10 +10840,10 @@
         <v>0.1884899539434938</v>
       </c>
       <c r="F115" t="n">
-        <v>0.095975282564396</v>
+        <v>0.09597528307177164</v>
       </c>
       <c r="G115" t="n">
-        <v>0.1286399757668549</v>
+        <v>0.1286399983643523</v>
       </c>
       <c r="H115" t="n">
         <v>0.745973544696887</v>
@@ -10931,10 +10931,10 @@
         <v>0.2161324775894491</v>
       </c>
       <c r="F116" t="n">
-        <v>0.1430504284929129</v>
+        <v>0.1430504572892343</v>
       </c>
       <c r="G116" t="n">
-        <v>0.1026486004329924</v>
+        <v>0.1026486248074793</v>
       </c>
       <c r="H116" t="n">
         <v>0.8791106428021422</v>
@@ -11022,10 +11022,10 @@
         <v>0.01874731439354337</v>
       </c>
       <c r="F117" t="n">
-        <v>0.01717630988365427</v>
+        <v>0.01717631079170108</v>
       </c>
       <c r="G117" t="n">
-        <v>0.01512689717165412</v>
+        <v>0.01512689979810011</v>
       </c>
       <c r="H117" t="n">
         <v>0.2183882729589028</v>
@@ -11113,10 +11113,10 @@
         <v>0.009061516450549619</v>
       </c>
       <c r="F118" t="n">
-        <v>0.01008626667992845</v>
+        <v>0.01008626824784472</v>
       </c>
       <c r="G118" t="n">
-        <v>0.007653461075037736</v>
+        <v>0.007653463469987432</v>
       </c>
       <c r="H118" t="n">
         <v>0.1647401054134016</v>
@@ -11204,10 +11204,10 @@
         <v>0.01964576803818497</v>
       </c>
       <c r="F119" t="n">
-        <v>0.01577672210436288</v>
+        <v>0.01577672484035846</v>
       </c>
       <c r="G119" t="n">
-        <v>0.009606417163219506</v>
+        <v>0.009606419944413629</v>
       </c>
       <c r="H119" t="n">
         <v>0.1959608041850188</v>
@@ -11295,10 +11295,10 @@
         <v>0.09221646573179659</v>
       </c>
       <c r="F120" t="n">
-        <v>0.1294307936834268</v>
+        <v>0.1294307987901991</v>
       </c>
       <c r="G120" t="n">
-        <v>0.09627477826946783</v>
+        <v>0.09627478451649035</v>
       </c>
       <c r="H120" t="n">
         <v>0.2169573885097784</v>
@@ -11386,10 +11386,10 @@
         <v>0.01809470170044845</v>
       </c>
       <c r="F121" t="n">
-        <v>0.02255881004644447</v>
+        <v>0.02255881370627735</v>
       </c>
       <c r="G121" t="n">
-        <v>0.01457183946276761</v>
+        <v>0.01457184340721434</v>
       </c>
       <c r="H121" t="n">
         <v>0.1861185602553873</v>
@@ -11477,10 +11477,10 @@
         <v>0.04967587733612646</v>
       </c>
       <c r="F122" t="n">
-        <v>0.03890910685417902</v>
+        <v>0.03890910910015466</v>
       </c>
       <c r="G122" t="n">
-        <v>0.03667968206703212</v>
+        <v>0.03667968735316986</v>
       </c>
       <c r="H122" t="n">
         <v>0.278485987840173</v>
@@ -11568,10 +11568,10 @@
         <v>0.1381698460164195</v>
       </c>
       <c r="F123" t="n">
-        <v>0.2073808365177841</v>
+        <v>0.2073808378199536</v>
       </c>
       <c r="G123" t="n">
-        <v>0.138855547354429</v>
+        <v>0.1388555602519722</v>
       </c>
       <c r="H123" t="n">
         <v>0.4358591106778351</v>
@@ -11659,10 +11659,10 @@
         <v>0.06696826455044233</v>
       </c>
       <c r="F124" t="n">
-        <v>0.05689703393935722</v>
+        <v>0.05689703599904646</v>
       </c>
       <c r="G124" t="n">
-        <v>0.06124543306164329</v>
+        <v>0.06124543786926742</v>
       </c>
       <c r="H124" t="n">
         <v>0.2375175161157313</v>
@@ -11750,10 +11750,10 @@
         <v>0.07652871069541536</v>
       </c>
       <c r="F125" t="n">
-        <v>0.06384417130343652</v>
+        <v>0.06384418923809534</v>
       </c>
       <c r="G125" t="n">
-        <v>0.03258321381367214</v>
+        <v>0.03258323150260768</v>
       </c>
       <c r="H125" t="n">
         <v>0.5139083244130161</v>
@@ -11841,10 +11841,10 @@
         <v>0.3256464167387856</v>
       </c>
       <c r="F126" t="n">
-        <v>0.6727522289968535</v>
+        <v>0.6727522773730734</v>
       </c>
       <c r="G126" t="n">
-        <v>0.3375657558032504</v>
+        <v>0.3375658125797012</v>
       </c>
       <c r="H126" t="n">
         <v>1.052655847663158</v>
@@ -11932,10 +11932,10 @@
         <v>0.05205516902535588</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0477515975066941</v>
+        <v>0.0477516000263609</v>
       </c>
       <c r="G127" t="n">
-        <v>0.03778689535253126</v>
+        <v>0.03778690027441944</v>
       </c>
       <c r="H127" t="n">
         <v>0.2993369040417522</v>
@@ -12023,10 +12023,10 @@
         <v>0.2364746105131447</v>
       </c>
       <c r="F128" t="n">
-        <v>0.3231363996707271</v>
+        <v>0.3231364362126281</v>
       </c>
       <c r="G128" t="n">
-        <v>0.2885524714865467</v>
+        <v>0.2885525063476767</v>
       </c>
       <c r="H128" t="n">
         <v>1.006886985595747</v>
@@ -12114,10 +12114,10 @@
         <v>0.01404682664169479</v>
       </c>
       <c r="F129" t="n">
-        <v>0.02230769985141002</v>
+        <v>0.02230770290649821</v>
       </c>
       <c r="G129" t="n">
-        <v>0.01395673740741249</v>
+        <v>0.01395674153317657</v>
       </c>
       <c r="H129" t="n">
         <v>0.129182604735649</v>
@@ -12205,10 +12205,10 @@
         <v>0.2825370106397438</v>
       </c>
       <c r="F130" t="n">
-        <v>0.1637980018307499</v>
+        <v>0.1637980136788706</v>
       </c>
       <c r="G130" t="n">
-        <v>0.2343844772776312</v>
+        <v>0.2343844979357377</v>
       </c>
       <c r="H130" t="n">
         <v>0.7778554304874405</v>
@@ -12296,10 +12296,10 @@
         <v>0.07671664578867474</v>
       </c>
       <c r="F131" t="n">
-        <v>0.1497395030858048</v>
+        <v>0.1497395132029042</v>
       </c>
       <c r="G131" t="n">
-        <v>0.080429094745254</v>
+        <v>0.08042910193524888</v>
       </c>
       <c r="H131" t="n">
         <v>0.3482352089914686</v>
@@ -12387,10 +12387,10 @@
         <v>0.09241961747205141</v>
       </c>
       <c r="F132" t="n">
-        <v>0.1619272377675503</v>
+        <v>0.1619272524291063</v>
       </c>
       <c r="G132" t="n">
-        <v>0.08525566519149724</v>
+        <v>0.08525567358200996</v>
       </c>
       <c r="H132" t="n">
         <v>0.5850765240017057</v>
@@ -12478,10 +12478,10 @@
         <v>0.1665759667256722</v>
       </c>
       <c r="F133" t="n">
-        <v>0.4829359857889134</v>
+        <v>0.4829360777201449</v>
       </c>
       <c r="G133" t="n">
-        <v>0.2793887409357622</v>
+        <v>0.2793888278313847</v>
       </c>
       <c r="H133" t="n">
         <v>1.40754481138985</v>
@@ -12569,10 +12569,10 @@
         <v>0.2225362651727793</v>
       </c>
       <c r="F134" t="n">
-        <v>0.08923385197820913</v>
+        <v>0.08923388626328596</v>
       </c>
       <c r="G134" t="n">
-        <v>0.2926566267244143</v>
+        <v>0.2926567027267167</v>
       </c>
       <c r="H134" t="n">
         <v>1.310460382339101</v>
@@ -12660,10 +12660,10 @@
         <v>0.1894000350173234</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1348361186767563</v>
+        <v>0.1348361291519312</v>
       </c>
       <c r="G135" t="n">
-        <v>0.1481791784382658</v>
+        <v>0.1481791939828249</v>
       </c>
       <c r="H135" t="n">
         <v>0.7232811916098527</v>
@@ -12751,10 +12751,10 @@
         <v>0.2435661535021833</v>
       </c>
       <c r="F136" t="n">
-        <v>0.1627989797773725</v>
+        <v>0.1627990067419064</v>
       </c>
       <c r="G136" t="n">
-        <v>0.275619918385709</v>
+        <v>0.2756199639496786</v>
       </c>
       <c r="H136" t="n">
         <v>1.245537054766756</v>
@@ -12842,10 +12842,10 @@
         <v>0.1788194337159455</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1333808554548116</v>
+        <v>0.1333808618288841</v>
       </c>
       <c r="G137" t="n">
-        <v>0.1541852170912223</v>
+        <v>0.1541852293420014</v>
       </c>
       <c r="H137" t="n">
         <v>0.6575556533639743</v>
@@ -12933,10 +12933,10 @@
         <v>0.1196984841591649</v>
       </c>
       <c r="F138" t="n">
-        <v>1.001696572773989</v>
+        <v>1.001696631873696</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2352065092399827</v>
+        <v>0.2352065499382154</v>
       </c>
       <c r="H138" t="n">
         <v>1.272182588215972</v>
@@ -13024,10 +13024,10 @@
         <v>0.1170661748165055</v>
       </c>
       <c r="F139" t="n">
-        <v>0.1729284444312357</v>
+        <v>0.1729284475495815</v>
       </c>
       <c r="G139" t="n">
-        <v>0.09222640954862085</v>
+        <v>0.09222641480147908</v>
       </c>
       <c r="H139" t="n">
         <v>0.4595522319585266</v>
@@ -13115,10 +13115,10 @@
         <v>0.6271805761179865</v>
       </c>
       <c r="F140" t="n">
-        <v>0.3444718552330144</v>
+        <v>0.3444720903685026</v>
       </c>
       <c r="G140" t="n">
-        <v>0.2547595111969015</v>
+        <v>0.2547601048684854</v>
       </c>
       <c r="H140" t="n">
         <v>2.199285093667711</v>
@@ -13206,10 +13206,10 @@
         <v>0.1159372083374286</v>
       </c>
       <c r="F141" t="n">
-        <v>0.09258465912369279</v>
+        <v>0.092584640881574</v>
       </c>
       <c r="G141" t="n">
-        <v>0.07558486367840019</v>
+        <v>0.07558489368647045</v>
       </c>
       <c r="H141" t="n">
         <v>1.034221944058446</v>
@@ -13297,10 +13297,10 @@
         <v>0.4751017764463643</v>
       </c>
       <c r="F142" t="n">
-        <v>0.2117382522170572</v>
+        <v>0.211738264644283</v>
       </c>
       <c r="G142" t="n">
-        <v>0.06111396606437294</v>
+        <v>0.06111400872981042</v>
       </c>
       <c r="H142" t="n">
         <v>1.568007141874413</v>
@@ -13388,10 +13388,10 @@
         <v>0.2612831845767706</v>
       </c>
       <c r="F143" t="n">
-        <v>0.1735547947539693</v>
+        <v>0.1735547986916973</v>
       </c>
       <c r="G143" t="n">
-        <v>0.169140188527995</v>
+        <v>0.1691401972767189</v>
       </c>
       <c r="H143" t="n">
         <v>0.3989257195156556</v>
@@ -13475,10 +13475,10 @@
         <v>0.1337120246751101</v>
       </c>
       <c r="F144" t="n">
-        <v>0.07513908384716733</v>
+        <v>0.07513910876814404</v>
       </c>
       <c r="G144" t="n">
-        <v>0.03954289101888558</v>
+        <v>0.03954291976834542</v>
       </c>
       <c r="H144" t="n">
         <v>0.9837663146858279</v>
@@ -13566,10 +13566,10 @@
         <v>0.1265298485155069</v>
       </c>
       <c r="F145" t="n">
-        <v>0.1434345429253467</v>
+        <v>0.143434537068119</v>
       </c>
       <c r="G145" t="n">
-        <v>0.1258605961919481</v>
+        <v>0.1258606154272406</v>
       </c>
       <c r="H145" t="n">
         <v>0.7490184834473188</v>
@@ -13657,10 +13657,10 @@
         <v>0.1219578055977806</v>
       </c>
       <c r="F146" t="n">
-        <v>0.2105031452254743</v>
+        <v>0.2105031570042323</v>
       </c>
       <c r="G146" t="n">
-        <v>0.1163385721003859</v>
+        <v>0.1163385888055059</v>
       </c>
       <c r="H146" t="n">
         <v>0.7619135220461626</v>
@@ -13748,10 +13748,10 @@
         <v>0.1337151129423892</v>
       </c>
       <c r="F147" t="n">
-        <v>0.08397766131928372</v>
+        <v>0.08397766681681898</v>
       </c>
       <c r="G147" t="n">
-        <v>0.1015613734751795</v>
+        <v>0.1015613853822166</v>
       </c>
       <c r="H147" t="n">
         <v>0.7272922710971119</v>
@@ -13839,10 +13839,10 @@
         <v>0.1367483991725467</v>
       </c>
       <c r="F148" t="n">
-        <v>0.3122949767513783</v>
+        <v>0.312294988252446</v>
       </c>
       <c r="G148" t="n">
-        <v>0.1279130184091268</v>
+        <v>0.1279130289170497</v>
       </c>
       <c r="H148" t="n">
         <v>0.4845021405176518</v>
@@ -13930,10 +13930,10 @@
         <v>0.241331831114811</v>
       </c>
       <c r="F149" t="n">
-        <v>0.1973063816292741</v>
+        <v>0.1973063851018139</v>
       </c>
       <c r="G149" t="n">
-        <v>0.1805939988813581</v>
+        <v>0.1805940064143288</v>
       </c>
       <c r="H149" t="n">
         <v>0.4204852656376782</v>
@@ -14021,10 +14021,10 @@
         <v>0.07834503336702708</v>
       </c>
       <c r="F150" t="n">
-        <v>0.1772166013950209</v>
+        <v>0.1772166105656603</v>
       </c>
       <c r="G150" t="n">
-        <v>0.07412487343656173</v>
+        <v>0.0741248824099774</v>
       </c>
       <c r="H150" t="n">
         <v>0.3367819149821296</v>

--- a/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
+++ b/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
@@ -2087,10 +2087,10 @@
         <v>0.09293681618496408</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>0.3622193416706191</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="19">
@@ -5810,7 +5810,7 @@
         <v>0.009230255466642488</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>0.2482240629063026</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -13905,7 +13905,7 @@
         <v>0.2444793042576891</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>0.01969552426254956</v>
       </c>
       <c r="AC148" t="n">
         <v>0.1428571428571428</v>

--- a/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
+++ b/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
@@ -9554,88 +9554,88 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>10.92774024835316</v>
+        <v>1.279760791213202</v>
       </c>
       <c r="C101" t="n">
-        <v>10.65807978599021</v>
+        <v>1.255553344220396</v>
       </c>
       <c r="D101" t="n">
-        <v>1.641143427548982</v>
+        <v>0.5276659040889232</v>
       </c>
       <c r="E101" t="n">
-        <v>1.581580416673479</v>
+        <v>0.5172632476958068</v>
       </c>
       <c r="F101" t="n">
-        <v>1.277735089320379</v>
+        <v>0.3201913892413951</v>
       </c>
       <c r="G101" t="n">
-        <v>1.292397975605228</v>
+        <v>0.3453364852878835</v>
       </c>
       <c r="H101" t="n">
-        <v>13.40409564039896</v>
+        <v>2.029460048637381</v>
       </c>
       <c r="I101" t="n">
-        <v>12.82854672118702</v>
+        <v>2.055861454624757</v>
       </c>
       <c r="J101" t="n">
-        <v>4.175688026156342</v>
+        <v>1.385904764890303</v>
       </c>
       <c r="K101" t="n">
-        <v>4.146832406273914</v>
+        <v>1.200377348323862</v>
       </c>
       <c r="L101" t="n">
-        <v>0.233075422137223</v>
+        <v>2.758357898540478</v>
       </c>
       <c r="M101" t="n">
-        <v>0.1942530625767057</v>
+        <v>2.867950817169004</v>
       </c>
       <c r="N101" t="n">
-        <v>0.9299110110853639</v>
+        <v>0.9239818202435618</v>
       </c>
       <c r="O101" t="n">
-        <v>0.9237387140813667</v>
+        <v>0.912141377651869</v>
       </c>
       <c r="P101" t="n">
-        <v>0.03933279113409365</v>
+        <v>0.5215875085852623</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.04600312568793574</v>
+        <v>0.5105591663139327</v>
       </c>
       <c r="R101" t="n">
-        <v>347.0233764045531</v>
+        <v>28.28160030708699</v>
       </c>
       <c r="S101" t="n">
-        <v>317.9583438867255</v>
+        <v>30.45870415093044</v>
       </c>
       <c r="T101" t="n">
-        <v>0.9333797658356822</v>
+        <v>0.9947237430837617</v>
       </c>
       <c r="U101" t="n">
         <v>1</v>
       </c>
       <c r="V101" t="n">
-        <v>1.004094196054909</v>
+        <v>1.014016365397673</v>
       </c>
       <c r="W101" t="n">
-        <v>1.005043833147337</v>
+        <v>1.013484922788592</v>
       </c>
       <c r="X101" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="Y101" t="n">
-        <v>18.3304796368036</v>
+        <v>4.343920701537407</v>
       </c>
       <c r="Z101" t="n">
-        <v>17.41288271073222</v>
+        <v>4.609640689229552</v>
       </c>
       <c r="AA101" t="n">
-        <v>0.1138608317178825</v>
+        <v>0.06895988746928795</v>
       </c>
       <c r="AB101" t="n">
-        <v>0.1635946369790653</v>
+        <v>0.1594215066973216</v>
       </c>
       <c r="AC101" t="n">
-        <v>0.1425</v>
+        <v>0.1407035175879397</v>
       </c>
     </row>
     <row r="102">

--- a/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
+++ b/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
@@ -565,22 +565,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1579117507680596</v>
+        <v>0.1564542754725723</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1740679758248979</v>
+        <v>0.1727979785462384</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2057238869812682</v>
+        <v>0.2062075910944513</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1720860246432098</v>
+        <v>0.1718111595107314</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1273740542584842</v>
+        <v>0.126559822087519</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1400390726444159</v>
+        <v>0.1377741904634835</v>
       </c>
       <c r="H2" t="n">
         <v>0.7166120797150832</v>
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2043305030917656</v>
+        <v>0.2035934772675008</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1965886852111632</v>
+        <v>0.1956305041645806</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1476844369546735</v>
+        <v>0.1474645064903849</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1467325311721351</v>
+        <v>0.1469008933607462</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1573648241743622</v>
+        <v>0.1563752072998496</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1775298224001822</v>
+        <v>0.1760769615457662</v>
       </c>
       <c r="H3" t="n">
         <v>0.7455856917047092</v>
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.014118759408285</v>
+        <v>1.006133780202406</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9638252520237753</v>
+        <v>0.9557259856948994</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3127347675843605</v>
+        <v>0.3069261954638245</v>
       </c>
       <c r="E4" t="n">
-        <v>0.313998201622595</v>
+        <v>0.3089492053511059</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1419279000171653</v>
+        <v>0.1357193355120803</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05491595376520338</v>
+        <v>0.04853382749492939</v>
       </c>
       <c r="H4" t="n">
         <v>1.753597408313792</v>
@@ -838,22 +838,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.094804944706176</v>
+        <v>6.025081420096317</v>
       </c>
       <c r="C5" t="n">
-        <v>7.8121960354921</v>
+        <v>7.742741003733363</v>
       </c>
       <c r="D5" t="n">
-        <v>1.415498204403719</v>
+        <v>1.333676076948186</v>
       </c>
       <c r="E5" t="n">
-        <v>1.657163376752953</v>
+        <v>1.571568005711917</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8255153910616979</v>
+        <v>0.3441381870592167</v>
       </c>
       <c r="G5" t="n">
-        <v>1.300082273967572</v>
+        <v>0.6505307457453205</v>
       </c>
       <c r="H5" t="n">
         <v>6.929448083639498</v>
@@ -929,22 +929,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3132039402088189</v>
+        <v>0.3110932880698722</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3506631218404138</v>
+        <v>0.3484502322206205</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09710073730632504</v>
+        <v>0.09726754896629644</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09137818446875293</v>
+        <v>0.09117061356504343</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1153528808962908</v>
+        <v>0.113410322628134</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1111403729493941</v>
+        <v>0.1087691114656592</v>
       </c>
       <c r="H6" t="n">
         <v>0.9001384470221278</v>
@@ -1020,22 +1020,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3434942079489071</v>
+        <v>0.3425721440237243</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3624075030777073</v>
+        <v>0.3613966982176853</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1600487101812928</v>
+        <v>0.1600120820661372</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1636387163519396</v>
+        <v>0.1636650101404095</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09213263163930216</v>
+        <v>0.0921663089138389</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1442557739768458</v>
+        <v>0.08247536550503323</v>
       </c>
       <c r="H7" t="n">
         <v>0.8514955388435604</v>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2923729604292518</v>
+        <v>0.2913725238506178</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2449955119307025</v>
+        <v>0.244241979399558</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1795042584615387</v>
+        <v>0.1815934436893237</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1736541581897918</v>
+        <v>0.1745185376626968</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2376049888306456</v>
+        <v>0.2299622651585019</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1763318582883934</v>
+        <v>0.1755946903419718</v>
       </c>
       <c r="H8" t="n">
         <v>0.8218833647220964</v>
@@ -1202,22 +1202,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3038469416724189</v>
+        <v>0.3039711669414104</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2664802318111055</v>
+        <v>0.2664943991235195</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3040106936128512</v>
+        <v>0.3041345686626021</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2666309112809248</v>
+        <v>0.2666432549250946</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2812971030545254</v>
+        <v>0.2817041488126172</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2469102482581059</v>
+        <v>0.2468974672696067</v>
       </c>
       <c r="H9" t="n">
         <v>0.4755023523128038</v>
@@ -1289,22 +1289,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5123386570784337</v>
+        <v>0.5090525456941374</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6166961246108762</v>
+        <v>0.6132271194235208</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3399072976960608</v>
+        <v>0.3428233582259079</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3247393788989229</v>
+        <v>0.3287732820670674</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3085017787144878</v>
+        <v>0.2743993234338228</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4909540193772712</v>
+        <v>0.4857053844878985</v>
       </c>
       <c r="H10" t="n">
         <v>1.126897749532528</v>
@@ -1380,22 +1380,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0548987986634983</v>
+        <v>0.05488259419306068</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05043681071314247</v>
+        <v>0.05041681564700241</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03293969915098341</v>
+        <v>0.03292619418347428</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03136588166417283</v>
+        <v>0.0313537386634372</v>
       </c>
       <c r="F11" t="n">
-        <v>0.006335482454821448</v>
+        <v>0.006164547827169517</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003159287104943196</v>
+        <v>0.002869162047199943</v>
       </c>
       <c r="H11" t="n">
         <v>0.2600988575656265</v>
@@ -1471,22 +1471,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7535164775973885</v>
+        <v>0.7492176664208927</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7844580791732065</v>
+        <v>0.7802178812393754</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3092875230603637</v>
+        <v>0.3056179213489899</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3050554147939886</v>
+        <v>0.30133215876627</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1756797844410787</v>
+        <v>0.1709091459189878</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4665941072374336</v>
+        <v>0.2447701931904981</v>
       </c>
       <c r="H12" t="n">
         <v>1.373425403558954</v>
@@ -1562,22 +1562,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3051383967140744</v>
+        <v>0.3037885667935559</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3427674292607265</v>
+        <v>0.3412760054295455</v>
       </c>
       <c r="D13" t="n">
-        <v>0.115370626172102</v>
+        <v>0.1153182779046153</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1078043511487605</v>
+        <v>0.1078343549367641</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08944856859919559</v>
+        <v>0.08965737744849965</v>
       </c>
       <c r="G13" t="n">
-        <v>0.09695018629000249</v>
+        <v>0.09650311227384581</v>
       </c>
       <c r="H13" t="n">
         <v>0.8934721382063724</v>
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2932412115747531</v>
+        <v>0.2926607399582407</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1046349187084708</v>
+        <v>0.104414241682984</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1965580513942289</v>
+        <v>0.1964328729300407</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07905761631300896</v>
+        <v>0.07901789673683859</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2431239268906061</v>
+        <v>0.2117148137007583</v>
       </c>
       <c r="G14" t="n">
-        <v>0.07453068819359338</v>
+        <v>0.07444940510988042</v>
       </c>
       <c r="H14" t="n">
         <v>0.5768557783561169</v>
@@ -1744,22 +1744,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5620314611665793</v>
+        <v>0.5605709651952656</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4005005943763199</v>
+        <v>0.3994016153559959</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1697377313713465</v>
+        <v>0.1696339676443774</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1192092154191906</v>
+        <v>0.1191792895020432</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1194818471064708</v>
+        <v>0.1190786687198225</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03488179007474622</v>
+        <v>0.0347831430895236</v>
       </c>
       <c r="H15" t="n">
         <v>0.9740152227653087</v>
@@ -1835,22 +1835,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4431110251831236</v>
+        <v>0.4426584737263628</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2119657789465685</v>
+        <v>0.2119754937624252</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6393940890752158</v>
+        <v>0.6776224432413257</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2120875018020139</v>
+        <v>0.2120959796720211</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5672645445490903</v>
+        <v>0.5665677747737586</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2009399902647157</v>
+        <v>0.2007821781873968</v>
       </c>
       <c r="H16" t="n">
         <v>0.4381367147839849</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6479219387602613</v>
+        <v>0.6450698453677368</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6328189223419141</v>
+        <v>0.6298332651966274</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2208205716346336</v>
+        <v>0.2203781394591999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2160907278267805</v>
+        <v>0.2158775826340549</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1305474512840755</v>
+        <v>0.1297010550905297</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05211861221050579</v>
+        <v>0.05168761111519902</v>
       </c>
       <c r="H17" t="n">
         <v>1.267429584043156</v>
@@ -2013,22 +2013,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6406279695536129</v>
+        <v>0.6390331909013044</v>
       </c>
       <c r="C18" t="n">
-        <v>0.654072195018223</v>
+        <v>0.6524106251058965</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6207277136611566</v>
+        <v>0.6322866746235792</v>
       </c>
       <c r="E18" t="n">
-        <v>0.64030076757404</v>
+        <v>0.6613504180969065</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6334147271751526</v>
+        <v>0.6303418307863142</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7212781824496957</v>
+        <v>0.7180782970522642</v>
       </c>
       <c r="H18" t="n">
         <v>1.125928035226928</v>
@@ -2100,22 +2100,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1896278569531041</v>
+        <v>0.1900190559899986</v>
       </c>
       <c r="C19" t="n">
-        <v>0.188118634723341</v>
+        <v>0.1882655780453046</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1537774145378446</v>
+        <v>0.1545549644513988</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1432952211848578</v>
+        <v>0.143365920339972</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1744901483636978</v>
+        <v>0.1749074916263711</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1694077001538937</v>
+        <v>0.1696999769744638</v>
       </c>
       <c r="H19" t="n">
         <v>0.5491815241612263</v>
@@ -2191,22 +2191,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7406468574923799</v>
+        <v>0.7349138044082288</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4574777834158045</v>
+        <v>0.453020185371623</v>
       </c>
       <c r="D20" t="n">
-        <v>0.186486781650812</v>
+        <v>0.1829193753987896</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1679186370778793</v>
+        <v>0.1656558160028125</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3177717463832374</v>
+        <v>0.3134254406237676</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2585525949178351</v>
+        <v>0.1771403652728223</v>
       </c>
       <c r="H20" t="n">
         <v>1.089294365184146</v>
@@ -2282,22 +2282,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7303025044867844</v>
+        <v>0.7270841257493305</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4179685807933835</v>
+        <v>0.4160689168358572</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1993850063364833</v>
+        <v>0.1987639337941945</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1959113675490289</v>
+        <v>0.1961295165207923</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3072943092144789</v>
+        <v>0.3058489501862094</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2383820560929755</v>
+        <v>0.1730263498738827</v>
       </c>
       <c r="H21" t="n">
         <v>1.062546466477206</v>
@@ -2373,22 +2373,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7389075598362194</v>
+        <v>0.735463502641162</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9285619804635556</v>
+        <v>0.9248563148493131</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3888982418054168</v>
+        <v>0.3884967894196186</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3908363836904335</v>
+        <v>0.3887274607435048</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3571124160388545</v>
+        <v>0.3540977108571027</v>
       </c>
       <c r="G22" t="n">
-        <v>0.560716996428976</v>
+        <v>0.5551819548957816</v>
       </c>
       <c r="H22" t="n">
         <v>1.313835537124292</v>
@@ -2464,22 +2464,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1506717094638826</v>
+        <v>0.1509191366673557</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1751068087826258</v>
+        <v>0.175047780426626</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1014638664029113</v>
+        <v>0.1014913983952132</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05475782605272433</v>
+        <v>0.05471446439554508</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1067015024276023</v>
+        <v>0.1068817944838088</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0628029259425547</v>
+        <v>0.06281893700571951</v>
       </c>
       <c r="H23" t="n">
         <v>0.6014370052190726</v>
@@ -2555,22 +2555,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3879212202361371</v>
+        <v>0.3874504233674058</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3060617672104368</v>
+        <v>0.305650091875142</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3011984837515304</v>
+        <v>0.313111790933893</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2203032240731948</v>
+        <v>0.2242823587647351</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3549278683596653</v>
+        <v>0.354092560590088</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2349687770242841</v>
+        <v>0.2343810344994887</v>
       </c>
       <c r="H24" t="n">
         <v>0.821026555289418</v>
@@ -2646,22 +2646,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3295116663328739</v>
+        <v>0.3281318756913603</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2561222235387318</v>
+        <v>0.254971880914115</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1162607454884587</v>
+        <v>0.1162657791131764</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08587497005443874</v>
+        <v>0.08601312379679785</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1896969874558544</v>
+        <v>0.1884637482977953</v>
       </c>
       <c r="G25" t="n">
-        <v>0.07977925622478291</v>
+        <v>0.07894819811701426</v>
       </c>
       <c r="H25" t="n">
         <v>0.8337220581801408</v>
@@ -2737,22 +2737,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.883211571559205</v>
+        <v>0.8779507478750599</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7604182013317495</v>
+        <v>0.755436250062104</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2568436513644693</v>
+        <v>0.2557593299145072</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2162202262127234</v>
+        <v>0.2156379575629639</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1058820842209599</v>
+        <v>0.1041925137365477</v>
       </c>
       <c r="G26" t="n">
-        <v>0.030569648360533</v>
+        <v>0.02948387530261077</v>
       </c>
       <c r="H26" t="n">
         <v>1.470782642072603</v>
@@ -2828,22 +2828,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.06209220599517896</v>
+        <v>0.06207388693130207</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0605726526230637</v>
+        <v>0.0605774752884498</v>
       </c>
       <c r="D27" t="n">
-        <v>0.05461616686306563</v>
+        <v>0.05458207995637606</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04623868421689228</v>
+        <v>0.04622029063232052</v>
       </c>
       <c r="F27" t="n">
-        <v>0.04331180491745713</v>
+        <v>0.04328923765206946</v>
       </c>
       <c r="G27" t="n">
-        <v>0.03175851567364049</v>
+        <v>0.03173528442858103</v>
       </c>
       <c r="H27" t="n">
         <v>0.3074293300784401</v>
@@ -2919,22 +2919,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1789506407839042</v>
+        <v>0.1789655005846158</v>
       </c>
       <c r="C28" t="n">
-        <v>0.08619385602205371</v>
+        <v>0.08619350451733843</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1937587760809739</v>
+        <v>0.1937717258770215</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0861956375987431</v>
+        <v>0.08619294909028766</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1826432066121919</v>
+        <v>0.1826498894309261</v>
       </c>
       <c r="G28" t="n">
-        <v>0.06945223307838413</v>
+        <v>0.06943043821063653</v>
       </c>
       <c r="H28" t="n">
         <v>0.3217073324512321</v>
@@ -3010,22 +3010,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.05062347217280656</v>
+        <v>0.05062021196639092</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03198416287305984</v>
+        <v>0.03197766054045453</v>
       </c>
       <c r="D29" t="n">
-        <v>0.04653655240745246</v>
+        <v>0.04652818760502312</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03036483750533457</v>
+        <v>0.03035235703411378</v>
       </c>
       <c r="F29" t="n">
-        <v>0.05504613725488824</v>
+        <v>0.05503844962322328</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03312566231462633</v>
+        <v>0.03311477498782771</v>
       </c>
       <c r="H29" t="n">
         <v>0.09125397575447609</v>
@@ -3101,22 +3101,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.08740411312750856</v>
+        <v>0.08742953106736807</v>
       </c>
       <c r="C30" t="n">
-        <v>0.07498045169947692</v>
+        <v>0.07500231926812009</v>
       </c>
       <c r="D30" t="n">
-        <v>0.04116516601734409</v>
+        <v>0.04115308929629166</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03221851295698297</v>
+        <v>0.03218995455454213</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0393838223659965</v>
+        <v>0.03937925821502111</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02059667152757904</v>
+        <v>0.02056506804364397</v>
       </c>
       <c r="H30" t="n">
         <v>0.3364356123183577</v>
@@ -3192,22 +3192,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.08182893705165355</v>
+        <v>0.08182643247157914</v>
       </c>
       <c r="C31" t="n">
-        <v>0.06479137392805756</v>
+        <v>0.06477085591513414</v>
       </c>
       <c r="D31" t="n">
-        <v>0.08908041772602046</v>
+        <v>0.08908223319650851</v>
       </c>
       <c r="E31" t="n">
-        <v>0.06482343969746326</v>
+        <v>0.06480292727428162</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1087807681972566</v>
+        <v>0.1087904557351222</v>
       </c>
       <c r="G31" t="n">
-        <v>0.06964512133161786</v>
+        <v>0.06963845488919049</v>
       </c>
       <c r="H31" t="n">
         <v>0.1898985606099392</v>
@@ -3283,22 +3283,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.08980417516897896</v>
+        <v>0.08977873164219138</v>
       </c>
       <c r="C32" t="n">
-        <v>0.04867463037246214</v>
+        <v>0.04866815029499763</v>
       </c>
       <c r="D32" t="n">
-        <v>0.06835947207071258</v>
+        <v>0.06834767330570328</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03852836558066905</v>
+        <v>0.03854450403594292</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07390302492749348</v>
+        <v>0.07388045002427068</v>
       </c>
       <c r="G32" t="n">
-        <v>0.03806254976290487</v>
+        <v>0.03807119030344252</v>
       </c>
       <c r="H32" t="n">
         <v>0.2272640433410283</v>
@@ -3374,22 +3374,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6527772214040108</v>
+        <v>0.6483473332437145</v>
       </c>
       <c r="C33" t="n">
-        <v>0.563245596371019</v>
+        <v>0.5591465006485221</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2037849108871594</v>
+        <v>0.2004392153178149</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1940490257510064</v>
+        <v>0.1914385221817014</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2591532240054552</v>
+        <v>0.2528945913851281</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3397615999614645</v>
+        <v>0.2337579271861558</v>
       </c>
       <c r="H33" t="n">
         <v>1.247560275116454</v>
@@ -3465,22 +3465,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.08536305205716556</v>
+        <v>0.08540258178448085</v>
       </c>
       <c r="C34" t="n">
-        <v>0.08501923761903513</v>
+        <v>0.08504262494770862</v>
       </c>
       <c r="D34" t="n">
-        <v>0.04378010929919791</v>
+        <v>0.0437410667210726</v>
       </c>
       <c r="E34" t="n">
-        <v>0.04348458337406332</v>
+        <v>0.0434441623193047</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01346907431322228</v>
+        <v>0.01331963457462606</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01403620669519386</v>
+        <v>0.01391906268104152</v>
       </c>
       <c r="H34" t="n">
         <v>0.463096312708327</v>
@@ -3556,22 +3556,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.04836425064970992</v>
+        <v>0.04834709807962682</v>
       </c>
       <c r="C35" t="n">
-        <v>0.05108781164030386</v>
+        <v>0.05107661617171957</v>
       </c>
       <c r="D35" t="n">
-        <v>0.02903071827914915</v>
+        <v>0.02898294086609664</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0259860054391326</v>
+        <v>0.02595996916104477</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02253846416659469</v>
+        <v>0.02249581156851674</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02048879720718558</v>
+        <v>0.02047942788530573</v>
       </c>
       <c r="H35" t="n">
         <v>0.3093751617228926</v>
@@ -3647,22 +3647,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.06675795015819569</v>
+        <v>0.0667939560390499</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07000986079852171</v>
+        <v>0.07009371026513035</v>
       </c>
       <c r="D36" t="n">
-        <v>0.04111648293305144</v>
+        <v>0.04107045024060469</v>
       </c>
       <c r="E36" t="n">
-        <v>0.04638968454756125</v>
+        <v>0.04634418424166064</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01635358780568565</v>
+        <v>0.01625129383931121</v>
       </c>
       <c r="G36" t="n">
-        <v>0.01218325201718701</v>
+        <v>0.0119106438294502</v>
       </c>
       <c r="H36" t="n">
         <v>0.4447191641064449</v>
@@ -3738,22 +3738,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.14634961076987</v>
+        <v>0.1464041190137369</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1408043783363082</v>
+        <v>0.140857786790505</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08802569492734642</v>
+        <v>0.08806578157084073</v>
       </c>
       <c r="E37" t="n">
-        <v>0.08792673443779837</v>
+        <v>0.08792720280098572</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1009469725886986</v>
+        <v>0.07907836553756208</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0858132376117228</v>
+        <v>0.08588864214746358</v>
       </c>
       <c r="H37" t="n">
         <v>0.5039765573286296</v>
@@ -3829,22 +3829,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.09876249192127846</v>
+        <v>0.09879046112130907</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1026693005871327</v>
+        <v>0.1027096772821009</v>
       </c>
       <c r="D38" t="n">
-        <v>0.03468468189346886</v>
+        <v>0.03461846968698081</v>
       </c>
       <c r="E38" t="n">
-        <v>0.03567638319215124</v>
+        <v>0.03565639558925297</v>
       </c>
       <c r="F38" t="n">
-        <v>0.00766646736416937</v>
+        <v>0.007420056334630616</v>
       </c>
       <c r="G38" t="n">
-        <v>0.00686862154816409</v>
+        <v>0.00666189886109348</v>
       </c>
       <c r="H38" t="n">
         <v>0.3771355762613469</v>
@@ -3920,22 +3920,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.2323461754632751</v>
+        <v>0.2308096423441239</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2499494337485818</v>
+        <v>0.2485157647253419</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1687390987338374</v>
+        <v>0.1773619515997136</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1183132221393223</v>
+        <v>0.1200908829687772</v>
       </c>
       <c r="F39" t="n">
-        <v>0.158059197515376</v>
+        <v>0.1555146779571564</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1571382477854752</v>
+        <v>0.1363959873216422</v>
       </c>
       <c r="H39" t="n">
         <v>0.7973738576699186</v>
@@ -4011,22 +4011,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.138271207485173</v>
+        <v>0.1378192895454343</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1690372876687692</v>
+        <v>0.1681666541472387</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1217941967342034</v>
+        <v>0.1217167751301444</v>
       </c>
       <c r="E40" t="n">
-        <v>0.09778313137220958</v>
+        <v>0.09761965155738274</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1139819738602772</v>
+        <v>0.1138799180787355</v>
       </c>
       <c r="G40" t="n">
-        <v>0.07645373973253095</v>
+        <v>0.07610273952234106</v>
       </c>
       <c r="H40" t="n">
         <v>0.6797073731912212</v>
@@ -4102,22 +4102,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1137540587471809</v>
+        <v>0.1138437039555843</v>
       </c>
       <c r="C41" t="n">
-        <v>0.06945355244657436</v>
+        <v>0.06943424603509075</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1171555275060012</v>
+        <v>0.1171812707469262</v>
       </c>
       <c r="E41" t="n">
-        <v>0.06041729594430501</v>
+        <v>0.06042369572399547</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1435575876224533</v>
+        <v>0.1436002500085728</v>
       </c>
       <c r="G41" t="n">
-        <v>0.06958372774369592</v>
+        <v>0.06958253905563412</v>
       </c>
       <c r="H41" t="n">
         <v>0.2705128397863901</v>
@@ -4193,22 +4193,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3446482940635034</v>
+        <v>0.3445711937904057</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3440874118987211</v>
+        <v>0.3439924473536555</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3448294206419265</v>
+        <v>0.3447512077648349</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3442702888129965</v>
+        <v>0.3441747689096942</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3047264049561575</v>
+        <v>0.3044262292238669</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3248897114670982</v>
+        <v>0.3245416956158956</v>
       </c>
       <c r="H42" t="n">
         <v>0.5606279224051089</v>
@@ -4280,22 +4280,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.655287961883142</v>
+        <v>2.633721468121753</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9573762377795885</v>
+        <v>0.93750627345477</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3414221180999144</v>
+        <v>0.3216694299083735</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1801894130515869</v>
+        <v>0.1713731789032631</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4303250134745844</v>
+        <v>0.4054784679504758</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0762329505872211</v>
+        <v>0.06199875641522061</v>
       </c>
       <c r="H43" t="n">
         <v>2.229510190828526</v>
@@ -4371,22 +4371,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.03332803834677197</v>
+        <v>0.03330823031460627</v>
       </c>
       <c r="C44" t="n">
-        <v>0.03193866572211082</v>
+        <v>0.03192992666598724</v>
       </c>
       <c r="D44" t="n">
-        <v>0.03316634188493844</v>
+        <v>0.03314961271633698</v>
       </c>
       <c r="E44" t="n">
-        <v>0.03192361493182582</v>
+        <v>0.03191428229436224</v>
       </c>
       <c r="F44" t="n">
-        <v>0.01936615053964751</v>
+        <v>0.01935806309614276</v>
       </c>
       <c r="G44" t="n">
-        <v>0.02154674223558054</v>
+        <v>0.02153108724405666</v>
       </c>
       <c r="H44" t="n">
         <v>0.219637958318896</v>
@@ -4462,22 +4462,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.03222301259357571</v>
+        <v>0.03221219265134713</v>
       </c>
       <c r="C45" t="n">
-        <v>0.03274604300008147</v>
+        <v>0.03274065164384684</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0259369108901331</v>
+        <v>0.02591954535897539</v>
       </c>
       <c r="E45" t="n">
-        <v>0.02454787902311676</v>
+        <v>0.02452199359124536</v>
       </c>
       <c r="F45" t="n">
-        <v>0.01845343614192424</v>
+        <v>0.01842923187463541</v>
       </c>
       <c r="G45" t="n">
-        <v>0.01729974914431417</v>
+        <v>0.01728399232106188</v>
       </c>
       <c r="H45" t="n">
         <v>0.2253013199805374</v>
@@ -4553,22 +4553,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.09631688033969857</v>
+        <v>0.09630334253644893</v>
       </c>
       <c r="C46" t="n">
-        <v>0.05391620063076814</v>
+        <v>0.05390673528200461</v>
       </c>
       <c r="D46" t="n">
-        <v>0.08686628374878885</v>
+        <v>0.08685679098089252</v>
       </c>
       <c r="E46" t="n">
-        <v>0.05174559238114183</v>
+        <v>0.05186069995904886</v>
       </c>
       <c r="F46" t="n">
-        <v>0.09293864197937197</v>
+        <v>0.09292089567095477</v>
       </c>
       <c r="G46" t="n">
-        <v>0.03870416641070391</v>
+        <v>0.03870498844302602</v>
       </c>
       <c r="H46" t="n">
         <v>0.2500371999588092</v>
@@ -4644,22 +4644,22 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.06368051490744006</v>
+        <v>0.06368009529909434</v>
       </c>
       <c r="C47" t="n">
-        <v>0.04579888969273014</v>
+        <v>0.0457955456039836</v>
       </c>
       <c r="D47" t="n">
-        <v>0.06372858256602375</v>
+        <v>0.06372848922639786</v>
       </c>
       <c r="E47" t="n">
-        <v>0.04583886555291042</v>
+        <v>0.04583603001885744</v>
       </c>
       <c r="F47" t="n">
-        <v>0.05398308160788012</v>
+        <v>0.05397840973382861</v>
       </c>
       <c r="G47" t="n">
-        <v>0.04321498853737334</v>
+        <v>0.04320600337558316</v>
       </c>
       <c r="H47" t="n">
         <v>0.2334066842779279</v>
@@ -4735,22 +4735,22 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3059927557710973</v>
+        <v>0.3059778988519284</v>
       </c>
       <c r="C48" t="n">
-        <v>0.07169326760165609</v>
+        <v>0.07166397487212992</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1371160641778377</v>
+        <v>0.1371081671453661</v>
       </c>
       <c r="E48" t="n">
-        <v>0.05564348626170174</v>
+        <v>0.05557839511833085</v>
       </c>
       <c r="F48" t="n">
-        <v>0.179317927629405</v>
+        <v>0.1792881884099726</v>
       </c>
       <c r="G48" t="n">
-        <v>0.05428571473020685</v>
+        <v>0.05422099248120438</v>
       </c>
       <c r="H48" t="n">
         <v>0.3379122681153697</v>
@@ -4826,22 +4826,22 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6909651190270951</v>
+        <v>0.6875192323982778</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5979419600217496</v>
+        <v>0.5941492719670419</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2909470387874272</v>
+        <v>0.2870687588357115</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1774640663746824</v>
+        <v>0.1746167740482679</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4038510805080942</v>
+        <v>0.398657720171792</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2491540847866877</v>
+        <v>0.2430429087916893</v>
       </c>
       <c r="H49" t="n">
         <v>1.363451004429825</v>
@@ -4917,22 +4917,22 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.2051319963174478</v>
+        <v>0.2049282177144851</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2153930489723502</v>
+        <v>0.215145744293515</v>
       </c>
       <c r="D50" t="n">
-        <v>0.122807371894588</v>
+        <v>0.1228404743055463</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1115520870578637</v>
+        <v>0.111621362955489</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1130308119804937</v>
+        <v>0.1133797562537238</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1141402443308982</v>
+        <v>0.1129706382659624</v>
       </c>
       <c r="H50" t="n">
         <v>0.670665120055479</v>
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.894771884312891</v>
+        <v>1.883760202748403</v>
       </c>
       <c r="C51" t="n">
-        <v>1.812001984309809</v>
+        <v>1.801043269094024</v>
       </c>
       <c r="D51" t="n">
-        <v>0.5887883204810218</v>
+        <v>0.5784958372661392</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5757460453968697</v>
+        <v>0.5660761009362293</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1434336818139095</v>
+        <v>0.1388710229328567</v>
       </c>
       <c r="G51" t="n">
-        <v>0.06545887409551812</v>
+        <v>0.05671124332544618</v>
       </c>
       <c r="H51" t="n">
         <v>2.498364972397039</v>
@@ -5099,22 +5099,22 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.308702605760026</v>
+        <v>1.299291193379578</v>
       </c>
       <c r="C52" t="n">
-        <v>1.252326923232603</v>
+        <v>1.24285466549652</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5273374400992737</v>
+        <v>0.5152212380865674</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5198032238083614</v>
+        <v>0.5083481328140047</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3823268548098825</v>
+        <v>0.3427698616804288</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2847849757982369</v>
+        <v>0.2388242623049852</v>
       </c>
       <c r="H52" t="n">
         <v>2.028441185139194</v>
@@ -5190,22 +5190,22 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.213056838755463</v>
+        <v>0.2134853946045837</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1739100192788041</v>
+        <v>0.1739984898829535</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2910446101855437</v>
+        <v>0.2922750484403725</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1461670215316392</v>
+        <v>0.1462023644766806</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2431414379640667</v>
+        <v>0.2435947772079181</v>
       </c>
       <c r="G53" t="n">
-        <v>0.1612973517414728</v>
+        <v>0.1614388371344374</v>
       </c>
       <c r="H53" t="n">
         <v>0.4376089963335965</v>
@@ -5281,22 +5281,22 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.04714998855346699</v>
+        <v>0.0471449332708825</v>
       </c>
       <c r="C54" t="n">
-        <v>0.03961087926114863</v>
+        <v>0.03961027617096617</v>
       </c>
       <c r="D54" t="n">
-        <v>0.04716150579924855</v>
+        <v>0.04715760625909386</v>
       </c>
       <c r="E54" t="n">
-        <v>0.03958345147957278</v>
+        <v>0.03958135666431695</v>
       </c>
       <c r="F54" t="n">
-        <v>0.04799402851400786</v>
+        <v>0.04799600226272516</v>
       </c>
       <c r="G54" t="n">
-        <v>0.02055371301835657</v>
+        <v>0.02053445517115431</v>
       </c>
       <c r="H54" t="n">
         <v>0.236689300497001</v>
@@ -5372,22 +5372,22 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.2527411499812227</v>
+        <v>0.2524551472420774</v>
       </c>
       <c r="C55" t="n">
-        <v>0.2387002626353951</v>
+        <v>0.2385085466461309</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3705614831269312</v>
+        <v>0.3907920279978311</v>
       </c>
       <c r="E55" t="n">
-        <v>0.3824114236315139</v>
+        <v>0.4110618668552029</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2872885036427358</v>
+        <v>0.2866945656317785</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2544658003741349</v>
+        <v>0.2538707419968914</v>
       </c>
       <c r="H55" t="n">
         <v>0.6666406779747963</v>
@@ -5463,22 +5463,22 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.1027988154319533</v>
+        <v>0.1025903022321615</v>
       </c>
       <c r="C56" t="n">
-        <v>0.09880985155960867</v>
+        <v>0.09864198018867899</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1074578636293353</v>
+        <v>0.1073403579392961</v>
       </c>
       <c r="E56" t="n">
-        <v>0.100515956161974</v>
+        <v>0.1003826590013413</v>
       </c>
       <c r="F56" t="n">
-        <v>0.09521978077929036</v>
+        <v>0.09487840350900813</v>
       </c>
       <c r="G56" t="n">
-        <v>0.08887673068112426</v>
+        <v>0.08842039213361622</v>
       </c>
       <c r="H56" t="n">
         <v>0.5431663794570629</v>
@@ -5554,22 +5554,22 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5545646363365251</v>
+        <v>0.5520725371348393</v>
       </c>
       <c r="C57" t="n">
-        <v>0.3114093782532871</v>
+        <v>0.3095529053602163</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1306651476089649</v>
+        <v>0.129944276455478</v>
       </c>
       <c r="E57" t="n">
-        <v>0.09084150395632271</v>
+        <v>0.09058539555967353</v>
       </c>
       <c r="F57" t="n">
-        <v>0.193456926768778</v>
+        <v>0.1924806508443604</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1266567521439173</v>
+        <v>0.09372572401842069</v>
       </c>
       <c r="H57" t="n">
         <v>0.9187102398267176</v>
@@ -5645,22 +5645,22 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.01070180768731761</v>
+        <v>0.01068605521040134</v>
       </c>
       <c r="C58" t="n">
-        <v>0.003505680930805725</v>
+        <v>0.00350041061804758</v>
       </c>
       <c r="D58" t="n">
-        <v>0.01010799363433923</v>
+        <v>0.01056939009607541</v>
       </c>
       <c r="E58" t="n">
-        <v>0.002045224741455347</v>
+        <v>0.002017902773918819</v>
       </c>
       <c r="F58" t="n">
-        <v>0.01161240912094508</v>
+        <v>0.01160003975057617</v>
       </c>
       <c r="G58" t="n">
-        <v>0.003430083797853129</v>
+        <v>0.003424436394132164</v>
       </c>
       <c r="H58" t="n">
         <v>0.006201137995202942</v>
@@ -5732,22 +5732,22 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1.213570924243425</v>
+        <v>1.206804414118065</v>
       </c>
       <c r="C59" t="n">
-        <v>1.007183481380457</v>
+        <v>1.000584039568822</v>
       </c>
       <c r="D59" t="n">
-        <v>0.5767649320092227</v>
+        <v>0.5688339432501592</v>
       </c>
       <c r="E59" t="n">
-        <v>0.5287418907149984</v>
+        <v>0.5210467101828455</v>
       </c>
       <c r="F59" t="n">
-        <v>1.030351615500399</v>
+        <v>0.7303340534387879</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8669612099256673</v>
+        <v>0.8553388457711423</v>
       </c>
       <c r="H59" t="n">
         <v>1.935074098502654</v>
@@ -5823,22 +5823,22 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.9036267729760226</v>
+        <v>0.8992943732861131</v>
       </c>
       <c r="C60" t="n">
-        <v>0.8327522241917067</v>
+        <v>0.8283219632971955</v>
       </c>
       <c r="D60" t="n">
-        <v>0.4030928101472567</v>
+        <v>0.3992699674579335</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3576351673817741</v>
+        <v>0.3540118982655499</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5546181699272787</v>
+        <v>0.5487702634661585</v>
       </c>
       <c r="G60" t="n">
-        <v>0.5171499766514787</v>
+        <v>0.5112968109998602</v>
       </c>
       <c r="H60" t="n">
         <v>1.482727576453942</v>
@@ -5914,22 +5914,22 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4564630016561046</v>
+        <v>0.451878549814435</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5364328134386336</v>
+        <v>0.531613281787809</v>
       </c>
       <c r="D61" t="n">
-        <v>0.111314903893637</v>
+        <v>0.1104158907197382</v>
       </c>
       <c r="E61" t="n">
-        <v>0.09822912572090017</v>
+        <v>0.09493308181253432</v>
       </c>
       <c r="F61" t="n">
-        <v>0.08616001049285782</v>
+        <v>0.08391620484197634</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1018971910396627</v>
+        <v>0.09675748451502367</v>
       </c>
       <c r="H61" t="n">
         <v>1.170048173221576</v>
@@ -6005,22 +6005,22 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.1887737044319772</v>
+        <v>0.1888553513518152</v>
       </c>
       <c r="C62" t="n">
-        <v>0.09455052318571666</v>
+        <v>0.09461974118246931</v>
       </c>
       <c r="D62" t="n">
-        <v>0.09675026292982283</v>
+        <v>0.09706124816534478</v>
       </c>
       <c r="E62" t="n">
-        <v>0.07228009391647686</v>
+        <v>0.07240075588870937</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1380224318073058</v>
+        <v>0.1193157924646424</v>
       </c>
       <c r="G62" t="n">
-        <v>0.07543653946723078</v>
+        <v>0.0754965135848904</v>
       </c>
       <c r="H62" t="n">
         <v>0.3847615424008634</v>
@@ -6096,22 +6096,22 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4070565983226671</v>
+        <v>0.4057186306245989</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4520187022178964</v>
+        <v>0.4503157731456378</v>
       </c>
       <c r="D63" t="n">
-        <v>0.2497286531485543</v>
+        <v>0.2502158108339501</v>
       </c>
       <c r="E63" t="n">
-        <v>0.2384426269210413</v>
+        <v>0.2403338624906481</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2438754000605045</v>
+        <v>0.213753104648562</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3021856899741042</v>
+        <v>0.2996691877074555</v>
       </c>
       <c r="H63" t="n">
         <v>0.9613842667655157</v>
@@ -6187,22 +6187,22 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8151406208621141</v>
+        <v>0.8126468881298975</v>
       </c>
       <c r="C64" t="n">
-        <v>0.8557139004397631</v>
+        <v>0.8530721133747085</v>
       </c>
       <c r="D64" t="n">
-        <v>0.4136129644443014</v>
+        <v>0.4135765734760165</v>
       </c>
       <c r="E64" t="n">
-        <v>0.4151763266802893</v>
+        <v>0.415110359457614</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4879494466561585</v>
+        <v>0.4846109585116196</v>
       </c>
       <c r="G64" t="n">
-        <v>0.5541227011653553</v>
+        <v>0.5497882431920267</v>
       </c>
       <c r="H64" t="n">
         <v>1.364498070866812</v>
@@ -6278,22 +6278,22 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5560811269541756</v>
+        <v>0.5530052834380154</v>
       </c>
       <c r="C65" t="n">
-        <v>0.2488801367927591</v>
+        <v>0.2469954647965427</v>
       </c>
       <c r="D65" t="n">
-        <v>0.1763583548488111</v>
+        <v>0.1745387981176564</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1294012003798869</v>
+        <v>0.1292009388540029</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2796814332296188</v>
+        <v>0.2765703453678259</v>
       </c>
       <c r="G65" t="n">
-        <v>0.157121059169276</v>
+        <v>0.1421196078054941</v>
       </c>
       <c r="H65" t="n">
         <v>0.8762976441872627</v>
@@ -6369,22 +6369,22 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.3089713355605678</v>
+        <v>0.3080061780014143</v>
       </c>
       <c r="C66" t="n">
-        <v>0.3407940458350395</v>
+        <v>0.339686921387015</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1232504414075233</v>
+        <v>0.1232049890022731</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1181106148798783</v>
+        <v>0.1181125117930658</v>
       </c>
       <c r="F66" t="n">
-        <v>0.03691941172092143</v>
+        <v>0.03678165940257595</v>
       </c>
       <c r="G66" t="n">
-        <v>0.02180497634582821</v>
+        <v>0.02123987718409241</v>
       </c>
       <c r="H66" t="n">
         <v>0.8890729753981951</v>
@@ -6460,22 +6460,22 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6631777913600052</v>
+        <v>0.6628133450041389</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6705564120270601</v>
+        <v>0.6693666910520283</v>
       </c>
       <c r="D67" t="n">
-        <v>0.8349100857559916</v>
+        <v>0.8351731975477521</v>
       </c>
       <c r="E67" t="n">
-        <v>0.6967626147329891</v>
+        <v>0.7187279484579806</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6062587762442808</v>
+        <v>0.6082529560423311</v>
       </c>
       <c r="G67" t="n">
-        <v>0.6059162098715113</v>
+        <v>0.6034659168081969</v>
       </c>
       <c r="H67" t="n">
         <v>0.822053537981963</v>
@@ -6551,22 +6551,22 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.05047220636443453</v>
+        <v>0.05048595313724757</v>
       </c>
       <c r="C68" t="n">
-        <v>0.04230920210331721</v>
+        <v>0.04232199902189816</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0504964250446171</v>
+        <v>0.05050988875114545</v>
       </c>
       <c r="E68" t="n">
-        <v>0.04233260812396031</v>
+        <v>0.04234574613356495</v>
       </c>
       <c r="F68" t="n">
-        <v>0.06302718579308185</v>
+        <v>0.0630342004261604</v>
       </c>
       <c r="G68" t="n">
-        <v>0.04504951793631422</v>
+        <v>0.04505846890331357</v>
       </c>
       <c r="H68" t="n">
         <v>0.1158922377181897</v>
@@ -6642,22 +6642,22 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.1273872508930199</v>
+        <v>0.1273751387692325</v>
       </c>
       <c r="C69" t="n">
-        <v>0.1236600940350201</v>
+        <v>0.123645429365804</v>
       </c>
       <c r="D69" t="n">
-        <v>0.1274038515006694</v>
+        <v>0.1273917580534896</v>
       </c>
       <c r="E69" t="n">
-        <v>0.1236753522000469</v>
+        <v>0.1236609263378652</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1113282116605571</v>
+        <v>0.1113183015726387</v>
       </c>
       <c r="G69" t="n">
-        <v>0.1156167595940635</v>
+        <v>0.1156122314556066</v>
       </c>
       <c r="H69" t="n">
         <v>0.2999663024798833</v>
@@ -6733,22 +6733,22 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6516565396681242</v>
+        <v>0.647062397280639</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5259812140853551</v>
+        <v>0.5215623854741231</v>
       </c>
       <c r="D70" t="n">
-        <v>0.1452827997299384</v>
+        <v>0.1422128665944157</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1076709468327376</v>
+        <v>0.1056105014151803</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1349873957491418</v>
+        <v>0.1312168236082282</v>
       </c>
       <c r="G70" t="n">
-        <v>0.079944758287669</v>
+        <v>0.07636959472438798</v>
       </c>
       <c r="H70" t="n">
         <v>1.182881379043306</v>
@@ -6824,22 +6824,22 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.1847881227531005</v>
+        <v>0.1846473975182666</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1909440198993982</v>
+        <v>0.1907699174151322</v>
       </c>
       <c r="D71" t="n">
-        <v>0.03835691720416959</v>
+        <v>0.03814930150911446</v>
       </c>
       <c r="E71" t="n">
-        <v>0.04036955990711219</v>
+        <v>0.0400407121706995</v>
       </c>
       <c r="F71" t="n">
-        <v>0.0231072581365963</v>
+        <v>0.02310561325370156</v>
       </c>
       <c r="G71" t="n">
-        <v>0.020364603507702</v>
+        <v>0.02023607732265282</v>
       </c>
       <c r="H71" t="n">
         <v>0.668404623200426</v>
@@ -6915,22 +6915,22 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.1353285334913661</v>
+        <v>0.1353598303622103</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0706640673046199</v>
+        <v>0.07066791454408344</v>
       </c>
       <c r="D72" t="n">
-        <v>0.1536640538217375</v>
+        <v>0.153647406175306</v>
       </c>
       <c r="E72" t="n">
-        <v>0.07068272011491204</v>
+        <v>0.07068504877160804</v>
       </c>
       <c r="F72" t="n">
-        <v>0.1386272820896443</v>
+        <v>0.1386314076648307</v>
       </c>
       <c r="G72" t="n">
-        <v>0.06505872083983669</v>
+        <v>0.06505380710447956</v>
       </c>
       <c r="H72" t="n">
         <v>0.3266677650070184</v>
@@ -7006,22 +7006,22 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.485487049704903</v>
+        <v>0.4846691750147248</v>
       </c>
       <c r="C73" t="n">
-        <v>0.4755706811882146</v>
+        <v>0.4747789332697916</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4917437421507509</v>
+        <v>0.5114083755556068</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4778745033745449</v>
+        <v>0.4912296168100817</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4687750654133777</v>
+        <v>0.4668088897522757</v>
       </c>
       <c r="G73" t="n">
-        <v>0.4572430322399906</v>
+        <v>0.455444479455177</v>
       </c>
       <c r="H73" t="n">
         <v>0.9493752443193544</v>
@@ -7097,22 +7097,22 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.05668207815560468</v>
+        <v>0.05671562615870713</v>
       </c>
       <c r="C74" t="n">
-        <v>0.07760132626553273</v>
+        <v>0.07759810311732163</v>
       </c>
       <c r="D74" t="n">
-        <v>0.06150672614568146</v>
+        <v>0.061473047807748</v>
       </c>
       <c r="E74" t="n">
-        <v>0.06571364627998162</v>
+        <v>0.06568862268949016</v>
       </c>
       <c r="F74" t="n">
-        <v>0.05023924867827139</v>
+        <v>0.05023017156969963</v>
       </c>
       <c r="G74" t="n">
-        <v>0.04239930400619293</v>
+        <v>0.04235843527439449</v>
       </c>
       <c r="H74" t="n">
         <v>0.4181268703617883</v>
@@ -7188,22 +7188,22 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4560973693380577</v>
+        <v>0.4542130751402489</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4327602875442319</v>
+        <v>0.4310334236928344</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1753063497338901</v>
+        <v>0.1755934280046847</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1804258979309288</v>
+        <v>0.1803011153084425</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0867980355586728</v>
+        <v>0.08713615481167204</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0579626271862215</v>
+        <v>0.05772982088569409</v>
       </c>
       <c r="H75" t="n">
         <v>0.9740670823972597</v>
@@ -7279,22 +7279,22 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.04192308441823638</v>
+        <v>0.04190402432688011</v>
       </c>
       <c r="C76" t="n">
-        <v>0.03823689010608669</v>
+        <v>0.03822294516062082</v>
       </c>
       <c r="D76" t="n">
-        <v>0.03220530403184958</v>
+        <v>0.03216071636127796</v>
       </c>
       <c r="E76" t="n">
-        <v>0.02573356602782632</v>
+        <v>0.02569052495116572</v>
       </c>
       <c r="F76" t="n">
-        <v>0.03180020358458894</v>
+        <v>0.03176795759019635</v>
       </c>
       <c r="G76" t="n">
-        <v>0.01679730265803739</v>
+        <v>0.01672205313749527</v>
       </c>
       <c r="H76" t="n">
         <v>0.2724125086601074</v>
@@ -7370,22 +7370,22 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.04768038653178022</v>
+        <v>0.04764733386436493</v>
       </c>
       <c r="C77" t="n">
-        <v>0.03695758665776566</v>
+        <v>0.03692355398164706</v>
       </c>
       <c r="D77" t="n">
-        <v>0.02387395440319208</v>
+        <v>0.02383917914244807</v>
       </c>
       <c r="E77" t="n">
-        <v>0.01414324716831614</v>
+        <v>0.01399470194456426</v>
       </c>
       <c r="F77" t="n">
-        <v>0.02758504248195386</v>
+        <v>0.02756477793738716</v>
       </c>
       <c r="G77" t="n">
-        <v>0.01506285574563983</v>
+        <v>0.01498763737170674</v>
       </c>
       <c r="H77" t="n">
         <v>0.2823531843116658</v>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4451411360154857</v>
+        <v>0.4444992821767497</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4106466389541653</v>
+        <v>0.4101348426216624</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2273081823840675</v>
+        <v>0.2275686361497538</v>
       </c>
       <c r="E78" t="n">
-        <v>0.238598667621214</v>
+        <v>0.2387024405416951</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1260361984012641</v>
+        <v>0.1260107992817844</v>
       </c>
       <c r="G78" t="n">
-        <v>0.2277751361195661</v>
+        <v>0.0819179641126084</v>
       </c>
       <c r="H78" t="n">
         <v>0.9166327752016876</v>
@@ -7552,22 +7552,22 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.1931900827163729</v>
+        <v>0.1932363898385596</v>
       </c>
       <c r="C79" t="n">
-        <v>0.1849764482176594</v>
+        <v>0.1850036673335594</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1932565142188136</v>
+        <v>0.1933031750998877</v>
       </c>
       <c r="E79" t="n">
-        <v>0.1850535555573287</v>
+        <v>0.1850802429486281</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1537793017001665</v>
+        <v>0.1539351295724022</v>
       </c>
       <c r="G79" t="n">
-        <v>0.1519475677281417</v>
+        <v>0.1519821796184135</v>
       </c>
       <c r="H79" t="n">
         <v>0.4638560507984801</v>
@@ -7643,22 +7643,22 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.175731116853999</v>
+        <v>0.1752190649705639</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1949730517241973</v>
+        <v>0.1944322421102406</v>
       </c>
       <c r="D80" t="n">
-        <v>0.1955475094318966</v>
+        <v>0.1970372443381554</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1867454436277563</v>
+        <v>0.1879790580379595</v>
       </c>
       <c r="F80" t="n">
-        <v>0.09872816318761739</v>
+        <v>0.0961272633102709</v>
       </c>
       <c r="G80" t="n">
-        <v>0.1317774167889548</v>
+        <v>0.1308899371140212</v>
       </c>
       <c r="H80" t="n">
         <v>0.7015311782717396</v>
@@ -7734,22 +7734,22 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4149946399151719</v>
+        <v>0.4149511849690195</v>
       </c>
       <c r="C81" t="n">
-        <v>0.3398436331489901</v>
+        <v>0.3399825225936571</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2131007723176298</v>
+        <v>0.2131757775622734</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1441034777410879</v>
+        <v>0.1441485815991801</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1862702558919239</v>
+        <v>0.1863089226992002</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1408375197216066</v>
+        <v>0.03366730965498069</v>
       </c>
       <c r="H81" t="n">
         <v>0.7520441762890825</v>
@@ -7825,22 +7825,22 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.1210964294675984</v>
+        <v>0.121111731929245</v>
       </c>
       <c r="C82" t="n">
-        <v>0.06816893956209111</v>
+        <v>0.06816282604125026</v>
       </c>
       <c r="D82" t="n">
-        <v>0.1195755864341048</v>
+        <v>0.1195760005542537</v>
       </c>
       <c r="E82" t="n">
-        <v>0.06389656552322329</v>
+        <v>0.0638764252544349</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1229021731329112</v>
+        <v>0.1110014702854218</v>
       </c>
       <c r="G82" t="n">
-        <v>0.04599845336065581</v>
+        <v>0.04598841801666581</v>
       </c>
       <c r="H82" t="n">
         <v>0.2231897293196931</v>
@@ -7916,22 +7916,22 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5134568511776598</v>
+        <v>0.5119563434534087</v>
       </c>
       <c r="C83" t="n">
-        <v>0.4423549872220918</v>
+        <v>0.4410508919541843</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2253463356779155</v>
+        <v>0.2256345070835162</v>
       </c>
       <c r="E83" t="n">
-        <v>0.2058105708765144</v>
+        <v>0.2058574890401488</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1738792950713167</v>
+        <v>0.1734795778864761</v>
       </c>
       <c r="G83" t="n">
-        <v>0.05044383135062347</v>
+        <v>0.05044677325189047</v>
       </c>
       <c r="H83" t="n">
         <v>0.9954997516854572</v>
@@ -8007,22 +8007,22 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.318521834830125</v>
+        <v>0.3194071945251563</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3606749140695932</v>
+        <v>0.3589162983011352</v>
       </c>
       <c r="D84" t="n">
-        <v>0.5775798131984072</v>
+        <v>0.5785534935794894</v>
       </c>
       <c r="E84" t="n">
-        <v>0.2266939034529027</v>
+        <v>0.2284050313419277</v>
       </c>
       <c r="F84" t="n">
-        <v>0.3971354999046038</v>
+        <v>0.4663671631288341</v>
       </c>
       <c r="G84" t="n">
-        <v>0.2631346074869656</v>
+        <v>0.2607331512204985</v>
       </c>
       <c r="H84" t="n">
         <v>0.7662289278414284</v>
@@ -8098,22 +8098,22 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.1922771564913701</v>
+        <v>0.1923359170449181</v>
       </c>
       <c r="C85" t="n">
-        <v>0.1969659347380368</v>
+        <v>0.1970097092554824</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1158358232167569</v>
+        <v>0.1158897199714543</v>
       </c>
       <c r="E85" t="n">
-        <v>0.112450366577684</v>
+        <v>0.1124556441804483</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1124389031926789</v>
+        <v>0.1127077238682392</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1255143831906435</v>
+        <v>0.1256346624698693</v>
       </c>
       <c r="H85" t="n">
         <v>0.6211718381693592</v>
@@ -8189,22 +8189,22 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.2498146035911715</v>
+        <v>0.2499556281353499</v>
       </c>
       <c r="C86" t="n">
-        <v>0.2250743739489326</v>
+        <v>0.2252331980617254</v>
       </c>
       <c r="D86" t="n">
-        <v>0.1740465573592646</v>
+        <v>0.1740779038643475</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1468791610224586</v>
+        <v>0.1468793639473467</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1837310280784069</v>
+        <v>0.1838230688026703</v>
       </c>
       <c r="G86" t="n">
-        <v>0.1424008878147927</v>
+        <v>0.142514602367822</v>
       </c>
       <c r="H86" t="n">
         <v>0.5425971346865082</v>
@@ -8280,22 +8280,22 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.1240731402737125</v>
+        <v>0.1240604093010345</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1072150119112024</v>
+        <v>0.1071978813708681</v>
       </c>
       <c r="D87" t="n">
-        <v>0.1169118752503499</v>
+        <v>0.1169060832240041</v>
       </c>
       <c r="E87" t="n">
-        <v>0.08795776493967382</v>
+        <v>0.08794507664240567</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1275708098222418</v>
+        <v>0.1275708486215023</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0944734550986594</v>
+        <v>0.09447615231732255</v>
       </c>
       <c r="H87" t="n">
         <v>0.190759435338714</v>
@@ -8371,22 +8371,22 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.1239208804852275</v>
+        <v>0.1238731919185449</v>
       </c>
       <c r="C88" t="n">
-        <v>0.08946455253497157</v>
+        <v>0.08947279363317097</v>
       </c>
       <c r="D88" t="n">
-        <v>0.1238402298880464</v>
+        <v>0.123792963364035</v>
       </c>
       <c r="E88" t="n">
-        <v>0.08845743782659278</v>
+        <v>0.08847765151793209</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1385606646733512</v>
+        <v>0.1385066838424337</v>
       </c>
       <c r="G88" t="n">
-        <v>0.08658458350994461</v>
+        <v>0.08664933437953667</v>
       </c>
       <c r="H88" t="n">
         <v>0.4537308513006609</v>
@@ -8462,22 +8462,22 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.1952531656077584</v>
+        <v>0.1951489481705387</v>
       </c>
       <c r="C89" t="n">
-        <v>0.1879454717026323</v>
+        <v>0.187946565817732</v>
       </c>
       <c r="D89" t="n">
-        <v>0.1657094297541303</v>
+        <v>0.1658242759699738</v>
       </c>
       <c r="E89" t="n">
-        <v>0.155149130453718</v>
+        <v>0.1551290203080474</v>
       </c>
       <c r="F89" t="n">
-        <v>0.1264489626935457</v>
+        <v>0.1266136326211225</v>
       </c>
       <c r="G89" t="n">
-        <v>0.08279293124880685</v>
+        <v>0.08295620583559878</v>
       </c>
       <c r="H89" t="n">
         <v>0.6277099064094847</v>
@@ -8553,22 +8553,22 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8576937447960855</v>
+        <v>0.851641288101229</v>
       </c>
       <c r="C90" t="n">
-        <v>0.9888837269216366</v>
+        <v>0.9827987275038074</v>
       </c>
       <c r="D90" t="n">
-        <v>0.335330810253567</v>
+        <v>0.3313756532078322</v>
       </c>
       <c r="E90" t="n">
-        <v>0.3681962388429534</v>
+        <v>0.3633016339837019</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1236447422801688</v>
+        <v>0.1230211613322603</v>
       </c>
       <c r="G90" t="n">
-        <v>0.07722040900588766</v>
+        <v>0.0715019186153649</v>
       </c>
       <c r="H90" t="n">
         <v>1.486341126158328</v>
@@ -8644,22 +8644,22 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.1717056402946943</v>
+        <v>0.1715886472487698</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1673793892983393</v>
+        <v>0.1672718683817267</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1343344686536336</v>
+        <v>0.1343414382852662</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1396814974513655</v>
+        <v>0.1398835487213639</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1509017732246477</v>
+        <v>0.1509217889284667</v>
       </c>
       <c r="G91" t="n">
-        <v>0.1226821874121261</v>
+        <v>0.1227511203289512</v>
       </c>
       <c r="H91" t="n">
         <v>0.5756149882544659</v>
@@ -8735,22 +8735,22 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6147044898013377</v>
+        <v>0.6114058613149633</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6221435814253925</v>
+        <v>0.6188835198794747</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3035324591454729</v>
+        <v>0.3015688182367602</v>
       </c>
       <c r="E92" t="n">
-        <v>0.3126300896715725</v>
+        <v>0.3117066704258012</v>
       </c>
       <c r="F92" t="n">
-        <v>0.2512768139179935</v>
+        <v>0.2454608721067457</v>
       </c>
       <c r="G92" t="n">
-        <v>0.4659309995229357</v>
+        <v>0.4599910830755168</v>
       </c>
       <c r="H92" t="n">
         <v>1.236937243017472</v>
@@ -8826,22 +8826,22 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.2843717171365708</v>
+        <v>0.2836087797164917</v>
       </c>
       <c r="C93" t="n">
-        <v>0.07651056468218326</v>
+        <v>0.07626402299458676</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1386240743615314</v>
+        <v>0.1385453860409279</v>
       </c>
       <c r="E93" t="n">
-        <v>0.0638123239152574</v>
+        <v>0.06370154640865755</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1826741599737865</v>
+        <v>0.1822958885176758</v>
       </c>
       <c r="G93" t="n">
-        <v>0.05751739863306474</v>
+        <v>0.05734790026905284</v>
       </c>
       <c r="H93" t="n">
         <v>0.5594639660662479</v>
@@ -8917,22 +8917,22 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5591830735531318</v>
+        <v>0.5562814462312548</v>
       </c>
       <c r="C94" t="n">
-        <v>0.7640293208274819</v>
+        <v>0.7602738181432417</v>
       </c>
       <c r="D94" t="n">
-        <v>0.21454219956666</v>
+        <v>0.2147185884231523</v>
       </c>
       <c r="E94" t="n">
-        <v>0.2247824687911161</v>
+        <v>0.22472768731432</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1204703072800358</v>
+        <v>0.1216949268591854</v>
       </c>
       <c r="G94" t="n">
-        <v>0.04631353435453027</v>
+        <v>0.04585844286760153</v>
       </c>
       <c r="H94" t="n">
         <v>1.284271140273298</v>
@@ -9008,22 +9008,22 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.2090658748283882</v>
+        <v>0.2090727230288681</v>
       </c>
       <c r="C95" t="n">
-        <v>0.06780222432650819</v>
+        <v>0.06779898318107815</v>
       </c>
       <c r="D95" t="n">
-        <v>0.1351553226387834</v>
+        <v>0.1359860186100393</v>
       </c>
       <c r="E95" t="n">
-        <v>0.05691390605230952</v>
+        <v>0.05718820867172966</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1835927285279103</v>
+        <v>0.1835815220971968</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0480985175036994</v>
+        <v>0.04807203291518417</v>
       </c>
       <c r="H95" t="n">
         <v>0.2177031397462812</v>
@@ -9099,22 +9099,22 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.2305983237504276</v>
+        <v>0.2298170794510778</v>
       </c>
       <c r="C96" t="n">
-        <v>0.2236125043047838</v>
+        <v>0.2228704110745094</v>
       </c>
       <c r="D96" t="n">
-        <v>0.2306047675261316</v>
+        <v>0.2298270977191737</v>
       </c>
       <c r="E96" t="n">
-        <v>0.2236513630439132</v>
+        <v>0.2229081883567726</v>
       </c>
       <c r="F96" t="n">
-        <v>0.2707490597345554</v>
+        <v>0.2688802761517678</v>
       </c>
       <c r="G96" t="n">
-        <v>0.2638116311229061</v>
+        <v>0.2619678698744545</v>
       </c>
       <c r="H96" t="n">
         <v>0.7651940787133368</v>
@@ -9190,22 +9190,22 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.4467583021343722</v>
+        <v>0.4434412377655851</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2772564808734791</v>
+        <v>0.2743934654642279</v>
       </c>
       <c r="D97" t="n">
-        <v>0.1478972113645169</v>
+        <v>0.1451156598072634</v>
       </c>
       <c r="E97" t="n">
-        <v>0.1102132991859153</v>
+        <v>0.1098389418564554</v>
       </c>
       <c r="F97" t="n">
-        <v>0.2394548926561686</v>
+        <v>0.2344586657567671</v>
       </c>
       <c r="G97" t="n">
-        <v>0.1344857095114406</v>
+        <v>0.1304239853612469</v>
       </c>
       <c r="H97" t="n">
         <v>0.9127531883440781</v>
@@ -9281,22 +9281,22 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6829196404785</v>
+        <v>0.6787427039107512</v>
       </c>
       <c r="C98" t="n">
-        <v>0.4197310918247357</v>
+        <v>0.4161804193438561</v>
       </c>
       <c r="D98" t="n">
-        <v>0.2532451715449641</v>
+        <v>0.2525779471741121</v>
       </c>
       <c r="E98" t="n">
-        <v>0.1570934386527884</v>
+        <v>0.1566084371026206</v>
       </c>
       <c r="F98" t="n">
-        <v>0.5242744569073967</v>
+        <v>0.5192000253282574</v>
       </c>
       <c r="G98" t="n">
-        <v>0.2277043817293981</v>
+        <v>0.2244813107035448</v>
       </c>
       <c r="H98" t="n">
         <v>1.04262150654369</v>
@@ -9372,22 +9372,22 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.3061434163667398</v>
+        <v>0.305369551818179</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0849367447967064</v>
+        <v>0.08501400414635085</v>
       </c>
       <c r="D99" t="n">
-        <v>0.1922713566412032</v>
+        <v>0.1922113398975273</v>
       </c>
       <c r="E99" t="n">
-        <v>0.09003259155030501</v>
+        <v>0.09005612711458374</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1733703766554069</v>
+        <v>0.1735929115223013</v>
       </c>
       <c r="G99" t="n">
-        <v>0.05422877064175191</v>
+        <v>0.05422358934998087</v>
       </c>
       <c r="H99" t="n">
         <v>0.4678895287272094</v>
@@ -9463,22 +9463,22 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.03570898262747438</v>
+        <v>0.03570937735397713</v>
       </c>
       <c r="C100" t="n">
-        <v>0.02739077908604821</v>
+        <v>0.02738594428316249</v>
       </c>
       <c r="D100" t="n">
-        <v>0.01981534658050626</v>
+        <v>0.01980409352840092</v>
       </c>
       <c r="E100" t="n">
-        <v>0.01400818481728265</v>
+        <v>0.01398467594595955</v>
       </c>
       <c r="F100" t="n">
-        <v>0.02687533143881958</v>
+        <v>0.02687075178124612</v>
       </c>
       <c r="G100" t="n">
-        <v>0.01773998963467797</v>
+        <v>0.01773001477149008</v>
       </c>
       <c r="H100" t="n">
         <v>0.1147432029708231</v>
@@ -9554,22 +9554,22 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1.279760791213202</v>
+        <v>1.269122362460018</v>
       </c>
       <c r="C101" t="n">
-        <v>1.255553344220396</v>
+        <v>1.245016936279405</v>
       </c>
       <c r="D101" t="n">
-        <v>0.5276659040889232</v>
+        <v>0.5164604176611134</v>
       </c>
       <c r="E101" t="n">
-        <v>0.5172632476958068</v>
+        <v>0.505857146288878</v>
       </c>
       <c r="F101" t="n">
-        <v>0.3201913892413951</v>
+        <v>0.2839539280448209</v>
       </c>
       <c r="G101" t="n">
-        <v>0.3453364852878835</v>
+        <v>0.3073713787483474</v>
       </c>
       <c r="H101" t="n">
         <v>2.029460048637381</v>
@@ -9645,22 +9645,22 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.1346145233633526</v>
+        <v>0.1347231018369469</v>
       </c>
       <c r="C102" t="n">
-        <v>0.1092314534953667</v>
+        <v>0.1093283019514915</v>
       </c>
       <c r="D102" t="n">
-        <v>0.07341275131329915</v>
+        <v>0.07341330073597337</v>
       </c>
       <c r="E102" t="n">
-        <v>0.07022701871687015</v>
+        <v>0.07022790823368349</v>
       </c>
       <c r="F102" t="n">
-        <v>0.02971926623301586</v>
+        <v>0.02963224866141808</v>
       </c>
       <c r="G102" t="n">
-        <v>0.01625671930986485</v>
+        <v>0.01619418875840192</v>
       </c>
       <c r="H102" t="n">
         <v>0.3786825381440391</v>
@@ -9736,22 +9736,22 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6821826283417045</v>
+        <v>0.6769493513436099</v>
       </c>
       <c r="C103" t="n">
-        <v>0.8036315011375185</v>
+        <v>0.798537516284292</v>
       </c>
       <c r="D103" t="n">
-        <v>0.288366049971629</v>
+        <v>0.2875408832550455</v>
       </c>
       <c r="E103" t="n">
-        <v>0.2389954831576384</v>
+        <v>0.2341508587038877</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1588875832806832</v>
+        <v>0.1556238400776608</v>
       </c>
       <c r="G103" t="n">
-        <v>0.303290637923062</v>
+        <v>0.2936473213257534</v>
       </c>
       <c r="H103" t="n">
         <v>1.33446238571039</v>
@@ -9827,22 +9827,22 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.02382371000229128</v>
+        <v>0.02377991177491433</v>
       </c>
       <c r="C104" t="n">
-        <v>0.02412986494980979</v>
+        <v>0.02408800107344168</v>
       </c>
       <c r="D104" t="n">
-        <v>0.003891128287518297</v>
+        <v>0.003640944143433588</v>
       </c>
       <c r="E104" t="n">
-        <v>0.003903726054257696</v>
+        <v>0.003674887242874753</v>
       </c>
       <c r="F104" t="n">
-        <v>0.00256754203938992</v>
+        <v>0.002201955455974289</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0027444286909228</v>
+        <v>0.002460924717737135</v>
       </c>
       <c r="H104" t="n">
         <v>0.2493107544939339</v>
@@ -9918,22 +9918,22 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.01875795019854319</v>
+        <v>0.01872513860902862</v>
       </c>
       <c r="C105" t="n">
-        <v>0.01920085534960884</v>
+        <v>0.0191816106692629</v>
       </c>
       <c r="D105" t="n">
-        <v>0.003410800873290537</v>
+        <v>0.003130964892837188</v>
       </c>
       <c r="E105" t="n">
-        <v>0.003462519821082707</v>
+        <v>0.003164611608152304</v>
       </c>
       <c r="F105" t="n">
-        <v>0.002070749657900144</v>
+        <v>0.00155447383305144</v>
       </c>
       <c r="G105" t="n">
-        <v>0.002337794684092714</v>
+        <v>0.001912032883378575</v>
       </c>
       <c r="H105" t="n">
         <v>0.2431184488471118</v>
@@ -10009,22 +10009,22 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.01211857737633174</v>
+        <v>0.01204319505269798</v>
       </c>
       <c r="C106" t="n">
-        <v>0.01240567385470582</v>
+        <v>0.01230733996979118</v>
       </c>
       <c r="D106" t="n">
-        <v>0.008345759369360122</v>
+        <v>0.008199495044937994</v>
       </c>
       <c r="E106" t="n">
-        <v>0.008195547529182877</v>
+        <v>0.008032603095585979</v>
       </c>
       <c r="F106" t="n">
-        <v>0.003549546306436448</v>
+        <v>0.003307434042000564</v>
       </c>
       <c r="G106" t="n">
-        <v>0.002961116073382836</v>
+        <v>0.002677679931586795</v>
       </c>
       <c r="H106" t="n">
         <v>0.2447316180012817</v>
@@ -10100,22 +10100,22 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.02162785341314849</v>
+        <v>0.02153316687310626</v>
       </c>
       <c r="C107" t="n">
-        <v>0.01974487678779715</v>
+        <v>0.01972830073866649</v>
       </c>
       <c r="D107" t="n">
-        <v>0.02647420065543236</v>
+        <v>0.02646514799710868</v>
       </c>
       <c r="E107" t="n">
-        <v>0.0229287772940192</v>
+        <v>0.02290938582251965</v>
       </c>
       <c r="F107" t="n">
-        <v>0.009427342827301241</v>
+        <v>0.009388846963103834</v>
       </c>
       <c r="G107" t="n">
-        <v>0.005634852582150887</v>
+        <v>0.005463932710701695</v>
       </c>
       <c r="H107" t="n">
         <v>0.2967165783205413</v>
@@ -10191,22 +10191,22 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.01792427212202553</v>
+        <v>0.01791706659157739</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0158706180630374</v>
+        <v>0.01581371573199286</v>
       </c>
       <c r="D108" t="n">
-        <v>0.008987180292485672</v>
+        <v>0.008814244373738274</v>
       </c>
       <c r="E108" t="n">
-        <v>0.009136679650261695</v>
+        <v>0.009026150616503959</v>
       </c>
       <c r="F108" t="n">
-        <v>0.006034511699066506</v>
+        <v>0.005861369084486108</v>
       </c>
       <c r="G108" t="n">
-        <v>0.00390524413825604</v>
+        <v>0.003647078978879365</v>
       </c>
       <c r="H108" t="n">
         <v>0.2496204874837848</v>
@@ -10282,22 +10282,22 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.07969118302103703</v>
+        <v>0.07971662478351171</v>
       </c>
       <c r="C109" t="n">
-        <v>0.07885551632454917</v>
+        <v>0.07889825329983721</v>
       </c>
       <c r="D109" t="n">
-        <v>0.01476412503290059</v>
+        <v>0.01427659271396422</v>
       </c>
       <c r="E109" t="n">
-        <v>0.01449679666553838</v>
+        <v>0.01388344896525143</v>
       </c>
       <c r="F109" t="n">
-        <v>0.006128649794285152</v>
+        <v>0.005321316602960769</v>
       </c>
       <c r="G109" t="n">
-        <v>0.007122468771629018</v>
+        <v>0.006561773245746303</v>
       </c>
       <c r="H109" t="n">
         <v>0.4667631816385235</v>
@@ -10373,22 +10373,22 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.3400643999581208</v>
+        <v>0.338673679163203</v>
       </c>
       <c r="C110" t="n">
-        <v>0.3372322383771206</v>
+        <v>0.3358569056264085</v>
       </c>
       <c r="D110" t="n">
-        <v>0.1435398675811958</v>
+        <v>0.1435643577651277</v>
       </c>
       <c r="E110" t="n">
-        <v>0.147447388732114</v>
+        <v>0.1475108871310485</v>
       </c>
       <c r="F110" t="n">
-        <v>0.05842332243852807</v>
+        <v>0.05813966215239565</v>
       </c>
       <c r="G110" t="n">
-        <v>0.04556782809660388</v>
+        <v>0.04528488687097919</v>
       </c>
       <c r="H110" t="n">
         <v>0.9342361934783976</v>
@@ -10464,22 +10464,22 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5591421456199412</v>
+        <v>0.5578491714602538</v>
       </c>
       <c r="C111" t="n">
-        <v>0.5674442055444691</v>
+        <v>0.5661357504748894</v>
       </c>
       <c r="D111" t="n">
-        <v>0.2243371809869525</v>
+        <v>0.2243613947745872</v>
       </c>
       <c r="E111" t="n">
-        <v>0.2286475797645283</v>
+        <v>0.2286469892752312</v>
       </c>
       <c r="F111" t="n">
-        <v>0.02959033678276873</v>
+        <v>0.0292443205140462</v>
       </c>
       <c r="G111" t="n">
-        <v>0.02286796641940448</v>
+        <v>0.02252490293825131</v>
       </c>
       <c r="H111" t="n">
         <v>1.084354343907561</v>
@@ -10555,22 +10555,22 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.08166888814237851</v>
+        <v>0.08165173022679861</v>
       </c>
       <c r="C112" t="n">
-        <v>0.08269349664589358</v>
+        <v>0.08267082197597263</v>
       </c>
       <c r="D112" t="n">
-        <v>0.08174200124607806</v>
+        <v>0.08172452093387636</v>
       </c>
       <c r="E112" t="n">
-        <v>0.0827735265571856</v>
+        <v>0.08275130808887045</v>
       </c>
       <c r="F112" t="n">
-        <v>0.06501121579889166</v>
+        <v>0.06040328728484097</v>
       </c>
       <c r="G112" t="n">
-        <v>0.05187495246131572</v>
+        <v>0.05186814533372432</v>
       </c>
       <c r="H112" t="n">
         <v>0.2052640089593039</v>
@@ -10646,22 +10646,22 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.1736170819464353</v>
+        <v>0.1722189490412641</v>
       </c>
       <c r="C113" t="n">
-        <v>0.2081410617551657</v>
+        <v>0.2067786093847541</v>
       </c>
       <c r="D113" t="n">
-        <v>0.2108848407534259</v>
+        <v>0.2123419213179572</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1884899539434938</v>
+        <v>0.1907740175572568</v>
       </c>
       <c r="F113" t="n">
-        <v>0.09597528307177164</v>
+        <v>0.09584238782839646</v>
       </c>
       <c r="G113" t="n">
-        <v>0.1286399983643523</v>
+        <v>0.1266408387294835</v>
       </c>
       <c r="H113" t="n">
         <v>0.745973544696887</v>
@@ -10737,22 +10737,22 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.3607080039561872</v>
+        <v>0.3599753228277472</v>
       </c>
       <c r="C114" t="n">
-        <v>0.3485392636705892</v>
+        <v>0.3479094458485996</v>
       </c>
       <c r="D114" t="n">
-        <v>0.2091398685758772</v>
+        <v>0.2096078388930629</v>
       </c>
       <c r="E114" t="n">
-        <v>0.2161324775894491</v>
+        <v>0.2163222654467029</v>
       </c>
       <c r="F114" t="n">
-        <v>0.1430504572892343</v>
+        <v>0.1424997212317195</v>
       </c>
       <c r="G114" t="n">
-        <v>0.1026486248074793</v>
+        <v>0.1025364772341436</v>
       </c>
       <c r="H114" t="n">
         <v>0.8791106428021422</v>
@@ -10828,22 +10828,22 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.02022255179434573</v>
+        <v>0.02021158961578566</v>
       </c>
       <c r="C115" t="n">
-        <v>0.01734680018096111</v>
+        <v>0.01729822771882028</v>
       </c>
       <c r="D115" t="n">
-        <v>0.020610549561881</v>
+        <v>0.02058469708962286</v>
       </c>
       <c r="E115" t="n">
-        <v>0.01874731439354337</v>
+        <v>0.0187326166190581</v>
       </c>
       <c r="F115" t="n">
-        <v>0.01717631079170108</v>
+        <v>0.01715861651359383</v>
       </c>
       <c r="G115" t="n">
-        <v>0.01512689979810011</v>
+        <v>0.01510815666149116</v>
       </c>
       <c r="H115" t="n">
         <v>0.2183882729589028</v>
@@ -10919,22 +10919,22 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.01293262924810876</v>
+        <v>0.01290233207349537</v>
       </c>
       <c r="C116" t="n">
-        <v>0.009898062763932116</v>
+        <v>0.009877437073773239</v>
       </c>
       <c r="D116" t="n">
-        <v>0.01098410169691732</v>
+        <v>0.01094289681395057</v>
       </c>
       <c r="E116" t="n">
-        <v>0.009061516450549619</v>
+        <v>0.009040412149458974</v>
       </c>
       <c r="F116" t="n">
-        <v>0.01008626824784472</v>
+        <v>0.01003031349869805</v>
       </c>
       <c r="G116" t="n">
-        <v>0.007653463469987432</v>
+        <v>0.007630477235657111</v>
       </c>
       <c r="H116" t="n">
         <v>0.1647401054134016</v>
@@ -11010,22 +11010,22 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.02326392553017943</v>
+        <v>0.02325353304454688</v>
       </c>
       <c r="C117" t="n">
-        <v>0.02250538219734631</v>
+        <v>0.02247224324170698</v>
       </c>
       <c r="D117" t="n">
-        <v>0.01843051430379153</v>
+        <v>0.01841598235315933</v>
       </c>
       <c r="E117" t="n">
-        <v>0.01964576803818497</v>
+        <v>0.01963921488424883</v>
       </c>
       <c r="F117" t="n">
-        <v>0.01577672484035846</v>
+        <v>0.01575754964659502</v>
       </c>
       <c r="G117" t="n">
-        <v>0.009606419944413629</v>
+        <v>0.009563741301986037</v>
       </c>
       <c r="H117" t="n">
         <v>0.1959608041850188</v>
@@ -11101,22 +11101,22 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.1218293490008251</v>
+        <v>0.1218405131979036</v>
       </c>
       <c r="C118" t="n">
-        <v>0.09220865952051852</v>
+        <v>0.09221947074630707</v>
       </c>
       <c r="D118" t="n">
-        <v>0.144616355368143</v>
+        <v>0.1446887830834837</v>
       </c>
       <c r="E118" t="n">
-        <v>0.09221646573179659</v>
+        <v>0.0922271888526006</v>
       </c>
       <c r="F118" t="n">
-        <v>0.1294307987901991</v>
+        <v>0.1294281403152775</v>
       </c>
       <c r="G118" t="n">
-        <v>0.09627478451649035</v>
+        <v>0.09627114333082984</v>
       </c>
       <c r="H118" t="n">
         <v>0.2169573885097784</v>
@@ -11192,22 +11192,22 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.03284540274001947</v>
+        <v>0.03283609681991959</v>
       </c>
       <c r="C119" t="n">
-        <v>0.02796987764592603</v>
+        <v>0.02796112559499681</v>
       </c>
       <c r="D119" t="n">
-        <v>0.020483832974817</v>
+        <v>0.02045853025362208</v>
       </c>
       <c r="E119" t="n">
-        <v>0.01809470170044845</v>
+        <v>0.01807704344729608</v>
       </c>
       <c r="F119" t="n">
-        <v>0.02255881370627735</v>
+        <v>0.02254108714559968</v>
       </c>
       <c r="G119" t="n">
-        <v>0.01457184340721434</v>
+        <v>0.0145467006253405</v>
       </c>
       <c r="H119" t="n">
         <v>0.1861185602553873</v>
@@ -11283,22 +11283,22 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.07923430657206081</v>
+        <v>0.07921871292780576</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0950327243814096</v>
+        <v>0.09502436808439847</v>
       </c>
       <c r="D120" t="n">
-        <v>0.0507612211309937</v>
+        <v>0.05073765715169388</v>
       </c>
       <c r="E120" t="n">
-        <v>0.04967587733612646</v>
+        <v>0.04964641415830182</v>
       </c>
       <c r="F120" t="n">
-        <v>0.03890910910015466</v>
+        <v>0.0388933245606785</v>
       </c>
       <c r="G120" t="n">
-        <v>0.03667968735316986</v>
+        <v>0.03665548244577988</v>
       </c>
       <c r="H120" t="n">
         <v>0.278485987840173</v>
@@ -11374,22 +11374,22 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.2241120651840995</v>
+        <v>0.2241892993310552</v>
       </c>
       <c r="C121" t="n">
-        <v>0.1890845800804842</v>
+        <v>0.1891646081037996</v>
       </c>
       <c r="D121" t="n">
-        <v>0.2171356640255903</v>
+        <v>0.2171485135331446</v>
       </c>
       <c r="E121" t="n">
-        <v>0.1381698460164195</v>
+        <v>0.1386901139235041</v>
       </c>
       <c r="F121" t="n">
-        <v>0.2073808378199536</v>
+        <v>0.2069526856014565</v>
       </c>
       <c r="G121" t="n">
-        <v>0.1388555602519722</v>
+        <v>0.1389351326072474</v>
       </c>
       <c r="H121" t="n">
         <v>0.4358591106778351</v>
@@ -11465,22 +11465,22 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.06366449065049024</v>
+        <v>0.06365863891746464</v>
       </c>
       <c r="C122" t="n">
-        <v>0.06158459413170859</v>
+        <v>0.0615775885085238</v>
       </c>
       <c r="D122" t="n">
-        <v>0.06359608007490654</v>
+        <v>0.06358799352742592</v>
       </c>
       <c r="E122" t="n">
-        <v>0.06696826455044233</v>
+        <v>0.06698909068954209</v>
       </c>
       <c r="F122" t="n">
-        <v>0.05689703599904646</v>
+        <v>0.05688364621664244</v>
       </c>
       <c r="G122" t="n">
-        <v>0.06124543786926742</v>
+        <v>0.06123296493304392</v>
       </c>
       <c r="H122" t="n">
         <v>0.2375175161157313</v>
@@ -11556,22 +11556,22 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.2223906463592042</v>
+        <v>0.2226470905945946</v>
       </c>
       <c r="C123" t="n">
-        <v>0.1684052107591407</v>
+        <v>0.1686449970047895</v>
       </c>
       <c r="D123" t="n">
-        <v>0.09655907990974942</v>
+        <v>0.09651406649233034</v>
       </c>
       <c r="E123" t="n">
-        <v>0.07652871069541536</v>
+        <v>0.07644803716239706</v>
       </c>
       <c r="F123" t="n">
-        <v>0.06384418923809534</v>
+        <v>0.06379250422547776</v>
       </c>
       <c r="G123" t="n">
-        <v>0.03258323150260768</v>
+        <v>0.03249822400684612</v>
       </c>
       <c r="H123" t="n">
         <v>0.5139083244130161</v>
@@ -11647,22 +11647,22 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.7633572061806128</v>
+        <v>0.7585346179015962</v>
       </c>
       <c r="C124" t="n">
-        <v>0.3974864585217165</v>
+        <v>0.3942418871289511</v>
       </c>
       <c r="D124" t="n">
-        <v>0.374815161830878</v>
+        <v>0.3716174743086698</v>
       </c>
       <c r="E124" t="n">
-        <v>0.3256464167387856</v>
+        <v>0.3237645424919536</v>
       </c>
       <c r="F124" t="n">
-        <v>0.6727522773730734</v>
+        <v>0.6111573091285377</v>
       </c>
       <c r="G124" t="n">
-        <v>0.3375658125797012</v>
+        <v>0.3321400275213003</v>
       </c>
       <c r="H124" t="n">
         <v>1.052655847663158</v>
@@ -11738,22 +11738,22 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.05719778995349321</v>
+        <v>0.05719951475991292</v>
       </c>
       <c r="C125" t="n">
-        <v>0.05504196992996413</v>
+        <v>0.05504893381062918</v>
       </c>
       <c r="D125" t="n">
-        <v>0.05669198293535255</v>
+        <v>0.05669457303367327</v>
       </c>
       <c r="E125" t="n">
-        <v>0.05205516902535588</v>
+        <v>0.05204902493524494</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0477516000263609</v>
+        <v>0.04775026666182813</v>
       </c>
       <c r="G125" t="n">
-        <v>0.03778690027441944</v>
+        <v>0.03777362384639651</v>
       </c>
       <c r="H125" t="n">
         <v>0.2993369040417522</v>
@@ -11829,22 +11829,22 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5542821547541514</v>
+        <v>0.5529922509464232</v>
       </c>
       <c r="C126" t="n">
-        <v>0.4761265700246667</v>
+        <v>0.474918692242627</v>
       </c>
       <c r="D126" t="n">
-        <v>0.2677585566763096</v>
+        <v>0.2679024991233426</v>
       </c>
       <c r="E126" t="n">
-        <v>0.2364746105131447</v>
+        <v>0.2365847788786888</v>
       </c>
       <c r="F126" t="n">
-        <v>0.3231364362126281</v>
+        <v>0.3219415576863928</v>
       </c>
       <c r="G126" t="n">
-        <v>0.2885525063476767</v>
+        <v>0.2876243678071118</v>
       </c>
       <c r="H126" t="n">
         <v>1.006886985595747</v>
@@ -11920,22 +11920,22 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.03650091120697645</v>
+        <v>0.03650158404054951</v>
       </c>
       <c r="C127" t="n">
-        <v>0.02896218865509</v>
+        <v>0.02895631630547025</v>
       </c>
       <c r="D127" t="n">
-        <v>0.01622234106303301</v>
+        <v>0.01619054670682294</v>
       </c>
       <c r="E127" t="n">
-        <v>0.01404682664169479</v>
+        <v>0.01402809734912791</v>
       </c>
       <c r="F127" t="n">
-        <v>0.02230770290649821</v>
+        <v>0.02228105413134626</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01395674153317657</v>
+        <v>0.0139226020496163</v>
       </c>
       <c r="H127" t="n">
         <v>0.129182604735649</v>
@@ -12011,22 +12011,22 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.2548188455773535</v>
+        <v>0.253491479971056</v>
       </c>
       <c r="C128" t="n">
-        <v>0.2902292829210268</v>
+        <v>0.2890656229940394</v>
       </c>
       <c r="D128" t="n">
-        <v>0.3512355044054678</v>
+        <v>0.3593494865653111</v>
       </c>
       <c r="E128" t="n">
-        <v>0.2825370106397438</v>
+        <v>0.2861089264105197</v>
       </c>
       <c r="F128" t="n">
-        <v>0.1637980136788706</v>
+        <v>0.1625873721559921</v>
       </c>
       <c r="G128" t="n">
-        <v>0.2343844979357377</v>
+        <v>0.2322339454102383</v>
       </c>
       <c r="H128" t="n">
         <v>0.7778554304874405</v>
@@ -12102,22 +12102,22 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.1398974881555076</v>
+        <v>0.1400063429155644</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0789832111609249</v>
+        <v>0.07897339022108103</v>
       </c>
       <c r="D129" t="n">
-        <v>0.1171150530365744</v>
+        <v>0.1171254611661385</v>
       </c>
       <c r="E129" t="n">
-        <v>0.07671664578867474</v>
+        <v>0.07668414077933325</v>
       </c>
       <c r="F129" t="n">
-        <v>0.1497395132029042</v>
+        <v>0.1497915095063004</v>
       </c>
       <c r="G129" t="n">
-        <v>0.08042910193524888</v>
+        <v>0.08045171975076212</v>
       </c>
       <c r="H129" t="n">
         <v>0.3482352089914686</v>
@@ -12193,22 +12193,22 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.1916403163303129</v>
+        <v>0.1908012545303878</v>
       </c>
       <c r="C130" t="n">
-        <v>0.1188137424074162</v>
+        <v>0.1182962977352434</v>
       </c>
       <c r="D130" t="n">
-        <v>0.1305723396332828</v>
+        <v>0.1304517353996944</v>
       </c>
       <c r="E130" t="n">
-        <v>0.09241961747205141</v>
+        <v>0.09225806483811053</v>
       </c>
       <c r="F130" t="n">
-        <v>0.1619272524291063</v>
+        <v>0.1613767118169882</v>
       </c>
       <c r="G130" t="n">
-        <v>0.08525567358200996</v>
+        <v>0.08503258249906945</v>
       </c>
       <c r="H130" t="n">
         <v>0.5850765240017057</v>
@@ -12284,22 +12284,22 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.8212051835409249</v>
+        <v>0.8152825961161358</v>
       </c>
       <c r="C131" t="n">
-        <v>0.570814659812197</v>
+        <v>0.5652462685629582</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3061815579964894</v>
+        <v>0.2955284003542695</v>
       </c>
       <c r="E131" t="n">
-        <v>0.1665759667256722</v>
+        <v>0.1615649595201772</v>
       </c>
       <c r="F131" t="n">
-        <v>0.4829360777201449</v>
+        <v>0.4711296942484131</v>
       </c>
       <c r="G131" t="n">
-        <v>0.2793888278313847</v>
+        <v>0.2685951569330928</v>
       </c>
       <c r="H131" t="n">
         <v>1.40754481138985</v>
@@ -12375,22 +12375,22 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.7689287446491848</v>
+        <v>0.7647581908225013</v>
       </c>
       <c r="C132" t="n">
-        <v>0.690232064500526</v>
+        <v>0.6863422191730941</v>
       </c>
       <c r="D132" t="n">
-        <v>0.2285178705926094</v>
+        <v>0.2281312667962338</v>
       </c>
       <c r="E132" t="n">
-        <v>0.2225362651727793</v>
+        <v>0.222277567520809</v>
       </c>
       <c r="F132" t="n">
-        <v>0.08923388626328596</v>
+        <v>0.08864482897389499</v>
       </c>
       <c r="G132" t="n">
-        <v>0.2926567027267167</v>
+        <v>0.07691070227921051</v>
       </c>
       <c r="H132" t="n">
         <v>1.310460382339101</v>
@@ -12466,22 +12466,22 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.2354275534748884</v>
+        <v>0.2348288727096076</v>
       </c>
       <c r="C133" t="n">
-        <v>0.2399057276373681</v>
+        <v>0.2392856746235035</v>
       </c>
       <c r="D133" t="n">
-        <v>0.1913815735907635</v>
+        <v>0.1962088237240728</v>
       </c>
       <c r="E133" t="n">
-        <v>0.1894000350173234</v>
+        <v>0.1945936210871995</v>
       </c>
       <c r="F133" t="n">
-        <v>0.1348361291519312</v>
+        <v>0.1342255630003297</v>
       </c>
       <c r="G133" t="n">
-        <v>0.1481791939828249</v>
+        <v>0.1473403754110973</v>
       </c>
       <c r="H133" t="n">
         <v>0.7232811916098527</v>
@@ -12557,22 +12557,22 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.6920785936621305</v>
+        <v>0.6887473965641584</v>
       </c>
       <c r="C134" t="n">
-        <v>0.6380441251544235</v>
+        <v>0.6346983240754389</v>
       </c>
       <c r="D134" t="n">
-        <v>0.2605160855994468</v>
+        <v>0.2583821305102311</v>
       </c>
       <c r="E134" t="n">
-        <v>0.2435661535021833</v>
+        <v>0.2418845112857763</v>
       </c>
       <c r="F134" t="n">
-        <v>0.1627990067419064</v>
+        <v>0.1597810507090881</v>
       </c>
       <c r="G134" t="n">
-        <v>0.2756199639496786</v>
+        <v>0.08098745874854847</v>
       </c>
       <c r="H134" t="n">
         <v>1.245537054766756</v>
@@ -12648,22 +12648,22 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.1819793153000726</v>
+        <v>0.1816021101124735</v>
       </c>
       <c r="C135" t="n">
-        <v>0.1933850581528877</v>
+        <v>0.1928933544962687</v>
       </c>
       <c r="D135" t="n">
-        <v>0.1743715090208504</v>
+        <v>0.1745069929684225</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1788194337159455</v>
+        <v>0.1791007718575811</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1333808618288841</v>
+        <v>0.1331865354292969</v>
       </c>
       <c r="G135" t="n">
-        <v>0.1541852293420014</v>
+        <v>0.1536726285392772</v>
       </c>
       <c r="H135" t="n">
         <v>0.6575556533639743</v>
@@ -12739,22 +12739,22 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1.011407331524651</v>
+        <v>1.007407621476734</v>
       </c>
       <c r="C136" t="n">
-        <v>0.3791329657605487</v>
+        <v>0.3757043281926236</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4931784823591041</v>
+        <v>0.4880784621961658</v>
       </c>
       <c r="E136" t="n">
-        <v>0.1196984841591649</v>
+        <v>0.1184755234831405</v>
       </c>
       <c r="F136" t="n">
-        <v>1.001696631873696</v>
+        <v>0.9951678084714012</v>
       </c>
       <c r="G136" t="n">
-        <v>0.2352065499382154</v>
+        <v>0.2308892510447274</v>
       </c>
       <c r="H136" t="n">
         <v>1.272182588215972</v>
@@ -12830,22 +12830,22 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.1937248717271416</v>
+        <v>0.1937346794248321</v>
       </c>
       <c r="C137" t="n">
-        <v>0.1089048181743816</v>
+        <v>0.1089455831871634</v>
       </c>
       <c r="D137" t="n">
-        <v>0.172903304215616</v>
+        <v>0.172917248430325</v>
       </c>
       <c r="E137" t="n">
-        <v>0.1170661748165055</v>
+        <v>0.1218183725123083</v>
       </c>
       <c r="F137" t="n">
-        <v>0.172928447549581</v>
+        <v>0.17293474736815</v>
       </c>
       <c r="G137" t="n">
-        <v>0.09222641480147931</v>
+        <v>0.09230734109950871</v>
       </c>
       <c r="H137" t="n">
         <v>0.4595522319585268</v>
@@ -12921,22 +12921,22 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1.563554567728067</v>
+        <v>1.549862196537567</v>
       </c>
       <c r="C138" t="n">
-        <v>1.603845610262348</v>
+        <v>1.590507209360802</v>
       </c>
       <c r="D138" t="n">
-        <v>0.6147355877298267</v>
+        <v>0.6004014670049019</v>
       </c>
       <c r="E138" t="n">
-        <v>0.6271805761179865</v>
+        <v>0.6105112088913315</v>
       </c>
       <c r="F138" t="n">
-        <v>0.3444720903685026</v>
+        <v>0.3319022122488025</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2547601048684854</v>
+        <v>0.2227867282754526</v>
       </c>
       <c r="H138" t="n">
         <v>2.199285093667711</v>
@@ -13012,22 +13012,22 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.3662744880133005</v>
+        <v>0.3635880978496436</v>
       </c>
       <c r="C139" t="n">
-        <v>0.500775383654272</v>
+        <v>0.4978721268489525</v>
       </c>
       <c r="D139" t="n">
-        <v>0.1491487849298938</v>
+        <v>0.1498983836600324</v>
       </c>
       <c r="E139" t="n">
-        <v>0.1159372083374286</v>
+        <v>0.1149687412666042</v>
       </c>
       <c r="F139" t="n">
-        <v>0.092584640881574</v>
+        <v>0.09330537550397505</v>
       </c>
       <c r="G139" t="n">
-        <v>0.07558489368647045</v>
+        <v>0.07368648617630229</v>
       </c>
       <c r="H139" t="n">
         <v>1.034221944058446</v>
@@ -13103,22 +13103,22 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.9622878130602048</v>
+        <v>0.9581039195892079</v>
       </c>
       <c r="C140" t="n">
-        <v>1.212627717261468</v>
+        <v>1.207946375398225</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4386191876296217</v>
+        <v>0.4384642657719623</v>
       </c>
       <c r="E140" t="n">
-        <v>0.4751017764463643</v>
+        <v>0.4741890041090594</v>
       </c>
       <c r="F140" t="n">
-        <v>0.211738264644283</v>
+        <v>0.2128691352265779</v>
       </c>
       <c r="G140" t="n">
-        <v>0.06111400872981042</v>
+        <v>0.06025794860952925</v>
       </c>
       <c r="H140" t="n">
         <v>1.568007141874413</v>
@@ -13194,22 +13194,22 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.1697730569607195</v>
+        <v>0.1698329778236009</v>
       </c>
       <c r="C141" t="n">
-        <v>0.1706645246156291</v>
+        <v>0.1706942218668353</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2641900630602997</v>
+        <v>0.2749456006769462</v>
       </c>
       <c r="E141" t="n">
-        <v>0.2612831845767706</v>
+        <v>0.2773735266827101</v>
       </c>
       <c r="F141" t="n">
-        <v>0.1735547986916973</v>
+        <v>0.1737068670438273</v>
       </c>
       <c r="G141" t="n">
-        <v>0.1691401972767189</v>
+        <v>0.1692451199044345</v>
       </c>
       <c r="H141" t="n">
         <v>0.3989257195156556</v>
@@ -13281,22 +13281,22 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4222540350733293</v>
+        <v>0.4194283264069655</v>
       </c>
       <c r="C142" t="n">
-        <v>0.404470814232269</v>
+        <v>0.4017050193022286</v>
       </c>
       <c r="D142" t="n">
-        <v>0.1415481519353839</v>
+        <v>0.1411518451782344</v>
       </c>
       <c r="E142" t="n">
-        <v>0.1337120246751101</v>
+        <v>0.1336859351688658</v>
       </c>
       <c r="F142" t="n">
-        <v>0.07513910876814404</v>
+        <v>0.07356074306436632</v>
       </c>
       <c r="G142" t="n">
-        <v>0.03954291976834542</v>
+        <v>0.03801065915547484</v>
       </c>
       <c r="H142" t="n">
         <v>0.9837663146858279</v>
@@ -13372,22 +13372,22 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.2619724860018365</v>
+        <v>0.2604630716950514</v>
       </c>
       <c r="C143" t="n">
-        <v>0.2513362772565932</v>
+        <v>0.2501518267356753</v>
       </c>
       <c r="D143" t="n">
-        <v>0.1397505398218033</v>
+        <v>0.1399903359661087</v>
       </c>
       <c r="E143" t="n">
-        <v>0.1265298485155069</v>
+        <v>0.1267092741641203</v>
       </c>
       <c r="F143" t="n">
-        <v>0.143434537068119</v>
+        <v>0.1441694089160436</v>
       </c>
       <c r="G143" t="n">
-        <v>0.1258606154272406</v>
+        <v>0.0884834391966724</v>
       </c>
       <c r="H143" t="n">
         <v>0.7490184834473188</v>
@@ -13463,22 +13463,22 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.3234921770774981</v>
+        <v>0.3222840238928049</v>
       </c>
       <c r="C144" t="n">
-        <v>0.2288424982993892</v>
+        <v>0.2279611738298532</v>
       </c>
       <c r="D144" t="n">
-        <v>0.1919519246754832</v>
+        <v>0.1918873439618065</v>
       </c>
       <c r="E144" t="n">
-        <v>0.1219578055977806</v>
+        <v>0.1219145994583109</v>
       </c>
       <c r="F144" t="n">
-        <v>0.2105031570042323</v>
+        <v>0.2096035566565423</v>
       </c>
       <c r="G144" t="n">
-        <v>0.1163385888055059</v>
+        <v>0.1155667051148312</v>
       </c>
       <c r="H144" t="n">
         <v>0.7619135220461626</v>
@@ -13554,22 +13554,22 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.1949025965643612</v>
+        <v>0.193771246543747</v>
       </c>
       <c r="C145" t="n">
-        <v>0.2106230896176913</v>
+        <v>0.2095537236409708</v>
       </c>
       <c r="D145" t="n">
-        <v>0.1476382452068859</v>
+        <v>0.1481343230427474</v>
       </c>
       <c r="E145" t="n">
-        <v>0.1337151129423892</v>
+        <v>0.1338529573296296</v>
       </c>
       <c r="F145" t="n">
-        <v>0.08397766681681898</v>
+        <v>0.08384009936851858</v>
       </c>
       <c r="G145" t="n">
-        <v>0.1015613853822166</v>
+        <v>0.1008888194026603</v>
       </c>
       <c r="H145" t="n">
         <v>0.7272922710971119</v>
@@ -13645,22 +13645,22 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.3052551400158964</v>
+        <v>0.3049796095801408</v>
       </c>
       <c r="C146" t="n">
-        <v>0.1316283835020373</v>
+        <v>0.1316833842378677</v>
       </c>
       <c r="D146" t="n">
-        <v>0.2660163353615496</v>
+        <v>0.265978561291897</v>
       </c>
       <c r="E146" t="n">
-        <v>0.1367483991725467</v>
+        <v>0.1367934268770089</v>
       </c>
       <c r="F146" t="n">
-        <v>0.312294988252446</v>
+        <v>0.3120586265874425</v>
       </c>
       <c r="G146" t="n">
-        <v>0.1279130289170497</v>
+        <v>0.1280303574207362</v>
       </c>
       <c r="H146" t="n">
         <v>0.4845021405176518</v>
@@ -13736,22 +13736,22 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.1901448063631196</v>
+        <v>0.1902872974624059</v>
       </c>
       <c r="C147" t="n">
-        <v>0.1770251182679217</v>
+        <v>0.1770725611530786</v>
       </c>
       <c r="D147" t="n">
-        <v>0.2658747529708259</v>
+        <v>0.2704864923447934</v>
       </c>
       <c r="E147" t="n">
-        <v>0.2413318311148106</v>
+        <v>0.2561180535826248</v>
       </c>
       <c r="F147" t="n">
-        <v>0.1973063851018137</v>
+        <v>0.197461019704803</v>
       </c>
       <c r="G147" t="n">
-        <v>0.1805940064143282</v>
+        <v>0.1806873722745586</v>
       </c>
       <c r="H147" t="n">
         <v>0.4204852656376783</v>
@@ -13827,22 +13827,22 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.1588434262714089</v>
+        <v>0.1588545478946679</v>
       </c>
       <c r="C148" t="n">
-        <v>0.07826764487422852</v>
+        <v>0.07828751995306629</v>
       </c>
       <c r="D148" t="n">
-        <v>0.152766089848965</v>
+        <v>0.15275482728912</v>
       </c>
       <c r="E148" t="n">
-        <v>0.07834503336702708</v>
+        <v>0.07836470527400402</v>
       </c>
       <c r="F148" t="n">
-        <v>0.1772166105656603</v>
+        <v>0.1772662665427848</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0741248824099774</v>
+        <v>0.07419737432565976</v>
       </c>
       <c r="H148" t="n">
         <v>0.3367819149821296</v>

--- a/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
+++ b/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
@@ -571,10 +571,10 @@
         <v>0.1727979785462384</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2062075910944513</v>
+        <v>0.2063530857686883</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1718111595107314</v>
+        <v>0.1718379751295964</v>
       </c>
       <c r="F2" t="n">
         <v>0.126559822087519</v>
@@ -662,10 +662,10 @@
         <v>0.1956305041645806</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1474645064903849</v>
+        <v>0.1474660152868277</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1469008933607462</v>
+        <v>0.146968658800029</v>
       </c>
       <c r="F3" t="n">
         <v>0.1563752072998496</v>
@@ -753,10 +753,10 @@
         <v>0.9557259856948994</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3069261954638245</v>
+        <v>0.3069266769485491</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3089492053511059</v>
+        <v>0.3089492794350902</v>
       </c>
       <c r="F4" t="n">
         <v>0.1357193355120803</v>
@@ -935,10 +935,10 @@
         <v>0.3484502322206205</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09726754896629644</v>
+        <v>0.09733050173124318</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09117061356504343</v>
+        <v>0.09125766943161757</v>
       </c>
       <c r="F6" t="n">
         <v>0.113410322628134</v>
@@ -1026,10 +1026,10 @@
         <v>0.3613966982176853</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1600120820661372</v>
+        <v>0.1600216268056551</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1636650101404095</v>
+        <v>0.1636856954126692</v>
       </c>
       <c r="F7" t="n">
         <v>0.0921663089138389</v>
@@ -1117,10 +1117,10 @@
         <v>0.244241979399558</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1815934436893237</v>
+        <v>0.1821928859433549</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1745185376626968</v>
+        <v>0.1747374938486058</v>
       </c>
       <c r="F8" t="n">
         <v>0.2299622651585019</v>
@@ -1295,10 +1295,10 @@
         <v>0.6132271194235208</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3428233582259079</v>
+        <v>0.3439928982527894</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3287732820670674</v>
+        <v>0.3316622083172832</v>
       </c>
       <c r="F10" t="n">
         <v>0.2743993234338228</v>
@@ -1477,10 +1477,10 @@
         <v>0.7802178812393754</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3056179213489899</v>
+        <v>0.3057406571647968</v>
       </c>
       <c r="E12" t="n">
-        <v>0.30133215876627</v>
+        <v>0.3015712107926012</v>
       </c>
       <c r="F12" t="n">
         <v>0.1709091459189878</v>
@@ -1568,10 +1568,10 @@
         <v>0.3412760054295455</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1153182779046153</v>
+        <v>0.1153440842337027</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1078343549367641</v>
+        <v>0.1078802625379042</v>
       </c>
       <c r="F13" t="n">
         <v>0.08965737744849965</v>
@@ -1659,7 +1659,7 @@
         <v>0.104414241682984</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1964328729300407</v>
+        <v>0.1964332227538516</v>
       </c>
       <c r="E14" t="n">
         <v>0.07901789673683859</v>
@@ -1750,10 +1750,10 @@
         <v>0.3994016153559959</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1696339676443774</v>
+        <v>0.169635462522598</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1191792895020432</v>
+        <v>0.1191795527403103</v>
       </c>
       <c r="F15" t="n">
         <v>0.1190786687198225</v>
@@ -1841,7 +1841,7 @@
         <v>0.2119754937624252</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6776224432413257</v>
+        <v>0.6983432002421912</v>
       </c>
       <c r="E16" t="n">
         <v>0.2120959796720211</v>
@@ -1928,10 +1928,10 @@
         <v>0.6298332651966274</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2203781394591999</v>
+        <v>0.2203842239470827</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2158775826340549</v>
+        <v>0.215879339792772</v>
       </c>
       <c r="F17" t="n">
         <v>0.1297010550905297</v>
@@ -2019,10 +2019,10 @@
         <v>0.6524106251058965</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6322866746235792</v>
+        <v>0.6387885800788401</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6613504180969065</v>
+        <v>0.6747680652362954</v>
       </c>
       <c r="F18" t="n">
         <v>0.6303418307863142</v>
@@ -2106,10 +2106,10 @@
         <v>0.1882655780453046</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1545549644513988</v>
+        <v>0.1548215835263761</v>
       </c>
       <c r="E19" t="n">
-        <v>0.143365920339972</v>
+        <v>0.1433863775010243</v>
       </c>
       <c r="F19" t="n">
         <v>0.1749074916263711</v>
@@ -2197,10 +2197,10 @@
         <v>0.453020185371623</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1829193753987896</v>
+        <v>0.1829227112314944</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1656558160028125</v>
+        <v>0.165663655396856</v>
       </c>
       <c r="F20" t="n">
         <v>0.3134254406237676</v>
@@ -2288,10 +2288,10 @@
         <v>0.4160689168358572</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1987639337941945</v>
+        <v>0.1987736152140745</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1961295165207923</v>
+        <v>0.1961320345187428</v>
       </c>
       <c r="F21" t="n">
         <v>0.3058489501862094</v>
@@ -2379,10 +2379,10 @@
         <v>0.9248563148493131</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3884967894196186</v>
+        <v>0.38851383634131</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3887274607435048</v>
+        <v>0.3888614869920793</v>
       </c>
       <c r="F22" t="n">
         <v>0.3540977108571027</v>
@@ -2470,10 +2470,10 @@
         <v>0.175047780426626</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1014913983952132</v>
+        <v>0.1014954042124112</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05471446439554508</v>
+        <v>0.05473245609526536</v>
       </c>
       <c r="F23" t="n">
         <v>0.1068817944838088</v>
@@ -2561,10 +2561,10 @@
         <v>0.305650091875142</v>
       </c>
       <c r="D24" t="n">
-        <v>0.313111790933893</v>
+        <v>0.3185304651058397</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2242823587647351</v>
+        <v>0.2261003535739737</v>
       </c>
       <c r="F24" t="n">
         <v>0.354092560590088</v>
@@ -2652,10 +2652,10 @@
         <v>0.254971880914115</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1162657791131764</v>
+        <v>0.116392313314902</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08601312379679785</v>
+        <v>0.08603776991757449</v>
       </c>
       <c r="F25" t="n">
         <v>0.1884637482977953</v>
@@ -2743,10 +2743,10 @@
         <v>0.755436250062104</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2557593299145072</v>
+        <v>0.2557593446896501</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2156379575629639</v>
+        <v>0.2156379587730509</v>
       </c>
       <c r="F26" t="n">
         <v>0.1041925137365477</v>
@@ -2837,7 +2837,7 @@
         <v>0.05458207995637606</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04622029063232052</v>
+        <v>0.04622029067641806</v>
       </c>
       <c r="F27" t="n">
         <v>0.04328923765206946</v>
@@ -2925,7 +2925,7 @@
         <v>0.08619350451733843</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1937717258770215</v>
+        <v>0.1937717259847829</v>
       </c>
       <c r="E28" t="n">
         <v>0.08619294909028766</v>
@@ -3016,7 +3016,7 @@
         <v>0.03197766054045453</v>
       </c>
       <c r="D29" t="n">
-        <v>0.04652818760502312</v>
+        <v>0.04652818778023345</v>
       </c>
       <c r="E29" t="n">
         <v>0.03035235703411378</v>
@@ -3107,10 +3107,10 @@
         <v>0.07500231926812009</v>
       </c>
       <c r="D30" t="n">
-        <v>0.04115308929629166</v>
+        <v>0.04115315178920673</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03218995455454213</v>
+        <v>0.03218997075072093</v>
       </c>
       <c r="F30" t="n">
         <v>0.03937925821502111</v>
@@ -3198,7 +3198,7 @@
         <v>0.06477085591513414</v>
       </c>
       <c r="D31" t="n">
-        <v>0.08908223319650851</v>
+        <v>0.0890822340062209</v>
       </c>
       <c r="E31" t="n">
         <v>0.06480292727428162</v>
@@ -3289,10 +3289,10 @@
         <v>0.04866815029499763</v>
       </c>
       <c r="D32" t="n">
-        <v>0.06834767330570328</v>
+        <v>0.06834767796848798</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03854450403594292</v>
+        <v>0.03854456987449981</v>
       </c>
       <c r="F32" t="n">
         <v>0.07388045002427068</v>
@@ -3380,10 +3380,10 @@
         <v>0.5591465006485221</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2004392153178149</v>
+        <v>0.2006030489216315</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1914385221817014</v>
+        <v>0.1917095832125919</v>
       </c>
       <c r="F33" t="n">
         <v>0.2528945913851281</v>
@@ -3471,10 +3471,10 @@
         <v>0.08504262494770862</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0437410667210726</v>
+        <v>0.04374151629762139</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0434441623193047</v>
+        <v>0.04344469350307765</v>
       </c>
       <c r="F34" t="n">
         <v>0.01331963457462606</v>
@@ -3562,10 +3562,10 @@
         <v>0.05107661617171957</v>
       </c>
       <c r="D35" t="n">
-        <v>0.02898294086609664</v>
+        <v>0.02898352678106121</v>
       </c>
       <c r="E35" t="n">
-        <v>0.02595996916104477</v>
+        <v>0.02596036191515381</v>
       </c>
       <c r="F35" t="n">
         <v>0.02249581156851674</v>
@@ -3744,10 +3744,10 @@
         <v>0.140857786790505</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08806578157084073</v>
+        <v>0.08807413377403074</v>
       </c>
       <c r="E37" t="n">
-        <v>0.08792720280098572</v>
+        <v>0.0879277167183411</v>
       </c>
       <c r="F37" t="n">
         <v>0.07907836553756208</v>
@@ -3835,10 +3835,10 @@
         <v>0.1027096772821009</v>
       </c>
       <c r="D38" t="n">
-        <v>0.03461846968698081</v>
+        <v>0.03461846980117696</v>
       </c>
       <c r="E38" t="n">
-        <v>0.03565639558925297</v>
+        <v>0.03565639575879934</v>
       </c>
       <c r="F38" t="n">
         <v>0.007420056334630616</v>
@@ -3926,10 +3926,10 @@
         <v>0.2485157647253419</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1773619515997136</v>
+        <v>0.1805345648101746</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1200908829687772</v>
+        <v>0.1207314367465582</v>
       </c>
       <c r="F39" t="n">
         <v>0.1555146779571564</v>
@@ -4017,10 +4017,10 @@
         <v>0.1681666541472387</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1217167751301444</v>
+        <v>0.121716796881192</v>
       </c>
       <c r="E40" t="n">
-        <v>0.09761965155738274</v>
+        <v>0.09762118316136251</v>
       </c>
       <c r="F40" t="n">
         <v>0.1138799180787355</v>
@@ -4108,10 +4108,10 @@
         <v>0.06943424603509075</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1171812707469262</v>
+        <v>0.1171814300471436</v>
       </c>
       <c r="E41" t="n">
-        <v>0.06042369572399547</v>
+        <v>0.06042369630390779</v>
       </c>
       <c r="F41" t="n">
         <v>0.1436002500085728</v>
@@ -4559,10 +4559,10 @@
         <v>0.05390673528200461</v>
       </c>
       <c r="D46" t="n">
-        <v>0.08685679098089252</v>
+        <v>0.0868567977386574</v>
       </c>
       <c r="E46" t="n">
-        <v>0.05186069995904886</v>
+        <v>0.05188165638304125</v>
       </c>
       <c r="F46" t="n">
         <v>0.09292089567095477</v>
@@ -4741,10 +4741,10 @@
         <v>0.07166397487212992</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1371081671453661</v>
+        <v>0.1371145336101306</v>
       </c>
       <c r="E48" t="n">
-        <v>0.05557839511833085</v>
+        <v>0.05557841886334517</v>
       </c>
       <c r="F48" t="n">
         <v>0.1792881884099726</v>
@@ -4832,10 +4832,10 @@
         <v>0.5941492719670419</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2870687588357115</v>
+        <v>0.2874932819684468</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1746167740482679</v>
+        <v>0.1747449244759837</v>
       </c>
       <c r="F49" t="n">
         <v>0.398657720171792</v>
@@ -4923,10 +4923,10 @@
         <v>0.215145744293515</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1228404743055463</v>
+        <v>0.1228474290000726</v>
       </c>
       <c r="E50" t="n">
-        <v>0.111621362955489</v>
+        <v>0.1116313766974661</v>
       </c>
       <c r="F50" t="n">
         <v>0.1133797562537238</v>
@@ -5014,10 +5014,10 @@
         <v>1.801043269094024</v>
       </c>
       <c r="D51" t="n">
-        <v>0.5784958372661392</v>
+        <v>0.5784958388176882</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5660761009362293</v>
+        <v>0.5660761010376186</v>
       </c>
       <c r="F51" t="n">
         <v>0.1388710229328567</v>
@@ -5105,10 +5105,10 @@
         <v>1.24285466549652</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5152212380865674</v>
+        <v>0.5152406450114224</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5083481328140047</v>
+        <v>0.5083581686505584</v>
       </c>
       <c r="F52" t="n">
         <v>0.3427698616804288</v>
@@ -5196,10 +5196,10 @@
         <v>0.1739984898829535</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2922750484403725</v>
+        <v>0.2927826332241206</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1462023644766806</v>
+        <v>0.146209334791109</v>
       </c>
       <c r="F53" t="n">
         <v>0.2435947772079181</v>
@@ -5378,10 +5378,10 @@
         <v>0.2385085466461309</v>
       </c>
       <c r="D55" t="n">
-        <v>0.3907920279978311</v>
+        <v>0.400943477183642</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4110618668552029</v>
+        <v>0.4283734198039334</v>
       </c>
       <c r="F55" t="n">
         <v>0.2866945656317785</v>
@@ -5560,10 +5560,10 @@
         <v>0.3095529053602163</v>
       </c>
       <c r="D57" t="n">
-        <v>0.129944276455478</v>
+        <v>0.1299571743690428</v>
       </c>
       <c r="E57" t="n">
-        <v>0.09058539555967353</v>
+        <v>0.09058676116225803</v>
       </c>
       <c r="F57" t="n">
         <v>0.1924806508443604</v>
@@ -5651,10 +5651,10 @@
         <v>0.00350041061804758</v>
       </c>
       <c r="D58" t="n">
-        <v>0.01056939009607541</v>
+        <v>0.01079367823310745</v>
       </c>
       <c r="E58" t="n">
-        <v>0.002017902773918819</v>
+        <v>0.002018369418234298</v>
       </c>
       <c r="F58" t="n">
         <v>0.01160003975057617</v>
@@ -5738,10 +5738,10 @@
         <v>1.000584039568822</v>
       </c>
       <c r="D59" t="n">
-        <v>0.5688339432501592</v>
+        <v>0.5695029895382235</v>
       </c>
       <c r="E59" t="n">
-        <v>0.5210467101828455</v>
+        <v>0.5213918204846444</v>
       </c>
       <c r="F59" t="n">
         <v>0.7303340534387879</v>
@@ -5829,10 +5829,10 @@
         <v>0.8283219632971955</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3992699674579335</v>
+        <v>0.3995799302614583</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3540118982655499</v>
+        <v>0.3541066154722535</v>
       </c>
       <c r="F60" t="n">
         <v>0.5487702634661585</v>
@@ -5920,10 +5920,10 @@
         <v>0.531613281787809</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1104158907197382</v>
+        <v>0.1104173502564436</v>
       </c>
       <c r="E61" t="n">
-        <v>0.09493308181253432</v>
+        <v>0.09493834708178688</v>
       </c>
       <c r="F61" t="n">
         <v>0.08391620484197634</v>
@@ -6011,10 +6011,10 @@
         <v>0.09461974118246931</v>
       </c>
       <c r="D62" t="n">
-        <v>0.09706124816534478</v>
+        <v>0.09712450005509317</v>
       </c>
       <c r="E62" t="n">
-        <v>0.07240075588870937</v>
+        <v>0.07241742776939489</v>
       </c>
       <c r="F62" t="n">
         <v>0.1193157924646424</v>
@@ -6102,10 +6102,10 @@
         <v>0.4503157731456378</v>
       </c>
       <c r="D63" t="n">
-        <v>0.2502158108339501</v>
+        <v>0.2504194247512969</v>
       </c>
       <c r="E63" t="n">
-        <v>0.2403338624906481</v>
+        <v>0.241198163783708</v>
       </c>
       <c r="F63" t="n">
         <v>0.213753104648562</v>
@@ -6193,10 +6193,10 @@
         <v>0.8530721133747085</v>
       </c>
       <c r="D64" t="n">
-        <v>0.4135765734760165</v>
+        <v>0.4136509908256288</v>
       </c>
       <c r="E64" t="n">
-        <v>0.415110359457614</v>
+        <v>0.4152079061737333</v>
       </c>
       <c r="F64" t="n">
         <v>0.4846109585116196</v>
@@ -6284,10 +6284,10 @@
         <v>0.2469954647965427</v>
       </c>
       <c r="D65" t="n">
-        <v>0.1745387981176564</v>
+        <v>0.1745648786569929</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1292009388540029</v>
+        <v>0.1292083373569749</v>
       </c>
       <c r="F65" t="n">
         <v>0.2765703453678259</v>
@@ -6375,10 +6375,10 @@
         <v>0.339686921387015</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1232049890022731</v>
+        <v>0.1232053752527851</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1181125117930658</v>
+        <v>0.1181130185612264</v>
       </c>
       <c r="F66" t="n">
         <v>0.03678165940257595</v>
@@ -6466,10 +6466,10 @@
         <v>0.6693666910520283</v>
       </c>
       <c r="D67" t="n">
-        <v>0.8351731975477521</v>
+        <v>0.8352458810576215</v>
       </c>
       <c r="E67" t="n">
-        <v>0.7187279484579806</v>
+        <v>0.7294897199297996</v>
       </c>
       <c r="F67" t="n">
         <v>0.6082529560423311</v>
@@ -6739,10 +6739,10 @@
         <v>0.5215623854741231</v>
       </c>
       <c r="D70" t="n">
-        <v>0.1422128665944157</v>
+        <v>0.1422159594260567</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1056105014151803</v>
+        <v>0.1056113560276018</v>
       </c>
       <c r="F70" t="n">
         <v>0.1312168236082282</v>
@@ -6830,10 +6830,10 @@
         <v>0.1907699174151322</v>
       </c>
       <c r="D71" t="n">
-        <v>0.03814930150911446</v>
+        <v>0.03814934027413591</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0400407121706995</v>
+        <v>0.04004075388209836</v>
       </c>
       <c r="F71" t="n">
         <v>0.02310561325370156</v>
@@ -6921,7 +6921,7 @@
         <v>0.07066791454408344</v>
       </c>
       <c r="D72" t="n">
-        <v>0.153647406175306</v>
+        <v>0.1536474138919351</v>
       </c>
       <c r="E72" t="n">
         <v>0.07068504877160804</v>
@@ -7012,10 +7012,10 @@
         <v>0.4747789332697916</v>
       </c>
       <c r="D73" t="n">
-        <v>0.5114083755556068</v>
+        <v>0.5230308871005356</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4912296168100817</v>
+        <v>0.4984846833154721</v>
       </c>
       <c r="F73" t="n">
         <v>0.4668088897522757</v>
@@ -7106,7 +7106,7 @@
         <v>0.061473047807748</v>
       </c>
       <c r="E74" t="n">
-        <v>0.06568862268949016</v>
+        <v>0.06568862343286143</v>
       </c>
       <c r="F74" t="n">
         <v>0.05023017156969963</v>
@@ -7194,10 +7194,10 @@
         <v>0.4310334236928344</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1755934280046847</v>
+        <v>0.1756005492377556</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1803011153084425</v>
+        <v>0.1803073408017623</v>
       </c>
       <c r="F75" t="n">
         <v>0.08713615481167204</v>
@@ -7467,10 +7467,10 @@
         <v>0.4101348426216624</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2275686361497538</v>
+        <v>0.227674447935704</v>
       </c>
       <c r="E78" t="n">
-        <v>0.2387024405416951</v>
+        <v>0.238742189635288</v>
       </c>
       <c r="F78" t="n">
         <v>0.1260107992817844</v>
@@ -7649,10 +7649,10 @@
         <v>0.1944322421102406</v>
       </c>
       <c r="D80" t="n">
-        <v>0.1970372443381554</v>
+        <v>0.1974283208661482</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1879790580379595</v>
+        <v>0.1883206200808255</v>
       </c>
       <c r="F80" t="n">
         <v>0.0961272633102709</v>
@@ -7740,10 +7740,10 @@
         <v>0.3399825225936571</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2131757775622734</v>
+        <v>0.2131844858108515</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1441485815991801</v>
+        <v>0.144148674756563</v>
       </c>
       <c r="F81" t="n">
         <v>0.1863089226992002</v>
@@ -7922,10 +7922,10 @@
         <v>0.4410508919541843</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2256345070835162</v>
+        <v>0.2257281618807142</v>
       </c>
       <c r="E83" t="n">
-        <v>0.2058574890401488</v>
+        <v>0.2058649042407174</v>
       </c>
       <c r="F83" t="n">
         <v>0.1734795778864761</v>
@@ -8013,10 +8013,10 @@
         <v>0.3589162983011352</v>
       </c>
       <c r="D84" t="n">
-        <v>0.5785534935794894</v>
+        <v>0.5786565818926416</v>
       </c>
       <c r="E84" t="n">
-        <v>0.2284050313419277</v>
+        <v>0.2288652060312966</v>
       </c>
       <c r="F84" t="n">
         <v>0.4663671631288341</v>
@@ -8104,10 +8104,10 @@
         <v>0.1970097092554824</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1158897199714543</v>
+        <v>0.1159180650085006</v>
       </c>
       <c r="E85" t="n">
-        <v>0.1124556441804483</v>
+        <v>0.1124653960081582</v>
       </c>
       <c r="F85" t="n">
         <v>0.1127077238682392</v>
@@ -8195,10 +8195,10 @@
         <v>0.2252331980617254</v>
       </c>
       <c r="D86" t="n">
-        <v>0.1740779038643475</v>
+        <v>0.1740836765814558</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1468793639473467</v>
+        <v>0.1468797698668851</v>
       </c>
       <c r="F86" t="n">
         <v>0.1838230688026703</v>
@@ -8286,10 +8286,10 @@
         <v>0.1071978813708681</v>
       </c>
       <c r="D87" t="n">
-        <v>0.1169060832240041</v>
+        <v>0.1169065011399956</v>
       </c>
       <c r="E87" t="n">
-        <v>0.08794507664240567</v>
+        <v>0.08794515677020905</v>
       </c>
       <c r="F87" t="n">
         <v>0.1275708486215023</v>
@@ -8468,10 +8468,10 @@
         <v>0.187946565817732</v>
       </c>
       <c r="D89" t="n">
-        <v>0.1658242759699738</v>
+        <v>0.1658599440007824</v>
       </c>
       <c r="E89" t="n">
-        <v>0.1551290203080474</v>
+        <v>0.1551302276253412</v>
       </c>
       <c r="F89" t="n">
         <v>0.1266136326211225</v>
@@ -8559,10 +8559,10 @@
         <v>0.9827987275038074</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3313756532078322</v>
+        <v>0.3313758369541271</v>
       </c>
       <c r="E90" t="n">
-        <v>0.3633016339837019</v>
+        <v>0.3633035682769993</v>
       </c>
       <c r="F90" t="n">
         <v>0.1230211613322603</v>
@@ -8650,10 +8650,10 @@
         <v>0.1672718683817267</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1343414382852662</v>
+        <v>0.134343252380355</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1398835487213639</v>
+        <v>0.1399338130343685</v>
       </c>
       <c r="F91" t="n">
         <v>0.1509217889284667</v>
@@ -8741,10 +8741,10 @@
         <v>0.6188835198794747</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3015688182367602</v>
+        <v>0.3022245720327218</v>
       </c>
       <c r="E92" t="n">
-        <v>0.3117066704258012</v>
+        <v>0.313113130702445</v>
       </c>
       <c r="F92" t="n">
         <v>0.2454608721067457</v>
@@ -8832,7 +8832,7 @@
         <v>0.07626402299458676</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1385453860409279</v>
+        <v>0.1385461143220439</v>
       </c>
       <c r="E93" t="n">
         <v>0.06370154640865755</v>
@@ -8923,10 +8923,10 @@
         <v>0.7602738181432417</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2147185884231523</v>
+        <v>0.2147186180756945</v>
       </c>
       <c r="E94" t="n">
-        <v>0.22472768731432</v>
+        <v>0.2247277829767863</v>
       </c>
       <c r="F94" t="n">
         <v>0.1216949268591854</v>
@@ -9014,10 +9014,10 @@
         <v>0.06779898318107815</v>
       </c>
       <c r="D95" t="n">
-        <v>0.1359860186100393</v>
+        <v>0.1362111018887769</v>
       </c>
       <c r="E95" t="n">
-        <v>0.05718820867172966</v>
+        <v>0.05728227384940589</v>
       </c>
       <c r="F95" t="n">
         <v>0.1835815220971968</v>
@@ -9196,10 +9196,10 @@
         <v>0.2743934654642279</v>
       </c>
       <c r="D97" t="n">
-        <v>0.1451156598072634</v>
+        <v>0.1453127376371145</v>
       </c>
       <c r="E97" t="n">
-        <v>0.1098389418564554</v>
+        <v>0.1099340555783589</v>
       </c>
       <c r="F97" t="n">
         <v>0.2344586657567671</v>
@@ -9287,10 +9287,10 @@
         <v>0.4161804193438561</v>
       </c>
       <c r="D98" t="n">
-        <v>0.2525779471741121</v>
+        <v>0.2528610546217651</v>
       </c>
       <c r="E98" t="n">
-        <v>0.1566084371026206</v>
+        <v>0.1566119271314414</v>
       </c>
       <c r="F98" t="n">
         <v>0.5192000253282574</v>
@@ -9378,7 +9378,7 @@
         <v>0.08501400414635085</v>
       </c>
       <c r="D99" t="n">
-        <v>0.1922113398975273</v>
+        <v>0.1922139139207104</v>
       </c>
       <c r="E99" t="n">
         <v>0.09005612711458374</v>
@@ -9469,10 +9469,10 @@
         <v>0.02738594428316249</v>
       </c>
       <c r="D100" t="n">
-        <v>0.01980409352840092</v>
+        <v>0.01980437140854183</v>
       </c>
       <c r="E100" t="n">
-        <v>0.01398467594595955</v>
+        <v>0.01398590909255813</v>
       </c>
       <c r="F100" t="n">
         <v>0.02687075178124612</v>
@@ -9560,10 +9560,10 @@
         <v>1.245016936279405</v>
       </c>
       <c r="D101" t="n">
-        <v>0.5164604176611134</v>
+        <v>0.5164682039657934</v>
       </c>
       <c r="E101" t="n">
-        <v>0.505857146288878</v>
+        <v>0.5058688137196128</v>
       </c>
       <c r="F101" t="n">
         <v>0.2839539280448209</v>
@@ -9651,7 +9651,7 @@
         <v>0.1093283019514915</v>
       </c>
       <c r="D102" t="n">
-        <v>0.07341330073597337</v>
+        <v>0.07341330118538017</v>
       </c>
       <c r="E102" t="n">
         <v>0.07022790823368349</v>
@@ -9742,10 +9742,10 @@
         <v>0.798537516284292</v>
       </c>
       <c r="D103" t="n">
-        <v>0.2875408832550455</v>
+        <v>0.2876142625062075</v>
       </c>
       <c r="E103" t="n">
-        <v>0.2341508587038877</v>
+        <v>0.2345088109193128</v>
       </c>
       <c r="F103" t="n">
         <v>0.1556238400776608</v>
@@ -10288,10 +10288,10 @@
         <v>0.07889825329983721</v>
       </c>
       <c r="D109" t="n">
-        <v>0.01427659271396422</v>
+        <v>0.01427659290176402</v>
       </c>
       <c r="E109" t="n">
-        <v>0.01388344896525143</v>
+        <v>0.0138834492042188</v>
       </c>
       <c r="F109" t="n">
         <v>0.005321316602960769</v>
@@ -10379,10 +10379,10 @@
         <v>0.3358569056264085</v>
       </c>
       <c r="D110" t="n">
-        <v>0.1435643577651277</v>
+        <v>0.1435661108263564</v>
       </c>
       <c r="E110" t="n">
-        <v>0.1475108871310485</v>
+        <v>0.1475120305331584</v>
       </c>
       <c r="F110" t="n">
         <v>0.05813966215239565</v>
@@ -10470,10 +10470,10 @@
         <v>0.5661357504748894</v>
       </c>
       <c r="D111" t="n">
-        <v>0.2243613947745872</v>
+        <v>0.2243615628614161</v>
       </c>
       <c r="E111" t="n">
-        <v>0.2286469892752312</v>
+        <v>0.2286471824525416</v>
       </c>
       <c r="F111" t="n">
         <v>0.0292443205140462</v>
@@ -10652,10 +10652,10 @@
         <v>0.2067786093847541</v>
       </c>
       <c r="D113" t="n">
-        <v>0.2123419213179572</v>
+        <v>0.2127471171858691</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1907740175572568</v>
+        <v>0.1915595431419174</v>
       </c>
       <c r="F113" t="n">
         <v>0.09584238782839646</v>
@@ -10743,10 +10743,10 @@
         <v>0.3479094458485996</v>
       </c>
       <c r="D114" t="n">
-        <v>0.2096078388930629</v>
+        <v>0.2096640324170497</v>
       </c>
       <c r="E114" t="n">
-        <v>0.2163222654467029</v>
+        <v>0.2163349011951406</v>
       </c>
       <c r="F114" t="n">
         <v>0.1424997212317195</v>
@@ -11107,7 +11107,7 @@
         <v>0.09221947074630707</v>
       </c>
       <c r="D118" t="n">
-        <v>0.1446887830834837</v>
+        <v>0.1447029803012069</v>
       </c>
       <c r="E118" t="n">
         <v>0.0922271888526006</v>
@@ -11198,7 +11198,7 @@
         <v>0.02796112559499681</v>
       </c>
       <c r="D119" t="n">
-        <v>0.02045853025362208</v>
+        <v>0.02045853037943474</v>
       </c>
       <c r="E119" t="n">
         <v>0.01807704344729608</v>
@@ -11289,10 +11289,10 @@
         <v>0.09502436808439847</v>
       </c>
       <c r="D120" t="n">
-        <v>0.05073765715169388</v>
+        <v>0.05073769489589935</v>
       </c>
       <c r="E120" t="n">
-        <v>0.04964641415830182</v>
+        <v>0.0496468819803621</v>
       </c>
       <c r="F120" t="n">
         <v>0.0388933245606785</v>
@@ -11380,10 +11380,10 @@
         <v>0.1891646081037996</v>
       </c>
       <c r="D121" t="n">
-        <v>0.2171485135331446</v>
+        <v>0.2171489086713133</v>
       </c>
       <c r="E121" t="n">
-        <v>0.1386901139235041</v>
+        <v>0.1388335381061436</v>
       </c>
       <c r="F121" t="n">
         <v>0.2069526856014565</v>
@@ -11471,10 +11471,10 @@
         <v>0.0615775885085238</v>
       </c>
       <c r="D122" t="n">
-        <v>0.06358799352742592</v>
+        <v>0.06358799356885288</v>
       </c>
       <c r="E122" t="n">
-        <v>0.06698909068954209</v>
+        <v>0.0669912551286478</v>
       </c>
       <c r="F122" t="n">
         <v>0.05688364621664244</v>
@@ -11562,7 +11562,7 @@
         <v>0.1686449970047895</v>
       </c>
       <c r="D123" t="n">
-        <v>0.09651406649233034</v>
+        <v>0.09651406869608735</v>
       </c>
       <c r="E123" t="n">
         <v>0.07644803716239706</v>
@@ -11653,10 +11653,10 @@
         <v>0.3942418871289511</v>
       </c>
       <c r="D124" t="n">
-        <v>0.3716174743086698</v>
+        <v>0.3722626766436674</v>
       </c>
       <c r="E124" t="n">
-        <v>0.3237645424919536</v>
+        <v>0.3241979537473308</v>
       </c>
       <c r="F124" t="n">
         <v>0.6111573091285377</v>
@@ -11835,10 +11835,10 @@
         <v>0.474918692242627</v>
       </c>
       <c r="D126" t="n">
-        <v>0.2679024991233426</v>
+        <v>0.2679628936688173</v>
       </c>
       <c r="E126" t="n">
-        <v>0.2365847788786888</v>
+        <v>0.2366426103130069</v>
       </c>
       <c r="F126" t="n">
         <v>0.3219415576863928</v>
@@ -11926,10 +11926,10 @@
         <v>0.02895631630547025</v>
       </c>
       <c r="D127" t="n">
-        <v>0.01619054670682294</v>
+        <v>0.01619062218989057</v>
       </c>
       <c r="E127" t="n">
-        <v>0.01402809734912791</v>
+        <v>0.01402812433726591</v>
       </c>
       <c r="F127" t="n">
         <v>0.02228105413134626</v>
@@ -12017,10 +12017,10 @@
         <v>0.2890656229940394</v>
       </c>
       <c r="D128" t="n">
-        <v>0.3593494865653111</v>
+        <v>0.3623948454425374</v>
       </c>
       <c r="E128" t="n">
-        <v>0.2861089264105197</v>
+        <v>0.2873219551900806</v>
       </c>
       <c r="F128" t="n">
         <v>0.1625873721559921</v>
@@ -12108,7 +12108,7 @@
         <v>0.07897339022108103</v>
       </c>
       <c r="D129" t="n">
-        <v>0.1171254611661385</v>
+        <v>0.1171276616263264</v>
       </c>
       <c r="E129" t="n">
         <v>0.07668414077933325</v>
@@ -12199,10 +12199,10 @@
         <v>0.1182962977352434</v>
       </c>
       <c r="D130" t="n">
-        <v>0.1304517353996944</v>
+        <v>0.130458291373072</v>
       </c>
       <c r="E130" t="n">
-        <v>0.09225806483811053</v>
+        <v>0.09225806638990944</v>
       </c>
       <c r="F130" t="n">
         <v>0.1613767118169882</v>
@@ -12290,10 +12290,10 @@
         <v>0.5652462685629582</v>
       </c>
       <c r="D131" t="n">
-        <v>0.2955284003542695</v>
+        <v>0.2957260824677538</v>
       </c>
       <c r="E131" t="n">
-        <v>0.1615649595201772</v>
+        <v>0.1616477914778406</v>
       </c>
       <c r="F131" t="n">
         <v>0.4711296942484131</v>
@@ -12381,10 +12381,10 @@
         <v>0.6863422191730941</v>
       </c>
       <c r="D132" t="n">
-        <v>0.2281312667962338</v>
+        <v>0.2281315984958053</v>
       </c>
       <c r="E132" t="n">
-        <v>0.222277567520809</v>
+        <v>0.2222782178829268</v>
       </c>
       <c r="F132" t="n">
         <v>0.08864482897389499</v>
@@ -12472,10 +12472,10 @@
         <v>0.2392856746235035</v>
       </c>
       <c r="D133" t="n">
-        <v>0.1962088237240728</v>
+        <v>0.1982767270638798</v>
       </c>
       <c r="E133" t="n">
-        <v>0.1945936210871995</v>
+        <v>0.1967586501078624</v>
       </c>
       <c r="F133" t="n">
         <v>0.1342255630003297</v>
@@ -12563,10 +12563,10 @@
         <v>0.6346983240754389</v>
       </c>
       <c r="D134" t="n">
-        <v>0.2583821305102311</v>
+        <v>0.2584594606841544</v>
       </c>
       <c r="E134" t="n">
-        <v>0.2418845112857763</v>
+        <v>0.2419008328287784</v>
       </c>
       <c r="F134" t="n">
         <v>0.1597810507090881</v>
@@ -12654,10 +12654,10 @@
         <v>0.1928933544962687</v>
       </c>
       <c r="D135" t="n">
-        <v>0.1745069929684225</v>
+        <v>0.1745212094912219</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1791007718575811</v>
+        <v>0.1791517654604911</v>
       </c>
       <c r="F135" t="n">
         <v>0.1331865354292969</v>
@@ -12745,10 +12745,10 @@
         <v>0.3757043281926236</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4880784621961658</v>
+        <v>0.4884395142834155</v>
       </c>
       <c r="E136" t="n">
-        <v>0.1184755234831405</v>
+        <v>0.1184761487535144</v>
       </c>
       <c r="F136" t="n">
         <v>0.9951678084714012</v>
@@ -12836,10 +12836,10 @@
         <v>0.1089455831871634</v>
       </c>
       <c r="D137" t="n">
-        <v>0.172917248430325</v>
+        <v>0.1729172509146752</v>
       </c>
       <c r="E137" t="n">
-        <v>0.1218183725123083</v>
+        <v>0.1241948382104997</v>
       </c>
       <c r="F137" t="n">
         <v>0.17293474736815</v>
@@ -12927,10 +12927,10 @@
         <v>1.590507209360802</v>
       </c>
       <c r="D138" t="n">
-        <v>0.6004014670049019</v>
+        <v>0.600401471518295</v>
       </c>
       <c r="E138" t="n">
-        <v>0.6105112088913315</v>
+        <v>0.6105115102506138</v>
       </c>
       <c r="F138" t="n">
         <v>0.3319022122488025</v>
@@ -13018,10 +13018,10 @@
         <v>0.4978721268489525</v>
       </c>
       <c r="D139" t="n">
-        <v>0.1498983836600324</v>
+        <v>0.1499025089804646</v>
       </c>
       <c r="E139" t="n">
-        <v>0.1149687412666042</v>
+        <v>0.114983556280564</v>
       </c>
       <c r="F139" t="n">
         <v>0.09330537550397505</v>
@@ -13109,10 +13109,10 @@
         <v>1.207946375398225</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4384642657719623</v>
+        <v>0.4384649745313478</v>
       </c>
       <c r="E140" t="n">
-        <v>0.4741890041090594</v>
+        <v>0.4741940910689594</v>
       </c>
       <c r="F140" t="n">
         <v>0.2128691352265779</v>
@@ -13200,10 +13200,10 @@
         <v>0.1706942218668353</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2749456006769462</v>
+        <v>0.2814319593955685</v>
       </c>
       <c r="E141" t="n">
-        <v>0.2773735266827101</v>
+        <v>0.2870328576662894</v>
       </c>
       <c r="F141" t="n">
         <v>0.1737068670438273</v>
@@ -13287,10 +13287,10 @@
         <v>0.4017050193022286</v>
       </c>
       <c r="D142" t="n">
-        <v>0.1411518451782344</v>
+        <v>0.1411529949335098</v>
       </c>
       <c r="E142" t="n">
-        <v>0.1336859351688658</v>
+        <v>0.1336871354939648</v>
       </c>
       <c r="F142" t="n">
         <v>0.07356074306436632</v>
@@ -13378,10 +13378,10 @@
         <v>0.2501518267356753</v>
       </c>
       <c r="D143" t="n">
-        <v>0.1399903359661087</v>
+        <v>0.1400213285200137</v>
       </c>
       <c r="E143" t="n">
-        <v>0.1267092741641203</v>
+        <v>0.1267582675134189</v>
       </c>
       <c r="F143" t="n">
         <v>0.1441694089160436</v>
@@ -13469,10 +13469,10 @@
         <v>0.2279611738298532</v>
       </c>
       <c r="D144" t="n">
-        <v>0.1918873439618065</v>
+        <v>0.1919599881630009</v>
       </c>
       <c r="E144" t="n">
-        <v>0.1219145994583109</v>
+        <v>0.1219171474650272</v>
       </c>
       <c r="F144" t="n">
         <v>0.2096035566565423</v>
@@ -13560,10 +13560,10 @@
         <v>0.2095537236409708</v>
       </c>
       <c r="D145" t="n">
-        <v>0.1481343230427474</v>
+        <v>0.1482214391957</v>
       </c>
       <c r="E145" t="n">
-        <v>0.1338529573296296</v>
+        <v>0.1338885225237101</v>
       </c>
       <c r="F145" t="n">
         <v>0.08384009936851858</v>
@@ -13651,7 +13651,7 @@
         <v>0.1316833842378677</v>
       </c>
       <c r="D146" t="n">
-        <v>0.265978561291897</v>
+        <v>0.2659819235204327</v>
       </c>
       <c r="E146" t="n">
         <v>0.1367934268770089</v>
@@ -13742,10 +13742,10 @@
         <v>0.1770725611530786</v>
       </c>
       <c r="D147" t="n">
-        <v>0.2704864923447934</v>
+        <v>0.2732835861987756</v>
       </c>
       <c r="E147" t="n">
-        <v>0.2561180535826248</v>
+        <v>0.2657101726279573</v>
       </c>
       <c r="F147" t="n">
         <v>0.197461019704803</v>
@@ -13833,7 +13833,7 @@
         <v>0.07828751995306629</v>
       </c>
       <c r="D148" t="n">
-        <v>0.15275482728912</v>
+        <v>0.1527548698494082</v>
       </c>
       <c r="E148" t="n">
         <v>0.07836470527400402</v>

--- a/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
+++ b/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
@@ -571,10 +571,10 @@
         <v>0.1727979785462384</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2063530857686883</v>
+        <v>0.2063497773231385</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1718379751295964</v>
+        <v>0.1718359199382432</v>
       </c>
       <c r="F2" t="n">
         <v>0.126559822087519</v>
@@ -662,10 +662,10 @@
         <v>0.1956305041645806</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1474660152868277</v>
+        <v>0.1474650508841647</v>
       </c>
       <c r="E3" t="n">
-        <v>0.146968658800029</v>
+        <v>0.1469667885548225</v>
       </c>
       <c r="F3" t="n">
         <v>0.1563752072998496</v>
@@ -753,10 +753,10 @@
         <v>0.9557259856948994</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3069266769485491</v>
+        <v>0.3069261954638245</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3089492794350902</v>
+        <v>0.3089492053511059</v>
       </c>
       <c r="F4" t="n">
         <v>0.1357193355120803</v>
@@ -935,10 +935,10 @@
         <v>0.3484502322206205</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09733050173124318</v>
+        <v>0.09732673048209094</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09125766943161757</v>
+        <v>0.09125369012842226</v>
       </c>
       <c r="F6" t="n">
         <v>0.113410322628134</v>
@@ -1026,10 +1026,10 @@
         <v>0.3613966982176853</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1600216268056551</v>
+        <v>0.1600195962747348</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1636856954126692</v>
+        <v>0.163683357933051</v>
       </c>
       <c r="F7" t="n">
         <v>0.0921663089138389</v>
@@ -1117,10 +1117,10 @@
         <v>0.244241979399558</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1821928859433549</v>
+        <v>0.1821878565425161</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1747374938486058</v>
+        <v>0.1747335672858144</v>
       </c>
       <c r="F8" t="n">
         <v>0.2299622651585019</v>
@@ -1295,10 +1295,10 @@
         <v>0.6132271194235208</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3439928982527894</v>
+        <v>0.3439817334403211</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3316622083172832</v>
+        <v>0.3316484476014244</v>
       </c>
       <c r="F10" t="n">
         <v>0.2743993234338228</v>
@@ -1477,10 +1477,10 @@
         <v>0.7802178812393754</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3057406571647968</v>
+        <v>0.3057342305157922</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3015712107926012</v>
+        <v>0.301563710278226</v>
       </c>
       <c r="F12" t="n">
         <v>0.1709091459189878</v>
@@ -1568,10 +1568,10 @@
         <v>0.3412760054295455</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1153440842337027</v>
+        <v>0.1153409748071521</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1078802625379042</v>
+        <v>0.1078768019743305</v>
       </c>
       <c r="F13" t="n">
         <v>0.08965737744849965</v>
@@ -1659,7 +1659,7 @@
         <v>0.104414241682984</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1964332227538516</v>
+        <v>0.1964328729300407</v>
       </c>
       <c r="E14" t="n">
         <v>0.07901789673683859</v>
@@ -1750,10 +1750,10 @@
         <v>0.3994016153559959</v>
       </c>
       <c r="D15" t="n">
-        <v>0.169635462522598</v>
+        <v>0.1696339676443774</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1191795527403103</v>
+        <v>0.1191792895020432</v>
       </c>
       <c r="F15" t="n">
         <v>0.1190786687198225</v>
@@ -1841,7 +1841,7 @@
         <v>0.2119754937624252</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6983432002421912</v>
+        <v>0.6983232463122624</v>
       </c>
       <c r="E16" t="n">
         <v>0.2120959796720211</v>
@@ -1928,10 +1928,10 @@
         <v>0.6298332651966274</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2203842239470827</v>
+        <v>0.2203809669167946</v>
       </c>
       <c r="E17" t="n">
-        <v>0.215879339792772</v>
+        <v>0.2158775826340549</v>
       </c>
       <c r="F17" t="n">
         <v>0.1297010550905297</v>
@@ -2019,10 +2019,10 @@
         <v>0.6524106251058965</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6387885800788401</v>
+        <v>0.6387689326754922</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6747680652362954</v>
+        <v>0.6747398173359296</v>
       </c>
       <c r="F18" t="n">
         <v>0.6303418307863142</v>
@@ -2106,10 +2106,10 @@
         <v>0.1882655780453046</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1548215835263761</v>
+        <v>0.1548180565002662</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1433863775010243</v>
+        <v>0.14338474007007</v>
       </c>
       <c r="F19" t="n">
         <v>0.1749074916263711</v>
@@ -2197,10 +2197,10 @@
         <v>0.453020185371623</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1829227112314944</v>
+        <v>0.1829193753987896</v>
       </c>
       <c r="E20" t="n">
-        <v>0.165663655396856</v>
+        <v>0.16565910946076</v>
       </c>
       <c r="F20" t="n">
         <v>0.3134254406237676</v>
@@ -2288,10 +2288,10 @@
         <v>0.4160689168358572</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1987736152140745</v>
+        <v>0.1987698293745744</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1961320345187428</v>
+        <v>0.1961295165207923</v>
       </c>
       <c r="F21" t="n">
         <v>0.3058489501862094</v>
@@ -2379,10 +2379,10 @@
         <v>0.9248563148493131</v>
       </c>
       <c r="D22" t="n">
-        <v>0.38851383634131</v>
+        <v>0.3885094476830503</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3888614869920793</v>
+        <v>0.3888550703696546</v>
       </c>
       <c r="F22" t="n">
         <v>0.3540977108571027</v>
@@ -2470,10 +2470,10 @@
         <v>0.175047780426626</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1014954042124112</v>
+        <v>0.1014938687902971</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05473245609526536</v>
+        <v>0.05473048374167951</v>
       </c>
       <c r="F23" t="n">
         <v>0.1068817944838088</v>
@@ -2561,10 +2561,10 @@
         <v>0.305650091875142</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3185304651058397</v>
+        <v>0.3185201186940599</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2261003535739737</v>
+        <v>0.2260922723590497</v>
       </c>
       <c r="F24" t="n">
         <v>0.354092560590088</v>
@@ -2652,10 +2652,10 @@
         <v>0.254971880914115</v>
       </c>
       <c r="D25" t="n">
-        <v>0.116392313314902</v>
+        <v>0.1163888701157213</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08603776991757449</v>
+        <v>0.08603525616135733</v>
       </c>
       <c r="F25" t="n">
         <v>0.1884637482977953</v>
@@ -2743,10 +2743,10 @@
         <v>0.755436250062104</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2557593446896501</v>
+        <v>0.2557593299145072</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2156379587730509</v>
+        <v>0.2156379575629639</v>
       </c>
       <c r="F26" t="n">
         <v>0.1041925137365477</v>
@@ -2837,7 +2837,7 @@
         <v>0.05458207995637606</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04622029067641806</v>
+        <v>0.04622029063232052</v>
       </c>
       <c r="F27" t="n">
         <v>0.04328923765206946</v>
@@ -2925,7 +2925,7 @@
         <v>0.08619350451733843</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1937717259847829</v>
+        <v>0.1937717258770215</v>
       </c>
       <c r="E28" t="n">
         <v>0.08619294909028766</v>
@@ -3016,7 +3016,7 @@
         <v>0.03197766054045453</v>
       </c>
       <c r="D29" t="n">
-        <v>0.04652818778023345</v>
+        <v>0.04652818760502312</v>
       </c>
       <c r="E29" t="n">
         <v>0.03035235703411378</v>
@@ -3107,10 +3107,10 @@
         <v>0.07500231926812009</v>
       </c>
       <c r="D30" t="n">
-        <v>0.04115315178920673</v>
+        <v>0.04115308929629166</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03218997075072093</v>
+        <v>0.03218995455454213</v>
       </c>
       <c r="F30" t="n">
         <v>0.03937925821502111</v>
@@ -3198,7 +3198,7 @@
         <v>0.06477085591513414</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0890822340062209</v>
+        <v>0.08908223319650851</v>
       </c>
       <c r="E31" t="n">
         <v>0.06480292727428162</v>
@@ -3289,10 +3289,10 @@
         <v>0.04866815029499763</v>
       </c>
       <c r="D32" t="n">
-        <v>0.06834767796848798</v>
+        <v>0.06834767330570328</v>
       </c>
       <c r="E32" t="n">
-        <v>0.03854456987449981</v>
+        <v>0.03854450403594292</v>
       </c>
       <c r="F32" t="n">
         <v>0.07388045002427068</v>
@@ -3380,10 +3380,10 @@
         <v>0.5591465006485221</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2006030489216315</v>
+        <v>0.2005962924359451</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1917095832125919</v>
+        <v>0.1917015895739247</v>
       </c>
       <c r="F33" t="n">
         <v>0.2528945913851281</v>
@@ -3471,10 +3471,10 @@
         <v>0.08504262494770862</v>
       </c>
       <c r="D34" t="n">
-        <v>0.04374151629762139</v>
+        <v>0.0437410667210726</v>
       </c>
       <c r="E34" t="n">
-        <v>0.04344469350307765</v>
+        <v>0.0434441623193047</v>
       </c>
       <c r="F34" t="n">
         <v>0.01331963457462606</v>
@@ -3562,10 +3562,10 @@
         <v>0.05107661617171957</v>
       </c>
       <c r="D35" t="n">
-        <v>0.02898352678106121</v>
+        <v>0.02898301858951611</v>
       </c>
       <c r="E35" t="n">
-        <v>0.02596036191515381</v>
+        <v>0.02595996916104477</v>
       </c>
       <c r="F35" t="n">
         <v>0.02249581156851674</v>
@@ -3744,10 +3744,10 @@
         <v>0.140857786790505</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08807413377403074</v>
+        <v>0.08807312174175996</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0879277167183411</v>
+        <v>0.08792720280098572</v>
       </c>
       <c r="F37" t="n">
         <v>0.07907836553756208</v>
@@ -3835,10 +3835,10 @@
         <v>0.1027096772821009</v>
       </c>
       <c r="D38" t="n">
-        <v>0.03461846980117696</v>
+        <v>0.03461846968698081</v>
       </c>
       <c r="E38" t="n">
-        <v>0.03565639575879934</v>
+        <v>0.03565639558925297</v>
       </c>
       <c r="F38" t="n">
         <v>0.007420056334630616</v>
@@ -3926,10 +3926,10 @@
         <v>0.2485157647253419</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1805345648101746</v>
+        <v>0.180525512543861</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1207314367465582</v>
+        <v>0.1207267179680378</v>
       </c>
       <c r="F39" t="n">
         <v>0.1555146779571564</v>
@@ -4017,10 +4017,10 @@
         <v>0.1681666541472387</v>
       </c>
       <c r="D40" t="n">
-        <v>0.121716796881192</v>
+        <v>0.1217167751301444</v>
       </c>
       <c r="E40" t="n">
-        <v>0.09762118316136251</v>
+        <v>0.09761988597509962</v>
       </c>
       <c r="F40" t="n">
         <v>0.1138799180787355</v>
@@ -4108,10 +4108,10 @@
         <v>0.06943424603509075</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1171814300471436</v>
+        <v>0.1171812707469262</v>
       </c>
       <c r="E41" t="n">
-        <v>0.06042369630390779</v>
+        <v>0.06042369572399547</v>
       </c>
       <c r="F41" t="n">
         <v>0.1436002500085728</v>
@@ -4559,10 +4559,10 @@
         <v>0.05390673528200461</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0868567977386574</v>
+        <v>0.08685679098089252</v>
       </c>
       <c r="E46" t="n">
-        <v>0.05188165638304125</v>
+        <v>0.05188096996468297</v>
       </c>
       <c r="F46" t="n">
         <v>0.09292089567095477</v>
@@ -4741,10 +4741,10 @@
         <v>0.07166397487212992</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1371145336101306</v>
+        <v>0.1371129705375034</v>
       </c>
       <c r="E48" t="n">
-        <v>0.05557841886334517</v>
+        <v>0.05557839511833085</v>
       </c>
       <c r="F48" t="n">
         <v>0.1792881884099726</v>
@@ -4832,10 +4832,10 @@
         <v>0.5941492719670419</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2874932819684468</v>
+        <v>0.2874858737103661</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1747449244759837</v>
+        <v>0.1747391294122159</v>
       </c>
       <c r="F49" t="n">
         <v>0.398657720171792</v>
@@ -4923,10 +4923,10 @@
         <v>0.215145744293515</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1228474290000726</v>
+        <v>0.1228456882674846</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1116313766974661</v>
+        <v>0.1116295634389928</v>
       </c>
       <c r="F50" t="n">
         <v>0.1133797562537238</v>
@@ -5014,10 +5014,10 @@
         <v>1.801043269094024</v>
       </c>
       <c r="D51" t="n">
-        <v>0.5784958388176882</v>
+        <v>0.5784958372661392</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5660761010376186</v>
+        <v>0.5660761009362293</v>
       </c>
       <c r="F51" t="n">
         <v>0.1388710229328567</v>
@@ -5105,10 +5105,10 @@
         <v>1.24285466549652</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5152406450114224</v>
+        <v>0.5152321985481989</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5083581686505584</v>
+        <v>0.5083506388857849</v>
       </c>
       <c r="F52" t="n">
         <v>0.3427698616804288</v>
@@ -5196,10 +5196,10 @@
         <v>0.1739984898829535</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2927826332241206</v>
+        <v>0.2927792654478473</v>
       </c>
       <c r="E53" t="n">
-        <v>0.146209334791109</v>
+        <v>0.1462084338779073</v>
       </c>
       <c r="F53" t="n">
         <v>0.2435947772079181</v>
@@ -5378,10 +5378,10 @@
         <v>0.2385085466461309</v>
       </c>
       <c r="D55" t="n">
-        <v>0.400943477183642</v>
+        <v>0.4009307017378948</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4283734198039334</v>
+        <v>0.4283541685507145</v>
       </c>
       <c r="F55" t="n">
         <v>0.2866945656317785</v>
@@ -5560,10 +5560,10 @@
         <v>0.3095529053602163</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1299571743690428</v>
+        <v>0.1299540974205501</v>
       </c>
       <c r="E57" t="n">
-        <v>0.09058676116225803</v>
+        <v>0.09058539555967353</v>
       </c>
       <c r="F57" t="n">
         <v>0.1924806508443604</v>
@@ -5651,10 +5651,10 @@
         <v>0.00350041061804758</v>
       </c>
       <c r="D58" t="n">
-        <v>0.01079367823310745</v>
+        <v>0.01079341673949168</v>
       </c>
       <c r="E58" t="n">
-        <v>0.002018369418234298</v>
+        <v>0.002018317077468956</v>
       </c>
       <c r="F58" t="n">
         <v>0.01160003975057617</v>
@@ -5738,10 +5738,10 @@
         <v>1.000584039568822</v>
       </c>
       <c r="D59" t="n">
-        <v>0.5695029895382235</v>
+        <v>0.5694893725169086</v>
       </c>
       <c r="E59" t="n">
-        <v>0.5213918204846444</v>
+        <v>0.5213797200369358</v>
       </c>
       <c r="F59" t="n">
         <v>0.7303340534387879</v>
@@ -5829,10 +5829,10 @@
         <v>0.8283219632971955</v>
       </c>
       <c r="D60" t="n">
-        <v>0.3995799302614583</v>
+        <v>0.3995720841565115</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3541066154722535</v>
+        <v>0.3541006663407016</v>
       </c>
       <c r="F60" t="n">
         <v>0.5487702634661585</v>
@@ -5920,10 +5920,10 @@
         <v>0.531613281787809</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1104173502564436</v>
+        <v>0.1104158907197382</v>
       </c>
       <c r="E61" t="n">
-        <v>0.09493834708178688</v>
+        <v>0.09493435176575815</v>
       </c>
       <c r="F61" t="n">
         <v>0.08391620484197634</v>
@@ -6011,10 +6011,10 @@
         <v>0.09461974118246931</v>
       </c>
       <c r="D62" t="n">
-        <v>0.09712450005509317</v>
+        <v>0.09712253393721802</v>
       </c>
       <c r="E62" t="n">
-        <v>0.07241742776939489</v>
+        <v>0.07241584859213192</v>
       </c>
       <c r="F62" t="n">
         <v>0.1193157924646424</v>
@@ -6102,10 +6102,10 @@
         <v>0.4503157731456378</v>
       </c>
       <c r="D63" t="n">
-        <v>0.2504194247512969</v>
+        <v>0.2504149003773407</v>
       </c>
       <c r="E63" t="n">
-        <v>0.241198163783708</v>
+        <v>0.2411913800365212</v>
       </c>
       <c r="F63" t="n">
         <v>0.213753104648562</v>
@@ -6193,10 +6193,10 @@
         <v>0.8530721133747085</v>
       </c>
       <c r="D64" t="n">
-        <v>0.4136509908256288</v>
+        <v>0.4136454137261474</v>
       </c>
       <c r="E64" t="n">
-        <v>0.4152079061737333</v>
+        <v>0.4152020300003478</v>
       </c>
       <c r="F64" t="n">
         <v>0.4846109585116196</v>
@@ -6284,10 +6284,10 @@
         <v>0.2469954647965427</v>
       </c>
       <c r="D65" t="n">
-        <v>0.1745648786569929</v>
+        <v>0.174561024179357</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1292083373569749</v>
+        <v>0.1292050899633669</v>
       </c>
       <c r="F65" t="n">
         <v>0.2765703453678259</v>
@@ -6375,10 +6375,10 @@
         <v>0.339686921387015</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1232053752527851</v>
+        <v>0.1232049890022731</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1181130185612264</v>
+        <v>0.1181125117930658</v>
       </c>
       <c r="F66" t="n">
         <v>0.03678165940257595</v>
@@ -6466,10 +6466,10 @@
         <v>0.6693666910520283</v>
       </c>
       <c r="D67" t="n">
-        <v>0.8352458810576215</v>
+        <v>0.8352405067645737</v>
       </c>
       <c r="E67" t="n">
-        <v>0.7294897199297996</v>
+        <v>0.7294692334459616</v>
       </c>
       <c r="F67" t="n">
         <v>0.6082529560423311</v>
@@ -6739,10 +6739,10 @@
         <v>0.5215623854741231</v>
       </c>
       <c r="D70" t="n">
-        <v>0.1422159594260567</v>
+        <v>0.1422128665944157</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1056113560276018</v>
+        <v>0.1056105014151803</v>
       </c>
       <c r="F70" t="n">
         <v>0.1312168236082282</v>
@@ -6830,10 +6830,10 @@
         <v>0.1907699174151322</v>
       </c>
       <c r="D71" t="n">
-        <v>0.03814934027413591</v>
+        <v>0.03814930150911446</v>
       </c>
       <c r="E71" t="n">
-        <v>0.04004075388209836</v>
+        <v>0.0400407121706995</v>
       </c>
       <c r="F71" t="n">
         <v>0.02310561325370156</v>
@@ -6921,7 +6921,7 @@
         <v>0.07066791454408344</v>
       </c>
       <c r="D72" t="n">
-        <v>0.1536474138919351</v>
+        <v>0.153647406175306</v>
       </c>
       <c r="E72" t="n">
         <v>0.07068504877160804</v>
@@ -7012,10 +7012,10 @@
         <v>0.4747789332697916</v>
       </c>
       <c r="D73" t="n">
-        <v>0.5230308871005356</v>
+        <v>0.5230095735548882</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4984846833154721</v>
+        <v>0.4984676843907636</v>
       </c>
       <c r="F73" t="n">
         <v>0.4668088897522757</v>
@@ -7106,7 +7106,7 @@
         <v>0.061473047807748</v>
       </c>
       <c r="E74" t="n">
-        <v>0.06568862343286143</v>
+        <v>0.06568862268949016</v>
       </c>
       <c r="F74" t="n">
         <v>0.05023017156969963</v>
@@ -7194,10 +7194,10 @@
         <v>0.4310334236928344</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1756005492377556</v>
+        <v>0.1755979591583696</v>
       </c>
       <c r="E75" t="n">
-        <v>0.1803073408017623</v>
+        <v>0.1803048297268201</v>
       </c>
       <c r="F75" t="n">
         <v>0.08713615481167204</v>
@@ -7467,10 +7467,10 @@
         <v>0.4101348426216624</v>
       </c>
       <c r="D78" t="n">
-        <v>0.227674447935704</v>
+        <v>0.227670207560802</v>
       </c>
       <c r="E78" t="n">
-        <v>0.238742189635288</v>
+        <v>0.2387387822557609</v>
       </c>
       <c r="F78" t="n">
         <v>0.1260107992817844</v>
@@ -7649,10 +7649,10 @@
         <v>0.1944322421102406</v>
       </c>
       <c r="D80" t="n">
-        <v>0.1974283208661482</v>
+        <v>0.1974247615015275</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1883206200808255</v>
+        <v>0.1883173101508702</v>
       </c>
       <c r="F80" t="n">
         <v>0.0961272633102709</v>
@@ -7740,10 +7740,10 @@
         <v>0.3399825225936571</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2131844858108515</v>
+        <v>0.213182546935561</v>
       </c>
       <c r="E81" t="n">
-        <v>0.144148674756563</v>
+        <v>0.1441485815991801</v>
       </c>
       <c r="F81" t="n">
         <v>0.1863089226992002</v>
@@ -7922,10 +7922,10 @@
         <v>0.4410508919541843</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2257281618807142</v>
+        <v>0.2257238801875791</v>
       </c>
       <c r="E83" t="n">
-        <v>0.2058649042407174</v>
+        <v>0.205862292778892</v>
       </c>
       <c r="F83" t="n">
         <v>0.1734795778864761</v>
@@ -8013,10 +8013,10 @@
         <v>0.3589162983011352</v>
       </c>
       <c r="D84" t="n">
-        <v>0.5786565818926416</v>
+        <v>0.5786518131564522</v>
       </c>
       <c r="E84" t="n">
-        <v>0.2288652060312966</v>
+        <v>0.2288601773520736</v>
       </c>
       <c r="F84" t="n">
         <v>0.4663671631288341</v>
@@ -8104,10 +8104,10 @@
         <v>0.1970097092554824</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1159180650085006</v>
+        <v>0.1159159847828685</v>
       </c>
       <c r="E85" t="n">
-        <v>0.1124653960081582</v>
+        <v>0.1124637680375863</v>
       </c>
       <c r="F85" t="n">
         <v>0.1127077238682392</v>
@@ -8195,10 +8195,10 @@
         <v>0.2252331980617254</v>
       </c>
       <c r="D86" t="n">
-        <v>0.1740836765814558</v>
+        <v>0.174082655242504</v>
       </c>
       <c r="E86" t="n">
-        <v>0.1468797698668851</v>
+        <v>0.1468793639473467</v>
       </c>
       <c r="F86" t="n">
         <v>0.1838230688026703</v>
@@ -8286,10 +8286,10 @@
         <v>0.1071978813708681</v>
       </c>
       <c r="D87" t="n">
-        <v>0.1169065011399956</v>
+        <v>0.1169062259152567</v>
       </c>
       <c r="E87" t="n">
-        <v>0.08794515677020905</v>
+        <v>0.08794507664240567</v>
       </c>
       <c r="F87" t="n">
         <v>0.1275708486215023</v>
@@ -8468,10 +8468,10 @@
         <v>0.187946565817732</v>
       </c>
       <c r="D89" t="n">
-        <v>0.1658599440007824</v>
+        <v>0.1658578086303582</v>
       </c>
       <c r="E89" t="n">
-        <v>0.1551302276253412</v>
+        <v>0.1551291014110546</v>
       </c>
       <c r="F89" t="n">
         <v>0.1266136326211225</v>
@@ -8559,10 +8559,10 @@
         <v>0.9827987275038074</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3313758369541271</v>
+        <v>0.3313756532078322</v>
       </c>
       <c r="E90" t="n">
-        <v>0.3633035682769993</v>
+        <v>0.3633016339837019</v>
       </c>
       <c r="F90" t="n">
         <v>0.1230211613322603</v>
@@ -8650,10 +8650,10 @@
         <v>0.1672718683817267</v>
       </c>
       <c r="D91" t="n">
-        <v>0.134343252380355</v>
+        <v>0.1343424539559582</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1399338130343685</v>
+        <v>0.1399322470624257</v>
       </c>
       <c r="F91" t="n">
         <v>0.1509217889284667</v>
@@ -8741,10 +8741,10 @@
         <v>0.6188835198794747</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3022245720327218</v>
+        <v>0.3022158222494097</v>
       </c>
       <c r="E92" t="n">
-        <v>0.313113130702445</v>
+        <v>0.3131018683667818</v>
       </c>
       <c r="F92" t="n">
         <v>0.2454608721067457</v>
@@ -8832,7 +8832,7 @@
         <v>0.07626402299458676</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1385461143220439</v>
+        <v>0.1385453860409279</v>
       </c>
       <c r="E93" t="n">
         <v>0.06370154640865755</v>
@@ -8923,10 +8923,10 @@
         <v>0.7602738181432417</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2147186180756945</v>
+        <v>0.2147185884231523</v>
       </c>
       <c r="E94" t="n">
-        <v>0.2247277829767863</v>
+        <v>0.22472768731432</v>
       </c>
       <c r="F94" t="n">
         <v>0.1216949268591854</v>
@@ -9014,10 +9014,10 @@
         <v>0.06779898318107815</v>
       </c>
       <c r="D95" t="n">
-        <v>0.1362111018887769</v>
+        <v>0.1362086464171476</v>
       </c>
       <c r="E95" t="n">
-        <v>0.05728227384940589</v>
+        <v>0.05727961502989849</v>
       </c>
       <c r="F95" t="n">
         <v>0.1835815220971968</v>
@@ -9196,10 +9196,10 @@
         <v>0.2743934654642279</v>
       </c>
       <c r="D97" t="n">
-        <v>0.1453127376371145</v>
+        <v>0.145306979820865</v>
       </c>
       <c r="E97" t="n">
-        <v>0.1099340555783589</v>
+        <v>0.1099290012011739</v>
       </c>
       <c r="F97" t="n">
         <v>0.2344586657567671</v>
@@ -9287,10 +9287,10 @@
         <v>0.4161804193438561</v>
       </c>
       <c r="D98" t="n">
-        <v>0.2528610546217651</v>
+        <v>0.2528538668291991</v>
       </c>
       <c r="E98" t="n">
-        <v>0.1566119271314414</v>
+        <v>0.1566090864987488</v>
       </c>
       <c r="F98" t="n">
         <v>0.5192000253282574</v>
@@ -9378,7 +9378,7 @@
         <v>0.08501400414635085</v>
       </c>
       <c r="D99" t="n">
-        <v>0.1922139139207104</v>
+        <v>0.1922120071398941</v>
       </c>
       <c r="E99" t="n">
         <v>0.09005612711458374</v>
@@ -9469,10 +9469,10 @@
         <v>0.02738594428316249</v>
       </c>
       <c r="D100" t="n">
-        <v>0.01980437140854183</v>
+        <v>0.01980419538930315</v>
       </c>
       <c r="E100" t="n">
-        <v>0.01398590909255813</v>
+        <v>0.01398566384728145</v>
       </c>
       <c r="F100" t="n">
         <v>0.02687075178124612</v>
@@ -9560,10 +9560,10 @@
         <v>1.245016936279405</v>
       </c>
       <c r="D101" t="n">
-        <v>0.5164682039657934</v>
+        <v>0.5164608008396564</v>
       </c>
       <c r="E101" t="n">
-        <v>0.5058688137196128</v>
+        <v>0.5058607658825116</v>
       </c>
       <c r="F101" t="n">
         <v>0.2839539280448209</v>
@@ -9651,7 +9651,7 @@
         <v>0.1093283019514915</v>
       </c>
       <c r="D102" t="n">
-        <v>0.07341330118538017</v>
+        <v>0.07341330073597337</v>
       </c>
       <c r="E102" t="n">
         <v>0.07022790823368349</v>
@@ -9742,10 +9742,10 @@
         <v>0.798537516284292</v>
       </c>
       <c r="D103" t="n">
-        <v>0.2876142625062075</v>
+        <v>0.2876076529272695</v>
       </c>
       <c r="E103" t="n">
-        <v>0.2345088109193128</v>
+        <v>0.2344994152175302</v>
       </c>
       <c r="F103" t="n">
         <v>0.1556238400776608</v>
@@ -10288,10 +10288,10 @@
         <v>0.07889825329983721</v>
       </c>
       <c r="D109" t="n">
-        <v>0.01427659290176402</v>
+        <v>0.01427659271396422</v>
       </c>
       <c r="E109" t="n">
-        <v>0.0138834492042188</v>
+        <v>0.01388344896525143</v>
       </c>
       <c r="F109" t="n">
         <v>0.005321316602960769</v>
@@ -10379,10 +10379,10 @@
         <v>0.3358569056264085</v>
       </c>
       <c r="D110" t="n">
-        <v>0.1435661108263564</v>
+        <v>0.1435643577651277</v>
       </c>
       <c r="E110" t="n">
-        <v>0.1475120305331584</v>
+        <v>0.1475108871310485</v>
       </c>
       <c r="F110" t="n">
         <v>0.05813966215239565</v>
@@ -10470,10 +10470,10 @@
         <v>0.5661357504748894</v>
       </c>
       <c r="D111" t="n">
-        <v>0.2243615628614161</v>
+        <v>0.2243613947745872</v>
       </c>
       <c r="E111" t="n">
-        <v>0.2286471824525416</v>
+        <v>0.2286469892752312</v>
       </c>
       <c r="F111" t="n">
         <v>0.0292443205140462</v>
@@ -10652,10 +10652,10 @@
         <v>0.2067786093847541</v>
       </c>
       <c r="D113" t="n">
-        <v>0.2127471171858691</v>
+        <v>0.212742624812131</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1915595431419174</v>
+        <v>0.1915543543672964</v>
       </c>
       <c r="F113" t="n">
         <v>0.09584238782839646</v>
@@ -10743,10 +10743,10 @@
         <v>0.3479094458485996</v>
       </c>
       <c r="D114" t="n">
-        <v>0.2096640324170497</v>
+        <v>0.2096609101882655</v>
       </c>
       <c r="E114" t="n">
-        <v>0.2163349011951406</v>
+        <v>0.2163325738864884</v>
       </c>
       <c r="F114" t="n">
         <v>0.1424997212317195</v>
@@ -11107,7 +11107,7 @@
         <v>0.09221947074630707</v>
       </c>
       <c r="D118" t="n">
-        <v>0.1447029803012069</v>
+        <v>0.1447024863381481</v>
       </c>
       <c r="E118" t="n">
         <v>0.0922271888526006</v>
@@ -11198,7 +11198,7 @@
         <v>0.02796112559499681</v>
       </c>
       <c r="D119" t="n">
-        <v>0.02045853037943474</v>
+        <v>0.02045853025362208</v>
       </c>
       <c r="E119" t="n">
         <v>0.01807704344729608</v>
@@ -11289,10 +11289,10 @@
         <v>0.09502436808439847</v>
       </c>
       <c r="D120" t="n">
-        <v>0.05073769489589935</v>
+        <v>0.05073765715169388</v>
       </c>
       <c r="E120" t="n">
-        <v>0.0496468819803621</v>
+        <v>0.04964649207962125</v>
       </c>
       <c r="F120" t="n">
         <v>0.0388933245606785</v>
@@ -11380,10 +11380,10 @@
         <v>0.1891646081037996</v>
       </c>
       <c r="D121" t="n">
-        <v>0.2171489086713133</v>
+        <v>0.2171485135331446</v>
       </c>
       <c r="E121" t="n">
-        <v>0.1388335381061436</v>
+        <v>0.1388315780971986</v>
       </c>
       <c r="F121" t="n">
         <v>0.2069526856014565</v>
@@ -11471,10 +11471,10 @@
         <v>0.0615775885085238</v>
       </c>
       <c r="D122" t="n">
-        <v>0.06358799356885288</v>
+        <v>0.06358799352742592</v>
       </c>
       <c r="E122" t="n">
-        <v>0.0669912551286478</v>
+        <v>0.06699090634529044</v>
       </c>
       <c r="F122" t="n">
         <v>0.05688364621664244</v>
@@ -11562,7 +11562,7 @@
         <v>0.1686449970047895</v>
       </c>
       <c r="D123" t="n">
-        <v>0.09651406869608735</v>
+        <v>0.09651406649233034</v>
       </c>
       <c r="E123" t="n">
         <v>0.07644803716239706</v>
@@ -11653,10 +11653,10 @@
         <v>0.3942418871289511</v>
       </c>
       <c r="D124" t="n">
-        <v>0.3722626766436674</v>
+        <v>0.3722516363298688</v>
       </c>
       <c r="E124" t="n">
-        <v>0.3241979537473308</v>
+        <v>0.3241872982796467</v>
       </c>
       <c r="F124" t="n">
         <v>0.6111573091285377</v>
@@ -11835,10 +11835,10 @@
         <v>0.474918692242627</v>
       </c>
       <c r="D126" t="n">
-        <v>0.2679628936688173</v>
+        <v>0.2679592535324758</v>
       </c>
       <c r="E126" t="n">
-        <v>0.2366426103130069</v>
+        <v>0.2366387195234496</v>
       </c>
       <c r="F126" t="n">
         <v>0.3219415576863928</v>
@@ -11926,10 +11926,10 @@
         <v>0.02895631630547025</v>
       </c>
       <c r="D127" t="n">
-        <v>0.01619062218989057</v>
+        <v>0.01619054670682294</v>
       </c>
       <c r="E127" t="n">
-        <v>0.01402812433726591</v>
+        <v>0.01402809734912791</v>
       </c>
       <c r="F127" t="n">
         <v>0.02228105413134626</v>
@@ -12017,10 +12017,10 @@
         <v>0.2890656229940394</v>
       </c>
       <c r="D128" t="n">
-        <v>0.3623948454425374</v>
+        <v>0.3623850612260368</v>
       </c>
       <c r="E128" t="n">
-        <v>0.2873219551900806</v>
+        <v>0.2873162794259254</v>
       </c>
       <c r="F128" t="n">
         <v>0.1625873721559921</v>
@@ -12108,7 +12108,7 @@
         <v>0.07897339022108103</v>
       </c>
       <c r="D129" t="n">
-        <v>0.1171276616263264</v>
+        <v>0.1171268531866725</v>
       </c>
       <c r="E129" t="n">
         <v>0.07668414077933325</v>
@@ -12199,10 +12199,10 @@
         <v>0.1182962977352434</v>
       </c>
       <c r="D130" t="n">
-        <v>0.130458291373072</v>
+        <v>0.1304570069024353</v>
       </c>
       <c r="E130" t="n">
-        <v>0.09225806638990944</v>
+        <v>0.09225806483811053</v>
       </c>
       <c r="F130" t="n">
         <v>0.1613767118169882</v>
@@ -12290,10 +12290,10 @@
         <v>0.5652462685629582</v>
       </c>
       <c r="D131" t="n">
-        <v>0.2957260824677538</v>
+        <v>0.2957165959246806</v>
       </c>
       <c r="E131" t="n">
-        <v>0.1616477914778406</v>
+        <v>0.1616395235373468</v>
       </c>
       <c r="F131" t="n">
         <v>0.4711296942484131</v>
@@ -12381,10 +12381,10 @@
         <v>0.6863422191730941</v>
       </c>
       <c r="D132" t="n">
-        <v>0.2281315984958053</v>
+        <v>0.2281312667962338</v>
       </c>
       <c r="E132" t="n">
-        <v>0.2222782178829268</v>
+        <v>0.222277567520809</v>
       </c>
       <c r="F132" t="n">
         <v>0.08864482897389499</v>
@@ -12472,10 +12472,10 @@
         <v>0.2392856746235035</v>
       </c>
       <c r="D133" t="n">
-        <v>0.1982767270638798</v>
+        <v>0.1982698620254187</v>
       </c>
       <c r="E133" t="n">
-        <v>0.1967586501078624</v>
+        <v>0.1967518194583459</v>
       </c>
       <c r="F133" t="n">
         <v>0.1342255630003297</v>
@@ -12563,10 +12563,10 @@
         <v>0.6346983240754389</v>
       </c>
       <c r="D134" t="n">
-        <v>0.2584594606841544</v>
+        <v>0.2584548290409174</v>
       </c>
       <c r="E134" t="n">
-        <v>0.2419008328287784</v>
+        <v>0.2418974356146822</v>
       </c>
       <c r="F134" t="n">
         <v>0.1597810507090881</v>
@@ -12654,10 +12654,10 @@
         <v>0.1928933544962687</v>
       </c>
       <c r="D135" t="n">
-        <v>0.1745212094912219</v>
+        <v>0.1745198297609439</v>
       </c>
       <c r="E135" t="n">
-        <v>0.1791517654604911</v>
+        <v>0.1791500781945969</v>
       </c>
       <c r="F135" t="n">
         <v>0.1331865354292969</v>
@@ -12745,10 +12745,10 @@
         <v>0.3757043281926236</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4884395142834155</v>
+        <v>0.4884319127826126</v>
       </c>
       <c r="E136" t="n">
-        <v>0.1184761487535144</v>
+        <v>0.1184755234831405</v>
       </c>
       <c r="F136" t="n">
         <v>0.9951678084714012</v>
@@ -12836,10 +12836,10 @@
         <v>0.1089455831871634</v>
       </c>
       <c r="D137" t="n">
-        <v>0.1729172509146752</v>
+        <v>0.172917248430325</v>
       </c>
       <c r="E137" t="n">
-        <v>0.1241948382104997</v>
+        <v>0.124189524629587</v>
       </c>
       <c r="F137" t="n">
         <v>0.17293474736815</v>
@@ -12927,10 +12927,10 @@
         <v>1.590507209360802</v>
       </c>
       <c r="D138" t="n">
-        <v>0.600401471518295</v>
+        <v>0.6004014670049019</v>
       </c>
       <c r="E138" t="n">
-        <v>0.6105115102506138</v>
+        <v>0.6105112088913315</v>
       </c>
       <c r="F138" t="n">
         <v>0.3319022122488025</v>
@@ -13018,10 +13018,10 @@
         <v>0.4978721268489525</v>
       </c>
       <c r="D139" t="n">
-        <v>0.1499025089804646</v>
+        <v>0.1498997375041679</v>
       </c>
       <c r="E139" t="n">
-        <v>0.114983556280564</v>
+        <v>0.1149802219901982</v>
       </c>
       <c r="F139" t="n">
         <v>0.09330537550397505</v>
@@ -13109,10 +13109,10 @@
         <v>1.207946375398225</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4384649745313478</v>
+        <v>0.4384642657719623</v>
       </c>
       <c r="E140" t="n">
-        <v>0.4741940910689594</v>
+        <v>0.4741897786000658</v>
       </c>
       <c r="F140" t="n">
         <v>0.2128691352265779</v>
@@ -13200,10 +13200,10 @@
         <v>0.1706942218668353</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2814319593955685</v>
+        <v>0.2814231599070964</v>
       </c>
       <c r="E141" t="n">
-        <v>0.2870328576662894</v>
+        <v>0.2870233394122514</v>
       </c>
       <c r="F141" t="n">
         <v>0.1737068670438273</v>
@@ -13287,10 +13287,10 @@
         <v>0.4017050193022286</v>
       </c>
       <c r="D142" t="n">
-        <v>0.1411529949335098</v>
+        <v>0.1411518451782344</v>
       </c>
       <c r="E142" t="n">
-        <v>0.1336871354939648</v>
+        <v>0.1336859351688658</v>
       </c>
       <c r="F142" t="n">
         <v>0.07356074306436632</v>
@@ -13378,10 +13378,10 @@
         <v>0.2501518267356753</v>
       </c>
       <c r="D143" t="n">
-        <v>0.1400213285200137</v>
+        <v>0.140018223301986</v>
       </c>
       <c r="E143" t="n">
-        <v>0.1267582675134189</v>
+        <v>0.1267549297947174</v>
       </c>
       <c r="F143" t="n">
         <v>0.1441694089160436</v>
@@ -13469,10 +13469,10 @@
         <v>0.2279611738298532</v>
       </c>
       <c r="D144" t="n">
-        <v>0.1919599881630009</v>
+        <v>0.1919575124986195</v>
       </c>
       <c r="E144" t="n">
-        <v>0.1219171474650272</v>
+        <v>0.121915760802569</v>
       </c>
       <c r="F144" t="n">
         <v>0.2096035566565423</v>
@@ -13560,10 +13560,10 @@
         <v>0.2095537236409708</v>
       </c>
       <c r="D145" t="n">
-        <v>0.1482214391957</v>
+        <v>0.1482190310450445</v>
       </c>
       <c r="E145" t="n">
-        <v>0.1338885225237101</v>
+        <v>0.1338866239582152</v>
       </c>
       <c r="F145" t="n">
         <v>0.08384009936851858</v>
@@ -13651,7 +13651,7 @@
         <v>0.1316833842378677</v>
       </c>
       <c r="D146" t="n">
-        <v>0.2659819235204327</v>
+        <v>0.2659810599697178</v>
       </c>
       <c r="E146" t="n">
         <v>0.1367934268770089</v>
@@ -13742,10 +13742,10 @@
         <v>0.1770725611530786</v>
       </c>
       <c r="D147" t="n">
-        <v>0.2732835861987756</v>
+        <v>0.2732752238786685</v>
       </c>
       <c r="E147" t="n">
-        <v>0.2657101726279573</v>
+        <v>0.2656978404818304</v>
       </c>
       <c r="F147" t="n">
         <v>0.197461019704803</v>
@@ -13833,7 +13833,7 @@
         <v>0.07828751995306629</v>
       </c>
       <c r="D148" t="n">
-        <v>0.1527548698494082</v>
+        <v>0.15275482728912</v>
       </c>
       <c r="E148" t="n">
         <v>0.07836470527400402</v>

--- a/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
+++ b/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
@@ -479,22 +479,22 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>fit_lognorm_SW</t>
+          <t>fit_lognorm_SF</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>fit_lognorm_SW_uw</t>
+          <t>fit_lognorm_SF_uw</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>fit_norm_SW</t>
+          <t>fit_norm_SF</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>fit_norm_SW_uw</t>
+          <t>fit_norm_SF_uw</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
@@ -604,13 +604,13 @@
         <v>0.8494116503658599</v>
       </c>
       <c r="O2" t="n">
-        <v>0.912889545161801</v>
+        <v>0.9092060209108411</v>
       </c>
       <c r="P2" t="n">
         <v>0.9408523678774999</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8870817017132662</v>
+        <v>0.8835780693820586</v>
       </c>
       <c r="R2" t="n">
         <v>-0.4232017742483016</v>
@@ -695,13 +695,13 @@
         <v>0.8917379209458604</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9247448315443465</v>
+        <v>0.9176917024745919</v>
       </c>
       <c r="P3" t="n">
         <v>0.9666226237052599</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9467795739712258</v>
+        <v>0.9456204318122453</v>
       </c>
       <c r="R3" t="n">
         <v>0.1662591797972714</v>
@@ -786,13 +786,13 @@
         <v>0.9533433053206312</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9622585378473276</v>
+        <v>0.9620883018847108</v>
       </c>
       <c r="P4" t="n">
         <v>0.4489224569193863</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5006358208247527</v>
+        <v>0.4978144421636235</v>
       </c>
       <c r="R4" t="n">
         <v>42.28521597572163</v>
@@ -877,13 +877,13 @@
         <v>0.929692177466275</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9191877037826821</v>
+        <v>0.9184114196227847</v>
       </c>
       <c r="P5" t="n">
         <v>0.1013657572748851</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.09161637184597682</v>
+        <v>0.08750428201791764</v>
       </c>
       <c r="R5" t="n">
         <v>163.8665054210526</v>
@@ -968,13 +968,13 @@
         <v>0.972478099150505</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9537935662538458</v>
+        <v>0.9530177174944041</v>
       </c>
       <c r="P6" t="n">
         <v>0.8123807792000486</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.822467890478628</v>
+        <v>0.8180317221940644</v>
       </c>
       <c r="R6" t="n">
         <v>5.668478652861983</v>
@@ -1059,13 +1059,13 @@
         <v>0.9207403261318348</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9519748627859773</v>
+        <v>0.9440011262152957</v>
       </c>
       <c r="P7" t="n">
         <v>0.6899197883377912</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7183996529751426</v>
+        <v>0.7114210013043908</v>
       </c>
       <c r="R7" t="n">
         <v>6.812647729582318</v>
@@ -1150,13 +1150,13 @@
         <v>0.9474251833827445</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9510641296365299</v>
+        <v>0.9557090450612272</v>
       </c>
       <c r="P8" t="n">
         <v>0.8349972892712356</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8443267531038592</v>
+        <v>0.8479020220897057</v>
       </c>
       <c r="R8" t="n">
         <v>0.7931281673288593</v>
@@ -1247,7 +1247,7 @@
         <v>0.9955351590063858</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9998590287176354</v>
+        <v>0.9998590287176358</v>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
@@ -1328,13 +1328,13 @@
         <v>0.9030430298440333</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9093437360966836</v>
+        <v>0.911289510479757</v>
       </c>
       <c r="P10" t="n">
         <v>0.7920321457730231</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7629110641513599</v>
+        <v>0.7564910499909325</v>
       </c>
       <c r="R10" t="n">
         <v>2.269020227040517</v>
@@ -1419,13 +1419,13 @@
         <v>0.9652229947878748</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9678180434231227</v>
+        <v>0.9678621478402331</v>
       </c>
       <c r="P11" t="n">
         <v>0.9028121578587365</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8963405675894759</v>
+        <v>0.8963564790783439</v>
       </c>
       <c r="R11" t="n">
         <v>5.904110082353125</v>
@@ -1510,13 +1510,13 @@
         <v>0.9839805203242731</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9543715662249908</v>
+        <v>0.9603015742842809</v>
       </c>
       <c r="P12" t="n">
         <v>0.6822747554989643</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6497797011049407</v>
+        <v>0.6464974667569573</v>
       </c>
       <c r="R12" t="n">
         <v>5.190211222203374</v>
@@ -1601,13 +1601,13 @@
         <v>0.9780114202410796</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9883179098031101</v>
+        <v>0.9889175902627609</v>
       </c>
       <c r="P13" t="n">
         <v>0.7336423377662074</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7493861778079243</v>
+        <v>0.7419603693943674</v>
       </c>
       <c r="R13" t="n">
         <v>10.32890244783706</v>
@@ -1692,13 +1692,13 @@
         <v>0.8727234599054907</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8724002405574519</v>
+        <v>0.8690364524191365</v>
       </c>
       <c r="P14" t="n">
         <v>0.8705184285634944</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.7943923596512326</v>
+        <v>0.7862656126481635</v>
       </c>
       <c r="R14" t="n">
         <v>6.540705755360844</v>
@@ -1783,13 +1783,13 @@
         <v>0.9572999427082871</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9309556255000982</v>
+        <v>0.9318061333144438</v>
       </c>
       <c r="P15" t="n">
         <v>0.5829353329793079</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.5669579032811601</v>
+        <v>0.5664586343972672</v>
       </c>
       <c r="R15" t="n">
         <v>16.65055314118036</v>
@@ -1874,13 +1874,13 @@
         <v>0.9290963667493711</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9295911053734708</v>
+        <v>0.9295911053734703</v>
       </c>
       <c r="P16" t="n">
         <v>0.9965370912975703</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9955275127701789</v>
+        <v>0.9955275127701788</v>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
@@ -1961,13 +1961,13 @@
         <v>0.951626762063243</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9612540179928349</v>
+        <v>0.9620477983526827</v>
       </c>
       <c r="P17" t="n">
         <v>0.5589212807730928</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6383083103717502</v>
+        <v>0.6344410859030679</v>
       </c>
       <c r="R17" t="n">
         <v>15.7304797314563</v>
@@ -2052,13 +2052,13 @@
         <v>0.9796649449918181</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8678362403890658</v>
+        <v>0.8678362403890659</v>
       </c>
       <c r="P18" t="n">
         <v>0.9659464275170122</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.7774078101824612</v>
+        <v>0.7774078101824614</v>
       </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
@@ -2139,13 +2139,13 @@
         <v>0.9578191260316599</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9542076589471196</v>
+        <v>0.9582148841164957</v>
       </c>
       <c r="P19" t="n">
         <v>0.8499463737329206</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8034669915087368</v>
+        <v>0.7981866459686259</v>
       </c>
       <c r="R19" t="n">
         <v>3.002562856742959</v>
@@ -2230,13 +2230,13 @@
         <v>0.975434139575947</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9763024936774269</v>
+        <v>0.9741862180691335</v>
       </c>
       <c r="P20" t="n">
         <v>0.7372657332390844</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5220239953661741</v>
+        <v>0.5067517139688824</v>
       </c>
       <c r="R20" t="n">
         <v>11.96830709957616</v>
@@ -2321,13 +2321,13 @@
         <v>0.8956671122333576</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9362987071392876</v>
+        <v>0.9364420269624285</v>
       </c>
       <c r="P21" t="n">
         <v>0.6806677497662093</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.5664516080586816</v>
+        <v>0.5603242798676761</v>
       </c>
       <c r="R21" t="n">
         <v>9.549626396730812</v>
@@ -2412,13 +2412,13 @@
         <v>0.9531632821687459</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9766644527137446</v>
+        <v>0.9733576455854616</v>
       </c>
       <c r="P22" t="n">
         <v>0.6235227628305499</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.6386430733705381</v>
+        <v>0.6229215418397556</v>
       </c>
       <c r="R22" t="n">
         <v>4.580741592184308</v>
@@ -2503,13 +2503,13 @@
         <v>0.9883291140257277</v>
       </c>
       <c r="O23" t="n">
-        <v>0.976722031293628</v>
+        <v>0.9764788605215103</v>
       </c>
       <c r="P23" t="n">
         <v>0.8383344143204015</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.7744174689324486</v>
+        <v>0.7677189383203588</v>
       </c>
       <c r="R23" t="n">
         <v>5.286696521289679</v>
@@ -2594,13 +2594,13 @@
         <v>0.9022344079326899</v>
       </c>
       <c r="O24" t="n">
-        <v>0.895248868519865</v>
+        <v>0.9175311762105741</v>
       </c>
       <c r="P24" t="n">
         <v>0.7803373328992713</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.8234945768871653</v>
+        <v>0.8439091183293908</v>
       </c>
       <c r="R24" t="n">
         <v>1.06680996146393</v>
@@ -2685,13 +2685,13 @@
         <v>0.9654994347763881</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9604514402835619</v>
+        <v>0.958041135483536</v>
       </c>
       <c r="P25" t="n">
         <v>0.8378708341747267</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.8570248075475875</v>
+        <v>0.8577269340636383</v>
       </c>
       <c r="R25" t="n">
         <v>1.930820456870329</v>
@@ -2776,13 +2776,13 @@
         <v>0.9599137570001955</v>
       </c>
       <c r="O26" t="n">
-        <v>0.9602418130793022</v>
+        <v>0.9596970004623615</v>
       </c>
       <c r="P26" t="n">
         <v>0.401851652011318</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.4398563005030176</v>
+        <v>0.435425153916047</v>
       </c>
       <c r="R26" t="n">
         <v>47.20796066291464</v>
@@ -2867,13 +2867,13 @@
         <v>0.9684858514659004</v>
       </c>
       <c r="O27" t="n">
-        <v>0.9733156961631455</v>
+        <v>0.9745944148978668</v>
       </c>
       <c r="P27" t="n">
         <v>0.9597109699779091</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9594868617230063</v>
+        <v>0.9608978585480642</v>
       </c>
       <c r="R27" t="n">
         <v>-0.3973653073210545</v>
@@ -2958,13 +2958,13 @@
         <v>0.9795995889800222</v>
       </c>
       <c r="O28" t="n">
-        <v>0.9904931908448098</v>
+        <v>0.9894957426100602</v>
       </c>
       <c r="P28" t="n">
         <v>0.9811433589819321</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9606212700622762</v>
+        <v>0.959258370009439</v>
       </c>
       <c r="R28" t="n">
         <v>-1.353236489437302</v>
@@ -3049,13 +3049,13 @@
         <v>0.9022485624589032</v>
       </c>
       <c r="O29" t="n">
-        <v>0.9478327709605739</v>
+        <v>0.9285510909684714</v>
       </c>
       <c r="P29" t="n">
         <v>0.8891449008487291</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.9248111073270874</v>
+        <v>0.9053502333035361</v>
       </c>
       <c r="R29" t="n">
         <v>5.838767464500953</v>
@@ -3140,13 +3140,13 @@
         <v>0.9816310740309314</v>
       </c>
       <c r="O30" t="n">
-        <v>0.9799613530865678</v>
+        <v>0.9802206178601236</v>
       </c>
       <c r="P30" t="n">
         <v>0.9172249791720093</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.9043754404401715</v>
+        <v>0.9049070072377239</v>
       </c>
       <c r="R30" t="n">
         <v>1.412023702974907</v>
@@ -3231,13 +3231,13 @@
         <v>0.9731432497154273</v>
       </c>
       <c r="O31" t="n">
-        <v>0.9803959633627402</v>
+        <v>0.9826903094730325</v>
       </c>
       <c r="P31" t="n">
         <v>0.9802220681656316</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9733299166520434</v>
+        <v>0.9735941299923175</v>
       </c>
       <c r="R31" t="n">
         <v>-0.6157999738070424</v>
@@ -3322,13 +3322,13 @@
         <v>0.9465754317706573</v>
       </c>
       <c r="O32" t="n">
-        <v>0.9673180737593341</v>
+        <v>0.9672279193735077</v>
       </c>
       <c r="P32" t="n">
         <v>0.8794085062473335</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9213873827286474</v>
+        <v>0.9202025250993612</v>
       </c>
       <c r="R32" t="n">
         <v>3.34317902200783</v>
@@ -3413,13 +3413,13 @@
         <v>0.9186335129552035</v>
       </c>
       <c r="O33" t="n">
-        <v>0.9240961497292354</v>
+        <v>0.9284356708505789</v>
       </c>
       <c r="P33" t="n">
         <v>0.7226802181148442</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.6691699558470116</v>
+        <v>0.6631689950689539</v>
       </c>
       <c r="R33" t="n">
         <v>9.82683715516575</v>
@@ -3504,13 +3504,13 @@
         <v>0.9847308287724691</v>
       </c>
       <c r="O34" t="n">
-        <v>0.9862532986272947</v>
+        <v>0.9861897621005156</v>
       </c>
       <c r="P34" t="n">
         <v>0.9419396660461248</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.9448352377733952</v>
+        <v>0.9448869411265992</v>
       </c>
       <c r="R34" t="n">
         <v>-0.08586160146506275</v>
@@ -3595,13 +3595,13 @@
         <v>0.9854139733963865</v>
       </c>
       <c r="O35" t="n">
-        <v>0.9848214852912753</v>
+        <v>0.9857099336535577</v>
       </c>
       <c r="P35" t="n">
         <v>0.9410711935826805</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9433003010535914</v>
+        <v>0.9428425243038698</v>
       </c>
       <c r="R35" t="n">
         <v>1.08913324359499</v>
@@ -3686,13 +3686,13 @@
         <v>0.9412089093464671</v>
       </c>
       <c r="O36" t="n">
-        <v>0.9456228633803195</v>
+        <v>0.9455040331102524</v>
       </c>
       <c r="P36" t="n">
         <v>0.8688056087814576</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.8884211610099567</v>
+        <v>0.8876079866374171</v>
       </c>
       <c r="R36" t="n">
         <v>12.21131677476156</v>
@@ -3777,13 +3777,13 @@
         <v>0.9468811101110821</v>
       </c>
       <c r="O37" t="n">
-        <v>0.9445280525474916</v>
+        <v>0.9417552493518829</v>
       </c>
       <c r="P37" t="n">
         <v>0.8898171532143072</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.864462699249297</v>
+        <v>0.8683795528088797</v>
       </c>
       <c r="R37" t="n">
         <v>0.8204360219009512</v>
@@ -3868,13 +3868,13 @@
         <v>0.9706546985838592</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9748794474647776</v>
+        <v>0.9748370575681687</v>
       </c>
       <c r="P38" t="n">
         <v>0.8252870290484627</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.8410209673686802</v>
+        <v>0.8409040981188135</v>
       </c>
       <c r="R38" t="n">
         <v>10.87620022088294</v>
@@ -3959,13 +3959,13 @@
         <v>0.9467811380414417</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9180642120630196</v>
+        <v>0.9249435362049317</v>
       </c>
       <c r="P39" t="n">
         <v>0.8950699757770634</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.9043980327782193</v>
+        <v>0.9098367774503526</v>
       </c>
       <c r="R39" t="n">
         <v>0.6502411539271484</v>
@@ -4050,13 +4050,13 @@
         <v>0.9362699502971596</v>
       </c>
       <c r="O40" t="n">
-        <v>0.9436469094758352</v>
+        <v>0.9407788142431837</v>
       </c>
       <c r="P40" t="n">
         <v>0.8717929060913877</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.7827473234135598</v>
+        <v>0.7774113386726403</v>
       </c>
       <c r="R40" t="n">
         <v>5.712982870909621</v>
@@ -4141,13 +4141,13 @@
         <v>0.980670792735478</v>
       </c>
       <c r="O41" t="n">
-        <v>0.9633020898839904</v>
+        <v>0.9536016963377437</v>
       </c>
       <c r="P41" t="n">
         <v>0.9196367744331216</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.8762951649435859</v>
+        <v>0.863536014372004</v>
       </c>
       <c r="R41" t="n">
         <v>4.094525149186255</v>
@@ -4232,13 +4232,13 @@
         <v>0.8813815533659585</v>
       </c>
       <c r="O42" t="n">
-        <v>0.75870676392347</v>
+        <v>0.7587067639234697</v>
       </c>
       <c r="P42" t="n">
         <v>0.8881419827509356</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.7721721138764062</v>
+        <v>0.7721721138764063</v>
       </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
@@ -4319,13 +4319,13 @@
         <v>0.9748672079469952</v>
       </c>
       <c r="O43" t="n">
-        <v>0.971485193523098</v>
+        <v>0.96630985951165</v>
       </c>
       <c r="P43" t="n">
         <v>0.2112867046336534</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.1686344187607627</v>
+        <v>0.159177693493579</v>
       </c>
       <c r="R43" t="n">
         <v>525.1663376619023</v>
@@ -4410,13 +4410,13 @@
         <v>0.9633142632052857</v>
       </c>
       <c r="O44" t="n">
-        <v>0.9611221891369903</v>
+        <v>0.9645133852031788</v>
       </c>
       <c r="P44" t="n">
         <v>0.9676119139575859</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.9626791170066653</v>
+        <v>0.966680358069733</v>
       </c>
       <c r="R44" t="n">
         <v>-1.066623475499305</v>
@@ -4501,13 +4501,13 @@
         <v>0.982071153192389</v>
       </c>
       <c r="O45" t="n">
-        <v>0.9834011717462637</v>
+        <v>0.9827587906733408</v>
       </c>
       <c r="P45" t="n">
         <v>0.9656810495914704</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.970718581490819</v>
+        <v>0.9710239429878805</v>
       </c>
       <c r="R45" t="n">
         <v>0.1934105440441739</v>
@@ -4592,13 +4592,13 @@
         <v>0.9501898347653676</v>
       </c>
       <c r="O46" t="n">
-        <v>0.9203172267851878</v>
+        <v>0.9299070304301821</v>
       </c>
       <c r="P46" t="n">
         <v>0.930789213775484</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.9102495874274408</v>
+        <v>0.9198006311770659</v>
       </c>
       <c r="R46" t="n">
         <v>-0.8259364872851389</v>
@@ -4683,13 +4683,13 @@
         <v>0.9054869344259462</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9239109548009905</v>
+        <v>0.9307014047869741</v>
       </c>
       <c r="P47" t="n">
         <v>0.9497259045844483</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.9520711149135589</v>
+        <v>0.9591445608254481</v>
       </c>
       <c r="R47" t="n">
         <v>-0.7175555103435306</v>
@@ -4774,13 +4774,13 @@
         <v>0.9514305868631614</v>
       </c>
       <c r="O48" t="n">
-        <v>0.8839596731286349</v>
+        <v>0.8811535865145093</v>
       </c>
       <c r="P48" t="n">
         <v>0.8321404875263214</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.6270007800005779</v>
+        <v>0.6191353025216019</v>
       </c>
       <c r="R48" t="n">
         <v>17.45610091815069</v>
@@ -4865,13 +4865,13 @@
         <v>0.961968651691529</v>
       </c>
       <c r="O49" t="n">
-        <v>0.9355534595019865</v>
+        <v>0.9382383419651381</v>
       </c>
       <c r="P49" t="n">
         <v>0.6533444986987889</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.7367704200508431</v>
+        <v>0.7323263155781626</v>
       </c>
       <c r="R49" t="n">
         <v>12.11917777500005</v>
@@ -4956,13 +4956,13 @@
         <v>0.9532135184127367</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9573153188717286</v>
+        <v>0.9528255282056156</v>
       </c>
       <c r="P50" t="n">
         <v>0.8214356871280972</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.7554764800270884</v>
+        <v>0.750814084224615</v>
       </c>
       <c r="R50" t="n">
         <v>3.701598110423332</v>
@@ -5047,13 +5047,13 @@
         <v>0.942617875759766</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9285698432291277</v>
+        <v>0.927179826973757</v>
       </c>
       <c r="P51" t="n">
         <v>0.3040643543049877</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.3197038470529262</v>
+        <v>0.3160099443114681</v>
       </c>
       <c r="R51" t="n">
         <v>30.85059786755903</v>
@@ -5138,13 +5138,13 @@
         <v>0.9671375358809949</v>
       </c>
       <c r="O52" t="n">
-        <v>0.9697349107314407</v>
+        <v>0.9699044536362832</v>
       </c>
       <c r="P52" t="n">
         <v>0.5355876415060616</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.5564444850936798</v>
+        <v>0.5553793733772043</v>
       </c>
       <c r="R52" t="n">
         <v>11.49834456384718</v>
@@ -5229,13 +5229,13 @@
         <v>0.9736282514157977</v>
       </c>
       <c r="O53" t="n">
-        <v>0.9618989801768074</v>
+        <v>0.9531953703848772</v>
       </c>
       <c r="P53" t="n">
         <v>0.8841924993922177</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.8422786876312083</v>
+        <v>0.8308422751056909</v>
       </c>
       <c r="R53" t="n">
         <v>0.4152861003419528</v>
@@ -5320,13 +5320,13 @@
         <v>0.8819310189564558</v>
       </c>
       <c r="O54" t="n">
-        <v>0.8849505243937633</v>
+        <v>0.8845006482727006</v>
       </c>
       <c r="P54" t="n">
         <v>0.957828754145963</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9703162055578234</v>
+        <v>0.9710928362997387</v>
       </c>
       <c r="R54" t="n">
         <v>1.043583110562199</v>
@@ -5411,13 +5411,13 @@
         <v>0.9059134069707252</v>
       </c>
       <c r="O55" t="n">
-        <v>0.9480477544728466</v>
+        <v>0.9586864806868646</v>
       </c>
       <c r="P55" t="n">
         <v>0.9698747474161831</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.941591994063652</v>
+        <v>0.9542121420021797</v>
       </c>
       <c r="R55" t="n">
         <v>-2.355523716459283</v>
@@ -5502,13 +5502,13 @@
         <v>0.82514045651893</v>
       </c>
       <c r="O56" t="n">
-        <v>0.8632710164081342</v>
+        <v>0.8640016404242711</v>
       </c>
       <c r="P56" t="n">
         <v>0.9525832569828501</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.9642406132147385</v>
+        <v>0.9643369688067852</v>
       </c>
       <c r="R56" t="n">
         <v>0.1381867509915326</v>
@@ -5593,13 +5593,13 @@
         <v>0.9818598844200473</v>
       </c>
       <c r="O57" t="n">
-        <v>0.9733193275962856</v>
+        <v>0.9727929961398722</v>
       </c>
       <c r="P57" t="n">
         <v>0.6914038228070565</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.6428300351769272</v>
+        <v>0.639559644635877</v>
       </c>
       <c r="R57" t="n">
         <v>16.38871777755219</v>
@@ -5684,13 +5684,13 @@
         <v>0.9518464854848355</v>
       </c>
       <c r="O58" t="n">
-        <v>0.9820108264654308</v>
+        <v>0.9820108264654309</v>
       </c>
       <c r="P58" t="n">
         <v>0.949893963496349</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.9810450295997544</v>
+        <v>0.9810450295997541</v>
       </c>
       <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
@@ -5771,13 +5771,13 @@
         <v>0.9583520154878493</v>
       </c>
       <c r="O59" t="n">
-        <v>0.9426447578313228</v>
+        <v>0.9518279459515709</v>
       </c>
       <c r="P59" t="n">
         <v>0.5740443939582374</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.5969111209131408</v>
+        <v>0.5838970155092895</v>
       </c>
       <c r="R59" t="n">
         <v>10.6070709542266</v>
@@ -5862,13 +5862,13 @@
         <v>0.8042775435315257</v>
       </c>
       <c r="O60" t="n">
-        <v>0.8542875930837134</v>
+        <v>0.860521535210255</v>
       </c>
       <c r="P60" t="n">
         <v>0.556352334564728</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.6356484294516034</v>
+        <v>0.6174926891147209</v>
       </c>
       <c r="R60" t="n">
         <v>13.59504239802839</v>
@@ -5953,13 +5953,13 @@
         <v>0.9633672546730235</v>
       </c>
       <c r="O61" t="n">
-        <v>0.9633450856730293</v>
+        <v>0.9633842197958534</v>
       </c>
       <c r="P61" t="n">
         <v>0.6238243798519839</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.6304307068796957</v>
+        <v>0.6240837856174626</v>
       </c>
       <c r="R61" t="n">
         <v>40.22587551252376</v>
@@ -6044,13 +6044,13 @@
         <v>0.9440637496859311</v>
       </c>
       <c r="O62" t="n">
-        <v>0.9279110452090704</v>
+        <v>0.9272542758582301</v>
       </c>
       <c r="P62" t="n">
         <v>0.8240321768183324</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.7576271999845836</v>
+        <v>0.7502973278456877</v>
       </c>
       <c r="R62" t="n">
         <v>8.59685270788783</v>
@@ -6135,13 +6135,13 @@
         <v>0.972454540235953</v>
       </c>
       <c r="O63" t="n">
-        <v>0.9569623874889673</v>
+        <v>0.9606790295030297</v>
       </c>
       <c r="P63" t="n">
         <v>0.7781383125359719</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.8036513766302492</v>
+        <v>0.8032142940637226</v>
       </c>
       <c r="R63" t="n">
         <v>0.5015070220605585</v>
@@ -6226,13 +6226,13 @@
         <v>0.8670774729965373</v>
       </c>
       <c r="O64" t="n">
-        <v>0.8527623997462219</v>
+        <v>0.8516775957051272</v>
       </c>
       <c r="P64" t="n">
         <v>0.5649063131443962</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.6046637617537263</v>
+        <v>0.5913282496763302</v>
       </c>
       <c r="R64" t="n">
         <v>5.312004768479652</v>
@@ -6317,13 +6317,13 @@
         <v>0.9435590877433198</v>
       </c>
       <c r="O65" t="n">
-        <v>0.9589790051961298</v>
+        <v>0.952245173518852</v>
       </c>
       <c r="P65" t="n">
         <v>0.8411942932386974</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.6830020924039805</v>
+        <v>0.6715272529998201</v>
       </c>
       <c r="R65" t="n">
         <v>5.2699782656013</v>
@@ -6408,13 +6408,13 @@
         <v>0.9691571580090885</v>
       </c>
       <c r="O66" t="n">
-        <v>0.9762806236819012</v>
+        <v>0.9763129896924536</v>
       </c>
       <c r="P66" t="n">
         <v>0.6811891617803418</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.7203602888414968</v>
+        <v>0.7199936608870245</v>
       </c>
       <c r="R66" t="n">
         <v>18.38499780164793</v>
@@ -6499,13 +6499,13 @@
         <v>0.9751226878495491</v>
       </c>
       <c r="O67" t="n">
-        <v>0.897395668081957</v>
+        <v>0.8917968611009424</v>
       </c>
       <c r="P67" t="n">
         <v>0.8518677721517369</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.6525371122782042</v>
+        <v>0.6331597910179844</v>
       </c>
       <c r="R67" t="n">
         <v>-2.220394685081102</v>
@@ -6590,13 +6590,13 @@
         <v>0.8732917745311607</v>
       </c>
       <c r="O68" t="n">
-        <v>0.9509604236799754</v>
+        <v>0.9410733125656034</v>
       </c>
       <c r="P68" t="n">
         <v>0.9085826698003754</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.9752253426822088</v>
+        <v>0.9660497361050783</v>
       </c>
       <c r="R68" t="n">
         <v>4.772937894073056</v>
@@ -6681,13 +6681,13 @@
         <v>0.9019765646016595</v>
       </c>
       <c r="O69" t="n">
-        <v>0.8549245506455269</v>
+        <v>0.8754475673706901</v>
       </c>
       <c r="P69" t="n">
         <v>0.9078309723571365</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.8770109025523605</v>
+        <v>0.8966277838417209</v>
       </c>
       <c r="R69" t="n">
         <v>-2.445001271247021</v>
@@ -6772,13 +6772,13 @@
         <v>0.9429577987377119</v>
       </c>
       <c r="O70" t="n">
-        <v>0.9496420194823438</v>
+        <v>0.9495696726536563</v>
       </c>
       <c r="P70" t="n">
         <v>0.5733099477776068</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.5891387186684434</v>
+        <v>0.5837391670106539</v>
       </c>
       <c r="R70" t="n">
         <v>31.27006391293337</v>
@@ -6863,13 +6863,13 @@
         <v>0.9910023060328255</v>
       </c>
       <c r="O71" t="n">
-        <v>0.9896483556657156</v>
+        <v>0.9891615343512296</v>
       </c>
       <c r="P71" t="n">
         <v>0.7365906903457102</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.7216221720870823</v>
+        <v>0.7196268584327049</v>
       </c>
       <c r="R71" t="n">
         <v>26.04710035396777</v>
@@ -6954,13 +6954,13 @@
         <v>0.9638062333650304</v>
       </c>
       <c r="O72" t="n">
-        <v>0.9760458690286841</v>
+        <v>0.9818277296345798</v>
       </c>
       <c r="P72" t="n">
         <v>0.979065881907884</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.9594265198691596</v>
+        <v>0.9667346230623551</v>
       </c>
       <c r="R72" t="n">
         <v>-1.180608223118555</v>
@@ -7045,13 +7045,13 @@
         <v>0.8049473530115732</v>
       </c>
       <c r="O73" t="n">
-        <v>0.7592687740448255</v>
+        <v>0.7858857580675497</v>
       </c>
       <c r="P73" t="n">
         <v>0.7357057470331443</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.7157729723279735</v>
+        <v>0.7406169039146641</v>
       </c>
       <c r="R73" t="n">
         <v>-2.831062965873204</v>
@@ -7136,13 +7136,13 @@
         <v>0.9607344222142805</v>
       </c>
       <c r="O74" t="n">
-        <v>0.9597051473195952</v>
+        <v>0.9585332049395646</v>
       </c>
       <c r="P74" t="n">
         <v>0.8636545249880749</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.9369365116088233</v>
+        <v>0.9326458417713517</v>
       </c>
       <c r="R74" t="n">
         <v>6.418586757296552</v>
@@ -7227,13 +7227,13 @@
         <v>0.9709649683486649</v>
       </c>
       <c r="O75" t="n">
-        <v>0.9460763871725829</v>
+        <v>0.9451940771398796</v>
       </c>
       <c r="P75" t="n">
         <v>0.6906687116354306</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.6381903352266356</v>
+        <v>0.6370653038942111</v>
       </c>
       <c r="R75" t="n">
         <v>5.888071755774107</v>
@@ -7318,13 +7318,13 @@
         <v>0.9549130119249012</v>
       </c>
       <c r="O76" t="n">
-        <v>0.9743502442809521</v>
+        <v>0.9733198524388371</v>
       </c>
       <c r="P76" t="n">
         <v>0.971539430709338</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9655384155258485</v>
+        <v>0.9641084148715836</v>
       </c>
       <c r="R76" t="n">
         <v>0.491701708597072</v>
@@ -7409,13 +7409,13 @@
         <v>0.9941641181119407</v>
       </c>
       <c r="O77" t="n">
-        <v>0.9827670469312207</v>
+        <v>0.980332936119686</v>
       </c>
       <c r="P77" t="n">
         <v>0.9683949471962114</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.8893485653264389</v>
+        <v>0.885502409863439</v>
       </c>
       <c r="R77" t="n">
         <v>1.242473817405057</v>
@@ -7500,13 +7500,13 @@
         <v>0.8189997399018097</v>
       </c>
       <c r="O78" t="n">
-        <v>0.804588013685579</v>
+        <v>0.8084501702494555</v>
       </c>
       <c r="P78" t="n">
         <v>0.664865278428347</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.662859966700212</v>
+        <v>0.6623828205373704</v>
       </c>
       <c r="R78" t="n">
         <v>3.715861765493621</v>
@@ -7591,13 +7591,13 @@
         <v>0.8871627786014125</v>
       </c>
       <c r="O79" t="n">
-        <v>0.9221432656698454</v>
+        <v>0.9291331635779554</v>
       </c>
       <c r="P79" t="n">
         <v>0.918653701935489</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.9586818964757403</v>
+        <v>0.97209186221764</v>
       </c>
       <c r="R79" t="n">
         <v>-2.357515921651137</v>
@@ -7682,13 +7682,13 @@
         <v>0.9492397019991253</v>
       </c>
       <c r="O80" t="n">
-        <v>0.9402502757783897</v>
+        <v>0.9367588805273304</v>
       </c>
       <c r="P80" t="n">
         <v>0.9080328322905369</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9015980887993379</v>
+        <v>0.9064873100433711</v>
       </c>
       <c r="R80" t="n">
         <v>-0.6612397412624589</v>
@@ -7773,13 +7773,13 @@
         <v>0.7644668122055117</v>
       </c>
       <c r="O81" t="n">
-        <v>0.8981257801072224</v>
+        <v>0.8965292194046052</v>
       </c>
       <c r="P81" t="n">
         <v>0.4801638195630955</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.6750436308567354</v>
+        <v>0.66566430880327</v>
       </c>
       <c r="R81" t="n">
         <v>17.03093091271075</v>
@@ -7864,13 +7864,13 @@
         <v>0.8666386697230382</v>
       </c>
       <c r="O82" t="n">
-        <v>0.869410368239242</v>
+        <v>0.8580021566801009</v>
       </c>
       <c r="P82" t="n">
         <v>0.8643529163081951</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.9493417630816191</v>
+        <v>0.9449414651152082</v>
       </c>
       <c r="R82" t="n">
         <v>4.040924625639891</v>
@@ -7955,13 +7955,13 @@
         <v>0.9222809805022177</v>
       </c>
       <c r="O83" t="n">
-        <v>0.9230169916136531</v>
+        <v>0.9265793969273177</v>
       </c>
       <c r="P83" t="n">
         <v>0.6589279632167366</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.6961936673662437</v>
+        <v>0.6966262595037365</v>
       </c>
       <c r="R83" t="n">
         <v>3.607664401158456</v>
@@ -8046,13 +8046,13 @@
         <v>0.9498116266504352</v>
       </c>
       <c r="O84" t="n">
-        <v>0.960933685011536</v>
+        <v>0.9636120456832524</v>
       </c>
       <c r="P84" t="n">
         <v>0.9049703933468647</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.7460767094876462</v>
+        <v>0.7355695083195254</v>
       </c>
       <c r="R84" t="n">
         <v>0.7280829395190724</v>
@@ -8137,13 +8137,13 @@
         <v>0.9599285800621404</v>
       </c>
       <c r="O85" t="n">
-        <v>0.9720853567966534</v>
+        <v>0.9701110403934403</v>
       </c>
       <c r="P85" t="n">
         <v>0.822266568146786</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.7955210846159941</v>
+        <v>0.7910323883767763</v>
       </c>
       <c r="R85" t="n">
         <v>3.136191670406658</v>
@@ -8228,13 +8228,13 @@
         <v>0.8782070203855502</v>
       </c>
       <c r="O86" t="n">
-        <v>0.9107115863194318</v>
+        <v>0.899773458437987</v>
       </c>
       <c r="P86" t="n">
         <v>0.7512810186696256</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.8132098059093047</v>
+        <v>0.8117353379120892</v>
       </c>
       <c r="R86" t="n">
         <v>3.245556063192823</v>
@@ -8319,13 +8319,13 @@
         <v>0.7649096687182814</v>
       </c>
       <c r="O87" t="n">
-        <v>0.936883139231212</v>
+        <v>0.9167990364544711</v>
       </c>
       <c r="P87" t="n">
         <v>0.7341427109941541</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9022659119957648</v>
+        <v>0.8825244047854364</v>
       </c>
       <c r="R87" t="n">
         <v>1.779726648425777</v>
@@ -8410,13 +8410,13 @@
         <v>0.8456792844695598</v>
       </c>
       <c r="O88" t="n">
-        <v>0.8858439186529469</v>
+        <v>0.8823019265011078</v>
       </c>
       <c r="P88" t="n">
         <v>0.9510522837616211</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.9820656466956146</v>
+        <v>0.9844349107052071</v>
       </c>
       <c r="R88" t="n">
         <v>0.4329255601368591</v>
@@ -8501,13 +8501,13 @@
         <v>0.9074157726089733</v>
       </c>
       <c r="O89" t="n">
-        <v>0.9566613035823043</v>
+        <v>0.9580311469229821</v>
       </c>
       <c r="P89" t="n">
         <v>0.7473191323975155</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.8292234295161287</v>
+        <v>0.823994111691712</v>
       </c>
       <c r="R89" t="n">
         <v>9.845323307626238</v>
@@ -8592,13 +8592,13 @@
         <v>0.9640534188773633</v>
       </c>
       <c r="O90" t="n">
-        <v>0.975913112366247</v>
+        <v>0.9752017081213578</v>
       </c>
       <c r="P90" t="n">
         <v>0.5440253280148543</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.5156560993004654</v>
+        <v>0.5127725876558968</v>
       </c>
       <c r="R90" t="n">
         <v>14.54732306591537</v>
@@ -8683,13 +8683,13 @@
         <v>0.9309002681236365</v>
       </c>
       <c r="O91" t="n">
-        <v>0.9265091341415583</v>
+        <v>0.9367782791275058</v>
       </c>
       <c r="P91" t="n">
         <v>0.8551581230437142</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.939080963356312</v>
+        <v>0.9442475082074633</v>
       </c>
       <c r="R91" t="n">
         <v>1.145358191339976</v>
@@ -8774,13 +8774,13 @@
         <v>0.9338182611462942</v>
       </c>
       <c r="O92" t="n">
-        <v>0.9529889523315745</v>
+        <v>0.9595370042152918</v>
       </c>
       <c r="P92" t="n">
         <v>0.7813206850488175</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.7508793217006176</v>
+        <v>0.7486219534887986</v>
       </c>
       <c r="R92" t="n">
         <v>1.808846973688806</v>
@@ -8865,13 +8865,13 @@
         <v>0.9300680884117553</v>
       </c>
       <c r="O93" t="n">
-        <v>0.922348923426846</v>
+        <v>0.9151163940704784</v>
       </c>
       <c r="P93" t="n">
         <v>0.8935854149879883</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.7095817101604576</v>
+        <v>0.6957847408064634</v>
       </c>
       <c r="R93" t="n">
         <v>13.76239808991692</v>
@@ -8956,13 +8956,13 @@
         <v>0.9591795941151628</v>
       </c>
       <c r="O94" t="n">
-        <v>0.9692030010918883</v>
+        <v>0.9691209025025631</v>
       </c>
       <c r="P94" t="n">
         <v>0.4576718652063099</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.4711389954270896</v>
+        <v>0.4675584024669723</v>
       </c>
       <c r="R94" t="n">
         <v>31.59902578632765</v>
@@ -9047,13 +9047,13 @@
         <v>0.8871676685005473</v>
       </c>
       <c r="O95" t="n">
-        <v>0.8791687543492166</v>
+        <v>0.877284139880063</v>
       </c>
       <c r="P95" t="n">
         <v>0.8615573091733196</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.7648029350820403</v>
+        <v>0.7542001333170487</v>
       </c>
       <c r="R95" t="n">
         <v>1.177867813625812</v>
@@ -9138,13 +9138,13 @@
         <v>0.7612901986376266</v>
       </c>
       <c r="O96" t="n">
-        <v>0.7403192118213865</v>
+        <v>0.7460956573143133</v>
       </c>
       <c r="P96" t="n">
         <v>0.9110182257592286</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.9050004718726445</v>
+        <v>0.9167228067246915</v>
       </c>
       <c r="R96" t="n">
         <v>-1.362342062572789</v>
@@ -9229,13 +9229,13 @@
         <v>0.9282920417941357</v>
       </c>
       <c r="O97" t="n">
-        <v>0.9559257847486657</v>
+        <v>0.9559032996193716</v>
       </c>
       <c r="P97" t="n">
         <v>0.8594016593062725</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.7871854560053695</v>
+        <v>0.786064112358989</v>
       </c>
       <c r="R97" t="n">
         <v>4.46019112712948</v>
@@ -9320,13 +9320,13 @@
         <v>0.8996453009748022</v>
       </c>
       <c r="O98" t="n">
-        <v>0.9689069065859512</v>
+        <v>0.9715676722594047</v>
       </c>
       <c r="P98" t="n">
         <v>0.6459023844646231</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.6995724358613418</v>
+        <v>0.6869670475388048</v>
       </c>
       <c r="R98" t="n">
         <v>18.68211258309089</v>
@@ -9411,13 +9411,13 @@
         <v>0.9058623543096419</v>
       </c>
       <c r="O99" t="n">
-        <v>0.947195553437719</v>
+        <v>0.9441785518552663</v>
       </c>
       <c r="P99" t="n">
         <v>0.8473840760520954</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.6190449216717577</v>
+        <v>0.6083758802924011</v>
       </c>
       <c r="R99" t="n">
         <v>22.8655829224015</v>
@@ -9502,13 +9502,13 @@
         <v>0.9293062868562693</v>
       </c>
       <c r="O100" t="n">
-        <v>0.9584969216698123</v>
+        <v>0.9585585106523173</v>
       </c>
       <c r="P100" t="n">
         <v>0.8916938255182151</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.9296500354873902</v>
+        <v>0.9277877854150426</v>
       </c>
       <c r="R100" t="n">
         <v>2.432626933157633</v>
@@ -9593,13 +9593,13 @@
         <v>0.9239818202435618</v>
       </c>
       <c r="O101" t="n">
-        <v>0.912141377651869</v>
+        <v>0.9132418373642248</v>
       </c>
       <c r="P101" t="n">
         <v>0.5215875085852623</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.5105591663139327</v>
+        <v>0.5076411507337909</v>
       </c>
       <c r="R101" t="n">
         <v>28.28160030708699</v>
@@ -9684,13 +9684,13 @@
         <v>0.9470780582933653</v>
       </c>
       <c r="O102" t="n">
-        <v>0.9302077316110111</v>
+        <v>0.9299134235148441</v>
       </c>
       <c r="P102" t="n">
         <v>0.8140167374036025</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.7336729667981577</v>
+        <v>0.7329238611971077</v>
       </c>
       <c r="R102" t="n">
         <v>9.302569536348297</v>
@@ -9775,13 +9775,13 @@
         <v>0.9474301938836615</v>
       </c>
       <c r="O103" t="n">
-        <v>0.9607776179559141</v>
+        <v>0.9607672669319586</v>
       </c>
       <c r="P103" t="n">
         <v>0.7127931567166175</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.6561514067583674</v>
+        <v>0.6537992328993875</v>
       </c>
       <c r="R103" t="n">
         <v>6.993810882712427</v>
@@ -9866,13 +9866,13 @@
         <v>0.9982226333391805</v>
       </c>
       <c r="O104" t="n">
-        <v>0.9982933090642053</v>
+        <v>0.9982936450982198</v>
       </c>
       <c r="P104" t="n">
         <v>0.9764698273340006</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.977555538121432</v>
+        <v>0.9775417020016794</v>
       </c>
       <c r="R104" t="n">
         <v>1.197478685184682</v>
@@ -9957,13 +9957,13 @@
         <v>0.9951600253100358</v>
       </c>
       <c r="O105" t="n">
-        <v>0.9948166207658572</v>
+        <v>0.9948142636587471</v>
       </c>
       <c r="P105" t="n">
         <v>0.9831811815916462</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.9832220424239487</v>
+        <v>0.9832010788491115</v>
       </c>
       <c r="R105" t="n">
         <v>1.092873344384106</v>
@@ -10048,13 +10048,13 @@
         <v>0.9904101437830806</v>
       </c>
       <c r="O106" t="n">
-        <v>0.9883631389542754</v>
+        <v>0.9883531352673238</v>
       </c>
       <c r="P106" t="n">
         <v>0.9904478965219439</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.9931300444533219</v>
+        <v>0.9930934444985947</v>
       </c>
       <c r="R106" t="n">
         <v>0.2436625027678547</v>
@@ -10139,13 +10139,13 @@
         <v>0.9420908306441922</v>
       </c>
       <c r="O107" t="n">
-        <v>0.9470129275224937</v>
+        <v>0.9470602177097228</v>
       </c>
       <c r="P107" t="n">
         <v>0.9819348304737784</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.9812382151575246</v>
+        <v>0.9811897090239802</v>
       </c>
       <c r="R107" t="n">
         <v>1.558347150652827</v>
@@ -10230,13 +10230,13 @@
         <v>0.9892162023489297</v>
       </c>
       <c r="O108" t="n">
-        <v>0.9914994356276202</v>
+        <v>0.9914485725052155</v>
       </c>
       <c r="P108" t="n">
         <v>0.9892317502039953</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.9800361481877558</v>
+        <v>0.9798982908304719</v>
       </c>
       <c r="R108" t="n">
         <v>0.4960927669492675</v>
@@ -10321,13 +10321,13 @@
         <v>0.9963088097462847</v>
       </c>
       <c r="O109" t="n">
-        <v>0.99629012307829</v>
+        <v>0.9962489439232705</v>
       </c>
       <c r="P109" t="n">
         <v>0.9114715635752628</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.9049552834860752</v>
+        <v>0.9046781479075031</v>
       </c>
       <c r="R109" t="n">
         <v>9.980181674618628</v>
@@ -10412,13 +10412,13 @@
         <v>0.9680636738527292</v>
       </c>
       <c r="O110" t="n">
-        <v>0.9746013036068354</v>
+        <v>0.973226994892649</v>
       </c>
       <c r="P110" t="n">
         <v>0.6875658452951185</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.7006694797153243</v>
+        <v>0.6951756113592603</v>
       </c>
       <c r="R110" t="n">
         <v>20.99519948678543</v>
@@ -10503,13 +10503,13 @@
         <v>0.9384346422416922</v>
       </c>
       <c r="O111" t="n">
-        <v>0.9360211490591377</v>
+        <v>0.9361362546829023</v>
       </c>
       <c r="P111" t="n">
         <v>0.5506846500526584</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.5447395756348599</v>
+        <v>0.5444577826215516</v>
       </c>
       <c r="R111" t="n">
         <v>12.72678860894951</v>
@@ -10594,13 +10594,13 @@
         <v>0.7591825066523465</v>
       </c>
       <c r="O112" t="n">
-        <v>0.8980326989054888</v>
+        <v>0.8915433109914993</v>
       </c>
       <c r="P112" t="n">
         <v>0.8004099537943093</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.9393258346928226</v>
+        <v>0.9322944921273235</v>
       </c>
       <c r="R112" t="n">
         <v>0.04147614781625295</v>
@@ -10685,13 +10685,13 @@
         <v>0.9396276723664576</v>
       </c>
       <c r="O113" t="n">
-        <v>0.9652075554857067</v>
+        <v>0.9662086348327067</v>
       </c>
       <c r="P113" t="n">
         <v>0.923417045201437</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.8885601779274186</v>
+        <v>0.8886276215003057</v>
       </c>
       <c r="R113" t="n">
         <v>-0.4677286136268061</v>
@@ -10776,13 +10776,13 @@
         <v>0.8992945415794971</v>
       </c>
       <c r="O114" t="n">
-        <v>0.8999491904844276</v>
+        <v>0.8948838830670247</v>
       </c>
       <c r="P114" t="n">
         <v>0.7577563043655118</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.769626178997154</v>
+        <v>0.7694936180781276</v>
       </c>
       <c r="R114" t="n">
         <v>1.214287604857461</v>
@@ -10867,13 +10867,13 @@
         <v>0.978166977457074</v>
       </c>
       <c r="O115" t="n">
-        <v>0.9866280883807539</v>
+        <v>0.9887110291950253</v>
       </c>
       <c r="P115" t="n">
         <v>0.9805437258166971</v>
       </c>
       <c r="Q115" t="n">
-        <v>0.9801489765047542</v>
+        <v>0.9819876241925661</v>
       </c>
       <c r="R115" t="n">
         <v>-0.1096169878853978</v>
@@ -10958,13 +10958,13 @@
         <v>0.9880204707981585</v>
       </c>
       <c r="O116" t="n">
-        <v>0.9914188190924526</v>
+        <v>0.9913289303611895</v>
       </c>
       <c r="P116" t="n">
         <v>0.9913602682875844</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.9907614423500177</v>
+        <v>0.9907884797386597</v>
       </c>
       <c r="R116" t="n">
         <v>0.5749188139382382</v>
@@ -11049,13 +11049,13 @@
         <v>0.9864034584945446</v>
       </c>
       <c r="O117" t="n">
-        <v>0.9870566165438587</v>
+        <v>0.987361300594233</v>
       </c>
       <c r="P117" t="n">
         <v>0.9779659459498008</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.9818476886648675</v>
+        <v>0.9822040130008834</v>
       </c>
       <c r="R117" t="n">
         <v>-0.5370606658832376</v>
@@ -11140,13 +11140,13 @@
         <v>0.9794476579428474</v>
       </c>
       <c r="O118" t="n">
-        <v>0.9820462668309594</v>
+        <v>0.9895823945275486</v>
       </c>
       <c r="P118" t="n">
         <v>0.9641623915742111</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.9782483004075341</v>
+        <v>0.9856665716922525</v>
       </c>
       <c r="R118" t="n">
         <v>-3.626855520131396</v>
@@ -11231,13 +11231,13 @@
         <v>0.9831686753283008</v>
       </c>
       <c r="O119" t="n">
-        <v>0.9888880623919533</v>
+        <v>0.9893164097036903</v>
       </c>
       <c r="P119" t="n">
         <v>0.9626808423316935</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.9642943223867156</v>
+        <v>0.9645425927083429</v>
       </c>
       <c r="R119" t="n">
         <v>0.2386099610603775</v>
@@ -11322,13 +11322,13 @@
         <v>0.9222284188813621</v>
       </c>
       <c r="O120" t="n">
-        <v>0.942872009456861</v>
+        <v>0.9433847858561852</v>
       </c>
       <c r="P120" t="n">
         <v>0.8378095698334037</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.8611448834849338</v>
+        <v>0.8618962691893918</v>
       </c>
       <c r="R120" t="n">
         <v>1.415349233716116</v>
@@ -11413,13 +11413,13 @@
         <v>0.9226673453469799</v>
       </c>
       <c r="O121" t="n">
-        <v>0.9430512033296627</v>
+        <v>0.9395263163236349</v>
       </c>
       <c r="P121" t="n">
         <v>0.8318027219855723</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.8438402111619846</v>
+        <v>0.8362290943029386</v>
       </c>
       <c r="R121" t="n">
         <v>-0.2080023265869152</v>
@@ -11504,13 +11504,13 @@
         <v>0.9617146086840636</v>
       </c>
       <c r="O122" t="n">
-        <v>0.9442930210267295</v>
+        <v>0.9593252890926842</v>
       </c>
       <c r="P122" t="n">
         <v>0.9455208862675365</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.9477417689983973</v>
+        <v>0.9616281027964303</v>
       </c>
       <c r="R122" t="n">
         <v>-1.224529637038703</v>
@@ -11595,13 +11595,13 @@
         <v>0.9307528474348624</v>
       </c>
       <c r="O123" t="n">
-        <v>0.94268343126057</v>
+        <v>0.933817552141731</v>
       </c>
       <c r="P123" t="n">
         <v>0.646043008293982</v>
       </c>
       <c r="Q123" t="n">
-        <v>0.6277805150881279</v>
+        <v>0.6137239419878794</v>
       </c>
       <c r="R123" t="n">
         <v>35.68071805113103</v>
@@ -11686,13 +11686,13 @@
         <v>0.8871166200130614</v>
       </c>
       <c r="O124" t="n">
-        <v>0.912454605945104</v>
+        <v>0.9228536593474741</v>
       </c>
       <c r="P124" t="n">
         <v>0.7765846155466269</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.6706855173315315</v>
+        <v>0.6599686787855796</v>
       </c>
       <c r="R124" t="n">
         <v>7.807711274457489</v>
@@ -11777,13 +11777,13 @@
         <v>0.9496686631194888</v>
       </c>
       <c r="O125" t="n">
-        <v>0.9628177563247164</v>
+        <v>0.9618517984288576</v>
       </c>
       <c r="P125" t="n">
         <v>0.9567995493782506</v>
       </c>
       <c r="Q125" t="n">
-        <v>0.970432080527098</v>
+        <v>0.9727129014408951</v>
       </c>
       <c r="R125" t="n">
         <v>-0.1785070810978135</v>
@@ -11868,13 +11868,13 @@
         <v>0.8914574667257523</v>
       </c>
       <c r="O126" t="n">
-        <v>0.9069414764011795</v>
+        <v>0.8961807795808713</v>
       </c>
       <c r="P126" t="n">
         <v>0.6053408251649799</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.6129075333222098</v>
+        <v>0.5906057343076945</v>
       </c>
       <c r="R126" t="n">
         <v>11.98313305105714</v>
@@ -11959,13 +11959,13 @@
         <v>0.9498891688784538</v>
       </c>
       <c r="O127" t="n">
-        <v>0.9283842137379847</v>
+        <v>0.9248777936616797</v>
       </c>
       <c r="P127" t="n">
         <v>0.9214953156959456</v>
       </c>
       <c r="Q127" t="n">
-        <v>0.8455053260876462</v>
+        <v>0.8391944058063695</v>
       </c>
       <c r="R127" t="n">
         <v>0.9743820982059499</v>
@@ -12050,13 +12050,13 @@
         <v>0.8902670687288543</v>
       </c>
       <c r="O128" t="n">
-        <v>0.9293250095388597</v>
+        <v>0.9436109173660033</v>
       </c>
       <c r="P128" t="n">
         <v>0.9018427458553473</v>
       </c>
       <c r="Q128" t="n">
-        <v>0.8190954874447443</v>
+        <v>0.8334136120540182</v>
       </c>
       <c r="R128" t="n">
         <v>-1.103819071228612</v>
@@ -12141,13 +12141,13 @@
         <v>0.9209915505378991</v>
       </c>
       <c r="O129" t="n">
-        <v>0.961507346072651</v>
+        <v>0.9488926693878051</v>
       </c>
       <c r="P129" t="n">
         <v>0.916898270823452</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.8159698579517914</v>
+        <v>0.799562659104854</v>
       </c>
       <c r="R129" t="n">
         <v>5.078547098091626</v>
@@ -12232,13 +12232,13 @@
         <v>0.8198598691081508</v>
       </c>
       <c r="O130" t="n">
-        <v>0.8792057181561285</v>
+        <v>0.8662676572660597</v>
       </c>
       <c r="P130" t="n">
         <v>0.9348060212576879</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.9016795102115777</v>
+        <v>0.8975194774740543</v>
       </c>
       <c r="R130" t="n">
         <v>0.644274067629103</v>
@@ -12323,13 +12323,13 @@
         <v>0.8915580580551598</v>
       </c>
       <c r="O131" t="n">
-        <v>0.8940085624857316</v>
+        <v>0.8969832028968135</v>
       </c>
       <c r="P131" t="n">
         <v>0.6832362286231244</v>
       </c>
       <c r="Q131" t="n">
-        <v>0.6767488200663816</v>
+        <v>0.670999632215301</v>
       </c>
       <c r="R131" t="n">
         <v>23.20285075355689</v>
@@ -12414,13 +12414,13 @@
         <v>0.9606060147057622</v>
       </c>
       <c r="O132" t="n">
-        <v>0.9452086398049784</v>
+        <v>0.9385712269160629</v>
       </c>
       <c r="P132" t="n">
         <v>0.5296291252817421</v>
       </c>
       <c r="Q132" t="n">
-        <v>0.4942027505529892</v>
+        <v>0.4794716810707141</v>
       </c>
       <c r="R132" t="n">
         <v>23.0586054696122</v>
@@ -12505,13 +12505,13 @@
         <v>0.9682220641444185</v>
       </c>
       <c r="O133" t="n">
-        <v>0.9472277148076841</v>
+        <v>0.9613054723515849</v>
       </c>
       <c r="P133" t="n">
         <v>0.8957644788216702</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.8891830643148253</v>
+        <v>0.9001708912893635</v>
       </c>
       <c r="R133" t="n">
         <v>-0.5228737801711257</v>
@@ -12596,13 +12596,13 @@
         <v>0.9576374152704024</v>
       </c>
       <c r="O134" t="n">
-        <v>0.9549088030554224</v>
+        <v>0.9557356326244245</v>
       </c>
       <c r="P134" t="n">
         <v>0.6291891017625849</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.681419677490616</v>
+        <v>0.6805796100950823</v>
       </c>
       <c r="R134" t="n">
         <v>6.09647201553334</v>
@@ -12687,13 +12687,13 @@
         <v>0.9208483665563526</v>
       </c>
       <c r="O135" t="n">
-        <v>0.9393172999575172</v>
+        <v>0.9439898147956709</v>
       </c>
       <c r="P135" t="n">
         <v>0.9112207558086641</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.9022556790137422</v>
+        <v>0.9058722665286156</v>
       </c>
       <c r="R135" t="n">
         <v>-0.4165425314789139</v>
@@ -12778,13 +12778,13 @@
         <v>0.9720288126065325</v>
       </c>
       <c r="O136" t="n">
-        <v>0.9799075377812185</v>
+        <v>0.9798812251982769</v>
       </c>
       <c r="P136" t="n">
         <v>0.6382700162309799</v>
       </c>
       <c r="Q136" t="n">
-        <v>0.6868774911084219</v>
+        <v>0.6770545210433982</v>
       </c>
       <c r="R136" t="n">
         <v>23.00421932769493</v>
@@ -12869,13 +12869,13 @@
         <v>0.9681139100160303</v>
       </c>
       <c r="O137" t="n">
-        <v>0.9662404692278658</v>
+        <v>0.9705698082067098</v>
       </c>
       <c r="P137" t="n">
         <v>0.9269262931830056</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.9412145242170876</v>
+        <v>0.948094153253573</v>
       </c>
       <c r="R137" t="n">
         <v>0.2478778917058954</v>
@@ -12960,13 +12960,13 @@
         <v>0.9844274126410508</v>
       </c>
       <c r="O138" t="n">
-        <v>0.9809802278442254</v>
+        <v>0.9814364012966459</v>
       </c>
       <c r="P138" t="n">
         <v>0.4237422910337682</v>
       </c>
       <c r="Q138" t="n">
-        <v>0.3345254896314322</v>
+        <v>0.3261284892333517</v>
       </c>
       <c r="R138" t="n">
         <v>58.17265674559997</v>
@@ -13051,13 +13051,13 @@
         <v>0.9881674008309478</v>
       </c>
       <c r="O139" t="n">
-        <v>0.9856935628953374</v>
+        <v>0.9854820649293061</v>
       </c>
       <c r="P139" t="n">
         <v>0.6774120471869016</v>
       </c>
       <c r="Q139" t="n">
-        <v>0.6870348852696693</v>
+        <v>0.6838490914023931</v>
       </c>
       <c r="R139" t="n">
         <v>11.51200395612495</v>
@@ -13142,13 +13142,13 @@
         <v>0.8808236646950579</v>
       </c>
       <c r="O140" t="n">
-        <v>0.9252327779453707</v>
+        <v>0.926334301233642</v>
       </c>
       <c r="P140" t="n">
         <v>0.4720476949310664</v>
       </c>
       <c r="Q140" t="n">
-        <v>0.4928442127330489</v>
+        <v>0.484820296185451</v>
       </c>
       <c r="R140" t="n">
         <v>9.058462764842714</v>
@@ -13239,7 +13239,7 @@
         <v>0.9771598841771193</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.966668504417591</v>
+        <v>0.9666685044175909</v>
       </c>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr"/>
@@ -13320,13 +13320,13 @@
         <v>0.8976603124129124</v>
       </c>
       <c r="O142" t="n">
-        <v>0.9058813516735246</v>
+        <v>0.9060883283083991</v>
       </c>
       <c r="P142" t="n">
         <v>0.628474710843386</v>
       </c>
       <c r="Q142" t="n">
-        <v>0.6544545514974429</v>
+        <v>0.652155312741322</v>
       </c>
       <c r="R142" t="n">
         <v>19.87096425476178</v>
@@ -13411,13 +13411,13 @@
         <v>0.9643001620431965</v>
       </c>
       <c r="O143" t="n">
-        <v>0.9821929129457144</v>
+        <v>0.9828578935698389</v>
       </c>
       <c r="P143" t="n">
         <v>0.8243188167737956</v>
       </c>
       <c r="Q143" t="n">
-        <v>0.7204815130384645</v>
+        <v>0.7144007476165176</v>
       </c>
       <c r="R143" t="n">
         <v>5.227208621196781</v>
@@ -13502,13 +13502,13 @@
         <v>0.8624887507882475</v>
       </c>
       <c r="O144" t="n">
-        <v>0.88727920197009</v>
+        <v>0.8877342011445251</v>
       </c>
       <c r="P144" t="n">
         <v>0.8322231756648512</v>
       </c>
       <c r="Q144" t="n">
-        <v>0.8345202118701367</v>
+        <v>0.8359044723847456</v>
       </c>
       <c r="R144" t="n">
         <v>2.477569487998396</v>
@@ -13593,13 +13593,13 @@
         <v>0.8897426380015548</v>
       </c>
       <c r="O145" t="n">
-        <v>0.898500164593806</v>
+        <v>0.9019865339143576</v>
       </c>
       <c r="P145" t="n">
         <v>0.898153998545116</v>
       </c>
       <c r="Q145" t="n">
-        <v>0.8865250577638243</v>
+        <v>0.8896684165721219</v>
       </c>
       <c r="R145" t="n">
         <v>-0.1945256725278302</v>
@@ -13684,13 +13684,13 @@
         <v>0.8457985588734399</v>
       </c>
       <c r="O146" t="n">
-        <v>0.9330783948343561</v>
+        <v>0.9114634449684178</v>
       </c>
       <c r="P146" t="n">
         <v>0.8875395705508148</v>
       </c>
       <c r="Q146" t="n">
-        <v>0.8565311507370187</v>
+        <v>0.8363347776744712</v>
       </c>
       <c r="R146" t="n">
         <v>8.21800057730905</v>
@@ -13775,13 +13775,13 @@
         <v>0.9396581500159067</v>
       </c>
       <c r="O147" t="n">
-        <v>0.7946017684845508</v>
+        <v>0.8054616605726943</v>
       </c>
       <c r="P147" t="n">
         <v>0.9372025573840848</v>
       </c>
       <c r="Q147" t="n">
-        <v>0.7794993846516853</v>
+        <v>0.7837754558500371</v>
       </c>
       <c r="R147" t="n">
         <v>-1.178283734991258</v>
@@ -13866,13 +13866,13 @@
         <v>0.8062726345199401</v>
       </c>
       <c r="O148" t="n">
-        <v>0.931095573596477</v>
+        <v>0.9097264260400019</v>
       </c>
       <c r="P148" t="n">
         <v>0.9170056577822541</v>
       </c>
       <c r="Q148" t="n">
-        <v>0.8502937991478721</v>
+        <v>0.82891496565842</v>
       </c>
       <c r="R148" t="n">
         <v>3.033899820285974</v>

--- a/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
+++ b/tests/fixtures/TABLE_EmpiricalECCMetricsAndW1.xlsx
@@ -587,7 +587,7 @@
         <v>0.1736645453641016</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1628477574900307</v>
+        <v>0.1620439261246997</v>
       </c>
       <c r="G2" t="n">
         <v>0.1268074663708552</v>
@@ -641,7 +641,7 @@
         <v>1.001005137361129</v>
       </c>
       <c r="X2" t="n">
-        <v>1.040928943346033</v>
+        <v>1.041371815820066</v>
       </c>
       <c r="Y2" t="n">
         <v>1.028084151618127</v>
@@ -781,10 +781,10 @@
         <v>0.1732930838174779</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4805284989673036</v>
+        <v>0.4799394179677107</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02921413333683163</v>
+        <v>0.02906837221270595</v>
       </c>
       <c r="H4" t="n">
         <v>1.505181927625858</v>
@@ -832,10 +832,10 @@
         <v>1.016773947613548</v>
       </c>
       <c r="W4" t="n">
-        <v>1.117779760793197</v>
+        <v>1.118913806324753</v>
       </c>
       <c r="X4" t="n">
-        <v>1.074827170779614</v>
+        <v>1.075796374591005</v>
       </c>
       <c r="Y4" t="n">
         <v>1.008822288055942</v>
@@ -878,10 +878,10 @@
         <v>0.3850646813135739</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9428373745367373</v>
+        <v>0.9417983041577641</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2402051316555804</v>
+        <v>0.2395959963763158</v>
       </c>
       <c r="H5" t="n">
         <v>3.775077328088694</v>
@@ -929,10 +929,10 @@
         <v>1.005306417188222</v>
       </c>
       <c r="W5" t="n">
-        <v>1.135991607168941</v>
+        <v>1.136143049127039</v>
       </c>
       <c r="X5" t="n">
-        <v>1.106463291044453</v>
+        <v>1.106519789666069</v>
       </c>
       <c r="Y5" t="n">
         <v>1.005654889400433</v>
@@ -975,7 +975,7 @@
         <v>0.104578143633098</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2564365354832973</v>
+        <v>0.25567833677568</v>
       </c>
       <c r="G6" t="n">
         <v>0.1098200669127059</v>
@@ -1029,7 +1029,7 @@
         <v>1.017960331410465</v>
       </c>
       <c r="X6" t="n">
-        <v>1.034609716389288</v>
+        <v>1.035644061647895</v>
       </c>
       <c r="Y6" t="n">
         <v>1.017329270759607</v>
@@ -1072,7 +1072,7 @@
         <v>0.131816429117338</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2652594765113568</v>
+        <v>0.2650086038567128</v>
       </c>
       <c r="G7" t="n">
         <v>0.142065536836323</v>
@@ -1126,7 +1126,7 @@
         <v>1.014211249708263</v>
       </c>
       <c r="X7" t="n">
-        <v>1.159210556004727</v>
+        <v>1.161841353784153</v>
       </c>
       <c r="Y7" t="n">
         <v>1.070504973760363</v>
@@ -1169,7 +1169,7 @@
         <v>0.1254732822967411</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2942965322624375</v>
+        <v>0.2927865014674585</v>
       </c>
       <c r="G8" t="n">
         <v>0.1778259060959862</v>
@@ -1223,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.003307479763752</v>
+        <v>1.004320645346087</v>
       </c>
       <c r="Y8" t="n">
         <v>1</v>
@@ -1359,7 +1359,7 @@
         <v>0.3423568594501953</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3417079330330299</v>
+        <v>0.3405683692657197</v>
       </c>
       <c r="G10" t="n">
         <v>0.4422184290428836</v>
@@ -1413,7 +1413,7 @@
         <v>1.060612924990478</v>
       </c>
       <c r="X10" t="n">
-        <v>1.094247496742057</v>
+        <v>1.097297761196359</v>
       </c>
       <c r="Y10" t="n">
         <v>1.020400589490248</v>
@@ -1456,10 +1456,10 @@
         <v>0.03468221045901853</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06182877457343704</v>
+        <v>0.06182849007042836</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003563708859737274</v>
+        <v>0.003525298009250623</v>
       </c>
       <c r="H11" t="n">
         <v>0.2660496884648744</v>
@@ -1507,10 +1507,10 @@
         <v>1.013475204322204</v>
       </c>
       <c r="W11" t="n">
-        <v>1.028614414198721</v>
+        <v>1.028935613387999</v>
       </c>
       <c r="X11" t="n">
-        <v>1.025951272610127</v>
+        <v>1.026258495497775</v>
       </c>
       <c r="Y11" t="n">
         <v>1.009154565156715</v>
@@ -1553,10 +1553,10 @@
         <v>0.4515433974246209</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2317307587436733</v>
+        <v>0.2308701507374475</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2019610946521872</v>
+        <v>0.2004841494794881</v>
       </c>
       <c r="H12" t="n">
         <v>1.483104423321873</v>
@@ -1604,10 +1604,10 @@
         <v>1.080549448342853</v>
       </c>
       <c r="W12" t="n">
-        <v>1.201758612243786</v>
+        <v>1.204092102131916</v>
       </c>
       <c r="X12" t="n">
-        <v>1.137314367612276</v>
+        <v>1.13972238004452</v>
       </c>
       <c r="Y12" t="n">
         <v>1.037033785089428</v>
@@ -1650,10 +1650,10 @@
         <v>0.2112702306778599</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2049545534631889</v>
+        <v>0.2050454559727069</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1571160273736988</v>
+        <v>0.1557968324782339</v>
       </c>
       <c r="H13" t="n">
         <v>0.9998925825438851</v>
@@ -1701,10 +1701,10 @@
         <v>1.029396277306996</v>
       </c>
       <c r="W13" t="n">
-        <v>1.114368293052237</v>
+        <v>1.115693451104787</v>
       </c>
       <c r="X13" t="n">
-        <v>1.049153364533274</v>
+        <v>1.049770517554048</v>
       </c>
       <c r="Y13" t="n">
         <v>1.022207261993878</v>
@@ -1747,7 +1747,7 @@
         <v>0.2521259092245494</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2845356411346496</v>
+        <v>0.284309963601513</v>
       </c>
       <c r="G14" t="n">
         <v>0.1373633556609321</v>
@@ -1801,7 +1801,7 @@
         <v>1.04743179209658</v>
       </c>
       <c r="X14" t="n">
-        <v>1.095848139130641</v>
+        <v>1.096486527360492</v>
       </c>
       <c r="Y14" t="n">
         <v>1.060576411318667</v>
@@ -1844,10 +1844,10 @@
         <v>0.1143368333548252</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1480436482507306</v>
+        <v>0.1482039666649916</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07090361610597569</v>
+        <v>0.07017856502932182</v>
       </c>
       <c r="H15" t="n">
         <v>0.924063028695556</v>
@@ -1895,10 +1895,10 @@
         <v>1.048655536058486</v>
       </c>
       <c r="W15" t="n">
-        <v>1.059818382507851</v>
+        <v>1.06064613716609</v>
       </c>
       <c r="X15" t="n">
-        <v>1.098512757175423</v>
+        <v>1.0998850446617</v>
       </c>
       <c r="Y15" t="n">
         <v>1.053545989607294</v>
@@ -2034,10 +2034,10 @@
         <v>0.2913154915272795</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3805342360588891</v>
+        <v>0.3808943845343404</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1855204257534032</v>
+        <v>0.1836804869906245</v>
       </c>
       <c r="H17" t="n">
         <v>1.076291317357209</v>
@@ -2085,10 +2085,10 @@
         <v>1.001928862956075</v>
       </c>
       <c r="W17" t="n">
-        <v>1.067589308846356</v>
+        <v>1.069352440673402</v>
       </c>
       <c r="X17" t="n">
-        <v>1.090605257640002</v>
+        <v>1.091878950776468</v>
       </c>
       <c r="Y17" t="n">
         <v>1.012983759217844</v>
@@ -2321,10 +2321,10 @@
         <v>0.3988865576680816</v>
       </c>
       <c r="F20" t="n">
-        <v>0.283774293050236</v>
+        <v>0.2842926366834556</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2572210084676299</v>
+        <v>0.2557238135259512</v>
       </c>
       <c r="H20" t="n">
         <v>1.543283968480679</v>
@@ -2372,10 +2372,10 @@
         <v>1.054261395994039</v>
       </c>
       <c r="W20" t="n">
-        <v>1.183176781354193</v>
+        <v>1.185236522835171</v>
       </c>
       <c r="X20" t="n">
-        <v>1.093883842034411</v>
+        <v>1.09488092595851</v>
       </c>
       <c r="Y20" t="n">
         <v>1.028183096469301</v>
@@ -2418,7 +2418,7 @@
         <v>0.2173608497979083</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6025057928427886</v>
+        <v>0.6010621021425132</v>
       </c>
       <c r="G21" t="n">
         <v>0.2792690381821613</v>
@@ -2472,7 +2472,7 @@
         <v>1.013474520786705</v>
       </c>
       <c r="X21" t="n">
-        <v>1.102597468904421</v>
+        <v>1.10342149137605</v>
       </c>
       <c r="Y21" t="n">
         <v>1.040669813376224</v>
@@ -2612,10 +2612,10 @@
         <v>0.07836839058875449</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1093412211138805</v>
+        <v>0.1093387324261473</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0575972334903774</v>
+        <v>0.05729631747916546</v>
       </c>
       <c r="H23" t="n">
         <v>0.5194860764874193</v>
@@ -2663,10 +2663,10 @@
         <v>1.003368971976756</v>
       </c>
       <c r="W23" t="n">
-        <v>1.058232584769141</v>
+        <v>1.058955408914242</v>
       </c>
       <c r="X23" t="n">
-        <v>1.064295313634011</v>
+        <v>1.064910610970679</v>
       </c>
       <c r="Y23" t="n">
         <v>1.020510203801384</v>
@@ -2806,10 +2806,10 @@
         <v>0.06640593569090283</v>
       </c>
       <c r="F25" t="n">
-        <v>0.37455786394792</v>
+        <v>0.3735933601682493</v>
       </c>
       <c r="G25" t="n">
-        <v>0.05327592986765817</v>
+        <v>0.05275164488520545</v>
       </c>
       <c r="H25" t="n">
         <v>0.9332541441212289</v>
@@ -2857,10 +2857,10 @@
         <v>1.001474574675983</v>
       </c>
       <c r="W25" t="n">
-        <v>1.024118723169152</v>
+        <v>1.024365295147244</v>
       </c>
       <c r="X25" t="n">
-        <v>1.00044850973277</v>
+        <v>1.000594388582842</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
@@ -2903,10 +2903,10 @@
         <v>0.2682273604207194</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09128580878310588</v>
+        <v>0.09111758197614339</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03126120859723384</v>
+        <v>0.0309646710882149</v>
       </c>
       <c r="H26" t="n">
         <v>1.593272523634096</v>
@@ -2954,10 +2954,10 @@
         <v>1.022644424446105</v>
       </c>
       <c r="W26" t="n">
-        <v>1.111093477678355</v>
+        <v>1.111770225505706</v>
       </c>
       <c r="X26" t="n">
-        <v>1.146520993992054</v>
+        <v>1.147915825999789</v>
       </c>
       <c r="Y26" t="n">
         <v>1.020311499581628</v>
@@ -3000,10 +3000,10 @@
         <v>0.03767817490820777</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05926165889107683</v>
+        <v>0.05921077603890251</v>
       </c>
       <c r="G27" t="n">
-        <v>0.02749850528829298</v>
+        <v>0.02734080224409191</v>
       </c>
       <c r="H27" t="n">
         <v>0.2653037874719312</v>
@@ -3051,10 +3051,10 @@
         <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.066517157184333</v>
+        <v>1.070447850305662</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.000064240997709</v>
       </c>
       <c r="Y27" t="n">
         <v>1</v>
@@ -3291,10 +3291,10 @@
         <v>0.02811701154270001</v>
       </c>
       <c r="F30" t="n">
-        <v>0.08160635367892653</v>
+        <v>0.08144146287417929</v>
       </c>
       <c r="G30" t="n">
-        <v>0.01787679156823697</v>
+        <v>0.01769242928563266</v>
       </c>
       <c r="H30" t="n">
         <v>0.3169201709223302</v>
@@ -3342,10 +3342,10 @@
         <v>1.005232062798919</v>
       </c>
       <c r="W30" t="n">
-        <v>1.013401556433007</v>
+        <v>1.013570778072815</v>
       </c>
       <c r="X30" t="n">
-        <v>1.016649198754034</v>
+        <v>1.017572587536853</v>
       </c>
       <c r="Y30" t="n">
         <v>1.004047425114218</v>
@@ -3485,7 +3485,7 @@
         <v>0.05098819147404932</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05674583500925911</v>
+        <v>0.05658929175746988</v>
       </c>
       <c r="G32" t="n">
         <v>0.04268219969050385</v>
@@ -3539,7 +3539,7 @@
         <v>1.00565550153298</v>
       </c>
       <c r="X32" t="n">
-        <v>1.089840870387961</v>
+        <v>1.094016768518122</v>
       </c>
       <c r="Y32" t="n">
         <v>1.02100698543268</v>
@@ -3582,10 +3582,10 @@
         <v>0.1496733743708537</v>
       </c>
       <c r="F33" t="n">
-        <v>0.334160644008343</v>
+        <v>0.3332805744919317</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1325291054364143</v>
+        <v>0.1319203136430061</v>
       </c>
       <c r="H33" t="n">
         <v>1.006607348851978</v>
@@ -3633,10 +3633,10 @@
         <v>1.008108801711226</v>
       </c>
       <c r="W33" t="n">
-        <v>1.025978438358032</v>
+        <v>1.026398670056827</v>
       </c>
       <c r="X33" t="n">
-        <v>1.123139887123249</v>
+        <v>1.127000157449258</v>
       </c>
       <c r="Y33" t="n">
         <v>1.035324952445202</v>
@@ -3682,7 +3682,7 @@
         <v>0.2412039014228105</v>
       </c>
       <c r="G34" t="n">
-        <v>0.01233665996139364</v>
+        <v>0.01219926423769206</v>
       </c>
       <c r="H34" t="n">
         <v>0.4288254093334904</v>
@@ -3730,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.000025206500891</v>
+        <v>1.00002686342504</v>
       </c>
       <c r="X34" t="n">
         <v>1.011916826192858</v>
@@ -3779,7 +3779,7 @@
         <v>0.1790951475554913</v>
       </c>
       <c r="G35" t="n">
-        <v>0.03077472784481408</v>
+        <v>0.03050655937787709</v>
       </c>
       <c r="H35" t="n">
         <v>0.3322197833838556</v>
@@ -3827,7 +3827,7 @@
         <v>1.000279273016993</v>
       </c>
       <c r="W35" t="n">
-        <v>1.006796332644302</v>
+        <v>1.007290045400148</v>
       </c>
       <c r="X35" t="n">
         <v>1.012689686580874</v>
@@ -3873,10 +3873,10 @@
         <v>0.04185251850869178</v>
       </c>
       <c r="F36" t="n">
-        <v>0.04303658336275137</v>
+        <v>0.04308263487810936</v>
       </c>
       <c r="G36" t="n">
-        <v>0.01373339561274151</v>
+        <v>0.01361711728044478</v>
       </c>
       <c r="H36" t="n">
         <v>0.4286862127162542</v>
@@ -3924,10 +3924,10 @@
         <v>1.007528792011665</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02119732637524</v>
+        <v>1.021835127900505</v>
       </c>
       <c r="X36" t="n">
-        <v>1.013873069787575</v>
+        <v>1.014142832617421</v>
       </c>
       <c r="Y36" t="n">
         <v>1.007902376243321</v>
@@ -3970,7 +3970,7 @@
         <v>0.247757179849167</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3670955732479233</v>
+        <v>0.3670942139231067</v>
       </c>
       <c r="G37" t="n">
         <v>0.1956516755906542</v>
@@ -4024,7 +4024,7 @@
         <v>1.164500580507336</v>
       </c>
       <c r="X37" t="n">
-        <v>1.08355843659071</v>
+        <v>1.087129837971888</v>
       </c>
       <c r="Y37" t="n">
         <v>1</v>
@@ -4067,10 +4067,10 @@
         <v>0.03364655249077265</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1475828201914255</v>
+        <v>0.1475820012338706</v>
       </c>
       <c r="G38" t="n">
-        <v>0.009143991958985079</v>
+        <v>0.009041279642967722</v>
       </c>
       <c r="H38" t="n">
         <v>0.3463502036486705</v>
@@ -4118,10 +4118,10 @@
         <v>1.006818309509078</v>
       </c>
       <c r="W38" t="n">
-        <v>1.0150309908208</v>
+        <v>1.015500751504483</v>
       </c>
       <c r="X38" t="n">
-        <v>1.026112799374688</v>
+        <v>1.026685062060117</v>
       </c>
       <c r="Y38" t="n">
         <v>1.006566987101052</v>
@@ -4261,10 +4261,10 @@
         <v>0.1339596544915477</v>
       </c>
       <c r="F40" t="n">
-        <v>0.08901215144199583</v>
+        <v>0.08878006308804652</v>
       </c>
       <c r="G40" t="n">
-        <v>0.04617081584266562</v>
+        <v>0.04576369847244835</v>
       </c>
       <c r="H40" t="n">
         <v>0.5711355018057733</v>
@@ -4312,10 +4312,10 @@
         <v>1.017003241003839</v>
       </c>
       <c r="W40" t="n">
-        <v>1.034011606644861</v>
+        <v>1.036009599883016</v>
       </c>
       <c r="X40" t="n">
-        <v>1.09145096882896</v>
+        <v>1.095038354494908</v>
       </c>
       <c r="Y40" t="n">
         <v>1.016613509646723</v>
@@ -4548,10 +4548,10 @@
         <v>0.5926358630650038</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3678254827410988</v>
+        <v>0.3667519150454185</v>
       </c>
       <c r="G43" t="n">
-        <v>0.04899566156416662</v>
+        <v>0.04850436972301903</v>
       </c>
       <c r="H43" t="n">
         <v>5.04607478038343</v>
@@ -4599,10 +4599,10 @@
         <v>1.009466591963998</v>
       </c>
       <c r="W43" t="n">
-        <v>1.084583491593362</v>
+        <v>1.084964957231459</v>
       </c>
       <c r="X43" t="n">
-        <v>1.047501299852954</v>
+        <v>1.048384377869743</v>
       </c>
       <c r="Y43" t="n">
         <v>1.009314532090233</v>
@@ -4742,7 +4742,7 @@
         <v>0.03061669457563132</v>
       </c>
       <c r="F45" t="n">
-        <v>0.07865781581451006</v>
+        <v>0.07861617393364016</v>
       </c>
       <c r="G45" t="n">
         <v>0.02243520224125522</v>
@@ -4796,7 +4796,7 @@
         <v>1.112796744487812</v>
       </c>
       <c r="X45" t="n">
-        <v>1.002564935690344</v>
+        <v>1.003500405524472</v>
       </c>
       <c r="Y45" t="n">
         <v>1</v>
@@ -5033,7 +5033,7 @@
         <v>0.342220390318148</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6567562352156029</v>
+        <v>0.6567142207335912</v>
       </c>
       <c r="G48" t="n">
         <v>0.2856419014777551</v>
@@ -5087,7 +5087,7 @@
         <v>1.193671307438383</v>
       </c>
       <c r="X48" t="n">
-        <v>1.140283965988981</v>
+        <v>1.143732994453072</v>
       </c>
       <c r="Y48" t="n">
         <v>1.07071058825641</v>
@@ -5130,7 +5130,7 @@
         <v>0.2644564308569591</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2483621536659071</v>
+        <v>0.2485896959656235</v>
       </c>
       <c r="G49" t="n">
         <v>0.2463807721694883</v>
@@ -5184,7 +5184,7 @@
         <v>1.047403668878102</v>
       </c>
       <c r="X49" t="n">
-        <v>1.056382196913695</v>
+        <v>1.056585979120672</v>
       </c>
       <c r="Y49" t="n">
         <v>1.047719077478554</v>
@@ -5227,10 +5227,10 @@
         <v>0.1538879294220451</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1219168194965631</v>
+        <v>0.1212596427921064</v>
       </c>
       <c r="G50" t="n">
-        <v>0.09610432494851866</v>
+        <v>0.09531447707326526</v>
       </c>
       <c r="H50" t="n">
         <v>0.7900833484591432</v>
@@ -5278,10 +5278,10 @@
         <v>1.044027435087589</v>
       </c>
       <c r="W50" t="n">
-        <v>1.060968474854467</v>
+        <v>1.061375837601876</v>
       </c>
       <c r="X50" t="n">
-        <v>1.064229761868608</v>
+        <v>1.065551599416964</v>
       </c>
       <c r="Y50" t="n">
         <v>1.020328607656752</v>
@@ -5324,10 +5324,10 @@
         <v>0.8828792665879281</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2484642204213245</v>
+        <v>0.248138656409906</v>
       </c>
       <c r="G51" t="n">
-        <v>0.06328908574381328</v>
+        <v>0.06256292535749382</v>
       </c>
       <c r="H51" t="n">
         <v>3.010639368634546</v>
@@ -5375,10 +5375,10 @@
         <v>1.03071495916729</v>
       </c>
       <c r="W51" t="n">
-        <v>1.108714477349759</v>
+        <v>1.109515923361111</v>
       </c>
       <c r="X51" t="n">
-        <v>1.144649805670209</v>
+        <v>1.146002786956885</v>
       </c>
       <c r="Y51" t="n">
         <v>1.023438953331128</v>
@@ -5421,10 +5421,10 @@
         <v>0.4246112095708683</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5624186585590234</v>
+        <v>0.5634768498426591</v>
       </c>
       <c r="G52" t="n">
-        <v>0.49694663973898</v>
+        <v>0.4945248879533903</v>
       </c>
       <c r="H52" t="n">
         <v>1.465451905437245</v>
@@ -5472,10 +5472,10 @@
         <v>1.009637718721611</v>
       </c>
       <c r="W52" t="n">
-        <v>1.023846426141057</v>
+        <v>1.023987241206366</v>
       </c>
       <c r="X52" t="n">
-        <v>1.055061851730484</v>
+        <v>1.055754558196295</v>
       </c>
       <c r="Y52" t="n">
         <v>1.009498219147334</v>
@@ -5615,10 +5615,10 @@
         <v>0.04414896056659479</v>
       </c>
       <c r="F54" t="n">
-        <v>0.04690984527889156</v>
+        <v>0.04673759758422322</v>
       </c>
       <c r="G54" t="n">
-        <v>0.02655414351762753</v>
+        <v>0.02634523085010092</v>
       </c>
       <c r="H54" t="n">
         <v>0.2573094721427867</v>
@@ -5666,10 +5666,10 @@
         <v>1.000928172842933</v>
       </c>
       <c r="W54" t="n">
-        <v>1.100211466831979</v>
+        <v>1.101927690068251</v>
       </c>
       <c r="X54" t="n">
-        <v>1.097390961791228</v>
+        <v>1.100179195723765</v>
       </c>
       <c r="Y54" t="n">
         <v>1.005950304274737</v>
@@ -5906,10 +5906,10 @@
         <v>0.05867007505661821</v>
       </c>
       <c r="F57" t="n">
-        <v>0.5388834671071326</v>
+        <v>0.5381596976925622</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0359794328932878</v>
+        <v>0.03567239476907048</v>
       </c>
       <c r="H57" t="n">
         <v>1.078136046411011</v>
@@ -5957,10 +5957,10 @@
         <v>1.010334977323024</v>
       </c>
       <c r="W57" t="n">
-        <v>1.032153325114691</v>
+        <v>1.03240040044616</v>
       </c>
       <c r="X57" t="n">
-        <v>1.119521690979794</v>
+        <v>1.121337249992476</v>
       </c>
       <c r="Y57" t="n">
         <v>1.025420395412684</v>
@@ -6096,7 +6096,7 @@
         <v>0.7025427712650719</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4331248024374695</v>
+        <v>0.4320590046306207</v>
       </c>
       <c r="G59" t="n">
         <v>1.154869656388133</v>
@@ -6150,7 +6150,7 @@
         <v>1.083716170495417</v>
       </c>
       <c r="X59" t="n">
-        <v>1.241365995508224</v>
+        <v>1.242313264637713</v>
       </c>
       <c r="Y59" t="n">
         <v>1.053539405537984</v>
@@ -6290,10 +6290,10 @@
         <v>0.07537536666354265</v>
       </c>
       <c r="F61" t="n">
-        <v>0.09317732433523516</v>
+        <v>0.09352318269000086</v>
       </c>
       <c r="G61" t="n">
-        <v>0.08844038842683936</v>
+        <v>0.087744638585535</v>
       </c>
       <c r="H61" t="n">
         <v>0.959742001257093</v>
@@ -6341,10 +6341,10 @@
         <v>1.003257632254175</v>
       </c>
       <c r="W61" t="n">
-        <v>1.015930975536776</v>
+        <v>1.016565413489855</v>
       </c>
       <c r="X61" t="n">
-        <v>1.041323597038271</v>
+        <v>1.042621615051056</v>
       </c>
       <c r="Y61" t="n">
         <v>1.007126677254597</v>
@@ -6387,7 +6387,7 @@
         <v>0.08081294512231013</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1309211810807661</v>
+        <v>0.1305320374380107</v>
       </c>
       <c r="G62" t="n">
         <v>0.08041570887353232</v>
@@ -6441,7 +6441,7 @@
         <v>1.038206103802567</v>
       </c>
       <c r="X62" t="n">
-        <v>1.09524882328101</v>
+        <v>1.095233475569031</v>
       </c>
       <c r="Y62" t="n">
         <v>1.063776019084027</v>
@@ -6484,7 +6484,7 @@
         <v>0.2431786980187003</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1641248839412641</v>
+        <v>0.1637939181110217</v>
       </c>
       <c r="G63" t="n">
         <v>0.2633866997525802</v>
@@ -6538,7 +6538,7 @@
         <v>1.096863075106416</v>
       </c>
       <c r="X63" t="n">
-        <v>1.215258947895359</v>
+        <v>1.219112277842685</v>
       </c>
       <c r="Y63" t="n">
         <v>1.039811505058307</v>
@@ -6678,7 +6678,7 @@
         <v>0.1600372760088634</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2507240664172934</v>
+        <v>0.251185969618154</v>
       </c>
       <c r="G65" t="n">
         <v>0.1566795045044254</v>
@@ -6732,7 +6732,7 @@
         <v>1.008501710306724</v>
       </c>
       <c r="X65" t="n">
-        <v>1.070308258708538</v>
+        <v>1.071213945610821</v>
       </c>
       <c r="Y65" t="n">
         <v>1.031453791401421</v>
@@ -6775,10 +6775,10 @@
         <v>0.07924361114132135</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1471233946638645</v>
+        <v>0.1471375737648678</v>
       </c>
       <c r="G66" t="n">
-        <v>0.03069147890558154</v>
+        <v>0.03034451881458432</v>
       </c>
       <c r="H66" t="n">
         <v>0.7425514290863957</v>
@@ -6826,10 +6826,10 @@
         <v>1.010849983984087</v>
       </c>
       <c r="W66" t="n">
-        <v>1.021642759681015</v>
+        <v>1.021912895320703</v>
       </c>
       <c r="X66" t="n">
-        <v>1.044157757569472</v>
+        <v>1.044708832486122</v>
       </c>
       <c r="Y66" t="n">
         <v>1.015013990405764</v>
@@ -7163,10 +7163,10 @@
         <v>0.2743547076771681</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1919897653248321</v>
+        <v>0.191592854662689</v>
       </c>
       <c r="G70" t="n">
-        <v>0.07884369927181022</v>
+        <v>0.07828657167022265</v>
       </c>
       <c r="H70" t="n">
         <v>1.319995968247772</v>
@@ -7214,10 +7214,10 @@
         <v>1.052465911252749</v>
       </c>
       <c r="W70" t="n">
-        <v>1.08102935277936</v>
+        <v>1.08156199152313</v>
       </c>
       <c r="X70" t="n">
-        <v>1.037034672543807</v>
+        <v>1.037384215505138</v>
       </c>
       <c r="Y70" t="n">
         <v>1.023207025568986</v>
@@ -7260,10 +7260,10 @@
         <v>0.03405476482558858</v>
       </c>
       <c r="F71" t="n">
-        <v>0.09212871623001531</v>
+        <v>0.09201071193215579</v>
       </c>
       <c r="G71" t="n">
-        <v>0.01702223999727827</v>
+        <v>0.01685600697171072</v>
       </c>
       <c r="H71" t="n">
         <v>0.6121589369570332</v>
@@ -7311,10 +7311,10 @@
         <v>1.01250487802955</v>
       </c>
       <c r="W71" t="n">
-        <v>1.026156448743483</v>
+        <v>1.026353246044601</v>
       </c>
       <c r="X71" t="n">
-        <v>1.029419651223312</v>
+        <v>1.029702678114278</v>
       </c>
       <c r="Y71" t="n">
         <v>1.012630819694899</v>
@@ -7648,10 +7648,10 @@
         <v>0.1401518571270622</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2692334568515328</v>
+        <v>0.2689882990901395</v>
       </c>
       <c r="G75" t="n">
-        <v>0.03851762688462174</v>
+        <v>0.03826399024904</v>
       </c>
       <c r="H75" t="n">
         <v>0.8840788578857285</v>
@@ -7699,10 +7699,10 @@
         <v>1.01915392111379</v>
       </c>
       <c r="W75" t="n">
-        <v>1.183325607898676</v>
+        <v>1.184003819840244</v>
       </c>
       <c r="X75" t="n">
-        <v>1.299183612446371</v>
+        <v>1.30103486506603</v>
       </c>
       <c r="Y75" t="n">
         <v>1.035419072932095</v>
@@ -7745,10 +7745,10 @@
         <v>0.0318953997115442</v>
       </c>
       <c r="F76" t="n">
-        <v>0.03697226791042905</v>
+        <v>0.03696821695486537</v>
       </c>
       <c r="G76" t="n">
-        <v>0.01898516793053378</v>
+        <v>0.01882836103406731</v>
       </c>
       <c r="H76" t="n">
         <v>0.3458513982229685</v>
@@ -7796,10 +7796,10 @@
         <v>1.033475854842358</v>
       </c>
       <c r="W76" t="n">
-        <v>1.083085134862351</v>
+        <v>1.084752210383922</v>
       </c>
       <c r="X76" t="n">
-        <v>1.01472471618983</v>
+        <v>1.015188617681806</v>
       </c>
       <c r="Y76" t="n">
         <v>1.00935474362358</v>
@@ -7842,10 +7842,10 @@
         <v>0.02414369654251767</v>
       </c>
       <c r="F77" t="n">
-        <v>0.01759058728454068</v>
+        <v>0.01755823200808494</v>
       </c>
       <c r="G77" t="n">
-        <v>0.01379667140387761</v>
+        <v>0.01366986047196993</v>
       </c>
       <c r="H77" t="n">
         <v>0.35000644484989</v>
@@ -7893,10 +7893,10 @@
         <v>1.010086023593949</v>
       </c>
       <c r="W77" t="n">
-        <v>1.013758140317791</v>
+        <v>1.013841681361958</v>
       </c>
       <c r="X77" t="n">
-        <v>1.008408193453572</v>
+        <v>1.008466247582792</v>
       </c>
       <c r="Y77" t="n">
         <v>1.006702423634908</v>
@@ -7939,7 +7939,7 @@
         <v>0.3014357828174373</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1138188180417883</v>
+        <v>0.1131536025517219</v>
       </c>
       <c r="G78" t="n">
         <v>0.2843664737681545</v>
@@ -7993,7 +7993,7 @@
         <v>1.000105927208099</v>
       </c>
       <c r="X78" t="n">
-        <v>1.139678607190467</v>
+        <v>1.140490649595412</v>
       </c>
       <c r="Y78" t="n">
         <v>1.006423424039746</v>
@@ -8133,7 +8133,7 @@
         <v>0.196319080822493</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1426057577062835</v>
+        <v>0.1425607849136424</v>
       </c>
       <c r="G80" t="n">
         <v>0.1614547940009791</v>
@@ -8230,7 +8230,7 @@
         <v>0.278981715084419</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4422845427196455</v>
+        <v>0.4422709683701134</v>
       </c>
       <c r="G81" t="n">
         <v>0.2804804050869164</v>
@@ -8284,7 +8284,7 @@
         <v>1.085063658874821</v>
       </c>
       <c r="X81" t="n">
-        <v>1.098696964806258</v>
+        <v>1.099623643501167</v>
       </c>
       <c r="Y81" t="n">
         <v>1.025866133362981</v>
@@ -8327,7 +8327,7 @@
         <v>0.06736655155282197</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1455110832094848</v>
+        <v>0.1453409935963227</v>
       </c>
       <c r="G82" t="n">
         <v>0.07215455423707653</v>
@@ -8381,7 +8381,7 @@
         <v>1.008399520679616</v>
       </c>
       <c r="X82" t="n">
-        <v>1.05127383074672</v>
+        <v>1.052841477046448</v>
       </c>
       <c r="Y82" t="n">
         <v>1</v>
@@ -8424,10 +8424,10 @@
         <v>0.2999235855980502</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1061759869620355</v>
+        <v>0.1058236588228634</v>
       </c>
       <c r="G83" t="n">
-        <v>0.06735096055732995</v>
+        <v>0.0666925441477349</v>
       </c>
       <c r="H83" t="n">
         <v>1.040256313503158</v>
@@ -8475,10 +8475,10 @@
         <v>1.10023898526898</v>
       </c>
       <c r="W83" t="n">
-        <v>1.227149875949632</v>
+        <v>1.227728040334726</v>
       </c>
       <c r="X83" t="n">
-        <v>1.190435449306315</v>
+        <v>1.19126269922003</v>
       </c>
       <c r="Y83" t="n">
         <v>1.096834633890862</v>
@@ -8521,7 +8521,7 @@
         <v>0.1359384076920536</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1897400680440687</v>
+        <v>0.189025929118894</v>
       </c>
       <c r="G84" t="n">
         <v>0.2307278204665977</v>
@@ -8575,7 +8575,7 @@
         <v>1.001577046792815</v>
       </c>
       <c r="X84" t="n">
-        <v>1.162644459024371</v>
+        <v>1.164813175855732</v>
       </c>
       <c r="Y84" t="n">
         <v>1.016696448388154</v>
@@ -8618,7 +8618,7 @@
         <v>0.1050573766032133</v>
       </c>
       <c r="F85" t="n">
-        <v>0.3651820422015493</v>
+        <v>0.3649566444505912</v>
       </c>
       <c r="G85" t="n">
         <v>0.1424157645034361</v>
@@ -8672,7 +8672,7 @@
         <v>1.018685932803797</v>
       </c>
       <c r="X85" t="n">
-        <v>1.063993467385989</v>
+        <v>1.065899030805943</v>
       </c>
       <c r="Y85" t="n">
         <v>1.023267504114854</v>
@@ -9006,10 +9006,10 @@
         <v>0.1179668635308153</v>
       </c>
       <c r="F89" t="n">
-        <v>0.08738901824993905</v>
+        <v>0.0871655482716867</v>
       </c>
       <c r="G89" t="n">
-        <v>0.04966245930782417</v>
+        <v>0.04940741300933806</v>
       </c>
       <c r="H89" t="n">
         <v>0.6944633112123855</v>
@@ -9057,10 +9057,10 @@
         <v>1.036823526797908</v>
       </c>
       <c r="W89" t="n">
-        <v>1.130853435263917</v>
+        <v>1.13381697196313</v>
       </c>
       <c r="X89" t="n">
-        <v>1.056052410512879</v>
+        <v>1.059491866107141</v>
       </c>
       <c r="Y89" t="n">
         <v>1.022144060724332</v>
@@ -9103,10 +9103,10 @@
         <v>0.1958392268465931</v>
       </c>
       <c r="F90" t="n">
-        <v>0.2045857343590551</v>
+        <v>0.2040673461992708</v>
       </c>
       <c r="G90" t="n">
-        <v>0.03968373482250417</v>
+        <v>0.03931000039588752</v>
       </c>
       <c r="H90" t="n">
         <v>1.441697106386243</v>
@@ -9154,10 +9154,10 @@
         <v>1.016675447209708</v>
       </c>
       <c r="W90" t="n">
-        <v>1.066650411213881</v>
+        <v>1.067414600117276</v>
       </c>
       <c r="X90" t="n">
-        <v>1.098162439654083</v>
+        <v>1.0988971811051</v>
       </c>
       <c r="Y90" t="n">
         <v>1.022418497241333</v>
@@ -9297,7 +9297,7 @@
         <v>0.2794282500855682</v>
       </c>
       <c r="F92" t="n">
-        <v>0.2267737042281412</v>
+        <v>0.2258336389112884</v>
       </c>
       <c r="G92" t="n">
         <v>0.5011649292880543</v>
@@ -9351,7 +9351,7 @@
         <v>1.015491839119834</v>
       </c>
       <c r="X92" t="n">
-        <v>1.127756234512661</v>
+        <v>1.129756875595182</v>
       </c>
       <c r="Y92" t="n">
         <v>1.000255009972166</v>
@@ -9394,7 +9394,7 @@
         <v>0.07498639471060446</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1725929057406244</v>
+        <v>0.1720005889869156</v>
       </c>
       <c r="G93" t="n">
         <v>0.0711023243780232</v>
@@ -9448,7 +9448,7 @@
         <v>1.009574733636376</v>
       </c>
       <c r="X93" t="n">
-        <v>1.088386244467616</v>
+        <v>1.091325654718282</v>
       </c>
       <c r="Y93" t="n">
         <v>1.033688772809744</v>
@@ -9491,10 +9491,10 @@
         <v>0.1863954895890821</v>
       </c>
       <c r="F94" t="n">
-        <v>0.08465217145330056</v>
+        <v>0.08464530798195524</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0315047401471861</v>
+        <v>0.03129252748963079</v>
       </c>
       <c r="H94" t="n">
         <v>1.122836684900294</v>
@@ -9542,10 +9542,10 @@
         <v>1.017525371528395</v>
       </c>
       <c r="W94" t="n">
-        <v>1.132920330374832</v>
+        <v>1.134441569559192</v>
       </c>
       <c r="X94" t="n">
-        <v>1.165732751759302</v>
+        <v>1.169218555655489</v>
       </c>
       <c r="Y94" t="n">
         <v>1.039029327919982</v>
@@ -9782,10 +9782,10 @@
         <v>0.1220763470612821</v>
       </c>
       <c r="F97" t="n">
-        <v>0.1329263148087669</v>
+        <v>0.1335525956865797</v>
       </c>
       <c r="G97" t="n">
-        <v>0.1681798599025757</v>
+        <v>0.1669276249306447</v>
       </c>
       <c r="H97" t="n">
         <v>0.9114934514164214</v>
@@ -9833,10 +9833,10 @@
         <v>1.014104428106125</v>
       </c>
       <c r="W97" t="n">
-        <v>1.034277594365932</v>
+        <v>1.034829752274044</v>
       </c>
       <c r="X97" t="n">
-        <v>1.049673764268197</v>
+        <v>1.050741589488603</v>
       </c>
       <c r="Y97" t="n">
         <v>1.0090969367735</v>
@@ -9976,10 +9976,10 @@
         <v>0.1161690121028369</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1356104323854601</v>
+        <v>0.1355410805903267</v>
       </c>
       <c r="G99" t="n">
-        <v>0.05675822157438962</v>
+        <v>0.05638318811942167</v>
       </c>
       <c r="H99" t="n">
         <v>0.6035405067992963</v>
@@ -10027,10 +10027,10 @@
         <v>1.016251206873568</v>
       </c>
       <c r="W99" t="n">
-        <v>1.040146902911874</v>
+        <v>1.040664163486428</v>
       </c>
       <c r="X99" t="n">
-        <v>1.121475256785471</v>
+        <v>1.125190571316243</v>
       </c>
       <c r="Y99" t="n">
         <v>1.036482101907221</v>
@@ -10073,7 +10073,7 @@
         <v>0.01893686572046803</v>
       </c>
       <c r="F100" t="n">
-        <v>0.02200801979149335</v>
+        <v>0.02194251375517594</v>
       </c>
       <c r="G100" t="n">
         <v>0.01951215342037858</v>
@@ -10127,7 +10127,7 @@
         <v>1</v>
       </c>
       <c r="X100" t="n">
-        <v>1.020167778469986</v>
+        <v>1.021258290171881</v>
       </c>
       <c r="Y100" t="n">
         <v>1.000858196647481</v>
@@ -10170,10 +10170,10 @@
         <v>0.4497305728682977</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2818697550020213</v>
+        <v>0.2807973143851619</v>
       </c>
       <c r="G101" t="n">
-        <v>0.3064918318403957</v>
+        <v>0.3049897429177384</v>
       </c>
       <c r="H101" t="n">
         <v>1.964440928600887</v>
@@ -10221,10 +10221,10 @@
         <v>1.017535480649453</v>
       </c>
       <c r="W101" t="n">
-        <v>1.095040746556481</v>
+        <v>1.0960638649596</v>
       </c>
       <c r="X101" t="n">
-        <v>1.082533642224376</v>
+        <v>1.083347527794401</v>
       </c>
       <c r="Y101" t="n">
         <v>1.013484922788592</v>
@@ -10267,10 +10267,10 @@
         <v>0.07379223013912768</v>
       </c>
       <c r="F102" t="n">
-        <v>0.05115326620755899</v>
+        <v>0.05112193496851776</v>
       </c>
       <c r="G102" t="n">
-        <v>0.01318442187349694</v>
+        <v>0.01308248557949068</v>
       </c>
       <c r="H102" t="n">
         <v>0.3900454436755449</v>
@@ -10318,10 +10318,10 @@
         <v>1.009097458874169</v>
       </c>
       <c r="W102" t="n">
-        <v>1.040510312661889</v>
+        <v>1.041459514564951</v>
       </c>
       <c r="X102" t="n">
-        <v>1.051552741916877</v>
+        <v>1.053115674218995</v>
       </c>
       <c r="Y102" t="n">
         <v>1.015071317116978</v>
@@ -10364,10 +10364,10 @@
         <v>0.2215477178739216</v>
       </c>
       <c r="F103" t="n">
-        <v>0.7151302447035911</v>
+        <v>0.7138220067312592</v>
       </c>
       <c r="G103" t="n">
-        <v>0.1317979353148221</v>
+        <v>0.1310928311319332</v>
       </c>
       <c r="H103" t="n">
         <v>2.106824483731614</v>
@@ -10415,10 +10415,10 @@
         <v>1.010879044614635</v>
       </c>
       <c r="W103" t="n">
-        <v>1.044967177118566</v>
+        <v>1.045614230738552</v>
       </c>
       <c r="X103" t="n">
-        <v>1.047314072748331</v>
+        <v>1.047660121784866</v>
       </c>
       <c r="Y103" t="n">
         <v>1.020541475120251</v>
@@ -10461,10 +10461,10 @@
         <v>0.003519568167109633</v>
       </c>
       <c r="F104" t="n">
-        <v>0.002578909666310382</v>
+        <v>0.00258304118258462</v>
       </c>
       <c r="G104" t="n">
-        <v>0.002461290887773285</v>
+        <v>0.002438262441174478</v>
       </c>
       <c r="H104" t="n">
         <v>0.2523849574677205</v>
@@ -10512,10 +10512,10 @@
         <v>1.000745040550296</v>
       </c>
       <c r="W104" t="n">
-        <v>1.001455952920771</v>
+        <v>1.001512663626723</v>
       </c>
       <c r="X104" t="n">
-        <v>1.001772487326929</v>
+        <v>1.00182708648815</v>
       </c>
       <c r="Y104" t="n">
         <v>1.000830925627947</v>
@@ -10558,10 +10558,10 @@
         <v>0.003283289040542172</v>
       </c>
       <c r="F105" t="n">
-        <v>0.001916987410872407</v>
+        <v>0.001909547063298226</v>
       </c>
       <c r="G105" t="n">
-        <v>0.001875361364436537</v>
+        <v>0.00187042968926327</v>
       </c>
       <c r="H105" t="n">
         <v>0.2414080489297661</v>
@@ -10609,10 +10609,10 @@
         <v>1.001446298869981</v>
       </c>
       <c r="W105" t="n">
-        <v>1.002652126390932</v>
+        <v>1.002668142936662</v>
       </c>
       <c r="X105" t="n">
-        <v>1.00250265881513</v>
+        <v>1.002522392830705</v>
       </c>
       <c r="Y105" t="n">
         <v>1.001944668362955</v>
@@ -10752,10 +10752,10 @@
         <v>0.01885343947989479</v>
       </c>
       <c r="F107" t="n">
-        <v>0.09875839242953094</v>
+        <v>0.09875493018713423</v>
       </c>
       <c r="G107" t="n">
-        <v>0.005549874116161095</v>
+        <v>0.005497813103015686</v>
       </c>
       <c r="H107" t="n">
         <v>0.3052319898142227</v>
@@ -10803,10 +10803,10 @@
         <v>1.007528808882736</v>
       </c>
       <c r="W107" t="n">
-        <v>1.011366143999975</v>
+        <v>1.011830704961316</v>
       </c>
       <c r="X107" t="n">
-        <v>1.017536230417437</v>
+        <v>1.017791839749926</v>
       </c>
       <c r="Y107" t="n">
         <v>1.00994527209299</v>
@@ -10946,10 +10946,10 @@
         <v>0.01402659871691941</v>
       </c>
       <c r="F109" t="n">
-        <v>0.06154594633141319</v>
+        <v>0.06152600811933189</v>
       </c>
       <c r="G109" t="n">
-        <v>0.006061526360360272</v>
+        <v>0.005993774739849976</v>
       </c>
       <c r="H109" t="n">
         <v>0.4867810937918519</v>
@@ -10997,10 +10997,10 @@
         <v>1.002013807548805</v>
       </c>
       <c r="W109" t="n">
-        <v>1.003714004434963</v>
+        <v>1.003796442919276</v>
       </c>
       <c r="X109" t="n">
-        <v>1.007795364176455</v>
+        <v>1.008279082668069</v>
       </c>
       <c r="Y109" t="n">
         <v>1.003893016525779</v>
@@ -11043,10 +11043,10 @@
         <v>0.1439147192761868</v>
       </c>
       <c r="F110" t="n">
-        <v>0.06271139067798115</v>
+        <v>0.06283654378589101</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0637893341727403</v>
+        <v>0.06311338488611916</v>
       </c>
       <c r="H110" t="n">
         <v>0.9113955511351585</v>
@@ -11094,10 +11094,10 @@
         <v>1.014687776985438</v>
       </c>
       <c r="W110" t="n">
-        <v>1.142899371814483</v>
+        <v>1.144445338953628</v>
       </c>
       <c r="X110" t="n">
-        <v>1.112001908521034</v>
+        <v>1.112791113416083</v>
       </c>
       <c r="Y110" t="n">
         <v>1.025271466101481</v>
@@ -11140,10 +11140,10 @@
         <v>0.2518513739492185</v>
       </c>
       <c r="F111" t="n">
-        <v>0.1018078755452198</v>
+        <v>0.1018345643031001</v>
       </c>
       <c r="G111" t="n">
-        <v>0.02906895204789774</v>
+        <v>0.02883756332703105</v>
       </c>
       <c r="H111" t="n">
         <v>1.079857812293223</v>
@@ -11191,10 +11191,10 @@
         <v>1.044217537281513</v>
       </c>
       <c r="W111" t="n">
-        <v>1.233892375040221</v>
+        <v>1.2374806507151</v>
       </c>
       <c r="X111" t="n">
-        <v>1.137409975552358</v>
+        <v>1.13955957646049</v>
       </c>
       <c r="Y111" t="n">
         <v>1.037810624895072</v>
@@ -11237,7 +11237,7 @@
         <v>0.05243151975821789</v>
       </c>
       <c r="F112" t="n">
-        <v>0.08163471205857704</v>
+        <v>0.08162590048201165</v>
       </c>
       <c r="G112" t="n">
         <v>0.05036684231470341</v>
@@ -11291,7 +11291,7 @@
         <v>1</v>
       </c>
       <c r="X112" t="n">
-        <v>1.020594937432143</v>
+        <v>1.02283463239648</v>
       </c>
       <c r="Y112" t="n">
         <v>1</v>
@@ -11334,7 +11334,7 @@
         <v>0.1972036328253845</v>
       </c>
       <c r="F113" t="n">
-        <v>0.2073014293305606</v>
+        <v>0.2063200433203727</v>
       </c>
       <c r="G113" t="n">
         <v>0.1178862065763207</v>
@@ -11388,7 +11388,7 @@
         <v>1.102693387741539</v>
       </c>
       <c r="X113" t="n">
-        <v>1.001984070467864</v>
+        <v>1.002290808304046</v>
       </c>
       <c r="Y113" t="n">
         <v>1</v>
@@ -11431,10 +11431,10 @@
         <v>0.2307990333667189</v>
       </c>
       <c r="F114" t="n">
-        <v>0.2509948154456517</v>
+        <v>0.2501681162949014</v>
       </c>
       <c r="G114" t="n">
-        <v>0.02869181215745322</v>
+        <v>0.02847630352877566</v>
       </c>
       <c r="H114" t="n">
         <v>0.9925570196999212</v>
@@ -11482,10 +11482,10 @@
         <v>1.006012606692849</v>
       </c>
       <c r="W114" t="n">
-        <v>1.329854565967702</v>
+        <v>1.332158884173532</v>
       </c>
       <c r="X114" t="n">
-        <v>1.052413834280961</v>
+        <v>1.053861813538904</v>
       </c>
       <c r="Y114" t="n">
         <v>1.00123504297487</v>
@@ -11528,7 +11528,7 @@
         <v>0.01590635349061371</v>
       </c>
       <c r="F115" t="n">
-        <v>0.01563303777849473</v>
+        <v>0.01553989547022493</v>
       </c>
       <c r="G115" t="n">
         <v>0.01720161038844697</v>
@@ -11582,7 +11582,7 @@
         <v>1.002098553553409</v>
       </c>
       <c r="X115" t="n">
-        <v>1.029799443504566</v>
+        <v>1.03112065460028</v>
       </c>
       <c r="Y115" t="n">
         <v>1.004505860103953</v>
@@ -11625,10 +11625,10 @@
         <v>0.01054871901923202</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0360503573250801</v>
+        <v>0.03601922467888709</v>
       </c>
       <c r="G116" t="n">
-        <v>0.007204883634737224</v>
+        <v>0.007144306690890985</v>
       </c>
       <c r="H116" t="n">
         <v>0.141439694541074</v>
@@ -11676,10 +11676,10 @@
         <v>1</v>
       </c>
       <c r="W116" t="n">
-        <v>1.028423280103563</v>
+        <v>1.031202497954827</v>
       </c>
       <c r="X116" t="n">
-        <v>1.000574668343487</v>
+        <v>1.000640374866406</v>
       </c>
       <c r="Y116" t="n">
         <v>1</v>
@@ -11919,7 +11919,7 @@
         <v>0.08838011720995834</v>
       </c>
       <c r="G119" t="n">
-        <v>0.01279147269580741</v>
+        <v>0.01269398145416209</v>
       </c>
       <c r="H119" t="n">
         <v>0.187687105852183</v>
@@ -11967,7 +11967,7 @@
         <v>1</v>
       </c>
       <c r="W119" t="n">
-        <v>1.00101675698499</v>
+        <v>1.001120070844107</v>
       </c>
       <c r="X119" t="n">
         <v>1.000735000895359</v>
@@ -12013,10 +12013,10 @@
         <v>0.03877224209661922</v>
       </c>
       <c r="F120" t="n">
-        <v>0.02772400203042533</v>
+        <v>0.0276195821907471</v>
       </c>
       <c r="G120" t="n">
-        <v>0.02194654824499943</v>
+        <v>0.02180334186270698</v>
       </c>
       <c r="H120" t="n">
         <v>0.2631984943659176</v>
@@ -12064,10 +12064,10 @@
         <v>1.013094761109131</v>
       </c>
       <c r="W120" t="n">
-        <v>1.132042831740214</v>
+        <v>1.135627244828141</v>
       </c>
       <c r="X120" t="n">
-        <v>1.142472689829257</v>
+        <v>1.143816588786133</v>
       </c>
       <c r="Y120" t="n">
         <v>1.062296920709371</v>
@@ -12110,7 +12110,7 @@
         <v>0.07975096035568227</v>
       </c>
       <c r="F121" t="n">
-        <v>0.09871185629072057</v>
+        <v>0.09843098752511106</v>
       </c>
       <c r="G121" t="n">
         <v>0.09336146554502049</v>
@@ -12164,7 +12164,7 @@
         <v>1.014103998890121</v>
       </c>
       <c r="X121" t="n">
-        <v>1.044022486629834</v>
+        <v>1.044722607564978</v>
       </c>
       <c r="Y121" t="n">
         <v>1.022020897969908</v>
@@ -12304,10 +12304,10 @@
         <v>0.07000966372622601</v>
       </c>
       <c r="F123" t="n">
-        <v>0.09386967701427748</v>
+        <v>0.09366469389055661</v>
       </c>
       <c r="G123" t="n">
-        <v>0.03140266263476395</v>
+        <v>0.03116312030695173</v>
       </c>
       <c r="H123" t="n">
         <v>0.5088787888492297</v>
@@ -12355,10 +12355,10 @@
         <v>1.013149961933713</v>
       </c>
       <c r="W123" t="n">
-        <v>1.020380669778818</v>
+        <v>1.020622232544045</v>
       </c>
       <c r="X123" t="n">
-        <v>1.047682093341697</v>
+        <v>1.048224754289153</v>
       </c>
       <c r="Y123" t="n">
         <v>1.021223614675844</v>
@@ -12401,7 +12401,7 @@
         <v>0.3844943945727304</v>
       </c>
       <c r="F124" t="n">
-        <v>0.5845070474069464</v>
+        <v>0.5820762291093261</v>
       </c>
       <c r="G124" t="n">
         <v>0.6646142638441807</v>
@@ -12455,7 +12455,7 @@
         <v>1.05572362784677</v>
       </c>
       <c r="X124" t="n">
-        <v>1.056555648933941</v>
+        <v>1.057523612713476</v>
       </c>
       <c r="Y124" t="n">
         <v>1.045290362191896</v>
@@ -12498,7 +12498,7 @@
         <v>0.03263365558698497</v>
       </c>
       <c r="F125" t="n">
-        <v>0.1186851552409764</v>
+        <v>0.1186384106085195</v>
       </c>
       <c r="G125" t="n">
         <v>0.03229129136452564</v>
@@ -12692,10 +12692,10 @@
         <v>0.01328655884587228</v>
       </c>
       <c r="F127" t="n">
-        <v>0.02525711964862137</v>
+        <v>0.02518025271844578</v>
       </c>
       <c r="G127" t="n">
-        <v>0.01401420892743972</v>
+        <v>0.01390885594256809</v>
       </c>
       <c r="H127" t="n">
         <v>0.1477052233211524</v>
@@ -12743,10 +12743,10 @@
         <v>1.013106436406949</v>
       </c>
       <c r="W127" t="n">
-        <v>1.026421068886595</v>
+        <v>1.026916691563903</v>
       </c>
       <c r="X127" t="n">
-        <v>1.025586231826069</v>
+        <v>1.025750472503384</v>
       </c>
       <c r="Y127" t="n">
         <v>1.020658356003813</v>
@@ -13080,10 +13080,10 @@
         <v>0.2153615478839901</v>
       </c>
       <c r="F131" t="n">
-        <v>0.4762844432511034</v>
+        <v>0.477544782934934</v>
       </c>
       <c r="G131" t="n">
-        <v>0.2681919050259858</v>
+        <v>0.266336713283224</v>
       </c>
       <c r="H131" t="n">
         <v>0.8795977288584468</v>
@@ -13131,10 +13131,10 @@
         <v>1.015075583618936</v>
       </c>
       <c r="W131" t="n">
-        <v>1.017079013921605</v>
+        <v>1.017163306640877</v>
       </c>
       <c r="X131" t="n">
-        <v>1.069478841464237</v>
+        <v>1.070797261622067</v>
       </c>
       <c r="Y131" t="n">
         <v>1.010052084659834</v>
@@ -13177,10 +13177,10 @@
         <v>0.2168802682603749</v>
       </c>
       <c r="F132" t="n">
-        <v>0.1948979940849249</v>
+        <v>0.1944518383348885</v>
       </c>
       <c r="G132" t="n">
-        <v>0.06045538420715878</v>
+        <v>0.05998230057210428</v>
       </c>
       <c r="H132" t="n">
         <v>1.343955876171723</v>
@@ -13228,10 +13228,10 @@
         <v>1.020294196131324</v>
       </c>
       <c r="W132" t="n">
-        <v>1.126608841608396</v>
+        <v>1.128598743867653</v>
       </c>
       <c r="X132" t="n">
-        <v>1.188453484583632</v>
+        <v>1.190225530849396</v>
       </c>
       <c r="Y132" t="n">
         <v>1.028004806138072</v>
@@ -13371,10 +13371,10 @@
         <v>0.3279864389320018</v>
       </c>
       <c r="F134" t="n">
-        <v>0.173630774121596</v>
+        <v>0.1730845456631712</v>
       </c>
       <c r="G134" t="n">
-        <v>0.1802397912451069</v>
+        <v>0.178775558242271</v>
       </c>
       <c r="H134" t="n">
         <v>1.372301302122764</v>
@@ -13422,10 +13422,10 @@
         <v>1.046665800453953</v>
       </c>
       <c r="W134" t="n">
-        <v>1.141421819711912</v>
+        <v>1.14243025552887</v>
       </c>
       <c r="X134" t="n">
-        <v>1.160367896557249</v>
+        <v>1.162515577537538</v>
       </c>
       <c r="Y134" t="n">
         <v>1.021736585612737</v>
@@ -13759,10 +13759,10 @@
         <v>0.3085798791773611</v>
       </c>
       <c r="F138" t="n">
-        <v>0.3795871928037312</v>
+        <v>0.3785674011693373</v>
       </c>
       <c r="G138" t="n">
-        <v>0.1868512753269022</v>
+        <v>0.1856255793055665</v>
       </c>
       <c r="H138" t="n">
         <v>2.163292619666246</v>
@@ -13810,10 +13810,10 @@
         <v>1.028656088161708</v>
       </c>
       <c r="W138" t="n">
-        <v>1.08662541417153</v>
+        <v>1.086909725542303</v>
       </c>
       <c r="X138" t="n">
-        <v>1.091662236116571</v>
+        <v>1.092163920389355</v>
       </c>
       <c r="Y138" t="n">
         <v>1.010492619786958</v>
@@ -13856,10 +13856,10 @@
         <v>0.2052223856182797</v>
       </c>
       <c r="F139" t="n">
-        <v>0.1860035055614987</v>
+        <v>0.1862965648681459</v>
       </c>
       <c r="G139" t="n">
-        <v>0.08704435330170797</v>
+        <v>0.08633669179953882</v>
       </c>
       <c r="H139" t="n">
         <v>1.11503666229667</v>
@@ -13907,10 +13907,10 @@
         <v>1.038624047913878</v>
       </c>
       <c r="W139" t="n">
-        <v>1.124498478724844</v>
+        <v>1.126226182813179</v>
       </c>
       <c r="X139" t="n">
-        <v>1.078373366377271</v>
+        <v>1.07924387306207</v>
       </c>
       <c r="Y139" t="n">
         <v>1.033932292630582</v>
@@ -13953,10 +13953,10 @@
         <v>0.3384950386090789</v>
       </c>
       <c r="F140" t="n">
-        <v>0.34102671654056</v>
+        <v>0.3414472179696772</v>
       </c>
       <c r="G140" t="n">
-        <v>0.1862658671324942</v>
+        <v>0.1846092047520206</v>
       </c>
       <c r="H140" t="n">
         <v>1.202054363975474</v>
@@ -14004,10 +14004,10 @@
         <v>1.020158683026965</v>
       </c>
       <c r="W140" t="n">
-        <v>1.203888712261839</v>
+        <v>1.204627240844355</v>
       </c>
       <c r="X140" t="n">
-        <v>1.14277074835694</v>
+        <v>1.144111519999631</v>
       </c>
       <c r="Y140" t="n">
         <v>1.037569978740648</v>
@@ -14143,10 +14143,10 @@
         <v>0.2065879340095007</v>
       </c>
       <c r="F142" t="n">
-        <v>0.1917662117525475</v>
+        <v>0.191939592104189</v>
       </c>
       <c r="G142" t="n">
-        <v>0.05971316148607406</v>
+        <v>0.05935700660444061</v>
       </c>
       <c r="H142" t="n">
         <v>1.063192803963572</v>
@@ -14194,10 +14194,10 @@
         <v>1.012582012179135</v>
       </c>
       <c r="W142" t="n">
-        <v>1.177493547102611</v>
+        <v>1.180410714042639</v>
       </c>
       <c r="X142" t="n">
-        <v>1.097249940681272</v>
+        <v>1.098593285139021</v>
       </c>
       <c r="Y142" t="n">
         <v>1.012312089381855</v>
@@ -14240,10 +14240,10 @@
         <v>0.1128121165450138</v>
       </c>
       <c r="F143" t="n">
-        <v>0.1242596682491225</v>
+        <v>0.124136396111995</v>
       </c>
       <c r="G143" t="n">
-        <v>0.1162124442435519</v>
+        <v>0.115383894408825</v>
       </c>
       <c r="H143" t="n">
         <v>0.8513911735077774</v>
@@ -14291,10 +14291,10 @@
         <v>1.002986794977022</v>
       </c>
       <c r="W143" t="n">
-        <v>1.049754673128539</v>
+        <v>1.05075406396519</v>
       </c>
       <c r="X143" t="n">
-        <v>1.12562021534747</v>
+        <v>1.126286570838365</v>
       </c>
       <c r="Y143" t="n">
         <v>1.037900570163677</v>
@@ -14337,7 +14337,7 @@
         <v>0.1234120388917584</v>
       </c>
       <c r="F144" t="n">
-        <v>0.2551519687638231</v>
+        <v>0.2545916377297081</v>
       </c>
       <c r="G144" t="n">
         <v>0.1338174030643844</v>
@@ -14391,7 +14391,7 @@
         <v>1.012769096579075</v>
       </c>
       <c r="X144" t="n">
-        <v>1.068863888971745</v>
+        <v>1.069762181548098</v>
       </c>
       <c r="Y144" t="n">
         <v>1.000278931611801</v>
@@ -14434,10 +14434,10 @@
         <v>0.1578621739330778</v>
       </c>
       <c r="F145" t="n">
-        <v>0.10898719722364</v>
+        <v>0.1089317354628211</v>
       </c>
       <c r="G145" t="n">
-        <v>0.09198227558765167</v>
+        <v>0.09155651638549112</v>
       </c>
       <c r="H145" t="n">
         <v>0.7374300657938619</v>
@@ -14485,10 +14485,10 @@
         <v>1.017775406722974</v>
       </c>
       <c r="W145" t="n">
-        <v>1.173608048918247</v>
+        <v>1.175835024156027</v>
       </c>
       <c r="X145" t="n">
-        <v>1.076126932884518</v>
+        <v>1.077475759745978</v>
       </c>
       <c r="Y145" t="n">
         <v>1.000144120413532</v>
